--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="499">
   <si>
     <t>Date</t>
   </si>
@@ -1492,37 +1492,25 @@
     <t>2026-02-27</t>
   </si>
   <si>
-    <t>184965</t>
-  </si>
-  <si>
-    <t>186086</t>
-  </si>
-  <si>
-    <t>187207</t>
-  </si>
-  <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>23495.8</t>
-  </si>
-  <si>
-    <t>23492.43</t>
-  </si>
-  <si>
-    <t>23690.23</t>
-  </si>
-  <si>
-    <t>23796.65</t>
-  </si>
-  <si>
-    <t>24077.49</t>
-  </si>
-  <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>24278.46</t>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>148008</t>
+  </si>
+  <si>
+    <t>168000</t>
+  </si>
+  <si>
+    <t>20180.15</t>
+  </si>
+  <si>
+    <t>20208.42</t>
+  </si>
+  <si>
+    <t>20233.26</t>
+  </si>
+  <si>
+    <t>21605.62</t>
   </si>
 </sst>
 </file>
@@ -1880,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D491"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8532,30 +8520,30 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476" s="1">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="B476" t="s">
         <v>477</v>
       </c>
-      <c r="C476" t="s">
-        <v>492</v>
-      </c>
-      <c r="D476" t="s">
-        <v>496</v>
+      <c r="C476">
+        <v>184965</v>
+      </c>
+      <c r="D476">
+        <v>23495.8</v>
       </c>
     </row>
     <row r="477" spans="1:4">
       <c r="A477" s="1">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="B477" t="s">
         <v>478</v>
       </c>
-      <c r="C477" t="s">
-        <v>492</v>
-      </c>
-      <c r="D477" t="s">
-        <v>497</v>
+      <c r="C477">
+        <v>184965</v>
+      </c>
+      <c r="D477">
+        <v>23492.43</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8574,30 +8562,30 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" s="1">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="B479" t="s">
         <v>480</v>
       </c>
-      <c r="C479" t="s">
-        <v>493</v>
-      </c>
-      <c r="D479" t="s">
-        <v>498</v>
+      <c r="C479">
+        <v>186086</v>
+      </c>
+      <c r="D479">
+        <v>23690.23</v>
       </c>
     </row>
     <row r="480" spans="1:4">
       <c r="A480" s="1">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="B480" t="s">
         <v>481</v>
       </c>
-      <c r="C480" t="s">
-        <v>494</v>
-      </c>
-      <c r="D480" t="s">
-        <v>499</v>
+      <c r="C480">
+        <v>187207</v>
+      </c>
+      <c r="D480">
+        <v>23796.65</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8644,58 +8632,58 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
-      <c r="C484">
-        <v>148008</v>
-      </c>
-      <c r="D484">
-        <v>20180.15</v>
+      <c r="C484" t="s">
+        <v>493</v>
+      </c>
+      <c r="D484" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
-      <c r="C485" t="s">
-        <v>495</v>
-      </c>
-      <c r="D485" t="s">
-        <v>500</v>
+      <c r="C485">
+        <v>188328</v>
+      </c>
+      <c r="D485">
+        <v>24077.49</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486">
-        <v>148008</v>
-      </c>
-      <c r="D486">
-        <v>20208.42</v>
+      <c r="C486" t="s">
+        <v>493</v>
+      </c>
+      <c r="D486" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D487" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8714,16 +8702,16 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489" t="s">
-        <v>495</v>
-      </c>
-      <c r="D489" t="s">
-        <v>502</v>
+      <c r="C489">
+        <v>188328</v>
+      </c>
+      <c r="D489">
+        <v>24278.46</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8738,6 +8726,20 @@
       </c>
       <c r="D490">
         <v>21627.62</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4">
+      <c r="A491" s="1">
+        <v>503</v>
+      </c>
+      <c r="B491" t="s">
+        <v>492</v>
+      </c>
+      <c r="C491" t="s">
+        <v>494</v>
+      </c>
+      <c r="D491" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="507">
   <si>
     <t>Date</t>
   </si>
@@ -1495,22 +1495,46 @@
     <t>2026-03-02</t>
   </si>
   <si>
-    <t>148008</t>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>156206</t>
+  </si>
+  <si>
+    <t>157147</t>
+  </si>
+  <si>
+    <t>158088</t>
   </si>
   <si>
     <t>168000</t>
   </si>
   <si>
-    <t>20180.15</t>
-  </si>
-  <si>
-    <t>20208.42</t>
-  </si>
-  <si>
-    <t>20233.26</t>
-  </si>
-  <si>
-    <t>21605.62</t>
+    <t>18600.62</t>
+  </si>
+  <si>
+    <t>18618.28</t>
+  </si>
+  <si>
+    <t>18701.92</t>
+  </si>
+  <si>
+    <t>18823.64</t>
+  </si>
+  <si>
+    <t>18841.24</t>
+  </si>
+  <si>
+    <t>18901.33</t>
+  </si>
+  <si>
+    <t>18893.42</t>
+  </si>
+  <si>
+    <t>19053.93</t>
+  </si>
+  <si>
+    <t>21562.37</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D491"/>
+  <dimension ref="A1:D492"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8548,100 +8572,100 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" s="1">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="B478" t="s">
         <v>479</v>
       </c>
-      <c r="C478">
-        <v>146246</v>
-      </c>
-      <c r="D478">
-        <v>19867.4</v>
+      <c r="C478" t="s">
+        <v>494</v>
+      </c>
+      <c r="D478" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="479" spans="1:4">
       <c r="A479" s="1">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B479" t="s">
         <v>480</v>
       </c>
-      <c r="C479">
-        <v>186086</v>
-      </c>
-      <c r="D479">
-        <v>23690.23</v>
+      <c r="C479" t="s">
+        <v>494</v>
+      </c>
+      <c r="D479" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="480" spans="1:4">
       <c r="A480" s="1">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="B480" t="s">
         <v>481</v>
       </c>
-      <c r="C480">
-        <v>187207</v>
-      </c>
-      <c r="D480">
-        <v>23796.65</v>
+      <c r="C480" t="s">
+        <v>495</v>
+      </c>
+      <c r="D480" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="481" spans="1:4">
       <c r="A481" s="1">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="B481" t="s">
         <v>482</v>
       </c>
-      <c r="C481">
-        <v>148008</v>
-      </c>
-      <c r="D481">
-        <v>20105.61</v>
+      <c r="C481" t="s">
+        <v>496</v>
+      </c>
+      <c r="D481" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="482" spans="1:4">
       <c r="A482" s="1">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="B482" t="s">
         <v>483</v>
       </c>
-      <c r="C482">
-        <v>148008</v>
-      </c>
-      <c r="D482">
-        <v>20124.41</v>
+      <c r="C482" t="s">
+        <v>496</v>
+      </c>
+      <c r="D482" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="1">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B483" t="s">
         <v>484</v>
       </c>
-      <c r="C483">
-        <v>148008</v>
-      </c>
-      <c r="D483">
-        <v>20188.59</v>
+      <c r="C483" t="s">
+        <v>496</v>
+      </c>
+      <c r="D483" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
       <c r="C484" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="D484" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8660,30 +8684,30 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486" t="s">
-        <v>493</v>
-      </c>
-      <c r="D486" t="s">
-        <v>496</v>
+      <c r="C486">
+        <v>148008</v>
+      </c>
+      <c r="D486">
+        <v>20208.42</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487" t="s">
-        <v>493</v>
-      </c>
-      <c r="D487" t="s">
-        <v>497</v>
+      <c r="C487">
+        <v>148008</v>
+      </c>
+      <c r="D487">
+        <v>20233.26</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8716,30 +8740,44 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490">
-        <v>168000</v>
-      </c>
-      <c r="D490">
-        <v>21627.62</v>
+      <c r="C490" t="s">
+        <v>496</v>
+      </c>
+      <c r="D490" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491" t="s">
-        <v>494</v>
-      </c>
-      <c r="D491" t="s">
-        <v>498</v>
+      <c r="C491">
+        <v>168000</v>
+      </c>
+      <c r="D491">
+        <v>21605.62</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4">
+      <c r="A492" s="1">
+        <v>505</v>
+      </c>
+      <c r="B492" t="s">
+        <v>493</v>
+      </c>
+      <c r="C492" t="s">
+        <v>497</v>
+      </c>
+      <c r="D492" t="s">
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="510">
   <si>
     <t>Date</t>
   </si>
@@ -1498,6 +1498,9 @@
     <t>2026-03-03</t>
   </si>
   <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
     <t>156206</t>
   </si>
   <si>
@@ -1507,34 +1510,40 @@
     <t>158088</t>
   </si>
   <si>
-    <t>168000</t>
-  </si>
-  <si>
-    <t>18600.62</t>
-  </si>
-  <si>
-    <t>18618.28</t>
-  </si>
-  <si>
-    <t>18701.92</t>
-  </si>
-  <si>
-    <t>18823.64</t>
-  </si>
-  <si>
-    <t>18841.24</t>
-  </si>
-  <si>
-    <t>18901.33</t>
-  </si>
-  <si>
-    <t>18893.42</t>
-  </si>
-  <si>
-    <t>19053.93</t>
-  </si>
-  <si>
-    <t>21562.37</t>
+    <t>169000</t>
+  </si>
+  <si>
+    <t>23667.76</t>
+  </si>
+  <si>
+    <t>23690.23</t>
+  </si>
+  <si>
+    <t>23796.65</t>
+  </si>
+  <si>
+    <t>23951.53</t>
+  </si>
+  <si>
+    <t>23973.93</t>
+  </si>
+  <si>
+    <t>24050.38</t>
+  </si>
+  <si>
+    <t>24040.32</t>
+  </si>
+  <si>
+    <t>24077.49</t>
+  </si>
+  <si>
+    <t>24074.01</t>
+  </si>
+  <si>
+    <t>24103.6</t>
+  </si>
+  <si>
+    <t>21565.3</t>
   </si>
 </sst>
 </file>
@@ -1892,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D492"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8572,142 +8581,142 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" s="1">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B478" t="s">
         <v>479</v>
       </c>
       <c r="C478" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D478" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="479" spans="1:4">
       <c r="A479" s="1">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B479" t="s">
         <v>480</v>
       </c>
       <c r="C479" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D479" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="480" spans="1:4">
       <c r="A480" s="1">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B480" t="s">
         <v>481</v>
       </c>
       <c r="C480" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D480" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="481" spans="1:4">
       <c r="A481" s="1">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B481" t="s">
         <v>482</v>
       </c>
       <c r="C481" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D481" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="482" spans="1:4">
       <c r="A482" s="1">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B482" t="s">
         <v>483</v>
       </c>
       <c r="C482" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D482" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="1">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B483" t="s">
         <v>484</v>
       </c>
       <c r="C483" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D483" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
       <c r="C484" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D484" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
-      <c r="C485">
-        <v>188328</v>
-      </c>
-      <c r="D485">
-        <v>24077.49</v>
+      <c r="C485" t="s">
+        <v>497</v>
+      </c>
+      <c r="D485" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486">
-        <v>148008</v>
-      </c>
-      <c r="D486">
-        <v>20208.42</v>
+      <c r="C486" t="s">
+        <v>497</v>
+      </c>
+      <c r="D486" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487">
-        <v>148008</v>
-      </c>
-      <c r="D487">
-        <v>20233.26</v>
+      <c r="C487" t="s">
+        <v>497</v>
+      </c>
+      <c r="D487" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8740,16 +8749,16 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490" t="s">
-        <v>496</v>
-      </c>
-      <c r="D490" t="s">
-        <v>505</v>
+      <c r="C490">
+        <v>158088</v>
+      </c>
+      <c r="D490">
+        <v>19053.93</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8768,16 +8777,30 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492" t="s">
-        <v>497</v>
-      </c>
-      <c r="D492" t="s">
-        <v>506</v>
+      <c r="C492">
+        <v>168000</v>
+      </c>
+      <c r="D492">
+        <v>21562.37</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4">
+      <c r="A493" s="1">
+        <v>507</v>
+      </c>
+      <c r="B493" t="s">
+        <v>494</v>
+      </c>
+      <c r="C493" t="s">
+        <v>498</v>
+      </c>
+      <c r="D493" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="511">
   <si>
     <t>Date</t>
   </si>
@@ -1501,49 +1501,52 @@
     <t>2026-03-04</t>
   </si>
   <si>
-    <t>156206</t>
-  </si>
-  <si>
-    <t>157147</t>
-  </si>
-  <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>169000</t>
-  </si>
-  <si>
-    <t>23667.76</t>
-  </si>
-  <si>
-    <t>23690.23</t>
-  </si>
-  <si>
-    <t>23796.65</t>
-  </si>
-  <si>
-    <t>23951.53</t>
-  </si>
-  <si>
-    <t>23973.93</t>
-  </si>
-  <si>
-    <t>24050.38</t>
-  </si>
-  <si>
-    <t>24040.32</t>
-  </si>
-  <si>
-    <t>24077.49</t>
-  </si>
-  <si>
-    <t>24074.01</t>
-  </si>
-  <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>21565.3</t>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>186086</t>
+  </si>
+  <si>
+    <t>187207</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>170000</t>
+  </si>
+  <si>
+    <t>18618.28</t>
+  </si>
+  <si>
+    <t>18701.92</t>
+  </si>
+  <si>
+    <t>18823.64</t>
+  </si>
+  <si>
+    <t>18841.24</t>
+  </si>
+  <si>
+    <t>18901.33</t>
+  </si>
+  <si>
+    <t>18893.42</t>
+  </si>
+  <si>
+    <t>18922.63</t>
+  </si>
+  <si>
+    <t>18919.89</t>
+  </si>
+  <si>
+    <t>18943.15</t>
+  </si>
+  <si>
+    <t>19003.62</t>
+  </si>
+  <si>
+    <t>21806.42</t>
   </si>
 </sst>
 </file>
@@ -1901,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D493"/>
+  <dimension ref="A1:D494"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8581,16 +8584,16 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478" s="1">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="B478" t="s">
         <v>479</v>
       </c>
-      <c r="C478" t="s">
-        <v>495</v>
-      </c>
-      <c r="D478" t="s">
-        <v>499</v>
+      <c r="C478">
+        <v>156206</v>
+      </c>
+      <c r="D478">
+        <v>23667.76</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8601,7 +8604,7 @@
         <v>480</v>
       </c>
       <c r="C479" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D479" t="s">
         <v>500</v>
@@ -8615,7 +8618,7 @@
         <v>481</v>
       </c>
       <c r="C480" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D480" t="s">
         <v>501</v>
@@ -8629,7 +8632,7 @@
         <v>482</v>
       </c>
       <c r="C481" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D481" t="s">
         <v>502</v>
@@ -8643,7 +8646,7 @@
         <v>483</v>
       </c>
       <c r="C482" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D482" t="s">
         <v>503</v>
@@ -8657,7 +8660,7 @@
         <v>484</v>
       </c>
       <c r="C483" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D483" t="s">
         <v>504</v>
@@ -8671,7 +8674,7 @@
         <v>485</v>
       </c>
       <c r="C484" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D484" t="s">
         <v>505</v>
@@ -8685,7 +8688,7 @@
         <v>486</v>
       </c>
       <c r="C485" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D485" t="s">
         <v>506</v>
@@ -8699,7 +8702,7 @@
         <v>487</v>
       </c>
       <c r="C486" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D486" t="s">
         <v>507</v>
@@ -8713,7 +8716,7 @@
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D487" t="s">
         <v>508</v>
@@ -8721,16 +8724,16 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488">
-        <v>148008</v>
-      </c>
-      <c r="D488">
-        <v>22886.31</v>
+      <c r="C488" t="s">
+        <v>498</v>
+      </c>
+      <c r="D488" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8791,16 +8794,30 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
-      <c r="C493" t="s">
-        <v>498</v>
-      </c>
-      <c r="D493" t="s">
-        <v>509</v>
+      <c r="C493">
+        <v>169000</v>
+      </c>
+      <c r="D493">
+        <v>21565.3</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4">
+      <c r="A494" s="1">
+        <v>508</v>
+      </c>
+      <c r="B494" t="s">
+        <v>495</v>
+      </c>
+      <c r="C494" t="s">
+        <v>499</v>
+      </c>
+      <c r="D494" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="511">
   <si>
     <t>Date</t>
   </si>
@@ -1504,7 +1504,7 @@
     <t>2026-03-05</t>
   </si>
   <si>
-    <t>186086</t>
+    <t>2026-03-06</t>
   </si>
   <si>
     <t>187207</t>
@@ -1516,37 +1516,37 @@
     <t>170000</t>
   </si>
   <si>
-    <t>18618.28</t>
-  </si>
-  <si>
-    <t>18701.92</t>
-  </si>
-  <si>
-    <t>18823.64</t>
-  </si>
-  <si>
-    <t>18841.24</t>
-  </si>
-  <si>
-    <t>18901.33</t>
-  </si>
-  <si>
-    <t>18893.42</t>
-  </si>
-  <si>
-    <t>18922.63</t>
-  </si>
-  <si>
-    <t>18919.89</t>
-  </si>
-  <si>
-    <t>18943.15</t>
-  </si>
-  <si>
-    <t>19003.62</t>
-  </si>
-  <si>
-    <t>21806.42</t>
+    <t>22522.97</t>
+  </si>
+  <si>
+    <t>22669.56</t>
+  </si>
+  <si>
+    <t>22690.76</t>
+  </si>
+  <si>
+    <t>22763.12</t>
+  </si>
+  <si>
+    <t>22753.6</t>
+  </si>
+  <si>
+    <t>22788.77</t>
+  </si>
+  <si>
+    <t>22785.48</t>
+  </si>
+  <si>
+    <t>22813.49</t>
+  </si>
+  <si>
+    <t>22886.31</t>
+  </si>
+  <si>
+    <t>22978.99</t>
+  </si>
+  <si>
+    <t>21728.62</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D494"/>
+  <dimension ref="A1:D495"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8598,16 +8598,16 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479" s="1">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="B479" t="s">
         <v>480</v>
       </c>
-      <c r="C479" t="s">
-        <v>496</v>
-      </c>
-      <c r="D479" t="s">
-        <v>500</v>
+      <c r="C479">
+        <v>186086</v>
+      </c>
+      <c r="D479">
+        <v>18618.28</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8621,7 +8621,7 @@
         <v>497</v>
       </c>
       <c r="D480" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8635,7 +8635,7 @@
         <v>498</v>
       </c>
       <c r="D481" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8649,7 +8649,7 @@
         <v>498</v>
       </c>
       <c r="D482" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8663,7 +8663,7 @@
         <v>498</v>
       </c>
       <c r="D483" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8677,7 +8677,7 @@
         <v>498</v>
       </c>
       <c r="D484" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8691,7 +8691,7 @@
         <v>498</v>
       </c>
       <c r="D485" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8705,7 +8705,7 @@
         <v>498</v>
       </c>
       <c r="D486" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8719,7 +8719,7 @@
         <v>498</v>
       </c>
       <c r="D487" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8733,21 +8733,21 @@
         <v>498</v>
       </c>
       <c r="D488" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489">
-        <v>188328</v>
-      </c>
-      <c r="D489">
-        <v>24278.46</v>
+      <c r="C489" t="s">
+        <v>498</v>
+      </c>
+      <c r="D489" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8808,15 +8808,29 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494" t="s">
+      <c r="C494">
+        <v>170000</v>
+      </c>
+      <c r="D494">
+        <v>21806.42</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4">
+      <c r="A495" s="1">
+        <v>509</v>
+      </c>
+      <c r="B495" t="s">
+        <v>496</v>
+      </c>
+      <c r="C495" t="s">
         <v>499</v>
       </c>
-      <c r="D494" t="s">
+      <c r="D495" t="s">
         <v>510</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="504">
   <si>
     <t>Date</t>
   </si>
@@ -1507,46 +1507,25 @@
     <t>2026-03-06</t>
   </si>
   <si>
-    <t>187207</t>
-  </si>
-  <si>
-    <t>188328</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>178248</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>22522.97</t>
-  </si>
-  <si>
-    <t>22669.56</t>
-  </si>
-  <si>
-    <t>22690.76</t>
-  </si>
-  <si>
-    <t>22763.12</t>
-  </si>
-  <si>
-    <t>22753.6</t>
-  </si>
-  <si>
-    <t>22788.77</t>
-  </si>
-  <si>
-    <t>22785.48</t>
-  </si>
-  <si>
-    <t>22813.49</t>
-  </si>
-  <si>
-    <t>22886.31</t>
-  </si>
-  <si>
-    <t>22978.99</t>
-  </si>
-  <si>
-    <t>21728.62</t>
+    <t>24278.46</t>
+  </si>
+  <si>
+    <t>24219.9</t>
+  </si>
+  <si>
+    <t>24171.42</t>
+  </si>
+  <si>
+    <t>21671.03</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D495"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8612,133 +8591,133 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480" s="1">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="B480" t="s">
         <v>481</v>
       </c>
-      <c r="C480" t="s">
-        <v>497</v>
-      </c>
-      <c r="D480" t="s">
-        <v>500</v>
+      <c r="C480">
+        <v>187207</v>
+      </c>
+      <c r="D480">
+        <v>22522.97</v>
       </c>
     </row>
     <row r="481" spans="1:4">
       <c r="A481" s="1">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="B481" t="s">
         <v>482</v>
       </c>
-      <c r="C481" t="s">
-        <v>498</v>
-      </c>
-      <c r="D481" t="s">
-        <v>501</v>
+      <c r="C481">
+        <v>188328</v>
+      </c>
+      <c r="D481">
+        <v>22669.56</v>
       </c>
     </row>
     <row r="482" spans="1:4">
       <c r="A482" s="1">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B482" t="s">
         <v>483</v>
       </c>
-      <c r="C482" t="s">
-        <v>498</v>
-      </c>
-      <c r="D482" t="s">
-        <v>502</v>
+      <c r="C482">
+        <v>188328</v>
+      </c>
+      <c r="D482">
+        <v>22690.76</v>
       </c>
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="1">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="B483" t="s">
         <v>484</v>
       </c>
-      <c r="C483" t="s">
-        <v>498</v>
-      </c>
-      <c r="D483" t="s">
-        <v>503</v>
+      <c r="C483">
+        <v>188328</v>
+      </c>
+      <c r="D483">
+        <v>22763.12</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
-      <c r="C484" t="s">
-        <v>498</v>
-      </c>
-      <c r="D484" t="s">
-        <v>504</v>
+      <c r="C484">
+        <v>188328</v>
+      </c>
+      <c r="D484">
+        <v>22753.6</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
-      <c r="C485" t="s">
-        <v>498</v>
-      </c>
-      <c r="D485" t="s">
-        <v>505</v>
+      <c r="C485">
+        <v>188328</v>
+      </c>
+      <c r="D485">
+        <v>22788.77</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486" t="s">
-        <v>498</v>
-      </c>
-      <c r="D486" t="s">
-        <v>506</v>
+      <c r="C486">
+        <v>188328</v>
+      </c>
+      <c r="D486">
+        <v>22785.48</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487" t="s">
-        <v>498</v>
-      </c>
-      <c r="D487" t="s">
-        <v>507</v>
+      <c r="C487">
+        <v>188328</v>
+      </c>
+      <c r="D487">
+        <v>22813.49</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488" t="s">
-        <v>498</v>
-      </c>
-      <c r="D488" t="s">
-        <v>508</v>
+      <c r="C488">
+        <v>188328</v>
+      </c>
+      <c r="D488">
+        <v>22886.31</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
@@ -8747,7 +8726,7 @@
         <v>498</v>
       </c>
       <c r="D489" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8766,30 +8745,30 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491">
-        <v>168000</v>
-      </c>
-      <c r="D491">
-        <v>21605.62</v>
+      <c r="C491" t="s">
+        <v>498</v>
+      </c>
+      <c r="D491" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492">
-        <v>168000</v>
-      </c>
-      <c r="D492">
-        <v>21562.37</v>
+      <c r="C492" t="s">
+        <v>498</v>
+      </c>
+      <c r="D492" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8822,16 +8801,30 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
+      <c r="C495">
+        <v>170000</v>
+      </c>
+      <c r="D495">
+        <v>21728.62</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4">
+      <c r="A496" s="1">
+        <v>508</v>
+      </c>
+      <c r="B496" t="s">
+        <v>497</v>
+      </c>
+      <c r="C496" t="s">
         <v>499</v>
       </c>
-      <c r="D495" t="s">
-        <v>510</v>
+      <c r="D496" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="513">
   <si>
     <t>Date</t>
   </si>
@@ -1510,22 +1510,49 @@
     <t>2026-03-09</t>
   </si>
   <si>
-    <t>178248</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>148008</t>
+  </si>
+  <si>
+    <t>149770</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
+    <t>24050.38</t>
+  </si>
+  <si>
+    <t>24040.32</t>
+  </si>
+  <si>
+    <t>24077.49</t>
+  </si>
+  <si>
+    <t>24074.01</t>
+  </si>
+  <si>
+    <t>24103.6</t>
+  </si>
+  <si>
+    <t>24180.54</t>
+  </si>
+  <si>
     <t>24278.46</t>
   </si>
   <si>
-    <t>24219.9</t>
-  </si>
-  <si>
-    <t>24171.42</t>
-  </si>
-  <si>
-    <t>21671.03</t>
+    <t>24293.23</t>
+  </si>
+  <si>
+    <t>24411.38</t>
+  </si>
+  <si>
+    <t>21866.32</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D496"/>
+  <dimension ref="A1:D498"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8633,100 +8660,100 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="1">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="B483" t="s">
         <v>484</v>
       </c>
-      <c r="C483">
-        <v>188328</v>
-      </c>
-      <c r="D483">
-        <v>22763.12</v>
+      <c r="C483" t="s">
+        <v>500</v>
+      </c>
+      <c r="D483" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
-      <c r="C484">
-        <v>188328</v>
-      </c>
-      <c r="D484">
-        <v>22753.6</v>
+      <c r="C484" t="s">
+        <v>500</v>
+      </c>
+      <c r="D484" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
-      <c r="C485">
-        <v>188328</v>
-      </c>
-      <c r="D485">
-        <v>22788.77</v>
+      <c r="C485" t="s">
+        <v>500</v>
+      </c>
+      <c r="D485" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486">
-        <v>188328</v>
-      </c>
-      <c r="D486">
-        <v>22785.48</v>
+      <c r="C486" t="s">
+        <v>500</v>
+      </c>
+      <c r="D486" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487">
-        <v>188328</v>
-      </c>
-      <c r="D487">
-        <v>22813.49</v>
+      <c r="C487" t="s">
+        <v>500</v>
+      </c>
+      <c r="D487" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488">
-        <v>188328</v>
-      </c>
-      <c r="D488">
-        <v>22886.31</v>
+      <c r="C488" t="s">
+        <v>500</v>
+      </c>
+      <c r="D488" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D489" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8745,30 +8772,30 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491" t="s">
-        <v>498</v>
-      </c>
-      <c r="D491" t="s">
-        <v>501</v>
+      <c r="C491">
+        <v>178248</v>
+      </c>
+      <c r="D491">
+        <v>24219.9</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492" t="s">
-        <v>498</v>
-      </c>
-      <c r="D492" t="s">
-        <v>502</v>
+      <c r="C492">
+        <v>178248</v>
+      </c>
+      <c r="D492">
+        <v>24171.42</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8815,16 +8842,44 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
       <c r="C496" t="s">
+        <v>501</v>
+      </c>
+      <c r="D496" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4">
+      <c r="A497" s="1">
+        <v>510</v>
+      </c>
+      <c r="B497" t="s">
+        <v>498</v>
+      </c>
+      <c r="C497" t="s">
+        <v>501</v>
+      </c>
+      <c r="D497" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4">
+      <c r="A498" s="1">
+        <v>511</v>
+      </c>
+      <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="D496" t="s">
-        <v>503</v>
+      <c r="C498" t="s">
+        <v>502</v>
+      </c>
+      <c r="D498" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="513">
   <si>
     <t>Date</t>
   </si>
@@ -1516,43 +1516,43 @@
     <t>2026-03-11</t>
   </si>
   <si>
-    <t>148008</t>
-  </si>
-  <si>
-    <t>149770</t>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>190570</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>24050.38</t>
-  </si>
-  <si>
-    <t>24040.32</t>
-  </si>
-  <si>
-    <t>24077.49</t>
-  </si>
-  <si>
-    <t>24074.01</t>
-  </si>
-  <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>24180.54</t>
-  </si>
-  <si>
-    <t>24278.46</t>
-  </si>
-  <si>
-    <t>24293.23</t>
-  </si>
-  <si>
-    <t>24411.38</t>
-  </si>
-  <si>
-    <t>21866.32</t>
+    <t>22753.6</t>
+  </si>
+  <si>
+    <t>22788.77</t>
+  </si>
+  <si>
+    <t>22785.48</t>
+  </si>
+  <si>
+    <t>22813.49</t>
+  </si>
+  <si>
+    <t>22886.31</t>
+  </si>
+  <si>
+    <t>22978.99</t>
+  </si>
+  <si>
+    <t>23054.07</t>
+  </si>
+  <si>
+    <t>22992.97</t>
+  </si>
+  <si>
+    <t>21821.6</t>
   </si>
 </sst>
 </file>
@@ -1910,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D498"/>
+  <dimension ref="A1:D499"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8660,27 +8660,27 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483" s="1">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="B483" t="s">
         <v>484</v>
       </c>
-      <c r="C483" t="s">
-        <v>500</v>
-      </c>
-      <c r="D483" t="s">
-        <v>503</v>
+      <c r="C483">
+        <v>148008</v>
+      </c>
+      <c r="D483">
+        <v>24050.38</v>
       </c>
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
       <c r="C484" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D484" t="s">
         <v>504</v>
@@ -8688,13 +8688,13 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
       <c r="C485" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D485" t="s">
         <v>505</v>
@@ -8702,13 +8702,13 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
       <c r="C486" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D486" t="s">
         <v>506</v>
@@ -8716,13 +8716,13 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D487" t="s">
         <v>507</v>
@@ -8730,13 +8730,13 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
       <c r="C488" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D488" t="s">
         <v>508</v>
@@ -8744,13 +8744,13 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D489" t="s">
         <v>509</v>
@@ -8828,57 +8828,71 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495">
-        <v>170000</v>
-      </c>
-      <c r="D495">
-        <v>21728.62</v>
+      <c r="C495" t="s">
+        <v>502</v>
+      </c>
+      <c r="D495" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D496" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>501</v>
-      </c>
-      <c r="D497" t="s">
-        <v>511</v>
+      <c r="C497">
+        <v>149770</v>
+      </c>
+      <c r="D497">
+        <v>24411.38</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>502</v>
-      </c>
-      <c r="D498" t="s">
+      <c r="C498">
+        <v>170000</v>
+      </c>
+      <c r="D498">
+        <v>21866.32</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4">
+      <c r="A499" s="1">
+        <v>514</v>
+      </c>
+      <c r="B499" t="s">
+        <v>500</v>
+      </c>
+      <c r="C499" t="s">
+        <v>503</v>
+      </c>
+      <c r="D499" t="s">
         <v>512</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="514">
   <si>
     <t>Date</t>
   </si>
@@ -1519,40 +1519,43 @@
     <t>2026-03-12</t>
   </si>
   <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>190570</t>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>180370</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>22753.6</t>
-  </si>
-  <si>
-    <t>22788.77</t>
-  </si>
-  <si>
-    <t>22785.48</t>
-  </si>
-  <si>
-    <t>22813.49</t>
-  </si>
-  <si>
-    <t>22886.31</t>
-  </si>
-  <si>
-    <t>22978.99</t>
-  </si>
-  <si>
-    <t>23054.07</t>
-  </si>
-  <si>
-    <t>22992.97</t>
-  </si>
-  <si>
-    <t>21821.6</t>
+    <t>20211.34</t>
+  </si>
+  <si>
+    <t>20208.42</t>
+  </si>
+  <si>
+    <t>20233.26</t>
+  </si>
+  <si>
+    <t>20297.85</t>
+  </si>
+  <si>
+    <t>20380.05</t>
+  </si>
+  <si>
+    <t>20351.59</t>
+  </si>
+  <si>
+    <t>20392.44</t>
+  </si>
+  <si>
+    <t>20491.62</t>
+  </si>
+  <si>
+    <t>21803.26</t>
   </si>
 </sst>
 </file>
@@ -1910,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D499"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8674,16 +8677,16 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484" s="1">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="B484" t="s">
         <v>485</v>
       </c>
-      <c r="C484" t="s">
-        <v>501</v>
-      </c>
-      <c r="D484" t="s">
-        <v>504</v>
+      <c r="C484">
+        <v>188328</v>
+      </c>
+      <c r="D484">
+        <v>22753.6</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8694,7 +8697,7 @@
         <v>486</v>
       </c>
       <c r="C485" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D485" t="s">
         <v>505</v>
@@ -8708,7 +8711,7 @@
         <v>487</v>
       </c>
       <c r="C486" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D486" t="s">
         <v>506</v>
@@ -8722,7 +8725,7 @@
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D487" t="s">
         <v>507</v>
@@ -8736,7 +8739,7 @@
         <v>489</v>
       </c>
       <c r="C488" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D488" t="s">
         <v>508</v>
@@ -8750,7 +8753,7 @@
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D489" t="s">
         <v>509</v>
@@ -8758,16 +8761,16 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490">
-        <v>158088</v>
-      </c>
-      <c r="D490">
-        <v>19053.93</v>
+      <c r="C490" t="s">
+        <v>502</v>
+      </c>
+      <c r="D490" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8828,16 +8831,16 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
-        <v>502</v>
-      </c>
-      <c r="D495" t="s">
-        <v>510</v>
+      <c r="C495">
+        <v>190570</v>
+      </c>
+      <c r="D495">
+        <v>23054.07</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8848,7 +8851,7 @@
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D496" t="s">
         <v>511</v>
@@ -8856,16 +8859,16 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>149770</v>
-      </c>
-      <c r="D497">
-        <v>24411.38</v>
+      <c r="C497" t="s">
+        <v>503</v>
+      </c>
+      <c r="D497" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8884,16 +8887,30 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>503</v>
-      </c>
-      <c r="D499" t="s">
-        <v>512</v>
+      <c r="C499">
+        <v>170000</v>
+      </c>
+      <c r="D499">
+        <v>21821.6</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4">
+      <c r="A500" s="1">
+        <v>515</v>
+      </c>
+      <c r="B500" t="s">
+        <v>501</v>
+      </c>
+      <c r="C500" t="s">
+        <v>504</v>
+      </c>
+      <c r="D500" t="s">
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="512">
   <si>
     <t>Date</t>
   </si>
@@ -1522,40 +1522,34 @@
     <t>2026-03-13</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>170000</t>
-  </si>
-  <si>
-    <t>20211.34</t>
-  </si>
-  <si>
-    <t>20208.42</t>
-  </si>
-  <si>
-    <t>20233.26</t>
-  </si>
-  <si>
-    <t>20297.85</t>
-  </si>
-  <si>
-    <t>20380.05</t>
-  </si>
-  <si>
-    <t>20351.59</t>
-  </si>
-  <si>
-    <t>20392.44</t>
-  </si>
-  <si>
-    <t>20491.62</t>
-  </si>
-  <si>
-    <t>21803.26</t>
+    <t>148008</t>
+  </si>
+  <si>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>24077.49</t>
+  </si>
+  <si>
+    <t>24074.01</t>
+  </si>
+  <si>
+    <t>24103.6</t>
+  </si>
+  <si>
+    <t>24244.56</t>
+  </si>
+  <si>
+    <t>24219.9</t>
+  </si>
+  <si>
+    <t>24171.42</t>
+  </si>
+  <si>
+    <t>24293.23</t>
+  </si>
+  <si>
+    <t>24462.01</t>
   </si>
 </sst>
 </file>
@@ -8700,7 +8694,7 @@
         <v>502</v>
       </c>
       <c r="D485" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8714,7 +8708,7 @@
         <v>502</v>
       </c>
       <c r="D486" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8728,35 +8722,35 @@
         <v>502</v>
       </c>
       <c r="D487" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488" t="s">
-        <v>502</v>
-      </c>
-      <c r="D488" t="s">
-        <v>508</v>
+      <c r="C488">
+        <v>178248</v>
+      </c>
+      <c r="D488">
+        <v>20297.85</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489" t="s">
-        <v>502</v>
-      </c>
-      <c r="D489" t="s">
-        <v>509</v>
+      <c r="C489">
+        <v>178248</v>
+      </c>
+      <c r="D489">
+        <v>20380.05</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8770,35 +8764,35 @@
         <v>502</v>
       </c>
       <c r="D490" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491">
-        <v>178248</v>
-      </c>
-      <c r="D491">
-        <v>24219.9</v>
+      <c r="C491" t="s">
+        <v>502</v>
+      </c>
+      <c r="D491" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492">
-        <v>178248</v>
-      </c>
-      <c r="D492">
-        <v>24171.42</v>
+      <c r="C492" t="s">
+        <v>502</v>
+      </c>
+      <c r="D492" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8854,21 +8848,21 @@
         <v>503</v>
       </c>
       <c r="D496" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>503</v>
-      </c>
-      <c r="D497" t="s">
-        <v>512</v>
+      <c r="C497">
+        <v>180370</v>
+      </c>
+      <c r="D497">
+        <v>20491.62</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8887,30 +8881,30 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>170000</v>
-      </c>
-      <c r="D499">
-        <v>21821.6</v>
+      <c r="C499" t="s">
+        <v>503</v>
+      </c>
+      <c r="D499" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>504</v>
-      </c>
-      <c r="D500" t="s">
-        <v>513</v>
+      <c r="C500">
+        <v>170000</v>
+      </c>
+      <c r="D500">
+        <v>21803.26</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="518">
   <si>
     <t>Date</t>
   </si>
@@ -1522,34 +1522,52 @@
     <t>2026-03-13</t>
   </si>
   <si>
-    <t>148008</t>
-  </si>
-  <si>
-    <t>149770</t>
-  </si>
-  <si>
-    <t>24077.49</t>
-  </si>
-  <si>
-    <t>24074.01</t>
-  </si>
-  <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>24244.56</t>
-  </si>
-  <si>
-    <t>24219.9</t>
-  </si>
-  <si>
-    <t>24171.42</t>
-  </si>
-  <si>
-    <t>24293.23</t>
-  </si>
-  <si>
-    <t>24462.01</t>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>170000</t>
+  </si>
+  <si>
+    <t>19053.93</t>
+  </si>
+  <si>
+    <t>19034.55</t>
+  </si>
+  <si>
+    <t>18999.03</t>
+  </si>
+  <si>
+    <t>19211.45</t>
+  </si>
+  <si>
+    <t>19092.18</t>
+  </si>
+  <si>
+    <t>19185.04</t>
+  </si>
+  <si>
+    <t>19264.23</t>
+  </si>
+  <si>
+    <t>19208.67</t>
+  </si>
+  <si>
+    <t>19152.6</t>
+  </si>
+  <si>
+    <t>21794.1</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D502"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8685,44 +8703,44 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485" s="1">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="B485" t="s">
         <v>486</v>
       </c>
-      <c r="C485" t="s">
-        <v>502</v>
-      </c>
-      <c r="D485" t="s">
-        <v>504</v>
+      <c r="C485">
+        <v>148008</v>
+      </c>
+      <c r="D485">
+        <v>24077.49</v>
       </c>
     </row>
     <row r="486" spans="1:4">
       <c r="A486" s="1">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="B486" t="s">
         <v>487</v>
       </c>
-      <c r="C486" t="s">
-        <v>502</v>
-      </c>
-      <c r="D486" t="s">
-        <v>505</v>
+      <c r="C486">
+        <v>148008</v>
+      </c>
+      <c r="D486">
+        <v>24074.01</v>
       </c>
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487" t="s">
-        <v>502</v>
-      </c>
-      <c r="D487" t="s">
-        <v>506</v>
+      <c r="C487">
+        <v>148008</v>
+      </c>
+      <c r="D487">
+        <v>24103.6</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8755,72 +8773,72 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
       <c r="C490" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D490" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D491" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492" t="s">
-        <v>502</v>
-      </c>
-      <c r="D492" t="s">
-        <v>509</v>
+      <c r="C492">
+        <v>148008</v>
+      </c>
+      <c r="D492">
+        <v>24171.42</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
-      <c r="C493">
-        <v>169000</v>
-      </c>
-      <c r="D493">
-        <v>21565.3</v>
+      <c r="C493" t="s">
+        <v>505</v>
+      </c>
+      <c r="D493" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494">
-        <v>170000</v>
-      </c>
-      <c r="D494">
-        <v>21806.42</v>
+      <c r="C494" t="s">
+        <v>506</v>
+      </c>
+      <c r="D494" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8839,72 +8857,100 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D496" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>180370</v>
-      </c>
-      <c r="D497">
-        <v>20491.62</v>
+      <c r="C497" t="s">
+        <v>506</v>
+      </c>
+      <c r="D497" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498">
-        <v>170000</v>
-      </c>
-      <c r="D498">
-        <v>21866.32</v>
+      <c r="C498" t="s">
+        <v>506</v>
+      </c>
+      <c r="D498" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>503</v>
-      </c>
-      <c r="D499" t="s">
-        <v>511</v>
+      <c r="C499">
+        <v>149770</v>
+      </c>
+      <c r="D499">
+        <v>24462.01</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500">
-        <v>170000</v>
-      </c>
-      <c r="D500">
-        <v>21803.26</v>
+      <c r="C500" t="s">
+        <v>506</v>
+      </c>
+      <c r="D500" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4">
+      <c r="A501" s="1">
+        <v>513</v>
+      </c>
+      <c r="B501" t="s">
+        <v>502</v>
+      </c>
+      <c r="C501" t="s">
+        <v>506</v>
+      </c>
+      <c r="D501" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4">
+      <c r="A502" s="1">
+        <v>514</v>
+      </c>
+      <c r="B502" t="s">
+        <v>503</v>
+      </c>
+      <c r="C502" t="s">
+        <v>507</v>
+      </c>
+      <c r="D502" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="520">
   <si>
     <t>Date</t>
   </si>
@@ -1528,6 +1528,9 @@
     <t>2026-03-17</t>
   </si>
   <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
     <t>178248</t>
   </si>
   <si>
@@ -1540,34 +1543,37 @@
     <t>170000</t>
   </si>
   <si>
-    <t>19053.93</t>
-  </si>
-  <si>
-    <t>19034.55</t>
-  </si>
-  <si>
-    <t>18999.03</t>
-  </si>
-  <si>
-    <t>19211.45</t>
-  </si>
-  <si>
-    <t>19092.18</t>
-  </si>
-  <si>
-    <t>19185.04</t>
-  </si>
-  <si>
-    <t>19264.23</t>
-  </si>
-  <si>
-    <t>19208.67</t>
-  </si>
-  <si>
-    <t>19152.6</t>
-  </si>
-  <si>
-    <t>21794.1</t>
+    <t>24103.6</t>
+  </si>
+  <si>
+    <t>24180.54</t>
+  </si>
+  <si>
+    <t>24278.46</t>
+  </si>
+  <si>
+    <t>24244.56</t>
+  </si>
+  <si>
+    <t>24219.9</t>
+  </si>
+  <si>
+    <t>24171.42</t>
+  </si>
+  <si>
+    <t>24174.7</t>
+  </si>
+  <si>
+    <t>24444.99</t>
+  </si>
+  <si>
+    <t>24441.45</t>
+  </si>
+  <si>
+    <t>24370.11</t>
+  </si>
+  <si>
+    <t>21804.21</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +1931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D502"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8731,114 +8737,114 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487">
-        <v>148008</v>
-      </c>
-      <c r="D487">
-        <v>24103.6</v>
+      <c r="C487" t="s">
+        <v>505</v>
+      </c>
+      <c r="D487" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488">
-        <v>178248</v>
-      </c>
-      <c r="D488">
-        <v>20297.85</v>
+      <c r="C488" t="s">
+        <v>505</v>
+      </c>
+      <c r="D488" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489">
-        <v>178248</v>
-      </c>
-      <c r="D489">
-        <v>20380.05</v>
+      <c r="C489" t="s">
+        <v>505</v>
+      </c>
+      <c r="D489" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
       <c r="C490" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D490" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D491" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492">
-        <v>148008</v>
-      </c>
-      <c r="D492">
-        <v>24171.42</v>
+      <c r="C492" t="s">
+        <v>505</v>
+      </c>
+      <c r="D492" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D493" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
       <c r="C494" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D494" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8857,44 +8863,44 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496" t="s">
-        <v>506</v>
-      </c>
-      <c r="D496" t="s">
-        <v>512</v>
+      <c r="C496">
+        <v>180370</v>
+      </c>
+      <c r="D496">
+        <v>19092.18</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>509</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>506</v>
-      </c>
-      <c r="D497" t="s">
-        <v>513</v>
+      <c r="C497">
+        <v>180370</v>
+      </c>
+      <c r="D497">
+        <v>19185.04</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>506</v>
-      </c>
-      <c r="D498" t="s">
-        <v>514</v>
+      <c r="C498">
+        <v>180370</v>
+      </c>
+      <c r="D498">
+        <v>19264.23</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8913,44 +8919,58 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D500" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
       <c r="C501" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D501" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>507</v>
-      </c>
-      <c r="D502" t="s">
+      <c r="C502">
+        <v>170000</v>
+      </c>
+      <c r="D502">
+        <v>21794.1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4">
+      <c r="A503" s="1">
         <v>517</v>
+      </c>
+      <c r="B503" t="s">
+        <v>504</v>
+      </c>
+      <c r="C503" t="s">
+        <v>508</v>
+      </c>
+      <c r="D503" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="519">
   <si>
     <t>Date</t>
   </si>
@@ -1531,24 +1531,21 @@
     <t>2026-03-18</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>180370</t>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>189449</t>
+  </si>
+  <si>
+    <t>190570</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>24180.54</t>
-  </si>
-  <si>
     <t>24278.46</t>
   </si>
   <si>
@@ -1573,7 +1570,7 @@
     <t>24370.11</t>
   </si>
   <si>
-    <t>21804.21</t>
+    <t>21770.13</t>
   </si>
 </sst>
 </file>
@@ -1931,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D504"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8737,114 +8734,114 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487" t="s">
-        <v>505</v>
-      </c>
-      <c r="D487" t="s">
-        <v>509</v>
+      <c r="C487">
+        <v>178248</v>
+      </c>
+      <c r="D487">
+        <v>24103.6</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488" t="s">
-        <v>505</v>
-      </c>
-      <c r="D488" t="s">
-        <v>510</v>
+      <c r="C488">
+        <v>178248</v>
+      </c>
+      <c r="D488">
+        <v>24180.54</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D489" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
       <c r="C490" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D490" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D491" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
       <c r="C492" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D492" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D493" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
       <c r="C494" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D494" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8919,30 +8916,30 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D500" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
       <c r="C501" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D501" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8961,16 +8958,30 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>508</v>
-      </c>
-      <c r="D503" t="s">
+      <c r="C503">
+        <v>170000</v>
+      </c>
+      <c r="D503">
+        <v>21804.21</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4">
+      <c r="A504" s="1">
         <v>519</v>
+      </c>
+      <c r="B504" t="s">
+        <v>505</v>
+      </c>
+      <c r="C504" t="s">
+        <v>509</v>
+      </c>
+      <c r="D504" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="520">
   <si>
     <t>Date</t>
   </si>
@@ -1534,43 +1534,46 @@
     <t>2026-03-19</t>
   </si>
   <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>189449</t>
-  </si>
-  <si>
-    <t>190570</t>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>158088</t>
+  </si>
+  <si>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>159970</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>24278.46</t>
-  </si>
-  <si>
-    <t>24244.56</t>
-  </si>
-  <si>
-    <t>24219.9</t>
-  </si>
-  <si>
-    <t>24171.42</t>
-  </si>
-  <si>
-    <t>24174.7</t>
-  </si>
-  <si>
-    <t>24444.99</t>
-  </si>
-  <si>
-    <t>24441.45</t>
-  </si>
-  <si>
-    <t>24370.11</t>
-  </si>
-  <si>
-    <t>21770.13</t>
+    <t>20330.88</t>
+  </si>
+  <si>
+    <t>20290.19</t>
+  </si>
+  <si>
+    <t>20292.95</t>
+  </si>
+  <si>
+    <t>20519.84</t>
+  </si>
+  <si>
+    <t>20446.64</t>
+  </si>
+  <si>
+    <t>20392.44</t>
+  </si>
+  <si>
+    <t>20491.62</t>
+  </si>
+  <si>
+    <t>20485.69</t>
+  </si>
+  <si>
+    <t>21798.83</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D504"/>
+  <dimension ref="A1:D505"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8762,128 +8765,128 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489" t="s">
-        <v>506</v>
-      </c>
-      <c r="D489" t="s">
-        <v>510</v>
+      <c r="C489">
+        <v>188328</v>
+      </c>
+      <c r="D489">
+        <v>24278.46</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490" t="s">
-        <v>506</v>
-      </c>
-      <c r="D490" t="s">
-        <v>511</v>
+      <c r="C490">
+        <v>188328</v>
+      </c>
+      <c r="D490">
+        <v>24244.56</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D491" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
       <c r="C492" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D492" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D493" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
       <c r="C494" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D494" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495">
-        <v>190570</v>
-      </c>
-      <c r="D495">
-        <v>23054.07</v>
+      <c r="C495" t="s">
+        <v>509</v>
+      </c>
+      <c r="D495" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496">
-        <v>180370</v>
-      </c>
-      <c r="D496">
-        <v>19092.18</v>
+      <c r="C496" t="s">
+        <v>509</v>
+      </c>
+      <c r="D496" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>180370</v>
-      </c>
-      <c r="D497">
-        <v>19185.04</v>
+      <c r="C497" t="s">
+        <v>509</v>
+      </c>
+      <c r="D497" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8916,30 +8919,30 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>508</v>
-      </c>
-      <c r="D500" t="s">
-        <v>516</v>
+      <c r="C500">
+        <v>190570</v>
+      </c>
+      <c r="D500">
+        <v>24441.45</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501" t="s">
-        <v>508</v>
-      </c>
-      <c r="D501" t="s">
-        <v>517</v>
+      <c r="C501">
+        <v>190570</v>
+      </c>
+      <c r="D501">
+        <v>24370.11</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8972,7 +8975,7 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
@@ -8982,6 +8985,20 @@
       </c>
       <c r="D504" t="s">
         <v>518</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4">
+      <c r="A505" s="1">
+        <v>521</v>
+      </c>
+      <c r="B505" t="s">
+        <v>506</v>
+      </c>
+      <c r="C505" t="s">
+        <v>510</v>
+      </c>
+      <c r="D505" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="522">
   <si>
     <t>Date</t>
   </si>
@@ -1546,10 +1546,10 @@
     <t>159970</t>
   </si>
   <si>
-    <t>170000</t>
-  </si>
-  <si>
-    <t>20330.88</t>
+    <t>20233.26</t>
+  </si>
+  <si>
+    <t>20297.85</t>
   </si>
   <si>
     <t>20290.19</t>
@@ -1558,9 +1558,6 @@
     <t>20292.95</t>
   </si>
   <si>
-    <t>20519.84</t>
-  </si>
-  <si>
     <t>20446.64</t>
   </si>
   <si>
@@ -1570,10 +1567,19 @@
     <t>20491.62</t>
   </si>
   <si>
+    <t>20576.21</t>
+  </si>
+  <si>
+    <t>20534.13</t>
+  </si>
+  <si>
+    <t>20508.25</t>
+  </si>
+  <si>
+    <t>20517.76</t>
+  </si>
+  <si>
     <t>20485.69</t>
-  </si>
-  <si>
-    <t>21798.83</t>
   </si>
 </sst>
 </file>
@@ -8737,30 +8743,30 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487">
-        <v>178248</v>
-      </c>
-      <c r="D487">
-        <v>24103.6</v>
+      <c r="C487" t="s">
+        <v>507</v>
+      </c>
+      <c r="D487" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488">
-        <v>178248</v>
-      </c>
-      <c r="D488">
-        <v>24180.54</v>
+      <c r="C488" t="s">
+        <v>507</v>
+      </c>
+      <c r="D488" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8793,21 +8799,21 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491" t="s">
-        <v>507</v>
-      </c>
-      <c r="D491" t="s">
-        <v>511</v>
+      <c r="C491">
+        <v>158088</v>
+      </c>
+      <c r="D491">
+        <v>20330.88</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
@@ -8821,7 +8827,7 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
@@ -8835,21 +8841,21 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494" t="s">
-        <v>509</v>
-      </c>
-      <c r="D494" t="s">
-        <v>514</v>
+      <c r="C494">
+        <v>159970</v>
+      </c>
+      <c r="D494">
+        <v>20519.84</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
@@ -8858,12 +8864,12 @@
         <v>509</v>
       </c>
       <c r="D495" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
@@ -8872,12 +8878,12 @@
         <v>509</v>
       </c>
       <c r="D496" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
@@ -8886,35 +8892,35 @@
         <v>509</v>
       </c>
       <c r="D497" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498">
-        <v>180370</v>
-      </c>
-      <c r="D498">
-        <v>19264.23</v>
+      <c r="C498" t="s">
+        <v>509</v>
+      </c>
+      <c r="D498" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>149770</v>
-      </c>
-      <c r="D499">
-        <v>24462.01</v>
+      <c r="C499" t="s">
+        <v>509</v>
+      </c>
+      <c r="D499" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8947,35 +8953,35 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502">
-        <v>170000</v>
-      </c>
-      <c r="D502">
-        <v>21794.1</v>
+      <c r="C502" t="s">
+        <v>509</v>
+      </c>
+      <c r="D502" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503">
-        <v>170000</v>
-      </c>
-      <c r="D503">
-        <v>21804.21</v>
+      <c r="C503" t="s">
+        <v>509</v>
+      </c>
+      <c r="D503" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
@@ -8984,21 +8990,21 @@
         <v>509</v>
       </c>
       <c r="D504" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>510</v>
-      </c>
-      <c r="D505" t="s">
-        <v>519</v>
+      <c r="C505">
+        <v>170000</v>
+      </c>
+      <c r="D505">
+        <v>21798.83</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="521">
   <si>
     <t>Date</t>
   </si>
@@ -1537,49 +1537,46 @@
     <t>2026-03-20</t>
   </si>
   <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>20233.26</t>
-  </si>
-  <si>
-    <t>20297.85</t>
-  </si>
-  <si>
-    <t>20290.19</t>
-  </si>
-  <si>
-    <t>20292.95</t>
-  </si>
-  <si>
-    <t>20446.64</t>
-  </si>
-  <si>
-    <t>20392.44</t>
-  </si>
-  <si>
-    <t>20491.62</t>
-  </si>
-  <si>
-    <t>20576.21</t>
-  </si>
-  <si>
-    <t>20534.13</t>
-  </si>
-  <si>
-    <t>20508.25</t>
-  </si>
-  <si>
-    <t>20517.76</t>
-  </si>
-  <si>
-    <t>20485.69</t>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>170000</t>
+  </si>
+  <si>
+    <t>18943.15</t>
+  </si>
+  <si>
+    <t>19053.93</t>
+  </si>
+  <si>
+    <t>18999.03</t>
+  </si>
+  <si>
+    <t>19211.45</t>
+  </si>
+  <si>
+    <t>19264.23</t>
+  </si>
+  <si>
+    <t>19224.83</t>
+  </si>
+  <si>
+    <t>19208.67</t>
+  </si>
+  <si>
+    <t>19152.6</t>
+  </si>
+  <si>
+    <t>21716.08</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D506"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8749,24 +8746,24 @@
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D487" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488" t="s">
-        <v>507</v>
-      </c>
-      <c r="D488" t="s">
-        <v>511</v>
+      <c r="C488">
+        <v>158088</v>
+      </c>
+      <c r="D488">
+        <v>20297.85</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8785,16 +8782,16 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490">
-        <v>188328</v>
-      </c>
-      <c r="D490">
-        <v>24244.56</v>
+      <c r="C490" t="s">
+        <v>508</v>
+      </c>
+      <c r="D490" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8813,16 +8810,16 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492" t="s">
-        <v>507</v>
-      </c>
-      <c r="D492" t="s">
-        <v>512</v>
+      <c r="C492">
+        <v>158088</v>
+      </c>
+      <c r="D492">
+        <v>20290.19</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8833,66 +8830,66 @@
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D493" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494">
-        <v>159970</v>
-      </c>
-      <c r="D494">
-        <v>20519.84</v>
+      <c r="C494" t="s">
+        <v>510</v>
+      </c>
+      <c r="D494" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
-        <v>509</v>
-      </c>
-      <c r="D495" t="s">
-        <v>514</v>
+      <c r="C495">
+        <v>159970</v>
+      </c>
+      <c r="D495">
+        <v>20446.64</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496" t="s">
-        <v>509</v>
-      </c>
-      <c r="D496" t="s">
-        <v>515</v>
+      <c r="C496">
+        <v>159970</v>
+      </c>
+      <c r="D496">
+        <v>20392.44</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>509</v>
-      </c>
-      <c r="D497" t="s">
-        <v>516</v>
+      <c r="C497">
+        <v>159970</v>
+      </c>
+      <c r="D497">
+        <v>20491.62</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8903,10 +8900,10 @@
         <v>499</v>
       </c>
       <c r="C498" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D498" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8917,80 +8914,80 @@
         <v>500</v>
       </c>
       <c r="C499" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D499" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500">
-        <v>190570</v>
-      </c>
-      <c r="D500">
-        <v>24441.45</v>
+      <c r="C500" t="s">
+        <v>510</v>
+      </c>
+      <c r="D500" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501">
-        <v>190570</v>
-      </c>
-      <c r="D501">
-        <v>24370.11</v>
+      <c r="C501" t="s">
+        <v>510</v>
+      </c>
+      <c r="D501" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>509</v>
-      </c>
-      <c r="D502" t="s">
-        <v>519</v>
+      <c r="C502">
+        <v>159970</v>
+      </c>
+      <c r="D502">
+        <v>20508.25</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>509</v>
-      </c>
-      <c r="D503" t="s">
-        <v>520</v>
+      <c r="C503">
+        <v>159970</v>
+      </c>
+      <c r="D503">
+        <v>20517.76</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504" t="s">
-        <v>509</v>
-      </c>
-      <c r="D504" t="s">
-        <v>521</v>
+      <c r="C504">
+        <v>159970</v>
+      </c>
+      <c r="D504">
+        <v>20485.69</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -9005,6 +9002,20 @@
       </c>
       <c r="D505">
         <v>21798.83</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4">
+      <c r="A506" s="1">
+        <v>523</v>
+      </c>
+      <c r="B506" t="s">
+        <v>507</v>
+      </c>
+      <c r="C506" t="s">
+        <v>511</v>
+      </c>
+      <c r="D506" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="519">
   <si>
     <t>Date</t>
   </si>
@@ -1540,43 +1540,37 @@
     <t>2026-03-23</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>180370</t>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>148008</t>
+  </si>
+  <si>
+    <t>148889</t>
+  </si>
+  <si>
+    <t>149770</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>18943.15</t>
-  </si>
-  <si>
-    <t>19053.93</t>
-  </si>
-  <si>
-    <t>18999.03</t>
-  </si>
-  <si>
-    <t>19211.45</t>
-  </si>
-  <si>
-    <t>19264.23</t>
-  </si>
-  <si>
-    <t>19224.83</t>
-  </si>
-  <si>
-    <t>19208.67</t>
-  </si>
-  <si>
-    <t>19152.6</t>
-  </si>
-  <si>
-    <t>21716.08</t>
+    <t>24103.6</t>
+  </si>
+  <si>
+    <t>24174.7</t>
+  </si>
+  <si>
+    <t>24357.79</t>
+  </si>
+  <si>
+    <t>24293.23</t>
+  </si>
+  <si>
+    <t>24436.49</t>
+  </si>
+  <si>
+    <t>21776.43</t>
   </si>
 </sst>
 </file>
@@ -1934,7 +1928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D506"/>
+  <dimension ref="A1:D507"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8740,16 +8734,16 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D487" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8782,16 +8776,16 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490" t="s">
-        <v>508</v>
-      </c>
-      <c r="D490" t="s">
-        <v>513</v>
+      <c r="C490">
+        <v>178248</v>
+      </c>
+      <c r="D490">
+        <v>19053.93</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8824,13 +8818,13 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
       <c r="C493" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D493" t="s">
         <v>514</v>
@@ -8838,44 +8832,44 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494" t="s">
-        <v>510</v>
-      </c>
-      <c r="D494" t="s">
-        <v>515</v>
+      <c r="C494">
+        <v>180370</v>
+      </c>
+      <c r="D494">
+        <v>19211.45</v>
       </c>
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495">
-        <v>159970</v>
-      </c>
-      <c r="D495">
-        <v>20446.64</v>
+      <c r="C495" t="s">
+        <v>511</v>
+      </c>
+      <c r="D495" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496">
-        <v>159970</v>
-      </c>
-      <c r="D496">
-        <v>20392.44</v>
+      <c r="C496" t="s">
+        <v>511</v>
+      </c>
+      <c r="D496" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8894,58 +8888,58 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>510</v>
-      </c>
-      <c r="D498" t="s">
-        <v>516</v>
+      <c r="C498">
+        <v>180370</v>
+      </c>
+      <c r="D498">
+        <v>19264.23</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>510</v>
-      </c>
-      <c r="D499" t="s">
-        <v>517</v>
+      <c r="C499">
+        <v>180370</v>
+      </c>
+      <c r="D499">
+        <v>19224.83</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>510</v>
-      </c>
-      <c r="D500" t="s">
-        <v>518</v>
+      <c r="C500">
+        <v>180370</v>
+      </c>
+      <c r="D500">
+        <v>19208.67</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501" t="s">
-        <v>510</v>
-      </c>
-      <c r="D501" t="s">
-        <v>519</v>
+      <c r="C501">
+        <v>180370</v>
+      </c>
+      <c r="D501">
+        <v>19152.6</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8992,30 +8986,44 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>170000</v>
-      </c>
-      <c r="D505">
-        <v>21798.83</v>
+      <c r="C505" t="s">
+        <v>511</v>
+      </c>
+      <c r="D505" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>511</v>
-      </c>
-      <c r="D506" t="s">
-        <v>520</v>
+      <c r="C506">
+        <v>170000</v>
+      </c>
+      <c r="D506">
+        <v>21716.08</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4">
+      <c r="A507" s="1">
+        <v>525</v>
+      </c>
+      <c r="B507" t="s">
+        <v>508</v>
+      </c>
+      <c r="C507" t="s">
+        <v>512</v>
+      </c>
+      <c r="D507" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="518">
   <si>
     <t>Date</t>
   </si>
@@ -1543,34 +1543,31 @@
     <t>2026-03-24</t>
   </si>
   <si>
-    <t>148008</t>
-  </si>
-  <si>
-    <t>148889</t>
-  </si>
-  <si>
-    <t>149770</t>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>190570</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>24103.6</t>
-  </si>
-  <si>
-    <t>24174.7</t>
-  </si>
-  <si>
-    <t>24357.79</t>
-  </si>
-  <si>
-    <t>24293.23</t>
-  </si>
-  <si>
-    <t>24436.49</t>
-  </si>
-  <si>
-    <t>21776.43</t>
+    <t>18943.15</t>
+  </si>
+  <si>
+    <t>19092.18</t>
+  </si>
+  <si>
+    <t>19185.04</t>
+  </si>
+  <si>
+    <t>19204.77</t>
+  </si>
+  <si>
+    <t>21790.63</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D507"/>
+  <dimension ref="A1:D508"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8734,13 +8731,13 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
       <c r="C487" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D487" t="s">
         <v>513</v>
@@ -8818,16 +8815,16 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
-      <c r="C493" t="s">
-        <v>510</v>
-      </c>
-      <c r="D493" t="s">
-        <v>514</v>
+      <c r="C493">
+        <v>148889</v>
+      </c>
+      <c r="D493">
+        <v>24174.7</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8846,21 +8843,21 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
-        <v>511</v>
-      </c>
-      <c r="D495" t="s">
-        <v>515</v>
+      <c r="C495">
+        <v>149770</v>
+      </c>
+      <c r="D495">
+        <v>24357.79</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
@@ -8869,21 +8866,21 @@
         <v>511</v>
       </c>
       <c r="D496" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>159970</v>
-      </c>
-      <c r="D497">
-        <v>20491.62</v>
+      <c r="C497" t="s">
+        <v>511</v>
+      </c>
+      <c r="D497" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8986,7 +8983,7 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
@@ -8995,7 +8992,7 @@
         <v>511</v>
       </c>
       <c r="D505" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9014,16 +9011,30 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
+      <c r="C507">
+        <v>170000</v>
+      </c>
+      <c r="D507">
+        <v>21776.43</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4">
+      <c r="A508" s="1">
+        <v>527</v>
+      </c>
+      <c r="B508" t="s">
+        <v>509</v>
+      </c>
+      <c r="C508" t="s">
         <v>512</v>
       </c>
-      <c r="D507" t="s">
-        <v>518</v>
+      <c r="D508" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="524">
   <si>
     <t>Date</t>
   </si>
@@ -1546,28 +1546,46 @@
     <t>2026-03-25</t>
   </si>
   <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>190570</t>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>158088</t>
+  </si>
+  <si>
+    <t>159970</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>18943.15</t>
-  </si>
-  <si>
-    <t>19092.18</t>
-  </si>
-  <si>
-    <t>19185.04</t>
-  </si>
-  <si>
-    <t>19204.77</t>
-  </si>
-  <si>
-    <t>21790.63</t>
+    <t>22886.31</t>
+  </si>
+  <si>
+    <t>22978.99</t>
+  </si>
+  <si>
+    <t>22946.9</t>
+  </si>
+  <si>
+    <t>22992.97</t>
+  </si>
+  <si>
+    <t>23200.17</t>
+  </si>
+  <si>
+    <t>23152.72</t>
+  </si>
+  <si>
+    <t>23040.76</t>
+  </si>
+  <si>
+    <t>23104.79</t>
+  </si>
+  <si>
+    <t>23119.85</t>
+  </si>
+  <si>
+    <t>21737.1</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8731,58 +8749,58 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487" s="1">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="B487" t="s">
         <v>488</v>
       </c>
-      <c r="C487" t="s">
-        <v>510</v>
-      </c>
-      <c r="D487" t="s">
-        <v>513</v>
+      <c r="C487">
+        <v>188328</v>
+      </c>
+      <c r="D487">
+        <v>18943.15</v>
       </c>
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488">
-        <v>158088</v>
-      </c>
-      <c r="D488">
-        <v>20297.85</v>
+      <c r="C488" t="s">
+        <v>511</v>
+      </c>
+      <c r="D488" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489">
-        <v>188328</v>
-      </c>
-      <c r="D489">
-        <v>24278.46</v>
+      <c r="C489" t="s">
+        <v>511</v>
+      </c>
+      <c r="D489" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490">
-        <v>178248</v>
-      </c>
-      <c r="D490">
-        <v>19053.93</v>
+      <c r="C490" t="s">
+        <v>511</v>
+      </c>
+      <c r="D490" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8857,58 +8875,58 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D496" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>511</v>
-      </c>
-      <c r="D497" t="s">
-        <v>515</v>
+      <c r="C497">
+        <v>190570</v>
+      </c>
+      <c r="D497">
+        <v>19185.04</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498">
-        <v>180370</v>
-      </c>
-      <c r="D498">
-        <v>19264.23</v>
+      <c r="C498" t="s">
+        <v>512</v>
+      </c>
+      <c r="D498" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>519</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>180370</v>
-      </c>
-      <c r="D499">
-        <v>19224.83</v>
+      <c r="C499" t="s">
+        <v>512</v>
+      </c>
+      <c r="D499" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8983,49 +9001,49 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>511</v>
-      </c>
-      <c r="D505" t="s">
-        <v>516</v>
+      <c r="C505">
+        <v>190570</v>
+      </c>
+      <c r="D505">
+        <v>19204.77</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506">
-        <v>170000</v>
-      </c>
-      <c r="D506">
-        <v>21716.08</v>
+      <c r="C506" t="s">
+        <v>512</v>
+      </c>
+      <c r="D506" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>170000</v>
-      </c>
-      <c r="D507">
-        <v>21776.43</v>
+      <c r="C507" t="s">
+        <v>512</v>
+      </c>
+      <c r="D507" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
@@ -9034,7 +9052,21 @@
         <v>512</v>
       </c>
       <c r="D508" t="s">
-        <v>517</v>
+        <v>522</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4">
+      <c r="A509" s="1">
+        <v>529</v>
+      </c>
+      <c r="B509" t="s">
+        <v>510</v>
+      </c>
+      <c r="C509" t="s">
+        <v>513</v>
+      </c>
+      <c r="D509" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="522">
   <si>
     <t>Date</t>
   </si>
@@ -1549,43 +1549,37 @@
     <t>2026-03-26</t>
   </si>
   <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>170000</t>
-  </si>
-  <si>
-    <t>22886.31</t>
-  </si>
-  <si>
-    <t>22978.99</t>
-  </si>
-  <si>
-    <t>22946.9</t>
-  </si>
-  <si>
-    <t>22992.97</t>
-  </si>
-  <si>
-    <t>23200.17</t>
-  </si>
-  <si>
-    <t>23152.72</t>
-  </si>
-  <si>
-    <t>23040.76</t>
-  </si>
-  <si>
-    <t>23104.79</t>
-  </si>
-  <si>
-    <t>23119.85</t>
-  </si>
-  <si>
-    <t>21737.1</t>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>19080.58</t>
+  </si>
+  <si>
+    <t>19034.55</t>
+  </si>
+  <si>
+    <t>19142.92</t>
+  </si>
+  <si>
+    <t>19264.23</t>
+  </si>
+  <si>
+    <t>19208.67</t>
+  </si>
+  <si>
+    <t>19179.48</t>
+  </si>
+  <si>
+    <t>19204.77</t>
+  </si>
+  <si>
+    <t>19185.04</t>
   </si>
 </sst>
 </file>
@@ -1943,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8763,58 +8757,58 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488" s="1">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="B488" t="s">
         <v>489</v>
       </c>
-      <c r="C488" t="s">
-        <v>511</v>
-      </c>
-      <c r="D488" t="s">
-        <v>514</v>
+      <c r="C488">
+        <v>158088</v>
+      </c>
+      <c r="D488">
+        <v>22886.31</v>
       </c>
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
       <c r="C489" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D489" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="490" spans="1:4">
       <c r="A490" s="1">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="B490" t="s">
         <v>491</v>
       </c>
-      <c r="C490" t="s">
-        <v>511</v>
-      </c>
-      <c r="D490" t="s">
-        <v>516</v>
+      <c r="C490">
+        <v>148008</v>
+      </c>
+      <c r="D490">
+        <v>24244.56</v>
       </c>
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491">
-        <v>158088</v>
-      </c>
-      <c r="D491">
-        <v>20330.88</v>
+      <c r="C491" t="s">
+        <v>512</v>
+      </c>
+      <c r="D491" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8861,30 +8855,30 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495">
-        <v>149770</v>
-      </c>
-      <c r="D495">
-        <v>24357.79</v>
+      <c r="C495" t="s">
+        <v>513</v>
+      </c>
+      <c r="D495" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496" t="s">
-        <v>512</v>
-      </c>
-      <c r="D496" t="s">
-        <v>517</v>
+      <c r="C496">
+        <v>159970</v>
+      </c>
+      <c r="D496">
+        <v>22992.97</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8895,52 +8889,52 @@
         <v>498</v>
       </c>
       <c r="C497">
-        <v>190570</v>
+        <v>149770</v>
       </c>
       <c r="D497">
-        <v>19185.04</v>
+        <v>24411.38</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
       <c r="C498" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D498" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>512</v>
-      </c>
-      <c r="D499" t="s">
-        <v>519</v>
+      <c r="C499">
+        <v>149770</v>
+      </c>
+      <c r="D499">
+        <v>24462.01</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>498</v>
+        <v>521</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500">
-        <v>180370</v>
-      </c>
-      <c r="D500">
-        <v>19208.67</v>
+      <c r="C500" t="s">
+        <v>513</v>
+      </c>
+      <c r="D500" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8987,55 +8981,55 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504">
-        <v>159970</v>
-      </c>
-      <c r="D504">
-        <v>20485.69</v>
+      <c r="C504" t="s">
+        <v>513</v>
+      </c>
+      <c r="D504" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>190570</v>
-      </c>
-      <c r="D505">
-        <v>19204.77</v>
+      <c r="C505" t="s">
+        <v>513</v>
+      </c>
+      <c r="D505" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>512</v>
-      </c>
-      <c r="D506" t="s">
-        <v>520</v>
+      <c r="C506">
+        <v>159970</v>
+      </c>
+      <c r="D506">
+        <v>23040.76</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
       <c r="C507" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D507" t="s">
         <v>521</v>
@@ -9043,30 +9037,44 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>512</v>
-      </c>
-      <c r="D508" t="s">
-        <v>522</v>
+      <c r="C508">
+        <v>149770</v>
+      </c>
+      <c r="D508">
+        <v>24427.29</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509" t="s">
-        <v>513</v>
-      </c>
-      <c r="D509" t="s">
-        <v>523</v>
+      <c r="C509">
+        <v>149770</v>
+      </c>
+      <c r="D509">
+        <v>24367.29</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4">
+      <c r="A510" s="1">
+        <v>508</v>
+      </c>
+      <c r="B510" t="s">
+        <v>511</v>
+      </c>
+      <c r="C510">
+        <v>170000</v>
+      </c>
+      <c r="D510">
+        <v>21691.97</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="524">
   <si>
     <t>Date</t>
   </si>
@@ -1552,34 +1552,40 @@
     <t>2026-03-27</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>19080.58</t>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>190570</t>
+  </si>
+  <si>
+    <t>170000</t>
   </si>
   <si>
     <t>19034.55</t>
   </si>
   <si>
-    <t>19142.92</t>
-  </si>
-  <si>
-    <t>19264.23</t>
+    <t>19185.04</t>
+  </si>
+  <si>
+    <t>19224.83</t>
   </si>
   <si>
     <t>19208.67</t>
   </si>
   <si>
-    <t>19179.48</t>
-  </si>
-  <si>
-    <t>19204.77</t>
-  </si>
-  <si>
-    <t>19185.04</t>
+    <t>19150.39</t>
+  </si>
+  <si>
+    <t>19111.45</t>
+  </si>
+  <si>
+    <t>21718.59</t>
   </si>
 </sst>
 </file>
@@ -1937,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D510"/>
+  <dimension ref="A1:D512"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8771,16 +8777,16 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489" s="1">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="B489" t="s">
         <v>490</v>
       </c>
-      <c r="C489" t="s">
-        <v>512</v>
-      </c>
-      <c r="D489" t="s">
-        <v>514</v>
+      <c r="C489">
+        <v>178248</v>
+      </c>
+      <c r="D489">
+        <v>19080.58</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8799,16 +8805,16 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
       <c r="C491" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D491" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8855,16 +8861,16 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
-        <v>513</v>
-      </c>
-      <c r="D495" t="s">
-        <v>516</v>
+      <c r="C495">
+        <v>180370</v>
+      </c>
+      <c r="D495">
+        <v>19142.92</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8883,58 +8889,58 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>149770</v>
-      </c>
-      <c r="D497">
-        <v>24411.38</v>
+      <c r="C497" t="s">
+        <v>515</v>
+      </c>
+      <c r="D497" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>513</v>
-      </c>
-      <c r="D498" t="s">
-        <v>517</v>
+      <c r="C498">
+        <v>180370</v>
+      </c>
+      <c r="D498">
+        <v>19264.23</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>149770</v>
-      </c>
-      <c r="D499">
-        <v>24462.01</v>
+      <c r="C499" t="s">
+        <v>515</v>
+      </c>
+      <c r="D499" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D500" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8981,30 +8987,30 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504" t="s">
-        <v>513</v>
-      </c>
-      <c r="D504" t="s">
-        <v>519</v>
+      <c r="C504">
+        <v>180370</v>
+      </c>
+      <c r="D504">
+        <v>19179.48</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>513</v>
-      </c>
-      <c r="D505" t="s">
-        <v>520</v>
+      <c r="C505">
+        <v>180370</v>
+      </c>
+      <c r="D505">
+        <v>19204.77</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9023,16 +9029,16 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>513</v>
-      </c>
-      <c r="D507" t="s">
-        <v>521</v>
+      <c r="C507">
+        <v>180370</v>
+      </c>
+      <c r="D507">
+        <v>19185.04</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -9051,16 +9057,16 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509">
-        <v>149770</v>
-      </c>
-      <c r="D509">
-        <v>24367.29</v>
+      <c r="C509" t="s">
+        <v>515</v>
+      </c>
+      <c r="D509" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9075,6 +9081,34 @@
       </c>
       <c r="D510">
         <v>21691.97</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4">
+      <c r="A511" s="1">
+        <v>529</v>
+      </c>
+      <c r="B511" t="s">
+        <v>512</v>
+      </c>
+      <c r="C511" t="s">
+        <v>515</v>
+      </c>
+      <c r="D511" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4">
+      <c r="A512" s="1">
+        <v>530</v>
+      </c>
+      <c r="B512" t="s">
+        <v>513</v>
+      </c>
+      <c r="C512" t="s">
+        <v>516</v>
+      </c>
+      <c r="D512" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="529">
   <si>
     <t>Date</t>
   </si>
@@ -1558,34 +1558,49 @@
     <t>2026-03-31</t>
   </si>
   <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>190570</t>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>180370</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>19034.55</t>
-  </si>
-  <si>
-    <t>19185.04</t>
-  </si>
-  <si>
-    <t>19224.83</t>
-  </si>
-  <si>
-    <t>19208.67</t>
-  </si>
-  <si>
-    <t>19150.39</t>
-  </si>
-  <si>
-    <t>19111.45</t>
-  </si>
-  <si>
-    <t>21718.59</t>
+    <t>24171.42</t>
+  </si>
+  <si>
+    <t>24174.7</t>
+  </si>
+  <si>
+    <t>24444.99</t>
+  </si>
+  <si>
+    <t>24441.45</t>
+  </si>
+  <si>
+    <t>24431.18</t>
+  </si>
+  <si>
+    <t>24442.51</t>
+  </si>
+  <si>
+    <t>24316.7</t>
+  </si>
+  <si>
+    <t>24317.75</t>
+  </si>
+  <si>
+    <t>24346.54</t>
+  </si>
+  <si>
+    <t>21772.96</t>
   </si>
 </sst>
 </file>
@@ -1943,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D512"/>
+  <dimension ref="A1:D513"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8805,58 +8820,58 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491" s="1">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="B491" t="s">
         <v>492</v>
       </c>
-      <c r="C491" t="s">
-        <v>514</v>
-      </c>
-      <c r="D491" t="s">
-        <v>517</v>
+      <c r="C491">
+        <v>188328</v>
+      </c>
+      <c r="D491">
+        <v>19034.55</v>
       </c>
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492">
-        <v>158088</v>
-      </c>
-      <c r="D492">
-        <v>20290.19</v>
+      <c r="C492" t="s">
+        <v>515</v>
+      </c>
+      <c r="D492" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
-      <c r="C493">
-        <v>148889</v>
-      </c>
-      <c r="D493">
-        <v>24174.7</v>
+      <c r="C493" t="s">
+        <v>516</v>
+      </c>
+      <c r="D493" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494">
-        <v>180370</v>
-      </c>
-      <c r="D494">
-        <v>19211.45</v>
+      <c r="C494" t="s">
+        <v>517</v>
+      </c>
+      <c r="D494" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8889,16 +8904,16 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>515</v>
-      </c>
-      <c r="D497" t="s">
-        <v>518</v>
+      <c r="C497">
+        <v>190570</v>
+      </c>
+      <c r="D497">
+        <v>19185.04</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8917,30 +8932,30 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>515</v>
-      </c>
-      <c r="D499" t="s">
-        <v>519</v>
+      <c r="C499">
+        <v>190570</v>
+      </c>
+      <c r="D499">
+        <v>19224.83</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D500" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8959,30 +8974,30 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502">
-        <v>159970</v>
-      </c>
-      <c r="D502">
-        <v>20508.25</v>
+      <c r="C502" t="s">
+        <v>517</v>
+      </c>
+      <c r="D502" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>501</v>
+        <v>523</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503">
-        <v>159970</v>
-      </c>
-      <c r="D503">
-        <v>20517.76</v>
+      <c r="C503" t="s">
+        <v>517</v>
+      </c>
+      <c r="D503" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9057,58 +9072,72 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509" t="s">
-        <v>515</v>
-      </c>
-      <c r="D509" t="s">
-        <v>521</v>
+      <c r="C509">
+        <v>190570</v>
+      </c>
+      <c r="D509">
+        <v>19150.39</v>
       </c>
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510">
-        <v>170000</v>
-      </c>
-      <c r="D510">
-        <v>21691.97</v>
+      <c r="C510" t="s">
+        <v>517</v>
+      </c>
+      <c r="D510" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D511" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D512" t="s">
-        <v>523</v>
+        <v>527</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4">
+      <c r="A513" s="1">
+        <v>533</v>
+      </c>
+      <c r="B513" t="s">
+        <v>514</v>
+      </c>
+      <c r="C513" t="s">
+        <v>518</v>
+      </c>
+      <c r="D513" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="528">
   <si>
     <t>Date</t>
   </si>
@@ -1561,46 +1561,43 @@
     <t>2026-04-01</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>180370</t>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>159970</t>
   </si>
   <si>
     <t>170000</t>
   </si>
   <si>
-    <t>24171.42</t>
-  </si>
-  <si>
-    <t>24174.7</t>
-  </si>
-  <si>
-    <t>24444.99</t>
+    <t>24411.38</t>
+  </si>
+  <si>
+    <t>24512.15</t>
+  </si>
+  <si>
+    <t>24462.01</t>
   </si>
   <si>
     <t>24441.45</t>
   </si>
   <si>
-    <t>24431.18</t>
-  </si>
-  <si>
     <t>24442.51</t>
   </si>
   <si>
-    <t>24316.7</t>
-  </si>
-  <si>
-    <t>24317.75</t>
+    <t>24404.31</t>
+  </si>
+  <si>
+    <t>24436.49</t>
   </si>
   <si>
     <t>24346.54</t>
   </si>
   <si>
-    <t>21772.96</t>
+    <t>24407.49</t>
+  </si>
+  <si>
+    <t>21808.63</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D514"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8834,44 +8831,44 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492" s="1">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="B492" t="s">
         <v>493</v>
       </c>
-      <c r="C492" t="s">
-        <v>515</v>
-      </c>
-      <c r="D492" t="s">
-        <v>519</v>
+      <c r="C492">
+        <v>178248</v>
+      </c>
+      <c r="D492">
+        <v>24171.42</v>
       </c>
     </row>
     <row r="493" spans="1:4">
       <c r="A493" s="1">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="B493" t="s">
         <v>494</v>
       </c>
-      <c r="C493" t="s">
-        <v>516</v>
-      </c>
-      <c r="D493" t="s">
-        <v>520</v>
+      <c r="C493">
+        <v>179309</v>
+      </c>
+      <c r="D493">
+        <v>24174.7</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494" s="1">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="B494" t="s">
         <v>495</v>
       </c>
-      <c r="C494" t="s">
-        <v>517</v>
-      </c>
-      <c r="D494" t="s">
-        <v>521</v>
+      <c r="C494">
+        <v>180370</v>
+      </c>
+      <c r="D494">
+        <v>24444.99</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8904,58 +8901,58 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>190570</v>
-      </c>
-      <c r="D497">
-        <v>19185.04</v>
+      <c r="C497" t="s">
+        <v>516</v>
+      </c>
+      <c r="D497" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498">
-        <v>180370</v>
-      </c>
-      <c r="D498">
-        <v>19264.23</v>
+      <c r="C498" t="s">
+        <v>516</v>
+      </c>
+      <c r="D498" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>520</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>190570</v>
-      </c>
-      <c r="D499">
-        <v>19224.83</v>
+      <c r="C499" t="s">
+        <v>516</v>
+      </c>
+      <c r="D499" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D500" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8974,58 +8971,58 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>517</v>
-      </c>
-      <c r="D502" t="s">
-        <v>523</v>
+      <c r="C502">
+        <v>180370</v>
+      </c>
+      <c r="D502">
+        <v>24431.18</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
       <c r="C503" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D503" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>502</v>
+        <v>525</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504">
-        <v>180370</v>
-      </c>
-      <c r="D504">
-        <v>19179.48</v>
+      <c r="C504" t="s">
+        <v>516</v>
+      </c>
+      <c r="D504" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>180370</v>
-      </c>
-      <c r="D505">
-        <v>19204.77</v>
+      <c r="C505" t="s">
+        <v>516</v>
+      </c>
+      <c r="D505" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9086,58 +9083,72 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510" t="s">
-        <v>517</v>
-      </c>
-      <c r="D510" t="s">
-        <v>525</v>
+      <c r="C510">
+        <v>180370</v>
+      </c>
+      <c r="D510">
+        <v>24316.7</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511" t="s">
-        <v>517</v>
-      </c>
-      <c r="D511" t="s">
-        <v>526</v>
+      <c r="C511">
+        <v>180370</v>
+      </c>
+      <c r="D511">
+        <v>24317.75</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D512" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
       <c r="C513" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D513" t="s">
-        <v>528</v>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4">
+      <c r="A514" s="1">
+        <v>535</v>
+      </c>
+      <c r="B514" t="s">
+        <v>515</v>
+      </c>
+      <c r="C514" t="s">
+        <v>517</v>
+      </c>
+      <c r="D514" t="s">
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="529">
   <si>
     <t>Date</t>
   </si>
@@ -1564,13 +1564,13 @@
     <t>2026-04-02</t>
   </si>
   <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>170000</t>
-  </si>
-  <si>
-    <t>24411.38</t>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>169000</t>
   </si>
   <si>
     <t>24512.15</t>
@@ -1582,7 +1582,7 @@
     <t>24441.45</t>
   </si>
   <si>
-    <t>24442.51</t>
+    <t>24370.11</t>
   </si>
   <si>
     <t>24404.31</t>
@@ -1591,13 +1591,16 @@
     <t>24436.49</t>
   </si>
   <si>
-    <t>24346.54</t>
+    <t>24343.72</t>
   </si>
   <si>
     <t>24407.49</t>
   </si>
   <si>
-    <t>21808.63</t>
+    <t>24447.48</t>
+  </si>
+  <si>
+    <t>21660.56</t>
   </si>
 </sst>
 </file>
@@ -1955,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D514"/>
+  <dimension ref="A1:D515"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8901,16 +8904,16 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>516</v>
-      </c>
-      <c r="D497" t="s">
-        <v>518</v>
+      <c r="C497">
+        <v>159970</v>
+      </c>
+      <c r="D497">
+        <v>24411.38</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8921,7 +8924,7 @@
         <v>499</v>
       </c>
       <c r="C498" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D498" t="s">
         <v>519</v>
@@ -8935,7 +8938,7 @@
         <v>500</v>
       </c>
       <c r="C499" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D499" t="s">
         <v>520</v>
@@ -8949,7 +8952,7 @@
         <v>501</v>
       </c>
       <c r="C500" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D500" t="s">
         <v>521</v>
@@ -8957,16 +8960,16 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>499</v>
+        <v>522</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501">
-        <v>180370</v>
-      </c>
-      <c r="D501">
-        <v>19152.6</v>
+      <c r="C501" t="s">
+        <v>517</v>
+      </c>
+      <c r="D501" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8985,16 +8988,16 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>524</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>516</v>
-      </c>
-      <c r="D503" t="s">
-        <v>522</v>
+      <c r="C503">
+        <v>159970</v>
+      </c>
+      <c r="D503">
+        <v>24442.51</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9005,7 +9008,7 @@
         <v>505</v>
       </c>
       <c r="C504" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D504" t="s">
         <v>523</v>
@@ -9019,7 +9022,7 @@
         <v>506</v>
       </c>
       <c r="C505" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D505" t="s">
         <v>524</v>
@@ -9027,16 +9030,16 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>504</v>
+        <v>527</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506">
-        <v>159970</v>
-      </c>
-      <c r="D506">
-        <v>23040.76</v>
+      <c r="C506" t="s">
+        <v>517</v>
+      </c>
+      <c r="D506" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9111,16 +9114,16 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>533</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>516</v>
-      </c>
-      <c r="D512" t="s">
-        <v>525</v>
+      <c r="C512">
+        <v>159970</v>
+      </c>
+      <c r="D512">
+        <v>24346.54</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9131,7 +9134,7 @@
         <v>514</v>
       </c>
       <c r="C513" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D513" t="s">
         <v>526</v>
@@ -9149,6 +9152,20 @@
       </c>
       <c r="D514" t="s">
         <v>527</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4">
+      <c r="A515" s="1">
+        <v>536</v>
+      </c>
+      <c r="B515" t="s">
+        <v>516</v>
+      </c>
+      <c r="C515" t="s">
+        <v>518</v>
+      </c>
+      <c r="D515" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="526">
   <si>
     <t>Date</t>
   </si>
@@ -1567,40 +1567,31 @@
     <t>2026-04-03</t>
   </si>
   <si>
-    <t>149770</t>
-  </si>
-  <si>
-    <t>169000</t>
-  </si>
-  <si>
-    <t>24512.15</t>
-  </si>
-  <si>
-    <t>24462.01</t>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>24357.79</t>
+  </si>
+  <si>
+    <t>24293.23</t>
   </si>
   <si>
     <t>24441.45</t>
   </si>
   <si>
-    <t>24370.11</t>
-  </si>
-  <si>
-    <t>24404.31</t>
+    <t>24442.51</t>
   </si>
   <si>
     <t>24436.49</t>
   </si>
   <si>
-    <t>24343.72</t>
-  </si>
-  <si>
-    <t>24407.49</t>
-  </si>
-  <si>
-    <t>24447.48</t>
-  </si>
-  <si>
-    <t>21660.56</t>
+    <t>24367.29</t>
+  </si>
+  <si>
+    <t>24316.7</t>
+  </si>
+  <si>
+    <t>24346.54</t>
   </si>
 </sst>
 </file>
@@ -8876,30 +8867,30 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495">
-        <v>180370</v>
-      </c>
-      <c r="D495">
-        <v>19142.92</v>
+      <c r="C495" t="s">
+        <v>517</v>
+      </c>
+      <c r="D495" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496">
-        <v>159970</v>
-      </c>
-      <c r="D496">
-        <v>22992.97</v>
+      <c r="C496" t="s">
+        <v>517</v>
+      </c>
+      <c r="D496" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8918,30 +8909,30 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>519</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>517</v>
-      </c>
-      <c r="D498" t="s">
-        <v>519</v>
+      <c r="C498">
+        <v>149770</v>
+      </c>
+      <c r="D498">
+        <v>24512.15</v>
       </c>
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>520</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>517</v>
-      </c>
-      <c r="D499" t="s">
-        <v>520</v>
+      <c r="C499">
+        <v>149770</v>
+      </c>
+      <c r="D499">
+        <v>24462.01</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8955,21 +8946,21 @@
         <v>517</v>
       </c>
       <c r="D500" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501" t="s">
-        <v>517</v>
-      </c>
-      <c r="D501" t="s">
-        <v>522</v>
+      <c r="C501">
+        <v>149770</v>
+      </c>
+      <c r="D501">
+        <v>24370.11</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8988,30 +8979,30 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>501</v>
+        <v>524</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503">
-        <v>159970</v>
-      </c>
-      <c r="D503">
-        <v>24442.51</v>
+      <c r="C503" t="s">
+        <v>517</v>
+      </c>
+      <c r="D503" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504" t="s">
-        <v>517</v>
-      </c>
-      <c r="D504" t="s">
-        <v>523</v>
+      <c r="C504">
+        <v>149770</v>
+      </c>
+      <c r="D504">
+        <v>24404.31</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -9025,21 +9016,21 @@
         <v>517</v>
       </c>
       <c r="D505" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>517</v>
-      </c>
-      <c r="D506" t="s">
-        <v>525</v>
+      <c r="C506">
+        <v>149770</v>
+      </c>
+      <c r="D506">
+        <v>24343.72</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9072,30 +9063,30 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509">
-        <v>190570</v>
-      </c>
-      <c r="D509">
-        <v>19150.39</v>
+      <c r="C509" t="s">
+        <v>517</v>
+      </c>
+      <c r="D509" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510">
-        <v>180370</v>
-      </c>
-      <c r="D510">
-        <v>24316.7</v>
+      <c r="C510" t="s">
+        <v>517</v>
+      </c>
+      <c r="D510" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -9114,58 +9105,58 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512">
-        <v>159970</v>
-      </c>
-      <c r="D512">
-        <v>24346.54</v>
+      <c r="C512" t="s">
+        <v>517</v>
+      </c>
+      <c r="D512" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>534</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>517</v>
-      </c>
-      <c r="D513" t="s">
-        <v>526</v>
+      <c r="C513">
+        <v>149770</v>
+      </c>
+      <c r="D513">
+        <v>24407.49</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>535</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>517</v>
-      </c>
-      <c r="D514" t="s">
-        <v>527</v>
+      <c r="C514">
+        <v>149770</v>
+      </c>
+      <c r="D514">
+        <v>24447.48</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>536</v>
+        <v>513</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515" t="s">
-        <v>518</v>
-      </c>
-      <c r="D515" t="s">
-        <v>528</v>
+      <c r="C515">
+        <v>169000</v>
+      </c>
+      <c r="D515">
+        <v>21660.56</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="528">
   <si>
     <t>Date</t>
   </si>
@@ -1573,25 +1573,31 @@
     <t>24357.79</t>
   </si>
   <si>
-    <t>24293.23</t>
-  </si>
-  <si>
-    <t>24441.45</t>
+    <t>24370.11</t>
   </si>
   <si>
     <t>24442.51</t>
   </si>
   <si>
-    <t>24436.49</t>
+    <t>24411.38</t>
+  </si>
+  <si>
+    <t>24427.29</t>
   </si>
   <si>
     <t>24367.29</t>
   </si>
   <si>
-    <t>24316.7</t>
+    <t>24317.75</t>
   </si>
   <si>
     <t>24346.54</t>
+  </si>
+  <si>
+    <t>24407.49</t>
+  </si>
+  <si>
+    <t>24447.48</t>
   </si>
 </sst>
 </file>
@@ -8867,7 +8873,7 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
@@ -8881,16 +8887,16 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>517</v>
+        <v>494</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496" t="s">
-        <v>517</v>
-      </c>
-      <c r="D496" t="s">
-        <v>519</v>
+      <c r="C496">
+        <v>180370</v>
+      </c>
+      <c r="D496">
+        <v>24293.23</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8937,30 +8943,30 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>521</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>517</v>
-      </c>
-      <c r="D500" t="s">
-        <v>520</v>
+      <c r="C500">
+        <v>180370</v>
+      </c>
+      <c r="D500">
+        <v>24441.45</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501">
-        <v>149770</v>
-      </c>
-      <c r="D501">
-        <v>24370.11</v>
+      <c r="C501" t="s">
+        <v>517</v>
+      </c>
+      <c r="D501" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8979,7 +8985,7 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
@@ -8988,7 +8994,7 @@
         <v>517</v>
       </c>
       <c r="D503" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9007,16 +9013,16 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>517</v>
-      </c>
-      <c r="D505" t="s">
-        <v>522</v>
+      <c r="C505">
+        <v>180370</v>
+      </c>
+      <c r="D505">
+        <v>24436.49</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9035,35 +9041,35 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>180370</v>
-      </c>
-      <c r="D507">
-        <v>19185.04</v>
+      <c r="C507" t="s">
+        <v>517</v>
+      </c>
+      <c r="D507" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508">
-        <v>149770</v>
-      </c>
-      <c r="D508">
-        <v>24427.29</v>
+      <c r="C508" t="s">
+        <v>517</v>
+      </c>
+      <c r="D508" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
@@ -9077,35 +9083,35 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510" t="s">
-        <v>517</v>
-      </c>
-      <c r="D510" t="s">
-        <v>524</v>
+      <c r="C510">
+        <v>180370</v>
+      </c>
+      <c r="D510">
+        <v>24316.7</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511">
-        <v>180370</v>
-      </c>
-      <c r="D511">
-        <v>24317.75</v>
+      <c r="C511" t="s">
+        <v>517</v>
+      </c>
+      <c r="D511" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
@@ -9119,30 +9125,30 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>149770</v>
-      </c>
-      <c r="D513">
-        <v>24407.49</v>
+      <c r="C513" t="s">
+        <v>517</v>
+      </c>
+      <c r="D513" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>149770</v>
-      </c>
-      <c r="D514">
-        <v>24447.48</v>
+      <c r="C514" t="s">
+        <v>517</v>
+      </c>
+      <c r="D514" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="515" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="529">
   <si>
     <t>Date</t>
   </si>
@@ -1567,16 +1567,22 @@
     <t>2026-04-03</t>
   </si>
   <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>24357.79</t>
-  </si>
-  <si>
-    <t>24370.11</t>
-  </si>
-  <si>
-    <t>24442.51</t>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>24293.23</t>
+  </si>
+  <si>
+    <t>24462.01</t>
+  </si>
+  <si>
+    <t>24431.18</t>
+  </si>
+  <si>
+    <t>24436.49</t>
+  </si>
+  <si>
+    <t>24343.72</t>
   </si>
   <si>
     <t>24411.38</t>
@@ -1586,9 +1592,6 @@
   </si>
   <si>
     <t>24367.29</t>
-  </si>
-  <si>
-    <t>24317.75</t>
   </si>
   <si>
     <t>24346.54</t>
@@ -8873,30 +8876,30 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495" s="1">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="B495" t="s">
         <v>496</v>
       </c>
-      <c r="C495" t="s">
-        <v>517</v>
-      </c>
-      <c r="D495" t="s">
-        <v>518</v>
+      <c r="C495">
+        <v>180370</v>
+      </c>
+      <c r="D495">
+        <v>24357.79</v>
       </c>
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496">
-        <v>180370</v>
-      </c>
-      <c r="D496">
-        <v>24293.23</v>
+      <c r="C496" t="s">
+        <v>517</v>
+      </c>
+      <c r="D496" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8929,16 +8932,16 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>497</v>
+        <v>517</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499">
-        <v>149770</v>
-      </c>
-      <c r="D499">
-        <v>24462.01</v>
+      <c r="C499" t="s">
+        <v>517</v>
+      </c>
+      <c r="D499" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8957,44 +8960,44 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501" t="s">
-        <v>517</v>
-      </c>
-      <c r="D501" t="s">
-        <v>519</v>
+      <c r="C501">
+        <v>180370</v>
+      </c>
+      <c r="D501">
+        <v>24370.11</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502">
-        <v>180370</v>
-      </c>
-      <c r="D502">
-        <v>24431.18</v>
+      <c r="C502" t="s">
+        <v>517</v>
+      </c>
+      <c r="D502" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>517</v>
-      </c>
-      <c r="D503" t="s">
-        <v>520</v>
+      <c r="C503">
+        <v>180370</v>
+      </c>
+      <c r="D503">
+        <v>24442.51</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9013,35 +9016,35 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>180370</v>
-      </c>
-      <c r="D505">
-        <v>24436.49</v>
+      <c r="C505" t="s">
+        <v>517</v>
+      </c>
+      <c r="D505" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506">
-        <v>149770</v>
-      </c>
-      <c r="D506">
-        <v>24343.72</v>
+      <c r="C506" t="s">
+        <v>517</v>
+      </c>
+      <c r="D506" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
@@ -9050,12 +9053,12 @@
         <v>517</v>
       </c>
       <c r="D507" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
@@ -9064,12 +9067,12 @@
         <v>517</v>
       </c>
       <c r="D508" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
@@ -9078,7 +9081,7 @@
         <v>517</v>
       </c>
       <c r="D509" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9097,21 +9100,21 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511" t="s">
-        <v>517</v>
-      </c>
-      <c r="D511" t="s">
-        <v>524</v>
+      <c r="C511">
+        <v>180370</v>
+      </c>
+      <c r="D511">
+        <v>24317.75</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
@@ -9120,12 +9123,12 @@
         <v>517</v>
       </c>
       <c r="D512" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
@@ -9134,12 +9137,12 @@
         <v>517</v>
       </c>
       <c r="D513" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
@@ -9148,7 +9151,7 @@
         <v>517</v>
       </c>
       <c r="D514" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="515" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="529">
   <si>
     <t>Date</t>
   </si>
@@ -1567,16 +1567,25 @@
     <t>2026-04-03</t>
   </si>
   <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
     <t>149770</t>
   </si>
   <si>
+    <t>169000</t>
+  </si>
+  <si>
     <t>24293.23</t>
   </si>
   <si>
-    <t>24462.01</t>
-  </si>
-  <si>
-    <t>24431.18</t>
+    <t>24441.45</t>
+  </si>
+  <si>
+    <t>24442.51</t>
+  </si>
+  <si>
+    <t>24404.31</t>
   </si>
   <si>
     <t>24436.49</t>
@@ -1585,22 +1594,13 @@
     <t>24343.72</t>
   </si>
   <si>
-    <t>24411.38</t>
-  </si>
-  <si>
-    <t>24427.29</t>
-  </si>
-  <si>
     <t>24367.29</t>
   </si>
   <si>
     <t>24346.54</t>
   </si>
   <si>
-    <t>24407.49</t>
-  </si>
-  <si>
-    <t>24447.48</t>
+    <t>21703.31</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D515"/>
+  <dimension ref="A1:D516"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8896,10 +8896,10 @@
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D496" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8932,30 +8932,30 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499" s="1">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="B499" t="s">
         <v>500</v>
       </c>
-      <c r="C499" t="s">
-        <v>517</v>
-      </c>
-      <c r="D499" t="s">
-        <v>519</v>
+      <c r="C499">
+        <v>149770</v>
+      </c>
+      <c r="D499">
+        <v>24462.01</v>
       </c>
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500">
-        <v>180370</v>
-      </c>
-      <c r="D500">
-        <v>24441.45</v>
+      <c r="C500" t="s">
+        <v>518</v>
+      </c>
+      <c r="D500" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8974,44 +8974,44 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>517</v>
-      </c>
-      <c r="D502" t="s">
-        <v>520</v>
+      <c r="C502">
+        <v>149770</v>
+      </c>
+      <c r="D502">
+        <v>24431.18</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503">
-        <v>180370</v>
-      </c>
-      <c r="D503">
-        <v>24442.51</v>
+      <c r="C503" t="s">
+        <v>518</v>
+      </c>
+      <c r="D503" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504">
-        <v>149770</v>
-      </c>
-      <c r="D504">
-        <v>24404.31</v>
+      <c r="C504" t="s">
+        <v>518</v>
+      </c>
+      <c r="D504" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -9022,10 +9022,10 @@
         <v>506</v>
       </c>
       <c r="C505" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D505" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9036,38 +9036,38 @@
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D506" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>517</v>
-      </c>
-      <c r="D507" t="s">
-        <v>523</v>
+      <c r="C507">
+        <v>149770</v>
+      </c>
+      <c r="D507">
+        <v>24411.38</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>517</v>
-      </c>
-      <c r="D508" t="s">
-        <v>524</v>
+      <c r="C508">
+        <v>149770</v>
+      </c>
+      <c r="D508">
+        <v>24427.29</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9078,10 +9078,10 @@
         <v>510</v>
       </c>
       <c r="C509" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D509" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9120,38 +9120,38 @@
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D512" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>517</v>
-      </c>
-      <c r="D513" t="s">
-        <v>527</v>
+      <c r="C513">
+        <v>149770</v>
+      </c>
+      <c r="D513">
+        <v>24407.49</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>517</v>
-      </c>
-      <c r="D514" t="s">
-        <v>528</v>
+      <c r="C514">
+        <v>149770</v>
+      </c>
+      <c r="D514">
+        <v>24447.48</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9166,6 +9166,20 @@
       </c>
       <c r="D515">
         <v>21660.56</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4">
+      <c r="A516" s="1">
+        <v>534</v>
+      </c>
+      <c r="B516" t="s">
+        <v>517</v>
+      </c>
+      <c r="C516" t="s">
+        <v>519</v>
+      </c>
+      <c r="D516" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="526">
   <si>
     <t>Date</t>
   </si>
@@ -1570,37 +1570,28 @@
     <t>2026-04-07</t>
   </si>
   <si>
-    <t>149770</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>190570</t>
   </si>
   <si>
     <t>169000</t>
   </si>
   <si>
-    <t>24293.23</t>
-  </si>
-  <si>
-    <t>24441.45</t>
-  </si>
-  <si>
-    <t>24442.51</t>
-  </si>
-  <si>
-    <t>24404.31</t>
-  </si>
-  <si>
-    <t>24436.49</t>
-  </si>
-  <si>
-    <t>24343.72</t>
-  </si>
-  <si>
-    <t>24367.29</t>
-  </si>
-  <si>
-    <t>24346.54</t>
-  </si>
-  <si>
-    <t>21703.31</t>
+    <t>19092.18</t>
+  </si>
+  <si>
+    <t>19204.77</t>
+  </si>
+  <si>
+    <t>19131.87</t>
+  </si>
+  <si>
+    <t>19213.4</t>
+  </si>
+  <si>
+    <t>21779.8</t>
   </si>
 </sst>
 </file>
@@ -1958,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D516"/>
+  <dimension ref="A1:D517"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8890,16 +8881,16 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
       <c r="C496" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D496" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8946,16 +8937,16 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>518</v>
-      </c>
-      <c r="D500" t="s">
-        <v>521</v>
+      <c r="C500">
+        <v>149770</v>
+      </c>
+      <c r="D500">
+        <v>24441.45</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8988,58 +8979,58 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>518</v>
-      </c>
-      <c r="D503" t="s">
-        <v>522</v>
+      <c r="C503">
+        <v>149770</v>
+      </c>
+      <c r="D503">
+        <v>24442.51</v>
       </c>
     </row>
     <row r="504" spans="1:4">
       <c r="A504" s="1">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="B504" t="s">
         <v>505</v>
       </c>
-      <c r="C504" t="s">
-        <v>518</v>
-      </c>
-      <c r="D504" t="s">
-        <v>523</v>
+      <c r="C504">
+        <v>149770</v>
+      </c>
+      <c r="D504">
+        <v>24404.31</v>
       </c>
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
       <c r="C505" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D505" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D506" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9072,16 +9063,16 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509" t="s">
-        <v>518</v>
-      </c>
-      <c r="D509" t="s">
-        <v>526</v>
+      <c r="C509">
+        <v>149770</v>
+      </c>
+      <c r="D509">
+        <v>24367.29</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9114,16 +9105,16 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>518</v>
-      </c>
-      <c r="D512" t="s">
-        <v>527</v>
+      <c r="C512">
+        <v>149770</v>
+      </c>
+      <c r="D512">
+        <v>24346.54</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9142,16 +9133,16 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>149770</v>
-      </c>
-      <c r="D514">
-        <v>24447.48</v>
+      <c r="C514" t="s">
+        <v>519</v>
+      </c>
+      <c r="D514" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9170,16 +9161,30 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
-      <c r="C516" t="s">
-        <v>519</v>
-      </c>
-      <c r="D516" t="s">
-        <v>528</v>
+      <c r="C516">
+        <v>169000</v>
+      </c>
+      <c r="D516">
+        <v>21703.31</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4">
+      <c r="A517" s="1">
+        <v>536</v>
+      </c>
+      <c r="B517" t="s">
+        <v>518</v>
+      </c>
+      <c r="C517" t="s">
+        <v>520</v>
+      </c>
+      <c r="D517" t="s">
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="531">
   <si>
     <t>Date</t>
   </si>
@@ -1573,25 +1573,40 @@
     <t>2026-04-08</t>
   </si>
   <si>
-    <t>190570</t>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>179309</t>
   </si>
   <si>
     <t>169000</t>
   </si>
   <si>
-    <t>19092.18</t>
-  </si>
-  <si>
-    <t>19204.77</t>
-  </si>
-  <si>
-    <t>19131.87</t>
-  </si>
-  <si>
-    <t>19213.4</t>
-  </si>
-  <si>
-    <t>21779.8</t>
+    <t>24411.38</t>
+  </si>
+  <si>
+    <t>24427.29</t>
+  </si>
+  <si>
+    <t>24281.49</t>
+  </si>
+  <si>
+    <t>24329.41</t>
+  </si>
+  <si>
+    <t>24415.15</t>
+  </si>
+  <si>
+    <t>24461.82</t>
+  </si>
+  <si>
+    <t>21829.39</t>
   </si>
 </sst>
 </file>
@@ -1949,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D517"/>
+  <dimension ref="A1:D519"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8881,30 +8896,30 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496" s="1">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="B496" t="s">
         <v>497</v>
       </c>
-      <c r="C496" t="s">
-        <v>519</v>
-      </c>
-      <c r="D496" t="s">
-        <v>521</v>
+      <c r="C496">
+        <v>190570</v>
+      </c>
+      <c r="D496">
+        <v>19092.18</v>
       </c>
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497">
-        <v>159970</v>
-      </c>
-      <c r="D497">
-        <v>24411.38</v>
+      <c r="C497" t="s">
+        <v>521</v>
+      </c>
+      <c r="D497" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -9007,58 +9022,58 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>519</v>
-      </c>
-      <c r="D505" t="s">
-        <v>522</v>
+      <c r="C505">
+        <v>190570</v>
+      </c>
+      <c r="D505">
+        <v>19204.77</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>519</v>
-      </c>
-      <c r="D506" t="s">
-        <v>523</v>
+      <c r="C506">
+        <v>190570</v>
+      </c>
+      <c r="D506">
+        <v>19131.87</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>149770</v>
-      </c>
-      <c r="D507">
-        <v>24411.38</v>
+      <c r="C507" t="s">
+        <v>521</v>
+      </c>
+      <c r="D507" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508">
-        <v>149770</v>
-      </c>
-      <c r="D508">
-        <v>24427.29</v>
+      <c r="C508" t="s">
+        <v>521</v>
+      </c>
+      <c r="D508" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9133,44 +9148,44 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>519</v>
-      </c>
-      <c r="D514" t="s">
-        <v>524</v>
+      <c r="C514">
+        <v>190570</v>
+      </c>
+      <c r="D514">
+        <v>19213.4</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515">
-        <v>169000</v>
-      </c>
-      <c r="D515">
-        <v>21660.56</v>
+      <c r="C515" t="s">
+        <v>522</v>
+      </c>
+      <c r="D515" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
-      <c r="C516">
-        <v>169000</v>
-      </c>
-      <c r="D516">
-        <v>21703.31</v>
+      <c r="C516" t="s">
+        <v>522</v>
+      </c>
+      <c r="D516" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -9181,10 +9196,38 @@
         <v>518</v>
       </c>
       <c r="C517" t="s">
+        <v>522</v>
+      </c>
+      <c r="D517" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4">
+      <c r="A518" s="1">
+        <v>537</v>
+      </c>
+      <c r="B518" t="s">
+        <v>519</v>
+      </c>
+      <c r="C518" t="s">
+        <v>522</v>
+      </c>
+      <c r="D518" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4">
+      <c r="A519" s="1">
+        <v>538</v>
+      </c>
+      <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="D517" t="s">
-        <v>525</v>
+      <c r="C519" t="s">
+        <v>523</v>
+      </c>
+      <c r="D519" t="s">
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="528">
   <si>
     <t>Date</t>
   </si>
@@ -1579,34 +1579,25 @@
     <t>2026-04-10</t>
   </si>
   <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>169000</t>
-  </si>
-  <si>
-    <t>24411.38</t>
-  </si>
-  <si>
-    <t>24427.29</t>
-  </si>
-  <si>
-    <t>24281.49</t>
-  </si>
-  <si>
-    <t>24329.41</t>
-  </si>
-  <si>
-    <t>24415.15</t>
-  </si>
-  <si>
-    <t>24461.82</t>
-  </si>
-  <si>
-    <t>21829.39</t>
+    <t>190570</t>
+  </si>
+  <si>
+    <t>189449</t>
+  </si>
+  <si>
+    <t>19264.23</t>
+  </si>
+  <si>
+    <t>19197.54</t>
+  </si>
+  <si>
+    <t>19181.98</t>
+  </si>
+  <si>
+    <t>19213.4</t>
+  </si>
+  <si>
+    <t>19120.62</t>
   </si>
 </sst>
 </file>
@@ -8910,30 +8901,30 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497" s="1">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="B497" t="s">
         <v>498</v>
       </c>
-      <c r="C497" t="s">
-        <v>521</v>
-      </c>
-      <c r="D497" t="s">
-        <v>524</v>
+      <c r="C497">
+        <v>180370</v>
+      </c>
+      <c r="D497">
+        <v>24411.38</v>
       </c>
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498">
-        <v>149770</v>
-      </c>
-      <c r="D498">
-        <v>24512.15</v>
+      <c r="C498" t="s">
+        <v>521</v>
+      </c>
+      <c r="D498" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -9050,21 +9041,21 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>521</v>
-      </c>
-      <c r="D507" t="s">
-        <v>524</v>
+      <c r="C507">
+        <v>180370</v>
+      </c>
+      <c r="D507">
+        <v>24411.38</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
@@ -9073,7 +9064,7 @@
         <v>521</v>
       </c>
       <c r="D508" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9134,49 +9125,49 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>149770</v>
-      </c>
-      <c r="D513">
-        <v>24407.49</v>
+      <c r="C513" t="s">
+        <v>521</v>
+      </c>
+      <c r="D513" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>190570</v>
-      </c>
-      <c r="D514">
-        <v>19213.4</v>
+      <c r="C514" t="s">
+        <v>521</v>
+      </c>
+      <c r="D514" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515" t="s">
-        <v>522</v>
-      </c>
-      <c r="D515" t="s">
-        <v>526</v>
+      <c r="C515">
+        <v>179309</v>
+      </c>
+      <c r="D515">
+        <v>24281.49</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
@@ -9190,44 +9181,44 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>522</v>
-      </c>
-      <c r="D517" t="s">
-        <v>528</v>
+      <c r="C517">
+        <v>179309</v>
+      </c>
+      <c r="D517">
+        <v>24415.15</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>522</v>
-      </c>
-      <c r="D518" t="s">
-        <v>529</v>
+      <c r="C518">
+        <v>179309</v>
+      </c>
+      <c r="D518">
+        <v>24461.82</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>523</v>
-      </c>
-      <c r="D519" t="s">
-        <v>530</v>
+      <c r="C519">
+        <v>169000</v>
+      </c>
+      <c r="D519">
+        <v>21829.39</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="534">
   <si>
     <t>Date</t>
   </si>
@@ -1579,25 +1579,43 @@
     <t>2026-04-10</t>
   </si>
   <si>
-    <t>190570</t>
-  </si>
-  <si>
-    <t>189449</t>
-  </si>
-  <si>
-    <t>19264.23</t>
-  </si>
-  <si>
-    <t>19197.54</t>
-  </si>
-  <si>
-    <t>19181.98</t>
-  </si>
-  <si>
-    <t>19213.4</t>
-  </si>
-  <si>
-    <t>19120.62</t>
+    <t>159970</t>
+  </si>
+  <si>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>24441.45</t>
+  </si>
+  <si>
+    <t>24431.18</t>
+  </si>
+  <si>
+    <t>24343.72</t>
+  </si>
+  <si>
+    <t>24367.29</t>
+  </si>
+  <si>
+    <t>24316.7</t>
+  </si>
+  <si>
+    <t>24317.75</t>
+  </si>
+  <si>
+    <t>24346.54</t>
+  </si>
+  <si>
+    <t>24407.49</t>
+  </si>
+  <si>
+    <t>24329.41</t>
+  </si>
+  <si>
+    <t>24415.15</t>
+  </si>
+  <si>
+    <t>24461.82</t>
   </si>
 </sst>
 </file>
@@ -8915,16 +8933,16 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498" s="1">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="B498" t="s">
         <v>499</v>
       </c>
-      <c r="C498" t="s">
-        <v>521</v>
-      </c>
-      <c r="D498" t="s">
-        <v>523</v>
+      <c r="C498">
+        <v>190570</v>
+      </c>
+      <c r="D498">
+        <v>19264.23</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8943,16 +8961,16 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500">
-        <v>149770</v>
-      </c>
-      <c r="D500">
-        <v>24441.45</v>
+      <c r="C500" t="s">
+        <v>521</v>
+      </c>
+      <c r="D500" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8971,16 +8989,16 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502">
-        <v>149770</v>
-      </c>
-      <c r="D502">
-        <v>24431.18</v>
+      <c r="C502" t="s">
+        <v>521</v>
+      </c>
+      <c r="D502" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -9027,16 +9045,16 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506">
-        <v>190570</v>
-      </c>
-      <c r="D506">
-        <v>19131.87</v>
+      <c r="C506" t="s">
+        <v>521</v>
+      </c>
+      <c r="D506" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9055,77 +9073,77 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>521</v>
-      </c>
-      <c r="D508" t="s">
-        <v>524</v>
+      <c r="C508">
+        <v>190570</v>
+      </c>
+      <c r="D508">
+        <v>19197.54</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509">
-        <v>149770</v>
-      </c>
-      <c r="D509">
-        <v>24367.29</v>
+      <c r="C509" t="s">
+        <v>521</v>
+      </c>
+      <c r="D509" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510">
-        <v>180370</v>
-      </c>
-      <c r="D510">
-        <v>24316.7</v>
+      <c r="C510" t="s">
+        <v>521</v>
+      </c>
+      <c r="D510" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511">
-        <v>180370</v>
-      </c>
-      <c r="D511">
-        <v>24317.75</v>
+      <c r="C511" t="s">
+        <v>521</v>
+      </c>
+      <c r="D511" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512">
-        <v>149770</v>
-      </c>
-      <c r="D512">
-        <v>24346.54</v>
+      <c r="C512" t="s">
+        <v>521</v>
+      </c>
+      <c r="D512" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
@@ -9134,21 +9152,21 @@
         <v>521</v>
       </c>
       <c r="D513" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>521</v>
-      </c>
-      <c r="D514" t="s">
-        <v>526</v>
+      <c r="C514">
+        <v>190570</v>
+      </c>
+      <c r="D514">
+        <v>19213.4</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9167,7 +9185,7 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
@@ -9176,35 +9194,35 @@
         <v>522</v>
       </c>
       <c r="D516" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517">
-        <v>179309</v>
-      </c>
-      <c r="D517">
-        <v>24415.15</v>
+      <c r="C517" t="s">
+        <v>522</v>
+      </c>
+      <c r="D517" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518">
-        <v>179309</v>
-      </c>
-      <c r="D518">
-        <v>24461.82</v>
+      <c r="C518" t="s">
+        <v>522</v>
+      </c>
+      <c r="D518" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="519" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="535">
   <si>
     <t>Date</t>
   </si>
@@ -1579,43 +1579,46 @@
     <t>2026-04-10</t>
   </si>
   <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>24441.45</t>
-  </si>
-  <si>
-    <t>24431.18</t>
-  </si>
-  <si>
-    <t>24343.72</t>
-  </si>
-  <si>
-    <t>24367.29</t>
-  </si>
-  <si>
-    <t>24316.7</t>
-  </si>
-  <si>
-    <t>24317.75</t>
-  </si>
-  <si>
-    <t>24346.54</t>
-  </si>
-  <si>
-    <t>24407.49</t>
-  </si>
-  <si>
-    <t>24329.41</t>
-  </si>
-  <si>
-    <t>24415.15</t>
-  </si>
-  <si>
-    <t>24461.82</t>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>169000</t>
+  </si>
+  <si>
+    <t>23065.73</t>
+  </si>
+  <si>
+    <t>23123.54</t>
+  </si>
+  <si>
+    <t>23040.76</t>
+  </si>
+  <si>
+    <t>23104.79</t>
+  </si>
+  <si>
+    <t>23119.85</t>
+  </si>
+  <si>
+    <t>23063.06</t>
+  </si>
+  <si>
+    <t>23015.18</t>
+  </si>
+  <si>
+    <t>23016.17</t>
+  </si>
+  <si>
+    <t>23043.42</t>
+  </si>
+  <si>
+    <t>23101.12</t>
+  </si>
+  <si>
+    <t>21826.84</t>
   </si>
 </sst>
 </file>
@@ -1973,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D519"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8961,44 +8964,44 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500" s="1">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="B500" t="s">
         <v>501</v>
       </c>
-      <c r="C500" t="s">
-        <v>521</v>
-      </c>
-      <c r="D500" t="s">
-        <v>523</v>
+      <c r="C500">
+        <v>159970</v>
+      </c>
+      <c r="D500">
+        <v>24441.45</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501">
-        <v>180370</v>
-      </c>
-      <c r="D501">
-        <v>24370.11</v>
+      <c r="C501" t="s">
+        <v>522</v>
+      </c>
+      <c r="D501" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
       <c r="C502" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D502" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -9045,114 +9048,114 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D506" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>180370</v>
-      </c>
-      <c r="D507">
-        <v>24411.38</v>
+      <c r="C507" t="s">
+        <v>522</v>
+      </c>
+      <c r="D507" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508">
-        <v>190570</v>
-      </c>
-      <c r="D508">
-        <v>19197.54</v>
+      <c r="C508" t="s">
+        <v>522</v>
+      </c>
+      <c r="D508" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
       <c r="C509" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D509" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
       <c r="C510" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D510" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D511" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D512" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
       <c r="C513" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D513" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9185,44 +9188,44 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
-      <c r="C516" t="s">
-        <v>522</v>
-      </c>
-      <c r="D516" t="s">
-        <v>531</v>
+      <c r="C516">
+        <v>159029</v>
+      </c>
+      <c r="D516">
+        <v>24329.41</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>522</v>
-      </c>
-      <c r="D517" t="s">
-        <v>532</v>
+      <c r="C517">
+        <v>159029</v>
+      </c>
+      <c r="D517">
+        <v>24415.15</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>522</v>
-      </c>
-      <c r="D518" t="s">
-        <v>533</v>
+      <c r="C518">
+        <v>159029</v>
+      </c>
+      <c r="D518">
+        <v>24461.82</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -9237,6 +9240,20 @@
       </c>
       <c r="D519">
         <v>21829.39</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4">
+      <c r="A520" s="1">
+        <v>537</v>
+      </c>
+      <c r="B520" t="s">
+        <v>521</v>
+      </c>
+      <c r="C520" t="s">
+        <v>523</v>
+      </c>
+      <c r="D520" t="s">
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="535">
   <si>
     <t>Date</t>
   </si>
@@ -1582,43 +1582,43 @@
     <t>2026-04-13</t>
   </si>
   <si>
-    <t>149770</t>
-  </si>
-  <si>
-    <t>169000</t>
-  </si>
-  <si>
-    <t>23065.73</t>
-  </si>
-  <si>
-    <t>23123.54</t>
-  </si>
-  <si>
-    <t>23040.76</t>
-  </si>
-  <si>
-    <t>23104.79</t>
-  </si>
-  <si>
-    <t>23119.85</t>
-  </si>
-  <si>
-    <t>23063.06</t>
-  </si>
-  <si>
-    <t>23015.18</t>
-  </si>
-  <si>
-    <t>23016.17</t>
-  </si>
-  <si>
-    <t>23043.42</t>
-  </si>
-  <si>
-    <t>23101.12</t>
-  </si>
-  <si>
-    <t>21826.84</t>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>190570</t>
+  </si>
+  <si>
+    <t>189449</t>
+  </si>
+  <si>
+    <t>168000</t>
+  </si>
+  <si>
+    <t>19152.6</t>
+  </si>
+  <si>
+    <t>19204.77</t>
+  </si>
+  <si>
+    <t>19197.54</t>
+  </si>
+  <si>
+    <t>19150.39</t>
+  </si>
+  <si>
+    <t>19110.62</t>
+  </si>
+  <si>
+    <t>19111.45</t>
+  </si>
+  <si>
+    <t>19213.4</t>
+  </si>
+  <si>
+    <t>19188</t>
+  </si>
+  <si>
+    <t>21714.49</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8978,30 +8978,30 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
       <c r="C501" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D501" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>522</v>
-      </c>
-      <c r="D502" t="s">
-        <v>525</v>
+      <c r="C502">
+        <v>149770</v>
+      </c>
+      <c r="D502">
+        <v>23123.54</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -9034,55 +9034,55 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>190570</v>
-      </c>
-      <c r="D505">
-        <v>19204.77</v>
+      <c r="C505" t="s">
+        <v>523</v>
+      </c>
+      <c r="D505" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>522</v>
-      </c>
-      <c r="D506" t="s">
-        <v>526</v>
+      <c r="C506">
+        <v>149770</v>
+      </c>
+      <c r="D506">
+        <v>23040.76</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>522</v>
-      </c>
-      <c r="D507" t="s">
-        <v>527</v>
+      <c r="C507">
+        <v>149770</v>
+      </c>
+      <c r="D507">
+        <v>23104.79</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
       <c r="C508" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D508" t="s">
         <v>528</v>
@@ -9090,13 +9090,13 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
       <c r="C509" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D509" t="s">
         <v>529</v>
@@ -9104,13 +9104,13 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
       <c r="C510" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D510" t="s">
         <v>530</v>
@@ -9118,13 +9118,13 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D511" t="s">
         <v>531</v>
@@ -9132,44 +9132,44 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>522</v>
-      </c>
-      <c r="D512" t="s">
-        <v>532</v>
+      <c r="C512">
+        <v>149770</v>
+      </c>
+      <c r="D512">
+        <v>23043.42</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>522</v>
-      </c>
-      <c r="D513" t="s">
-        <v>533</v>
+      <c r="C513">
+        <v>149770</v>
+      </c>
+      <c r="D513">
+        <v>23101.12</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>190570</v>
-      </c>
-      <c r="D514">
-        <v>19213.4</v>
+      <c r="C514" t="s">
+        <v>523</v>
+      </c>
+      <c r="D514" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9202,16 +9202,16 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517">
-        <v>159029</v>
-      </c>
-      <c r="D517">
-        <v>24415.15</v>
+      <c r="C517" t="s">
+        <v>524</v>
+      </c>
+      <c r="D517" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -9244,15 +9244,29 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>523</v>
-      </c>
-      <c r="D520" t="s">
+      <c r="C520">
+        <v>169000</v>
+      </c>
+      <c r="D520">
+        <v>21826.84</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4">
+      <c r="A521" s="1">
+        <v>539</v>
+      </c>
+      <c r="B521" t="s">
+        <v>522</v>
+      </c>
+      <c r="C521" t="s">
+        <v>525</v>
+      </c>
+      <c r="D521" t="s">
         <v>534</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="532">
   <si>
     <t>Date</t>
   </si>
@@ -1585,40 +1585,31 @@
     <t>2026-04-14</t>
   </si>
   <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
     <t>190570</t>
   </si>
   <si>
     <t>189449</t>
   </si>
   <si>
-    <t>168000</t>
-  </si>
-  <si>
-    <t>19152.6</t>
-  </si>
-  <si>
-    <t>19204.77</t>
-  </si>
-  <si>
-    <t>19197.54</t>
-  </si>
-  <si>
-    <t>19150.39</t>
-  </si>
-  <si>
-    <t>19110.62</t>
-  </si>
-  <si>
-    <t>19111.45</t>
-  </si>
-  <si>
-    <t>19213.4</t>
-  </si>
-  <si>
-    <t>19188</t>
-  </si>
-  <si>
-    <t>21714.49</t>
+    <t>167000</t>
+  </si>
+  <si>
+    <t>23065.73</t>
+  </si>
+  <si>
+    <t>23015.18</t>
+  </si>
+  <si>
+    <t>23016.17</t>
+  </si>
+  <si>
+    <t>23160.98</t>
+  </si>
+  <si>
+    <t>21620.28</t>
   </si>
 </sst>
 </file>
@@ -1976,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8978,16 +8969,16 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
       <c r="C501" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D501" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -9034,16 +9025,16 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>523</v>
-      </c>
-      <c r="D505" t="s">
-        <v>527</v>
+      <c r="C505">
+        <v>190570</v>
+      </c>
+      <c r="D505">
+        <v>19204.77</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9076,58 +9067,58 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>523</v>
-      </c>
-      <c r="D508" t="s">
-        <v>528</v>
+      <c r="C508">
+        <v>190570</v>
+      </c>
+      <c r="D508">
+        <v>19197.54</v>
       </c>
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509" t="s">
-        <v>523</v>
-      </c>
-      <c r="D509" t="s">
-        <v>529</v>
+      <c r="C509">
+        <v>190570</v>
+      </c>
+      <c r="D509">
+        <v>19150.39</v>
       </c>
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
       <c r="C510" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D510" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D511" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -9160,16 +9151,16 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>523</v>
-      </c>
-      <c r="D514" t="s">
-        <v>532</v>
+      <c r="C514">
+        <v>190570</v>
+      </c>
+      <c r="D514">
+        <v>19213.4</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9202,16 +9193,16 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>524</v>
-      </c>
-      <c r="D517" t="s">
-        <v>533</v>
+      <c r="C517">
+        <v>189449</v>
+      </c>
+      <c r="D517">
+        <v>19188</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -9230,16 +9221,16 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>169000</v>
-      </c>
-      <c r="D519">
-        <v>21829.39</v>
+      <c r="C519" t="s">
+        <v>525</v>
+      </c>
+      <c r="D519" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9258,16 +9249,30 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521" t="s">
-        <v>525</v>
-      </c>
-      <c r="D521" t="s">
-        <v>534</v>
+      <c r="C521">
+        <v>168000</v>
+      </c>
+      <c r="D521">
+        <v>21714.49</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4">
+      <c r="A522" s="1">
+        <v>541</v>
+      </c>
+      <c r="B522" t="s">
+        <v>523</v>
+      </c>
+      <c r="C522" t="s">
+        <v>526</v>
+      </c>
+      <c r="D522" t="s">
+        <v>531</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="533">
   <si>
     <t>Date</t>
   </si>
@@ -1588,6 +1588,9 @@
     <t>2026-04-15</t>
   </si>
   <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
     <t>190570</t>
   </si>
   <si>
@@ -1597,19 +1600,19 @@
     <t>167000</t>
   </si>
   <si>
-    <t>23065.73</t>
-  </si>
-  <si>
-    <t>23015.18</t>
+    <t>23123.54</t>
   </si>
   <si>
     <t>23016.17</t>
   </si>
   <si>
-    <t>23160.98</t>
-  </si>
-  <si>
-    <t>21620.28</t>
+    <t>23043.42</t>
+  </si>
+  <si>
+    <t>23158.28</t>
+  </si>
+  <si>
+    <t>21615.54</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D522"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8969,30 +8972,30 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501" s="1">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="B501" t="s">
         <v>502</v>
       </c>
-      <c r="C501" t="s">
-        <v>524</v>
-      </c>
-      <c r="D501" t="s">
-        <v>527</v>
+      <c r="C501">
+        <v>190570</v>
+      </c>
+      <c r="D501">
+        <v>23065.73</v>
       </c>
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502">
-        <v>149770</v>
-      </c>
-      <c r="D502">
-        <v>23123.54</v>
+      <c r="C502" t="s">
+        <v>525</v>
+      </c>
+      <c r="D502" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -9095,16 +9098,16 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510" s="1">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="B510" t="s">
         <v>511</v>
       </c>
-      <c r="C510" t="s">
-        <v>524</v>
-      </c>
-      <c r="D510" t="s">
-        <v>528</v>
+      <c r="C510">
+        <v>190570</v>
+      </c>
+      <c r="D510">
+        <v>23015.18</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -9115,7 +9118,7 @@
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D511" t="s">
         <v>529</v>
@@ -9123,16 +9126,16 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512">
-        <v>149770</v>
-      </c>
-      <c r="D512">
-        <v>23043.42</v>
+      <c r="C512" t="s">
+        <v>525</v>
+      </c>
+      <c r="D512" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9221,30 +9224,30 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>525</v>
-      </c>
-      <c r="D519" t="s">
-        <v>530</v>
+      <c r="C519">
+        <v>189449</v>
+      </c>
+      <c r="D519">
+        <v>23160.98</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>169000</v>
-      </c>
-      <c r="D520">
-        <v>21826.84</v>
+      <c r="C520" t="s">
+        <v>526</v>
+      </c>
+      <c r="D520" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9263,16 +9266,30 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>526</v>
-      </c>
-      <c r="D522" t="s">
-        <v>531</v>
+      <c r="C522">
+        <v>167000</v>
+      </c>
+      <c r="D522">
+        <v>21620.28</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4">
+      <c r="A523" s="1">
+        <v>542</v>
+      </c>
+      <c r="B523" t="s">
+        <v>524</v>
+      </c>
+      <c r="C523" t="s">
+        <v>527</v>
+      </c>
+      <c r="D523" t="s">
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="539">
   <si>
     <t>Date</t>
   </si>
@@ -1591,16 +1591,25 @@
     <t>2026-04-16</t>
   </si>
   <si>
-    <t>190570</t>
-  </si>
-  <si>
-    <t>189449</t>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>148889</t>
+  </si>
+  <si>
+    <t>148008</t>
   </si>
   <si>
     <t>167000</t>
   </si>
   <si>
-    <t>23123.54</t>
+    <t>23134.26</t>
+  </si>
+  <si>
+    <t>23063.06</t>
   </si>
   <si>
     <t>23016.17</t>
@@ -1609,10 +1618,19 @@
     <t>23043.42</t>
   </si>
   <si>
+    <t>23101.12</t>
+  </si>
+  <si>
+    <t>23160.98</t>
+  </si>
+  <si>
     <t>23158.28</t>
   </si>
   <si>
-    <t>21615.54</t>
+    <t>23039.07</t>
+  </si>
+  <si>
+    <t>21597.22</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D524"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -8986,30 +9004,30 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502" s="1">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="B502" t="s">
         <v>503</v>
       </c>
-      <c r="C502" t="s">
-        <v>525</v>
-      </c>
-      <c r="D502" t="s">
-        <v>528</v>
+      <c r="C502">
+        <v>190570</v>
+      </c>
+      <c r="D502">
+        <v>23123.54</v>
       </c>
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503">
-        <v>149770</v>
-      </c>
-      <c r="D503">
-        <v>24442.51</v>
+      <c r="C503" t="s">
+        <v>526</v>
+      </c>
+      <c r="D503" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9084,16 +9102,16 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509">
-        <v>190570</v>
-      </c>
-      <c r="D509">
-        <v>19150.39</v>
+      <c r="C509" t="s">
+        <v>526</v>
+      </c>
+      <c r="D509" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9118,10 +9136,10 @@
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D511" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -9132,24 +9150,24 @@
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D512" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>149770</v>
-      </c>
-      <c r="D513">
-        <v>23101.12</v>
+      <c r="C513" t="s">
+        <v>526</v>
+      </c>
+      <c r="D513" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9224,16 +9242,16 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>189449</v>
-      </c>
-      <c r="D519">
-        <v>23160.98</v>
+      <c r="C519" t="s">
+        <v>527</v>
+      </c>
+      <c r="D519" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9244,24 +9262,24 @@
         <v>521</v>
       </c>
       <c r="C520" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D520" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521">
-        <v>168000</v>
-      </c>
-      <c r="D521">
-        <v>21714.49</v>
+      <c r="C521" t="s">
+        <v>528</v>
+      </c>
+      <c r="D521" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -9280,16 +9298,30 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523" t="s">
-        <v>527</v>
-      </c>
-      <c r="D523" t="s">
-        <v>532</v>
+      <c r="C523">
+        <v>167000</v>
+      </c>
+      <c r="D523">
+        <v>21615.54</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4">
+      <c r="A524" s="1">
+        <v>543</v>
+      </c>
+      <c r="B524" t="s">
+        <v>525</v>
+      </c>
+      <c r="C524" t="s">
+        <v>529</v>
+      </c>
+      <c r="D524" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="541">
   <si>
     <t>Date</t>
   </si>
@@ -1603,34 +1603,40 @@
     <t>148008</t>
   </si>
   <si>
-    <t>167000</t>
-  </si>
-  <si>
-    <t>23134.26</t>
-  </si>
-  <si>
-    <t>23063.06</t>
+    <t>147127</t>
+  </si>
+  <si>
+    <t>23128.56</t>
+  </si>
+  <si>
+    <t>23104.79</t>
   </si>
   <si>
     <t>23016.17</t>
   </si>
   <si>
-    <t>23043.42</t>
-  </si>
-  <si>
-    <t>23101.12</t>
-  </si>
-  <si>
-    <t>23160.98</t>
-  </si>
-  <si>
-    <t>23158.28</t>
+    <t>23138.96</t>
+  </si>
+  <si>
+    <t>22981.86</t>
+  </si>
+  <si>
+    <t>23027.21</t>
+  </si>
+  <si>
+    <t>23108.37</t>
+  </si>
+  <si>
+    <t>23152.54</t>
   </si>
   <si>
     <t>23039.07</t>
   </si>
   <si>
-    <t>21597.22</t>
+    <t>22939.12</t>
+  </si>
+  <si>
+    <t>22934.09</t>
   </si>
 </sst>
 </file>
@@ -9018,16 +9024,16 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503" s="1">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="B503" t="s">
         <v>504</v>
       </c>
-      <c r="C503" t="s">
-        <v>526</v>
-      </c>
-      <c r="D503" t="s">
-        <v>530</v>
+      <c r="C503">
+        <v>149770</v>
+      </c>
+      <c r="D503">
+        <v>23134.26</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -9046,16 +9052,16 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505">
-        <v>190570</v>
-      </c>
-      <c r="D505">
-        <v>19204.77</v>
+      <c r="C505" t="s">
+        <v>526</v>
+      </c>
+      <c r="D505" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -9074,16 +9080,16 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>149770</v>
-      </c>
-      <c r="D507">
-        <v>23104.79</v>
+      <c r="C507" t="s">
+        <v>526</v>
+      </c>
+      <c r="D507" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -9102,16 +9108,16 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509" s="1">
-        <v>528</v>
+        <v>507</v>
       </c>
       <c r="B509" t="s">
         <v>510</v>
       </c>
-      <c r="C509" t="s">
-        <v>526</v>
-      </c>
-      <c r="D509" t="s">
-        <v>531</v>
+      <c r="C509">
+        <v>149770</v>
+      </c>
+      <c r="D509">
+        <v>23063.06</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -9130,7 +9136,7 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
@@ -9144,133 +9150,133 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>526</v>
-      </c>
-      <c r="D512" t="s">
-        <v>533</v>
+      <c r="C512">
+        <v>149770</v>
+      </c>
+      <c r="D512">
+        <v>23043.42</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>526</v>
-      </c>
-      <c r="D513" t="s">
-        <v>534</v>
+      <c r="C513">
+        <v>149770</v>
+      </c>
+      <c r="D513">
+        <v>23101.12</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>190570</v>
-      </c>
-      <c r="D514">
-        <v>19213.4</v>
+      <c r="C514" t="s">
+        <v>526</v>
+      </c>
+      <c r="D514" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515">
-        <v>179309</v>
-      </c>
-      <c r="D515">
-        <v>24281.49</v>
+      <c r="C515" t="s">
+        <v>527</v>
+      </c>
+      <c r="D515" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
-      <c r="C516">
-        <v>159029</v>
-      </c>
-      <c r="D516">
-        <v>24329.41</v>
+      <c r="C516" t="s">
+        <v>527</v>
+      </c>
+      <c r="D516" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517">
-        <v>189449</v>
-      </c>
-      <c r="D517">
-        <v>19188</v>
+      <c r="C517" t="s">
+        <v>527</v>
+      </c>
+      <c r="D517" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518">
-        <v>159029</v>
-      </c>
-      <c r="D518">
-        <v>24461.82</v>
+      <c r="C518" t="s">
+        <v>527</v>
+      </c>
+      <c r="D518" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>527</v>
-      </c>
-      <c r="D519" t="s">
-        <v>535</v>
+      <c r="C519">
+        <v>148889</v>
+      </c>
+      <c r="D519">
+        <v>23160.98</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>527</v>
-      </c>
-      <c r="D520" t="s">
-        <v>536</v>
+      <c r="C520">
+        <v>148889</v>
+      </c>
+      <c r="D520">
+        <v>23158.28</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
@@ -9279,49 +9285,49 @@
         <v>528</v>
       </c>
       <c r="D521" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>167000</v>
-      </c>
-      <c r="D522">
-        <v>21620.28</v>
+      <c r="C522" t="s">
+        <v>529</v>
+      </c>
+      <c r="D522" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523">
-        <v>167000</v>
-      </c>
-      <c r="D523">
-        <v>21615.54</v>
+      <c r="C523" t="s">
+        <v>529</v>
+      </c>
+      <c r="D523" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>529</v>
-      </c>
-      <c r="D524" t="s">
-        <v>538</v>
+      <c r="C524">
+        <v>167000</v>
+      </c>
+      <c r="D524">
+        <v>21597.22</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="541">
   <si>
     <t>Date</t>
   </si>
@@ -1594,19 +1594,19 @@
     <t>2026-04-17</t>
   </si>
   <si>
-    <t>149770</t>
-  </si>
-  <si>
-    <t>148889</t>
-  </si>
-  <si>
-    <t>148008</t>
-  </si>
-  <si>
-    <t>147127</t>
-  </si>
-  <si>
-    <t>23128.56</t>
+    <t>2026-04-20</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>165500</t>
+  </si>
+  <si>
+    <t>23040.76</t>
   </si>
   <si>
     <t>23104.79</t>
@@ -1615,6 +1615,12 @@
     <t>23016.17</t>
   </si>
   <si>
+    <t>23043.42</t>
+  </si>
+  <si>
+    <t>23101.12</t>
+  </si>
+  <si>
     <t>23138.96</t>
   </si>
   <si>
@@ -1630,13 +1636,7 @@
     <t>23152.54</t>
   </si>
   <si>
-    <t>23039.07</t>
-  </si>
-  <si>
-    <t>22939.12</t>
-  </si>
-  <si>
-    <t>22934.09</t>
+    <t>21417.94</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D524"/>
+  <dimension ref="A1:D525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9052,41 +9052,41 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505" s="1">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
         <v>506</v>
       </c>
-      <c r="C505" t="s">
-        <v>526</v>
-      </c>
-      <c r="D505" t="s">
-        <v>530</v>
+      <c r="C505">
+        <v>149770</v>
+      </c>
+      <c r="D505">
+        <v>23128.56</v>
       </c>
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506">
-        <v>149770</v>
-      </c>
-      <c r="D506">
-        <v>23040.76</v>
+      <c r="C506" t="s">
+        <v>527</v>
+      </c>
+      <c r="D506" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
       <c r="C507" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D507" t="s">
         <v>531</v>
@@ -9136,13 +9136,13 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D511" t="s">
         <v>532</v>
@@ -9150,100 +9150,100 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512">
-        <v>149770</v>
-      </c>
-      <c r="D512">
-        <v>23043.42</v>
+      <c r="C512" t="s">
+        <v>527</v>
+      </c>
+      <c r="D512" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>149770</v>
-      </c>
-      <c r="D513">
-        <v>23101.12</v>
+      <c r="C513" t="s">
+        <v>527</v>
+      </c>
+      <c r="D513" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
       <c r="C514" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D514" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
       <c r="C515" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D515" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D516" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D517" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
       <c r="C518" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D518" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -9276,44 +9276,44 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521" t="s">
-        <v>528</v>
-      </c>
-      <c r="D521" t="s">
-        <v>538</v>
+      <c r="C521">
+        <v>148008</v>
+      </c>
+      <c r="D521">
+        <v>23039.07</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>529</v>
-      </c>
-      <c r="D522" t="s">
-        <v>539</v>
+      <c r="C522">
+        <v>147127</v>
+      </c>
+      <c r="D522">
+        <v>22939.12</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523" t="s">
-        <v>529</v>
-      </c>
-      <c r="D523" t="s">
-        <v>540</v>
+      <c r="C523">
+        <v>147127</v>
+      </c>
+      <c r="D523">
+        <v>22934.09</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -9328,6 +9328,20 @@
       </c>
       <c r="D524">
         <v>21597.22</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4">
+      <c r="A525" s="1">
+        <v>542</v>
+      </c>
+      <c r="B525" t="s">
+        <v>526</v>
+      </c>
+      <c r="C525" t="s">
+        <v>529</v>
+      </c>
+      <c r="D525" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="541">
   <si>
     <t>Date</t>
   </si>
@@ -1597,6 +1597,9 @@
     <t>2026-04-20</t>
   </si>
   <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
     <t>180370</t>
   </si>
   <si>
@@ -1609,10 +1612,7 @@
     <t>23040.76</t>
   </si>
   <si>
-    <t>23104.79</t>
-  </si>
-  <si>
-    <t>23016.17</t>
+    <t>23119.85</t>
   </si>
   <si>
     <t>23043.42</t>
@@ -1621,12 +1621,6 @@
     <t>23101.12</t>
   </si>
   <si>
-    <t>23138.96</t>
-  </si>
-  <si>
-    <t>22981.86</t>
-  </si>
-  <si>
     <t>23027.21</t>
   </si>
   <si>
@@ -1636,7 +1630,13 @@
     <t>23152.54</t>
   </si>
   <si>
-    <t>21417.94</t>
+    <t>23160.98</t>
+  </si>
+  <si>
+    <t>23158.28</t>
+  </si>
+  <si>
+    <t>21421.39</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D525"/>
+  <dimension ref="A1:D526"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9066,44 +9066,44 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D506" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>527</v>
-      </c>
-      <c r="D507" t="s">
-        <v>531</v>
+      <c r="C507">
+        <v>180370</v>
+      </c>
+      <c r="D507">
+        <v>23104.79</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508">
-        <v>190570</v>
-      </c>
-      <c r="D508">
-        <v>19197.54</v>
+      <c r="C508" t="s">
+        <v>528</v>
+      </c>
+      <c r="D508" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9136,27 +9136,27 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511" t="s">
-        <v>527</v>
-      </c>
-      <c r="D511" t="s">
-        <v>532</v>
+      <c r="C511">
+        <v>180370</v>
+      </c>
+      <c r="D511">
+        <v>23016.17</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D512" t="s">
         <v>533</v>
@@ -9164,13 +9164,13 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
       <c r="C513" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D513" t="s">
         <v>534</v>
@@ -9178,100 +9178,100 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>527</v>
-      </c>
-      <c r="D514" t="s">
-        <v>535</v>
+      <c r="C514">
+        <v>180370</v>
+      </c>
+      <c r="D514">
+        <v>23138.96</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515" t="s">
-        <v>528</v>
-      </c>
-      <c r="D515" t="s">
-        <v>536</v>
+      <c r="C515">
+        <v>179309</v>
+      </c>
+      <c r="D515">
+        <v>22981.86</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D516" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D517" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
       <c r="C518" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D518" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>148889</v>
-      </c>
-      <c r="D519">
-        <v>23160.98</v>
+      <c r="C519" t="s">
+        <v>529</v>
+      </c>
+      <c r="D519" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>148889</v>
-      </c>
-      <c r="D520">
-        <v>23158.28</v>
+      <c r="C520" t="s">
+        <v>529</v>
+      </c>
+      <c r="D520" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9332,15 +9332,29 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>529</v>
-      </c>
-      <c r="D525" t="s">
+      <c r="C525">
+        <v>165500</v>
+      </c>
+      <c r="D525">
+        <v>21417.94</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4">
+      <c r="A526" s="1">
+        <v>544</v>
+      </c>
+      <c r="B526" t="s">
+        <v>527</v>
+      </c>
+      <c r="C526" t="s">
+        <v>530</v>
+      </c>
+      <c r="D526" t="s">
         <v>540</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="542">
   <si>
     <t>Date</t>
   </si>
@@ -1600,43 +1600,46 @@
     <t>2026-04-21</t>
   </si>
   <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>165500</t>
-  </si>
-  <si>
-    <t>23040.76</t>
-  </si>
-  <si>
-    <t>23119.85</t>
-  </si>
-  <si>
-    <t>23043.42</t>
-  </si>
-  <si>
-    <t>23101.12</t>
-  </si>
-  <si>
-    <t>23027.21</t>
-  </si>
-  <si>
-    <t>23108.37</t>
-  </si>
-  <si>
-    <t>23152.54</t>
-  </si>
-  <si>
-    <t>23160.98</t>
-  </si>
-  <si>
-    <t>23158.28</t>
-  </si>
-  <si>
-    <t>21421.39</t>
+    <t>2026-04-22</t>
+  </si>
+  <si>
+    <t>159970</t>
+  </si>
+  <si>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>157147</t>
+  </si>
+  <si>
+    <t>163500</t>
+  </si>
+  <si>
+    <t>24343.72</t>
+  </si>
+  <si>
+    <t>24346.54</t>
+  </si>
+  <si>
+    <t>24447.48</t>
+  </si>
+  <si>
+    <t>24281.49</t>
+  </si>
+  <si>
+    <t>24329.41</t>
+  </si>
+  <si>
+    <t>24236.34</t>
+  </si>
+  <si>
+    <t>24231.02</t>
+  </si>
+  <si>
+    <t>24210.48</t>
+  </si>
+  <si>
+    <t>21135.93</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D526"/>
+  <dimension ref="A1:D527"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9066,16 +9069,16 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
       <c r="C506" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D506" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -9094,16 +9097,16 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>528</v>
-      </c>
-      <c r="D508" t="s">
-        <v>532</v>
+      <c r="C508">
+        <v>180370</v>
+      </c>
+      <c r="D508">
+        <v>23119.85</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9150,128 +9153,128 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
       <c r="C512" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D512" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>528</v>
-      </c>
-      <c r="D513" t="s">
-        <v>534</v>
+      <c r="C513">
+        <v>180370</v>
+      </c>
+      <c r="D513">
+        <v>23101.12</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>180370</v>
-      </c>
-      <c r="D514">
-        <v>23138.96</v>
+      <c r="C514" t="s">
+        <v>529</v>
+      </c>
+      <c r="D514" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515">
-        <v>179309</v>
-      </c>
-      <c r="D515">
-        <v>22981.86</v>
+      <c r="C515" t="s">
+        <v>530</v>
+      </c>
+      <c r="D515" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D516" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>529</v>
-      </c>
-      <c r="D517" t="s">
-        <v>536</v>
+      <c r="C517">
+        <v>179309</v>
+      </c>
+      <c r="D517">
+        <v>23108.37</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>529</v>
-      </c>
-      <c r="D518" t="s">
-        <v>537</v>
+      <c r="C518">
+        <v>179309</v>
+      </c>
+      <c r="D518">
+        <v>23152.54</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>529</v>
-      </c>
-      <c r="D519" t="s">
-        <v>538</v>
+      <c r="C519">
+        <v>179309</v>
+      </c>
+      <c r="D519">
+        <v>23160.98</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>529</v>
-      </c>
-      <c r="D520" t="s">
-        <v>539</v>
+      <c r="C520">
+        <v>179309</v>
+      </c>
+      <c r="D520">
+        <v>23158.28</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9290,44 +9293,44 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>147127</v>
-      </c>
-      <c r="D522">
-        <v>22939.12</v>
+      <c r="C522" t="s">
+        <v>531</v>
+      </c>
+      <c r="D522" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523">
-        <v>147127</v>
-      </c>
-      <c r="D523">
-        <v>22934.09</v>
+      <c r="C523" t="s">
+        <v>531</v>
+      </c>
+      <c r="D523" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>167000</v>
-      </c>
-      <c r="D524">
-        <v>21597.22</v>
+      <c r="C524" t="s">
+        <v>531</v>
+      </c>
+      <c r="D524" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -9346,16 +9349,30 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526" t="s">
-        <v>530</v>
-      </c>
-      <c r="D526" t="s">
-        <v>540</v>
+      <c r="C526">
+        <v>165500</v>
+      </c>
+      <c r="D526">
+        <v>21421.39</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4">
+      <c r="A527" s="1">
+        <v>546</v>
+      </c>
+      <c r="B527" t="s">
+        <v>528</v>
+      </c>
+      <c r="C527" t="s">
+        <v>532</v>
+      </c>
+      <c r="D527" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="544">
   <si>
     <t>Date</t>
   </si>
@@ -1603,43 +1603,49 @@
     <t>2026-04-22</t>
   </si>
   <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>157147</t>
+    <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>180370</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>177187</t>
+  </si>
+  <si>
+    <t>175595.5</t>
   </si>
   <si>
     <t>163500</t>
   </si>
   <si>
-    <t>24343.72</t>
-  </si>
-  <si>
-    <t>24346.54</t>
-  </si>
-  <si>
-    <t>24447.48</t>
-  </si>
-  <si>
-    <t>24281.49</t>
-  </si>
-  <si>
-    <t>24329.41</t>
-  </si>
-  <si>
-    <t>24236.34</t>
-  </si>
-  <si>
-    <t>24231.02</t>
-  </si>
-  <si>
-    <t>24210.48</t>
-  </si>
-  <si>
-    <t>21135.93</t>
+    <t>19185.04</t>
+  </si>
+  <si>
+    <t>19181.98</t>
+  </si>
+  <si>
+    <t>19082.96</t>
+  </si>
+  <si>
+    <t>19120.62</t>
+  </si>
+  <si>
+    <t>19188</t>
+  </si>
+  <si>
+    <t>19043.29</t>
+  </si>
+  <si>
+    <t>19027.15</t>
+  </si>
+  <si>
+    <t>18869.21</t>
+  </si>
+  <si>
+    <t>21128.22</t>
   </si>
 </sst>
 </file>
@@ -1997,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D527"/>
+  <dimension ref="A1:D528"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9069,30 +9075,30 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506" s="1">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B506" t="s">
         <v>507</v>
       </c>
-      <c r="C506" t="s">
-        <v>529</v>
-      </c>
-      <c r="D506" t="s">
-        <v>533</v>
+      <c r="C506">
+        <v>159970</v>
+      </c>
+      <c r="D506">
+        <v>24343.72</v>
       </c>
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507">
-        <v>180370</v>
-      </c>
-      <c r="D507">
-        <v>23104.79</v>
+      <c r="C507" t="s">
+        <v>530</v>
+      </c>
+      <c r="D507" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -9153,44 +9159,44 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>529</v>
-      </c>
-      <c r="D512" t="s">
-        <v>534</v>
+      <c r="C512">
+        <v>159970</v>
+      </c>
+      <c r="D512">
+        <v>24346.54</v>
       </c>
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>180370</v>
-      </c>
-      <c r="D513">
-        <v>23101.12</v>
+      <c r="C513" t="s">
+        <v>530</v>
+      </c>
+      <c r="D513" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>529</v>
-      </c>
-      <c r="D514" t="s">
-        <v>535</v>
+      <c r="C514">
+        <v>159970</v>
+      </c>
+      <c r="D514">
+        <v>24447.48</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -9201,10 +9207,10 @@
         <v>516</v>
       </c>
       <c r="C515" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D515" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -9215,24 +9221,24 @@
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D516" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517">
-        <v>179309</v>
-      </c>
-      <c r="D517">
-        <v>23108.37</v>
+      <c r="C517" t="s">
+        <v>531</v>
+      </c>
+      <c r="D517" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -9293,16 +9299,16 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>531</v>
-      </c>
-      <c r="D522" t="s">
-        <v>538</v>
+      <c r="C522">
+        <v>157147</v>
+      </c>
+      <c r="D522">
+        <v>24236.34</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9313,10 +9319,10 @@
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D523" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -9327,24 +9333,24 @@
         <v>525</v>
       </c>
       <c r="C524" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D524" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>165500</v>
-      </c>
-      <c r="D525">
-        <v>21417.94</v>
+      <c r="C525" t="s">
+        <v>533</v>
+      </c>
+      <c r="D525" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9363,16 +9369,30 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527" t="s">
-        <v>532</v>
-      </c>
-      <c r="D527" t="s">
-        <v>541</v>
+      <c r="C527">
+        <v>163500</v>
+      </c>
+      <c r="D527">
+        <v>21135.93</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4">
+      <c r="A528" s="1">
+        <v>547</v>
+      </c>
+      <c r="B528" t="s">
+        <v>529</v>
+      </c>
+      <c r="C528" t="s">
+        <v>534</v>
+      </c>
+      <c r="D528" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="545">
   <si>
     <t>Date</t>
   </si>
@@ -1606,46 +1606,49 @@
     <t>2026-04-23</t>
   </si>
   <si>
-    <t>180370</t>
-  </si>
-  <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>177187</t>
-  </si>
-  <si>
-    <t>175595.5</t>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>159970</t>
+  </si>
+  <si>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>157147</t>
+  </si>
+  <si>
+    <t>155735.5</t>
   </si>
   <si>
     <t>163500</t>
   </si>
   <si>
-    <t>19185.04</t>
-  </si>
-  <si>
-    <t>19181.98</t>
-  </si>
-  <si>
-    <t>19082.96</t>
-  </si>
-  <si>
-    <t>19120.62</t>
-  </si>
-  <si>
-    <t>19188</t>
-  </si>
-  <si>
-    <t>19043.29</t>
-  </si>
-  <si>
-    <t>19027.15</t>
-  </si>
-  <si>
-    <t>18869.21</t>
-  </si>
-  <si>
-    <t>21128.22</t>
+    <t>23119.85</t>
+  </si>
+  <si>
+    <t>23138.96</t>
+  </si>
+  <si>
+    <t>23027.21</t>
+  </si>
+  <si>
+    <t>23108.37</t>
+  </si>
+  <si>
+    <t>23152.54</t>
+  </si>
+  <si>
+    <t>22914.65</t>
+  </si>
+  <si>
+    <t>22724.44</t>
+  </si>
+  <si>
+    <t>22728.09</t>
+  </si>
+  <si>
+    <t>21114.34</t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D528"/>
+  <dimension ref="A1:D529"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9089,30 +9092,30 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507" s="1">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="B507" t="s">
         <v>508</v>
       </c>
-      <c r="C507" t="s">
-        <v>530</v>
-      </c>
-      <c r="D507" t="s">
-        <v>535</v>
+      <c r="C507">
+        <v>180370</v>
+      </c>
+      <c r="D507">
+        <v>19185.04</v>
       </c>
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508">
-        <v>180370</v>
-      </c>
-      <c r="D508">
-        <v>23119.85</v>
+      <c r="C508" t="s">
+        <v>531</v>
+      </c>
+      <c r="D508" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9173,44 +9176,44 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>530</v>
-      </c>
-      <c r="D513" t="s">
-        <v>536</v>
+      <c r="C513">
+        <v>180370</v>
+      </c>
+      <c r="D513">
+        <v>19181.98</v>
       </c>
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514">
-        <v>159970</v>
-      </c>
-      <c r="D514">
-        <v>24447.48</v>
+      <c r="C514" t="s">
+        <v>531</v>
+      </c>
+      <c r="D514" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515" t="s">
-        <v>531</v>
-      </c>
-      <c r="D515" t="s">
-        <v>537</v>
+      <c r="C515">
+        <v>179309</v>
+      </c>
+      <c r="D515">
+        <v>19082.96</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -9221,7 +9224,7 @@
         <v>517</v>
       </c>
       <c r="C516" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D516" t="s">
         <v>538</v>
@@ -9235,7 +9238,7 @@
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D517" t="s">
         <v>539</v>
@@ -9243,16 +9246,16 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518">
-        <v>179309</v>
-      </c>
-      <c r="D518">
-        <v>23152.54</v>
+      <c r="C518" t="s">
+        <v>532</v>
+      </c>
+      <c r="D518" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -9313,16 +9316,16 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523" t="s">
-        <v>532</v>
-      </c>
-      <c r="D523" t="s">
-        <v>540</v>
+      <c r="C523">
+        <v>177187</v>
+      </c>
+      <c r="D523">
+        <v>19043.29</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -9333,7 +9336,7 @@
         <v>525</v>
       </c>
       <c r="C524" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D524" t="s">
         <v>541</v>
@@ -9347,7 +9350,7 @@
         <v>526</v>
       </c>
       <c r="C525" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D525" t="s">
         <v>542</v>
@@ -9355,16 +9358,16 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526">
-        <v>165500</v>
-      </c>
-      <c r="D526">
-        <v>21421.39</v>
+      <c r="C526" t="s">
+        <v>534</v>
+      </c>
+      <c r="D526" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9383,16 +9386,30 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>534</v>
-      </c>
-      <c r="D528" t="s">
-        <v>543</v>
+      <c r="C528">
+        <v>163500</v>
+      </c>
+      <c r="D528">
+        <v>21128.22</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4">
+      <c r="A529" s="1">
+        <v>548</v>
+      </c>
+      <c r="B529" t="s">
+        <v>530</v>
+      </c>
+      <c r="C529" t="s">
+        <v>535</v>
+      </c>
+      <c r="D529" t="s">
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="548">
   <si>
     <t>Date</t>
   </si>
@@ -1609,46 +1609,55 @@
     <t>2026-04-24</t>
   </si>
   <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>157147</t>
-  </si>
-  <si>
-    <t>155735.5</t>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>177187</t>
+  </si>
+  <si>
+    <t>173473.5</t>
   </si>
   <si>
     <t>163500</t>
   </si>
   <si>
-    <t>23119.85</t>
-  </si>
-  <si>
-    <t>23138.96</t>
-  </si>
-  <si>
-    <t>23027.21</t>
-  </si>
-  <si>
-    <t>23108.37</t>
-  </si>
-  <si>
-    <t>23152.54</t>
-  </si>
-  <si>
-    <t>22914.65</t>
-  </si>
-  <si>
-    <t>22724.44</t>
-  </si>
-  <si>
-    <t>22728.09</t>
-  </si>
-  <si>
-    <t>21114.34</t>
+    <t>24281.49</t>
+  </si>
+  <si>
+    <t>24329.41</t>
+  </si>
+  <si>
+    <t>24415.15</t>
+  </si>
+  <si>
+    <t>24461.82</t>
+  </si>
+  <si>
+    <t>24470.75</t>
+  </si>
+  <si>
+    <t>24467.89</t>
+  </si>
+  <si>
+    <t>24341.94</t>
+  </si>
+  <si>
+    <t>24236.34</t>
+  </si>
+  <si>
+    <t>23684.73</t>
+  </si>
+  <si>
+    <t>23669.18</t>
+  </si>
+  <si>
+    <t>21136.24</t>
   </si>
 </sst>
 </file>
@@ -2006,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D529"/>
+  <dimension ref="A1:D530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9106,16 +9115,16 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508" s="1">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="B508" t="s">
         <v>509</v>
       </c>
-      <c r="C508" t="s">
-        <v>531</v>
-      </c>
-      <c r="D508" t="s">
-        <v>536</v>
+      <c r="C508">
+        <v>159970</v>
+      </c>
+      <c r="D508">
+        <v>23119.85</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -9190,35 +9199,35 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514" s="1">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B514" t="s">
         <v>515</v>
       </c>
-      <c r="C514" t="s">
-        <v>531</v>
-      </c>
-      <c r="D514" t="s">
-        <v>537</v>
+      <c r="C514">
+        <v>159970</v>
+      </c>
+      <c r="D514">
+        <v>23138.96</v>
       </c>
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515">
-        <v>179309</v>
-      </c>
-      <c r="D515">
-        <v>19082.96</v>
+      <c r="C515" t="s">
+        <v>532</v>
+      </c>
+      <c r="D515" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
@@ -9232,7 +9241,7 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
@@ -9246,7 +9255,7 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
@@ -9260,58 +9269,58 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>179309</v>
-      </c>
-      <c r="D519">
-        <v>23160.98</v>
+      <c r="C519" t="s">
+        <v>532</v>
+      </c>
+      <c r="D519" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>179309</v>
-      </c>
-      <c r="D520">
-        <v>23158.28</v>
+      <c r="C520" t="s">
+        <v>532</v>
+      </c>
+      <c r="D520" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521">
-        <v>148008</v>
-      </c>
-      <c r="D521">
-        <v>23039.07</v>
+      <c r="C521" t="s">
+        <v>533</v>
+      </c>
+      <c r="D521" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>157147</v>
-      </c>
-      <c r="D522">
-        <v>24236.34</v>
+      <c r="C522" t="s">
+        <v>534</v>
+      </c>
+      <c r="D522" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9330,44 +9339,44 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>533</v>
-      </c>
-      <c r="D524" t="s">
-        <v>541</v>
+      <c r="C524">
+        <v>157147</v>
+      </c>
+      <c r="D524">
+        <v>22914.65</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>534</v>
-      </c>
-      <c r="D525" t="s">
-        <v>542</v>
+      <c r="C525">
+        <v>155735.5</v>
+      </c>
+      <c r="D525">
+        <v>22724.44</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526" t="s">
-        <v>534</v>
-      </c>
-      <c r="D526" t="s">
-        <v>543</v>
+      <c r="C526">
+        <v>155735.5</v>
+      </c>
+      <c r="D526">
+        <v>22728.09</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9386,21 +9395,21 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>163500</v>
-      </c>
-      <c r="D528">
-        <v>21128.22</v>
+      <c r="C528" t="s">
+        <v>535</v>
+      </c>
+      <c r="D528" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
@@ -9409,7 +9418,21 @@
         <v>535</v>
       </c>
       <c r="D529" t="s">
-        <v>544</v>
+        <v>546</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
+      <c r="A530" s="1">
+        <v>547</v>
+      </c>
+      <c r="B530" t="s">
+        <v>531</v>
+      </c>
+      <c r="C530" t="s">
+        <v>536</v>
+      </c>
+      <c r="D530" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="549">
   <si>
     <t>Date</t>
   </si>
@@ -1612,52 +1612,55 @@
     <t>2026-04-27</t>
   </si>
   <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>177187</t>
-  </si>
-  <si>
-    <t>173473.5</t>
+    <t>2026-04-28</t>
+  </si>
+  <si>
+    <t>190570</t>
+  </si>
+  <si>
+    <t>189449</t>
+  </si>
+  <si>
+    <t>188328</t>
+  </si>
+  <si>
+    <t>187207</t>
+  </si>
+  <si>
+    <t>185525.5</t>
   </si>
   <si>
     <t>163500</t>
   </si>
   <si>
-    <t>24281.49</t>
-  </si>
-  <si>
-    <t>24329.41</t>
-  </si>
-  <si>
-    <t>24415.15</t>
-  </si>
-  <si>
-    <t>24461.82</t>
-  </si>
-  <si>
-    <t>24470.75</t>
-  </si>
-  <si>
-    <t>24467.89</t>
-  </si>
-  <si>
-    <t>24341.94</t>
-  </si>
-  <si>
-    <t>24236.34</t>
-  </si>
-  <si>
-    <t>23684.73</t>
-  </si>
-  <si>
-    <t>23669.18</t>
-  </si>
-  <si>
-    <t>21136.24</t>
+    <t>23016.17</t>
+  </si>
+  <si>
+    <t>23101.12</t>
+  </si>
+  <si>
+    <t>23108.37</t>
+  </si>
+  <si>
+    <t>23152.54</t>
+  </si>
+  <si>
+    <t>23039.07</t>
+  </si>
+  <si>
+    <t>22939.12</t>
+  </si>
+  <si>
+    <t>22934.09</t>
+  </si>
+  <si>
+    <t>22914.65</t>
+  </si>
+  <si>
+    <t>22724.44</t>
+  </si>
+  <si>
+    <t>21136.86</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D530"/>
+  <dimension ref="A1:D531"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9157,16 +9160,16 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511">
-        <v>180370</v>
-      </c>
-      <c r="D511">
-        <v>23016.17</v>
+      <c r="C511" t="s">
+        <v>533</v>
+      </c>
+      <c r="D511" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -9185,16 +9188,16 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513">
-        <v>180370</v>
-      </c>
-      <c r="D513">
-        <v>19181.98</v>
+      <c r="C513" t="s">
+        <v>533</v>
+      </c>
+      <c r="D513" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9213,97 +9216,97 @@
     </row>
     <row r="515" spans="1:4">
       <c r="A515" s="1">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="B515" t="s">
         <v>516</v>
       </c>
-      <c r="C515" t="s">
-        <v>532</v>
-      </c>
-      <c r="D515" t="s">
-        <v>537</v>
+      <c r="C515">
+        <v>179309</v>
+      </c>
+      <c r="D515">
+        <v>24281.49</v>
       </c>
     </row>
     <row r="516" spans="1:4">
       <c r="A516" s="1">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="B516" t="s">
         <v>517</v>
       </c>
-      <c r="C516" t="s">
-        <v>532</v>
-      </c>
-      <c r="D516" t="s">
-        <v>538</v>
+      <c r="C516">
+        <v>179309</v>
+      </c>
+      <c r="D516">
+        <v>24329.41</v>
       </c>
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D517" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
       <c r="C518" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D518" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>532</v>
-      </c>
-      <c r="D519" t="s">
-        <v>541</v>
+      <c r="C519">
+        <v>179309</v>
+      </c>
+      <c r="D519">
+        <v>24470.75</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>532</v>
-      </c>
-      <c r="D520" t="s">
-        <v>542</v>
+      <c r="C520">
+        <v>179309</v>
+      </c>
+      <c r="D520">
+        <v>24467.89</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
       <c r="C521" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D521" t="s">
         <v>543</v>
@@ -9311,13 +9314,13 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
       <c r="C522" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D522" t="s">
         <v>544</v>
@@ -9325,44 +9328,44 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523">
-        <v>177187</v>
-      </c>
-      <c r="D523">
-        <v>19043.29</v>
+      <c r="C523" t="s">
+        <v>536</v>
+      </c>
+      <c r="D523" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>157147</v>
-      </c>
-      <c r="D524">
-        <v>22914.65</v>
+      <c r="C524" t="s">
+        <v>536</v>
+      </c>
+      <c r="D524" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>155735.5</v>
-      </c>
-      <c r="D525">
-        <v>22724.44</v>
+      <c r="C525" t="s">
+        <v>537</v>
+      </c>
+      <c r="D525" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9395,44 +9398,58 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>535</v>
-      </c>
-      <c r="D528" t="s">
-        <v>545</v>
+      <c r="C528">
+        <v>173473.5</v>
+      </c>
+      <c r="D528">
+        <v>23684.73</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>535</v>
-      </c>
-      <c r="D529" t="s">
-        <v>546</v>
+      <c r="C529">
+        <v>173473.5</v>
+      </c>
+      <c r="D529">
+        <v>23669.18</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530" t="s">
-        <v>536</v>
-      </c>
-      <c r="D530" t="s">
-        <v>547</v>
+      <c r="C530">
+        <v>163500</v>
+      </c>
+      <c r="D530">
+        <v>21136.24</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
+      <c r="A531" s="1">
+        <v>549</v>
+      </c>
+      <c r="B531" t="s">
+        <v>532</v>
+      </c>
+      <c r="C531" t="s">
+        <v>538</v>
+      </c>
+      <c r="D531" t="s">
+        <v>548</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="548">
   <si>
     <t>Date</t>
   </si>
@@ -1615,52 +1615,49 @@
     <t>2026-04-28</t>
   </si>
   <si>
-    <t>190570</t>
-  </si>
-  <si>
-    <t>189449</t>
-  </si>
-  <si>
-    <t>188328</t>
-  </si>
-  <si>
-    <t>187207</t>
-  </si>
-  <si>
-    <t>185525.5</t>
-  </si>
-  <si>
-    <t>163500</t>
-  </si>
-  <si>
-    <t>23016.17</t>
-  </si>
-  <si>
-    <t>23101.12</t>
-  </si>
-  <si>
-    <t>23108.37</t>
-  </si>
-  <si>
-    <t>23152.54</t>
-  </si>
-  <si>
-    <t>23039.07</t>
-  </si>
-  <si>
-    <t>22939.12</t>
-  </si>
-  <si>
-    <t>22934.09</t>
-  </si>
-  <si>
-    <t>22914.65</t>
-  </si>
-  <si>
-    <t>22724.44</t>
-  </si>
-  <si>
-    <t>21136.86</t>
+    <t>2026-04-29</t>
+  </si>
+  <si>
+    <t>159970</t>
+  </si>
+  <si>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>158088</t>
+  </si>
+  <si>
+    <t>153853.5</t>
+  </si>
+  <si>
+    <t>162000</t>
+  </si>
+  <si>
+    <t>24317.75</t>
+  </si>
+  <si>
+    <t>24415.15</t>
+  </si>
+  <si>
+    <t>24470.75</t>
+  </si>
+  <si>
+    <t>24467.89</t>
+  </si>
+  <si>
+    <t>24341.94</t>
+  </si>
+  <si>
+    <t>23693.38</t>
+  </si>
+  <si>
+    <t>23684.73</t>
+  </si>
+  <si>
+    <t>23669.18</t>
+  </si>
+  <si>
+    <t>20899.29</t>
   </si>
 </sst>
 </file>
@@ -2018,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D531"/>
+  <dimension ref="A1:D532"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9160,13 +9157,13 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
       <c r="C511" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D511" t="s">
         <v>539</v>
@@ -9188,16 +9185,16 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513" s="1">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="B513" t="s">
         <v>514</v>
       </c>
-      <c r="C513" t="s">
-        <v>533</v>
-      </c>
-      <c r="D513" t="s">
-        <v>540</v>
+      <c r="C513">
+        <v>190570</v>
+      </c>
+      <c r="D513">
+        <v>23101.12</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -9244,69 +9241,69 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
       <c r="C517" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D517" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>534</v>
-      </c>
-      <c r="D518" t="s">
-        <v>542</v>
+      <c r="C518">
+        <v>189449</v>
+      </c>
+      <c r="D518">
+        <v>23152.54</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>179309</v>
-      </c>
-      <c r="D519">
-        <v>24470.75</v>
+      <c r="C519" t="s">
+        <v>535</v>
+      </c>
+      <c r="D519" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>179309</v>
-      </c>
-      <c r="D520">
-        <v>24467.89</v>
+      <c r="C520" t="s">
+        <v>535</v>
+      </c>
+      <c r="D520" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
       <c r="C521" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D521" t="s">
         <v>543</v>
@@ -9314,58 +9311,58 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>536</v>
-      </c>
-      <c r="D522" t="s">
-        <v>544</v>
+      <c r="C522">
+        <v>187207</v>
+      </c>
+      <c r="D522">
+        <v>22939.12</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523" t="s">
-        <v>536</v>
-      </c>
-      <c r="D523" t="s">
-        <v>545</v>
+      <c r="C523">
+        <v>187207</v>
+      </c>
+      <c r="D523">
+        <v>22934.09</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>536</v>
-      </c>
-      <c r="D524" t="s">
-        <v>546</v>
+      <c r="C524">
+        <v>187207</v>
+      </c>
+      <c r="D524">
+        <v>22914.65</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>537</v>
-      </c>
-      <c r="D525" t="s">
-        <v>547</v>
+      <c r="C525">
+        <v>185525.5</v>
+      </c>
+      <c r="D525">
+        <v>22724.44</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9384,44 +9381,44 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527">
-        <v>163500</v>
-      </c>
-      <c r="D527">
-        <v>21135.93</v>
+      <c r="C527" t="s">
+        <v>537</v>
+      </c>
+      <c r="D527" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>173473.5</v>
-      </c>
-      <c r="D528">
-        <v>23684.73</v>
+      <c r="C528" t="s">
+        <v>537</v>
+      </c>
+      <c r="D528" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529">
-        <v>173473.5</v>
-      </c>
-      <c r="D529">
-        <v>23669.18</v>
+      <c r="C529" t="s">
+        <v>537</v>
+      </c>
+      <c r="D529" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9440,16 +9437,30 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531" t="s">
+      <c r="C531">
+        <v>163500</v>
+      </c>
+      <c r="D531">
+        <v>21136.86</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
+      <c r="A532" s="1">
+        <v>551</v>
+      </c>
+      <c r="B532" t="s">
+        <v>533</v>
+      </c>
+      <c r="C532" t="s">
         <v>538</v>
       </c>
-      <c r="D531" t="s">
-        <v>548</v>
+      <c r="D532" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="550">
   <si>
     <t>Date</t>
   </si>
@@ -1618,46 +1618,52 @@
     <t>2026-04-29</t>
   </si>
   <si>
-    <t>159970</t>
-  </si>
-  <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>153853.5</t>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>149770</t>
+  </si>
+  <si>
+    <t>148889</t>
+  </si>
+  <si>
+    <t>148008</t>
+  </si>
+  <si>
+    <t>147127</t>
+  </si>
+  <si>
+    <t>144043.5</t>
   </si>
   <si>
     <t>162000</t>
   </si>
   <si>
-    <t>24317.75</t>
-  </si>
-  <si>
-    <t>24415.15</t>
-  </si>
-  <si>
-    <t>24470.75</t>
-  </si>
-  <si>
-    <t>24467.89</t>
-  </si>
-  <si>
-    <t>24341.94</t>
-  </si>
-  <si>
-    <t>23693.38</t>
-  </si>
-  <si>
-    <t>23684.73</t>
-  </si>
-  <si>
-    <t>23669.18</t>
-  </si>
-  <si>
-    <t>20899.29</t>
+    <t>20437.19</t>
+  </si>
+  <si>
+    <t>20533.96</t>
+  </si>
+  <si>
+    <t>20539.06</t>
+  </si>
+  <si>
+    <t>20433.33</t>
+  </si>
+  <si>
+    <t>20344.69</t>
+  </si>
+  <si>
+    <t>19881.65</t>
+  </si>
+  <si>
+    <t>19868.6</t>
+  </si>
+  <si>
+    <t>19889.2</t>
+  </si>
+  <si>
+    <t>20889.24</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D532"/>
+  <dimension ref="A1:D533"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9157,30 +9163,30 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511" s="1">
-        <v>530</v>
+        <v>509</v>
       </c>
       <c r="B511" t="s">
         <v>512</v>
       </c>
-      <c r="C511" t="s">
-        <v>534</v>
-      </c>
-      <c r="D511" t="s">
-        <v>539</v>
+      <c r="C511">
+        <v>159970</v>
+      </c>
+      <c r="D511">
+        <v>24317.75</v>
       </c>
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512">
-        <v>159970</v>
-      </c>
-      <c r="D512">
-        <v>24346.54</v>
+      <c r="C512" t="s">
+        <v>535</v>
+      </c>
+      <c r="D512" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9241,44 +9247,44 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>535</v>
-      </c>
-      <c r="D517" t="s">
-        <v>540</v>
+      <c r="C517">
+        <v>159029</v>
+      </c>
+      <c r="D517">
+        <v>24415.15</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518">
-        <v>189449</v>
-      </c>
-      <c r="D518">
-        <v>23152.54</v>
+      <c r="C518" t="s">
+        <v>536</v>
+      </c>
+      <c r="D518" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>535</v>
-      </c>
-      <c r="D519" t="s">
-        <v>541</v>
+      <c r="C519">
+        <v>159029</v>
+      </c>
+      <c r="D519">
+        <v>24470.75</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9289,10 +9295,10 @@
         <v>521</v>
       </c>
       <c r="C520" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D520" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9303,24 +9309,24 @@
         <v>522</v>
       </c>
       <c r="C521" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D521" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>187207</v>
-      </c>
-      <c r="D522">
-        <v>22939.12</v>
+      <c r="C522" t="s">
+        <v>538</v>
+      </c>
+      <c r="D522" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9381,16 +9387,16 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527" t="s">
-        <v>537</v>
-      </c>
-      <c r="D527" t="s">
-        <v>544</v>
+      <c r="C527">
+        <v>153853.5</v>
+      </c>
+      <c r="D527">
+        <v>23693.38</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -9401,10 +9407,10 @@
         <v>529</v>
       </c>
       <c r="C528" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D528" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9415,24 +9421,24 @@
         <v>530</v>
       </c>
       <c r="C529" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D529" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530">
-        <v>163500</v>
-      </c>
-      <c r="D530">
-        <v>21136.24</v>
+      <c r="C530" t="s">
+        <v>539</v>
+      </c>
+      <c r="D530" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9451,16 +9457,30 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532" t="s">
-        <v>538</v>
-      </c>
-      <c r="D532" t="s">
-        <v>547</v>
+      <c r="C532">
+        <v>162000</v>
+      </c>
+      <c r="D532">
+        <v>20899.29</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4">
+      <c r="A533" s="1">
+        <v>552</v>
+      </c>
+      <c r="B533" t="s">
+        <v>534</v>
+      </c>
+      <c r="C533" t="s">
+        <v>540</v>
+      </c>
+      <c r="D533" t="s">
+        <v>549</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="550">
   <si>
     <t>Date</t>
   </si>
@@ -1621,49 +1621,49 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>149770</t>
-  </si>
-  <si>
     <t>148889</t>
   </si>
   <si>
-    <t>148008</t>
-  </si>
-  <si>
     <t>147127</t>
   </si>
   <si>
+    <t>145805.5</t>
+  </si>
+  <si>
     <t>144043.5</t>
   </si>
   <si>
-    <t>162000</t>
-  </si>
-  <si>
-    <t>20437.19</t>
-  </si>
-  <si>
-    <t>20533.96</t>
-  </si>
-  <si>
-    <t>20539.06</t>
-  </si>
-  <si>
-    <t>20433.33</t>
-  </si>
-  <si>
-    <t>20344.69</t>
-  </si>
-  <si>
-    <t>19881.65</t>
-  </si>
-  <si>
-    <t>19868.6</t>
-  </si>
-  <si>
-    <t>19889.2</t>
-  </si>
-  <si>
-    <t>20889.24</t>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>19231.69</t>
+  </si>
+  <si>
+    <t>19229.45</t>
+  </si>
+  <si>
+    <t>19047.47</t>
+  </si>
+  <si>
+    <t>19043.29</t>
+  </si>
+  <si>
+    <t>19027.15</t>
+  </si>
+  <si>
+    <t>18869.21</t>
+  </si>
+  <si>
+    <t>18872.24</t>
+  </si>
+  <si>
+    <t>18621.03</t>
+  </si>
+  <si>
+    <t>18621.57</t>
+  </si>
+  <si>
+    <t>18412.27</t>
   </si>
 </sst>
 </file>
@@ -9177,16 +9177,16 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512" s="1">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B512" t="s">
         <v>513</v>
       </c>
-      <c r="C512" t="s">
-        <v>535</v>
-      </c>
-      <c r="D512" t="s">
-        <v>541</v>
+      <c r="C512">
+        <v>149770</v>
+      </c>
+      <c r="D512">
+        <v>20437.19</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -9261,128 +9261,128 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>536</v>
-      </c>
-      <c r="D518" t="s">
-        <v>542</v>
+      <c r="C518">
+        <v>148889</v>
+      </c>
+      <c r="D518">
+        <v>20533.96</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>517</v>
+        <v>537</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519">
-        <v>159029</v>
-      </c>
-      <c r="D519">
-        <v>24470.75</v>
+      <c r="C519" t="s">
+        <v>535</v>
+      </c>
+      <c r="D519" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
       <c r="C520" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D520" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521" t="s">
-        <v>537</v>
-      </c>
-      <c r="D521" t="s">
-        <v>544</v>
+      <c r="C521">
+        <v>148008</v>
+      </c>
+      <c r="D521">
+        <v>20433.33</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
       <c r="C522" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D522" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523">
-        <v>187207</v>
-      </c>
-      <c r="D523">
-        <v>22934.09</v>
+      <c r="C523" t="s">
+        <v>536</v>
+      </c>
+      <c r="D523" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>187207</v>
-      </c>
-      <c r="D524">
-        <v>22914.65</v>
+      <c r="C524" t="s">
+        <v>536</v>
+      </c>
+      <c r="D524" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>185525.5</v>
-      </c>
-      <c r="D525">
-        <v>22724.44</v>
+      <c r="C525" t="s">
+        <v>537</v>
+      </c>
+      <c r="D525" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526">
-        <v>155735.5</v>
-      </c>
-      <c r="D526">
-        <v>22728.09</v>
+      <c r="C526" t="s">
+        <v>537</v>
+      </c>
+      <c r="D526" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9401,86 +9401,86 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>539</v>
-      </c>
-      <c r="D528" t="s">
-        <v>546</v>
+      <c r="C528">
+        <v>144043.5</v>
+      </c>
+      <c r="D528">
+        <v>19881.65</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>539</v>
-      </c>
-      <c r="D529" t="s">
-        <v>547</v>
+      <c r="C529">
+        <v>144043.5</v>
+      </c>
+      <c r="D529">
+        <v>19868.6</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D530" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531">
-        <v>163500</v>
-      </c>
-      <c r="D531">
-        <v>21136.86</v>
+      <c r="C531" t="s">
+        <v>538</v>
+      </c>
+      <c r="D531" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532">
-        <v>162000</v>
-      </c>
-      <c r="D532">
-        <v>20899.29</v>
+      <c r="C532" t="s">
+        <v>539</v>
+      </c>
+      <c r="D532" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>540</v>
-      </c>
-      <c r="D533" t="s">
-        <v>549</v>
+      <c r="C533">
+        <v>162000</v>
+      </c>
+      <c r="D533">
+        <v>20889.24</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="548">
   <si>
     <t>Date</t>
   </si>
@@ -1621,49 +1621,43 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>148889</t>
-  </si>
-  <si>
-    <t>147127</t>
-  </si>
-  <si>
-    <t>145805.5</t>
-  </si>
-  <si>
-    <t>144043.5</t>
-  </si>
-  <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>19231.69</t>
-  </si>
-  <si>
-    <t>19229.45</t>
-  </si>
-  <si>
-    <t>19047.47</t>
-  </si>
-  <si>
-    <t>19043.29</t>
-  </si>
-  <si>
-    <t>19027.15</t>
-  </si>
-  <si>
-    <t>18869.21</t>
-  </si>
-  <si>
-    <t>18872.24</t>
-  </si>
-  <si>
-    <t>18621.03</t>
-  </si>
-  <si>
-    <t>18621.57</t>
-  </si>
-  <si>
-    <t>18412.27</t>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>158088</t>
+  </si>
+  <si>
+    <t>157147</t>
+  </si>
+  <si>
+    <t>153853.5</t>
+  </si>
+  <si>
+    <t>152442</t>
+  </si>
+  <si>
+    <t>20533.96</t>
+  </si>
+  <si>
+    <t>20541.46</t>
+  </si>
+  <si>
+    <t>20433.33</t>
+  </si>
+  <si>
+    <t>20344.69</t>
+  </si>
+  <si>
+    <t>20340.22</t>
+  </si>
+  <si>
+    <t>19881.65</t>
+  </si>
+  <si>
+    <t>19889.2</t>
+  </si>
+  <si>
+    <t>19666.23</t>
   </si>
 </sst>
 </file>
@@ -9261,21 +9255,21 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518">
-        <v>148889</v>
-      </c>
-      <c r="D518">
-        <v>20533.96</v>
+      <c r="C518" t="s">
+        <v>535</v>
+      </c>
+      <c r="D518" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
@@ -9284,105 +9278,105 @@
         <v>535</v>
       </c>
       <c r="D519" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>535</v>
-      </c>
-      <c r="D520" t="s">
-        <v>541</v>
+      <c r="C520">
+        <v>148889</v>
+      </c>
+      <c r="D520">
+        <v>19229.45</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521">
-        <v>148008</v>
-      </c>
-      <c r="D521">
-        <v>20433.33</v>
+      <c r="C521" t="s">
+        <v>536</v>
+      </c>
+      <c r="D521" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
       <c r="C522" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D522" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D523" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>536</v>
-      </c>
-      <c r="D524" t="s">
-        <v>544</v>
+      <c r="C524">
+        <v>147127</v>
+      </c>
+      <c r="D524">
+        <v>19027.15</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>537</v>
-      </c>
-      <c r="D525" t="s">
-        <v>545</v>
+      <c r="C525">
+        <v>145805.5</v>
+      </c>
+      <c r="D525">
+        <v>18869.21</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526" t="s">
-        <v>537</v>
-      </c>
-      <c r="D526" t="s">
-        <v>546</v>
+      <c r="C526">
+        <v>145805.5</v>
+      </c>
+      <c r="D526">
+        <v>18872.24</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9401,16 +9395,16 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>144043.5</v>
-      </c>
-      <c r="D528">
-        <v>19881.65</v>
+      <c r="C528" t="s">
+        <v>538</v>
+      </c>
+      <c r="D528" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9429,7 +9423,7 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
@@ -9438,26 +9432,26 @@
         <v>538</v>
       </c>
       <c r="D530" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531" t="s">
-        <v>538</v>
-      </c>
-      <c r="D531" t="s">
-        <v>548</v>
+      <c r="C531">
+        <v>144043.5</v>
+      </c>
+      <c r="D531">
+        <v>18621.57</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
@@ -9466,7 +9460,7 @@
         <v>539</v>
       </c>
       <c r="D532" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="533" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="549">
   <si>
     <t>Date</t>
   </si>
@@ -1621,43 +1621,46 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>157147</t>
-  </si>
-  <si>
-    <t>153853.5</t>
-  </si>
-  <si>
-    <t>152442</t>
-  </si>
-  <si>
-    <t>20533.96</t>
-  </si>
-  <si>
-    <t>20541.46</t>
-  </si>
-  <si>
-    <t>20433.33</t>
-  </si>
-  <si>
-    <t>20344.69</t>
-  </si>
-  <si>
-    <t>20340.22</t>
-  </si>
-  <si>
-    <t>19881.65</t>
-  </si>
-  <si>
-    <t>19889.2</t>
-  </si>
-  <si>
-    <t>19666.23</t>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>177187</t>
+  </si>
+  <si>
+    <t>175595.5</t>
+  </si>
+  <si>
+    <t>173473.5</t>
+  </si>
+  <si>
+    <t>171882</t>
+  </si>
+  <si>
+    <t>23108.37</t>
+  </si>
+  <si>
+    <t>23152.54</t>
+  </si>
+  <si>
+    <t>23160.98</t>
+  </si>
+  <si>
+    <t>22934.09</t>
+  </si>
+  <si>
+    <t>22914.65</t>
+  </si>
+  <si>
+    <t>22724.44</t>
+  </si>
+  <si>
+    <t>22417.04</t>
+  </si>
+  <si>
+    <t>22402.32</t>
+  </si>
+  <si>
+    <t>22174.14</t>
   </si>
 </sst>
 </file>
@@ -9241,21 +9244,21 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517">
-        <v>159029</v>
-      </c>
-      <c r="D517">
-        <v>24415.15</v>
+      <c r="C517" t="s">
+        <v>535</v>
+      </c>
+      <c r="D517" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
@@ -9264,12 +9267,12 @@
         <v>535</v>
       </c>
       <c r="D518" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
@@ -9278,7 +9281,7 @@
         <v>535</v>
       </c>
       <c r="D519" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -9297,72 +9300,72 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521" t="s">
-        <v>536</v>
-      </c>
-      <c r="D521" t="s">
-        <v>542</v>
+      <c r="C521">
+        <v>158088</v>
+      </c>
+      <c r="D521">
+        <v>20433.33</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>537</v>
-      </c>
-      <c r="D522" t="s">
-        <v>543</v>
+      <c r="C522">
+        <v>157147</v>
+      </c>
+      <c r="D522">
+        <v>20344.69</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D523" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>147127</v>
-      </c>
-      <c r="D524">
-        <v>19027.15</v>
+      <c r="C524" t="s">
+        <v>536</v>
+      </c>
+      <c r="D524" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>145805.5</v>
-      </c>
-      <c r="D525">
-        <v>18869.21</v>
+      <c r="C525" t="s">
+        <v>537</v>
+      </c>
+      <c r="D525" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9395,7 +9398,7 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
@@ -9404,35 +9407,35 @@
         <v>538</v>
       </c>
       <c r="D528" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529">
-        <v>144043.5</v>
-      </c>
-      <c r="D529">
-        <v>19868.6</v>
+      <c r="C529" t="s">
+        <v>538</v>
+      </c>
+      <c r="D529" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530" t="s">
-        <v>538</v>
-      </c>
-      <c r="D530" t="s">
-        <v>546</v>
+      <c r="C530">
+        <v>153853.5</v>
+      </c>
+      <c r="D530">
+        <v>19889.2</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9451,7 +9454,7 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
@@ -9460,7 +9463,7 @@
         <v>539</v>
       </c>
       <c r="D532" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="533" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -1621,19 +1621,19 @@
     <t>2026-04-30</t>
   </si>
   <si>
-    <t>179309</t>
-  </si>
-  <si>
-    <t>177187</t>
-  </si>
-  <si>
-    <t>175595.5</t>
-  </si>
-  <si>
-    <t>173473.5</t>
-  </si>
-  <si>
-    <t>171882</t>
+    <t>159029</t>
+  </si>
+  <si>
+    <t>157147</t>
+  </si>
+  <si>
+    <t>155735.5</t>
+  </si>
+  <si>
+    <t>153853.5</t>
+  </si>
+  <si>
+    <t>152442</t>
   </si>
   <si>
     <t>23108.37</t>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="551">
   <si>
     <t>Date</t>
   </si>
@@ -1621,22 +1621,22 @@
     <t>2026-04-30</t>
   </si>
   <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
     <t>159029</t>
   </si>
   <si>
+    <t>158088</t>
+  </si>
+  <si>
     <t>157147</t>
   </si>
   <si>
-    <t>155735.5</t>
-  </si>
-  <si>
     <t>153853.5</t>
   </si>
   <si>
-    <t>152442</t>
-  </si>
-  <si>
-    <t>23108.37</t>
+    <t>161000</t>
   </si>
   <si>
     <t>23152.54</t>
@@ -1645,22 +1645,28 @@
     <t>23160.98</t>
   </si>
   <si>
+    <t>23158.28</t>
+  </si>
+  <si>
+    <t>23039.07</t>
+  </si>
+  <si>
+    <t>22939.12</t>
+  </si>
+  <si>
     <t>22934.09</t>
   </si>
   <si>
-    <t>22914.65</t>
-  </si>
-  <si>
-    <t>22724.44</t>
-  </si>
-  <si>
     <t>22417.04</t>
   </si>
   <si>
     <t>22402.32</t>
   </si>
   <si>
-    <t>22174.14</t>
+    <t>22425.55</t>
+  </si>
+  <si>
+    <t>20834.06</t>
   </si>
 </sst>
 </file>
@@ -2018,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D533"/>
+  <dimension ref="A1:D534"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9244,16 +9250,16 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517" s="1">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="B517" t="s">
         <v>518</v>
       </c>
-      <c r="C517" t="s">
-        <v>535</v>
-      </c>
-      <c r="D517" t="s">
-        <v>540</v>
+      <c r="C517">
+        <v>159029</v>
+      </c>
+      <c r="D517">
+        <v>23108.37</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -9264,7 +9270,7 @@
         <v>519</v>
       </c>
       <c r="C518" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D518" t="s">
         <v>541</v>
@@ -9278,7 +9284,7 @@
         <v>520</v>
       </c>
       <c r="C519" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D519" t="s">
         <v>542</v>
@@ -9286,44 +9292,44 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>148889</v>
-      </c>
-      <c r="D520">
-        <v>19229.45</v>
+      <c r="C520" t="s">
+        <v>536</v>
+      </c>
+      <c r="D520" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521">
-        <v>158088</v>
-      </c>
-      <c r="D521">
-        <v>20433.33</v>
+      <c r="C521" t="s">
+        <v>537</v>
+      </c>
+      <c r="D521" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>157147</v>
-      </c>
-      <c r="D522">
-        <v>20344.69</v>
+      <c r="C522" t="s">
+        <v>538</v>
+      </c>
+      <c r="D522" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9334,38 +9340,38 @@
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D523" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>536</v>
-      </c>
-      <c r="D524" t="s">
-        <v>544</v>
+      <c r="C524">
+        <v>157147</v>
+      </c>
+      <c r="D524">
+        <v>22914.65</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>537</v>
-      </c>
-      <c r="D525" t="s">
-        <v>545</v>
+      <c r="C525">
+        <v>155735.5</v>
+      </c>
+      <c r="D525">
+        <v>22724.44</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9404,10 +9410,10 @@
         <v>529</v>
       </c>
       <c r="C528" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D528" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9418,24 +9424,24 @@
         <v>530</v>
       </c>
       <c r="C529" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D529" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530">
-        <v>153853.5</v>
-      </c>
-      <c r="D530">
-        <v>19889.2</v>
+      <c r="C530" t="s">
+        <v>539</v>
+      </c>
+      <c r="D530" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9454,16 +9460,16 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532" t="s">
-        <v>539</v>
-      </c>
-      <c r="D532" t="s">
-        <v>548</v>
+      <c r="C532">
+        <v>152442</v>
+      </c>
+      <c r="D532">
+        <v>22174.14</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9478,6 +9484,20 @@
       </c>
       <c r="D533">
         <v>20889.24</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
+      <c r="A534" s="1">
+        <v>550</v>
+      </c>
+      <c r="B534" t="s">
+        <v>535</v>
+      </c>
+      <c r="C534" t="s">
+        <v>540</v>
+      </c>
+      <c r="D534" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="556">
   <si>
     <t>Date</t>
   </si>
@@ -1624,49 +1624,64 @@
     <t>2026-05-06</t>
   </si>
   <si>
-    <t>159029</t>
-  </si>
-  <si>
-    <t>158088</t>
-  </si>
-  <si>
-    <t>157147</t>
-  </si>
-  <si>
-    <t>153853.5</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>179309</t>
+  </si>
+  <si>
+    <t>178248</t>
+  </si>
+  <si>
+    <t>177187</t>
+  </si>
+  <si>
+    <t>175595.5</t>
+  </si>
+  <si>
+    <t>173473.5</t>
+  </si>
+  <si>
+    <t>171882</t>
+  </si>
+  <si>
+    <t>170821</t>
   </si>
   <si>
     <t>161000</t>
   </si>
   <si>
-    <t>23152.54</t>
-  </si>
-  <si>
-    <t>23160.98</t>
-  </si>
-  <si>
-    <t>23158.28</t>
-  </si>
-  <si>
-    <t>23039.07</t>
-  </si>
-  <si>
-    <t>22939.12</t>
-  </si>
-  <si>
-    <t>22934.09</t>
-  </si>
-  <si>
-    <t>22417.04</t>
-  </si>
-  <si>
-    <t>22402.32</t>
-  </si>
-  <si>
-    <t>22425.55</t>
-  </si>
-  <si>
-    <t>20834.06</t>
+    <t>19229.45</t>
+  </si>
+  <si>
+    <t>19130.46</t>
+  </si>
+  <si>
+    <t>19047.47</t>
+  </si>
+  <si>
+    <t>19043.29</t>
+  </si>
+  <si>
+    <t>19027.15</t>
+  </si>
+  <si>
+    <t>18869.21</t>
+  </si>
+  <si>
+    <t>18872.24</t>
+  </si>
+  <si>
+    <t>18620.76</t>
+  </si>
+  <si>
+    <t>18403.42</t>
+  </si>
+  <si>
+    <t>18354.81</t>
+  </si>
+  <si>
+    <t>20875.27</t>
   </si>
 </sst>
 </file>
@@ -2024,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D534"/>
+  <dimension ref="A1:D535"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9264,184 +9279,184 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518" s="1">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="B518" t="s">
         <v>519</v>
       </c>
-      <c r="C518" t="s">
-        <v>536</v>
-      </c>
-      <c r="D518" t="s">
-        <v>541</v>
+      <c r="C518">
+        <v>159029</v>
+      </c>
+      <c r="D518">
+        <v>23152.54</v>
       </c>
     </row>
     <row r="519" spans="1:4">
       <c r="A519" s="1">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="B519" t="s">
         <v>520</v>
       </c>
-      <c r="C519" t="s">
-        <v>536</v>
-      </c>
-      <c r="D519" t="s">
-        <v>542</v>
+      <c r="C519">
+        <v>159029</v>
+      </c>
+      <c r="D519">
+        <v>23160.98</v>
       </c>
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
       <c r="C520" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D520" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
       <c r="C521" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D521" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
       <c r="C522" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D522" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D523" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>157147</v>
-      </c>
-      <c r="D524">
-        <v>22914.65</v>
+      <c r="C524" t="s">
+        <v>539</v>
+      </c>
+      <c r="D524" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>155735.5</v>
-      </c>
-      <c r="D525">
-        <v>22724.44</v>
+      <c r="C525" t="s">
+        <v>540</v>
+      </c>
+      <c r="D525" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526">
-        <v>145805.5</v>
-      </c>
-      <c r="D526">
-        <v>18872.24</v>
+      <c r="C526" t="s">
+        <v>540</v>
+      </c>
+      <c r="D526" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527">
-        <v>153853.5</v>
-      </c>
-      <c r="D527">
-        <v>23693.38</v>
+      <c r="C527" t="s">
+        <v>541</v>
+      </c>
+      <c r="D527" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>539</v>
-      </c>
-      <c r="D528" t="s">
-        <v>547</v>
+      <c r="C528">
+        <v>153853.5</v>
+      </c>
+      <c r="D528">
+        <v>22417.04</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>539</v>
-      </c>
-      <c r="D529" t="s">
-        <v>548</v>
+      <c r="C529">
+        <v>153853.5</v>
+      </c>
+      <c r="D529">
+        <v>22402.32</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530" t="s">
-        <v>539</v>
-      </c>
-      <c r="D530" t="s">
-        <v>549</v>
+      <c r="C530">
+        <v>153853.5</v>
+      </c>
+      <c r="D530">
+        <v>22425.55</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9474,30 +9489,44 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533">
-        <v>162000</v>
-      </c>
-      <c r="D533">
-        <v>20889.24</v>
+      <c r="C533" t="s">
+        <v>542</v>
+      </c>
+      <c r="D533" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D534" t="s">
-        <v>550</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4">
+      <c r="A535" s="1">
+        <v>552</v>
+      </c>
+      <c r="B535" t="s">
+        <v>536</v>
+      </c>
+      <c r="C535" t="s">
+        <v>544</v>
+      </c>
+      <c r="D535" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="555">
   <si>
     <t>Date</t>
   </si>
@@ -1627,7 +1627,7 @@
     <t>2026-05-07</t>
   </si>
   <si>
-    <t>179309</t>
+    <t>2026-05-08</t>
   </si>
   <si>
     <t>178248</t>
@@ -1642,18 +1642,12 @@
     <t>173473.5</t>
   </si>
   <si>
-    <t>171882</t>
-  </si>
-  <si>
     <t>170821</t>
   </si>
   <si>
     <t>161000</t>
   </si>
   <si>
-    <t>19229.45</t>
-  </si>
-  <si>
     <t>19130.46</t>
   </si>
   <si>
@@ -1675,13 +1669,16 @@
     <t>18620.76</t>
   </si>
   <si>
-    <t>18403.42</t>
+    <t>18613.96</t>
   </si>
   <si>
     <t>18354.81</t>
   </si>
   <si>
-    <t>20875.27</t>
+    <t>18391.11</t>
+  </si>
+  <si>
+    <t>20866.1</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D535"/>
+  <dimension ref="A1:D536"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9307,16 +9304,16 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520" t="s">
-        <v>537</v>
-      </c>
-      <c r="D520" t="s">
-        <v>545</v>
+      <c r="C520">
+        <v>179309</v>
+      </c>
+      <c r="D520">
+        <v>19229.45</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9330,7 +9327,7 @@
         <v>538</v>
       </c>
       <c r="D521" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -9344,7 +9341,7 @@
         <v>539</v>
       </c>
       <c r="D522" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9358,7 +9355,7 @@
         <v>539</v>
       </c>
       <c r="D523" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -9372,7 +9369,7 @@
         <v>539</v>
       </c>
       <c r="D524" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -9386,7 +9383,7 @@
         <v>540</v>
       </c>
       <c r="D525" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9400,7 +9397,7 @@
         <v>540</v>
       </c>
       <c r="D526" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9414,21 +9411,21 @@
         <v>541</v>
       </c>
       <c r="D527" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>153853.5</v>
-      </c>
-      <c r="D528">
-        <v>22417.04</v>
+      <c r="C528" t="s">
+        <v>541</v>
+      </c>
+      <c r="D528" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9489,16 +9486,16 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>542</v>
-      </c>
-      <c r="D533" t="s">
-        <v>553</v>
+      <c r="C533">
+        <v>171882</v>
+      </c>
+      <c r="D533">
+        <v>18403.42</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9509,10 +9506,10 @@
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D534" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9523,10 +9520,24 @@
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D535" t="s">
-        <v>555</v>
+        <v>553</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
+      <c r="A536" s="1">
+        <v>553</v>
+      </c>
+      <c r="B536" t="s">
+        <v>537</v>
+      </c>
+      <c r="C536" t="s">
+        <v>543</v>
+      </c>
+      <c r="D536" t="s">
+        <v>554</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="558">
   <si>
     <t>Date</t>
   </si>
@@ -1630,55 +1630,64 @@
     <t>2026-05-08</t>
   </si>
   <si>
-    <t>178248</t>
-  </si>
-  <si>
-    <t>177187</t>
-  </si>
-  <si>
-    <t>175595.5</t>
-  </si>
-  <si>
-    <t>173473.5</t>
-  </si>
-  <si>
-    <t>170821</t>
+    <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>2026-05-13</t>
+  </si>
+  <si>
+    <t>147127</t>
+  </si>
+  <si>
+    <t>145805.5</t>
+  </si>
+  <si>
+    <t>144043.5</t>
+  </si>
+  <si>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>141841</t>
   </si>
   <si>
     <t>161000</t>
   </si>
   <si>
-    <t>19130.46</t>
-  </si>
-  <si>
-    <t>19047.47</t>
-  </si>
-  <si>
-    <t>19043.29</t>
-  </si>
-  <si>
-    <t>19027.15</t>
-  </si>
-  <si>
-    <t>18869.21</t>
-  </si>
-  <si>
-    <t>18872.24</t>
-  </si>
-  <si>
-    <t>18620.76</t>
-  </si>
-  <si>
-    <t>18613.96</t>
-  </si>
-  <si>
-    <t>18354.81</t>
-  </si>
-  <si>
-    <t>18391.11</t>
-  </si>
-  <si>
-    <t>20866.1</t>
+    <t>20344.69</t>
+  </si>
+  <si>
+    <t>20340.22</t>
+  </si>
+  <si>
+    <t>20322.98</t>
+  </si>
+  <si>
+    <t>20154.28</t>
+  </si>
+  <si>
+    <t>20157.53</t>
+  </si>
+  <si>
+    <t>19881.65</t>
+  </si>
+  <si>
+    <t>19656.77</t>
+  </si>
+  <si>
+    <t>19604.85</t>
+  </si>
+  <si>
+    <t>19677.65</t>
+  </si>
+  <si>
+    <t>19683.14</t>
+  </si>
+  <si>
+    <t>20911.11</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D536"/>
+  <dimension ref="A1:D539"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9318,114 +9327,114 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521" s="1">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="B521" t="s">
         <v>522</v>
       </c>
-      <c r="C521" t="s">
-        <v>538</v>
-      </c>
-      <c r="D521" t="s">
-        <v>544</v>
+      <c r="C521">
+        <v>178248</v>
+      </c>
+      <c r="D521">
+        <v>19130.46</v>
       </c>
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
       <c r="C522" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D522" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
       <c r="C523" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D523" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
       <c r="C524" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D524" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
       <c r="C525" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D525" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
       <c r="C526" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D526" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527" t="s">
-        <v>541</v>
-      </c>
-      <c r="D527" t="s">
-        <v>550</v>
+      <c r="C527">
+        <v>173473.5</v>
+      </c>
+      <c r="D527">
+        <v>18620.76</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
       <c r="C528" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D528" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9486,58 +9495,100 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>531</v>
+        <v>548</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533">
-        <v>171882</v>
-      </c>
-      <c r="D533">
-        <v>18403.42</v>
+      <c r="C533" t="s">
+        <v>544</v>
+      </c>
+      <c r="D533" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D534" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535" t="s">
-        <v>542</v>
-      </c>
-      <c r="D535" t="s">
-        <v>553</v>
+      <c r="C535">
+        <v>170821</v>
+      </c>
+      <c r="D535">
+        <v>18391.11</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536" t="s">
-        <v>543</v>
-      </c>
-      <c r="D536" t="s">
+      <c r="C536">
+        <v>161000</v>
+      </c>
+      <c r="D536">
+        <v>20866.1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
+      <c r="A537" s="1">
+        <v>552</v>
+      </c>
+      <c r="B537" t="s">
+        <v>538</v>
+      </c>
+      <c r="C537" t="s">
+        <v>545</v>
+      </c>
+      <c r="D537" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
+      <c r="A538" s="1">
+        <v>553</v>
+      </c>
+      <c r="B538" t="s">
+        <v>539</v>
+      </c>
+      <c r="C538" t="s">
+        <v>545</v>
+      </c>
+      <c r="D538" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
+      <c r="A539" s="1">
         <v>554</v>
+      </c>
+      <c r="B539" t="s">
+        <v>540</v>
+      </c>
+      <c r="C539" t="s">
+        <v>546</v>
+      </c>
+      <c r="D539" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="555">
   <si>
     <t>Date</t>
   </si>
@@ -1639,31 +1639,16 @@
     <t>2026-05-13</t>
   </si>
   <si>
-    <t>147127</t>
-  </si>
-  <si>
-    <t>145805.5</t>
-  </si>
-  <si>
-    <t>144043.5</t>
-  </si>
-  <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>161000</t>
-  </si>
-  <si>
-    <t>20344.69</t>
-  </si>
-  <si>
-    <t>20340.22</t>
-  </si>
-  <si>
-    <t>20322.98</t>
+    <t>175595.5</t>
+  </si>
+  <si>
+    <t>173473.5</t>
+  </si>
+  <si>
+    <t>171882</t>
+  </si>
+  <si>
+    <t>170821</t>
   </si>
   <si>
     <t>20154.28</t>
@@ -1675,19 +1660,25 @@
     <t>19881.65</t>
   </si>
   <si>
-    <t>19656.77</t>
-  </si>
-  <si>
-    <t>19604.85</t>
+    <t>19868.6</t>
+  </si>
+  <si>
+    <t>19889.2</t>
+  </si>
+  <si>
+    <t>19889.79</t>
+  </si>
+  <si>
+    <t>19666.23</t>
+  </si>
+  <si>
+    <t>19635</t>
   </si>
   <si>
     <t>19677.65</t>
   </si>
   <si>
     <t>19683.14</t>
-  </si>
-  <si>
-    <t>20911.11</t>
   </si>
 </sst>
 </file>
@@ -9341,72 +9332,72 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>541</v>
-      </c>
-      <c r="D522" t="s">
-        <v>547</v>
+      <c r="C522">
+        <v>147127</v>
+      </c>
+      <c r="D522">
+        <v>20344.69</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523" s="1">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="B523" t="s">
         <v>524</v>
       </c>
-      <c r="C523" t="s">
-        <v>541</v>
-      </c>
-      <c r="D523" t="s">
-        <v>548</v>
+      <c r="C523">
+        <v>147127</v>
+      </c>
+      <c r="D523">
+        <v>20340.22</v>
       </c>
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>541</v>
-      </c>
-      <c r="D524" t="s">
-        <v>549</v>
+      <c r="C524">
+        <v>147127</v>
+      </c>
+      <c r="D524">
+        <v>20322.98</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
       <c r="C525" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D525" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
       <c r="C526" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D526" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -9425,100 +9416,100 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
       <c r="C528" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D528" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529">
-        <v>153853.5</v>
-      </c>
-      <c r="D529">
-        <v>22402.32</v>
+      <c r="C529" t="s">
+        <v>542</v>
+      </c>
+      <c r="D529" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530">
-        <v>153853.5</v>
-      </c>
-      <c r="D530">
-        <v>22425.55</v>
+      <c r="C530" t="s">
+        <v>542</v>
+      </c>
+      <c r="D530" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531">
-        <v>144043.5</v>
-      </c>
-      <c r="D531">
-        <v>18621.57</v>
+      <c r="C531" t="s">
+        <v>542</v>
+      </c>
+      <c r="D531" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532">
-        <v>152442</v>
-      </c>
-      <c r="D532">
-        <v>22174.14</v>
+      <c r="C532" t="s">
+        <v>543</v>
+      </c>
+      <c r="D532" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>544</v>
-      </c>
-      <c r="D533" t="s">
-        <v>553</v>
+      <c r="C533">
+        <v>142722</v>
+      </c>
+      <c r="D533">
+        <v>19656.77</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>545</v>
-      </c>
-      <c r="D534" t="s">
-        <v>554</v>
+      <c r="C534">
+        <v>141841</v>
+      </c>
+      <c r="D534">
+        <v>19604.85</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9537,58 +9528,58 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536">
-        <v>161000</v>
-      </c>
-      <c r="D536">
-        <v>20866.1</v>
+      <c r="C536" t="s">
+        <v>544</v>
+      </c>
+      <c r="D536" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
       <c r="C537" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D537" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D538" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>546</v>
-      </c>
-      <c r="D539" t="s">
-        <v>557</v>
+      <c r="C539">
+        <v>161000</v>
+      </c>
+      <c r="D539">
+        <v>20911.11</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="557">
   <si>
     <t>Date</t>
   </si>
@@ -1639,6 +1639,12 @@
     <t>2026-05-13</t>
   </si>
   <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>177187</t>
+  </si>
+  <si>
     <t>175595.5</t>
   </si>
   <si>
@@ -1651,34 +1657,34 @@
     <t>170821</t>
   </si>
   <si>
-    <t>20154.28</t>
-  </si>
-  <si>
-    <t>20157.53</t>
-  </si>
-  <si>
-    <t>19881.65</t>
-  </si>
-  <si>
-    <t>19868.6</t>
-  </si>
-  <si>
-    <t>19889.2</t>
-  </si>
-  <si>
-    <t>19889.79</t>
-  </si>
-  <si>
-    <t>19666.23</t>
-  </si>
-  <si>
-    <t>19635</t>
-  </si>
-  <si>
-    <t>19677.65</t>
-  </si>
-  <si>
-    <t>19683.14</t>
+    <t>161000</t>
+  </si>
+  <si>
+    <t>24467.89</t>
+  </si>
+  <si>
+    <t>24236.34</t>
+  </si>
+  <si>
+    <t>24013.38</t>
+  </si>
+  <si>
+    <t>23693.38</t>
+  </si>
+  <si>
+    <t>23693.73</t>
+  </si>
+  <si>
+    <t>23694.42</t>
+  </si>
+  <si>
+    <t>23428.1</t>
+  </si>
+  <si>
+    <t>23416.83</t>
+  </si>
+  <si>
+    <t>23354.98</t>
   </si>
 </sst>
 </file>
@@ -2036,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D539"/>
+  <dimension ref="A1:D540"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9304,16 +9310,13 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="C520">
-        <v>179309</v>
-      </c>
-      <c r="D520">
-        <v>19229.45</v>
+      <c r="D520" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9332,16 +9335,16 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522">
-        <v>147127</v>
-      </c>
-      <c r="D522">
-        <v>20344.69</v>
+      <c r="C522" t="s">
+        <v>542</v>
+      </c>
+      <c r="D522" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9374,16 +9377,16 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>541</v>
-      </c>
-      <c r="D525" t="s">
-        <v>545</v>
+      <c r="C525">
+        <v>175595.5</v>
+      </c>
+      <c r="D525">
+        <v>20154.28</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -9394,52 +9397,52 @@
         <v>527</v>
       </c>
       <c r="C526" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D526" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527">
-        <v>173473.5</v>
-      </c>
-      <c r="D527">
-        <v>18620.76</v>
+      <c r="C527" t="s">
+        <v>544</v>
+      </c>
+      <c r="D527" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>542</v>
-      </c>
-      <c r="D528" t="s">
-        <v>547</v>
+      <c r="C528">
+        <v>173473.5</v>
+      </c>
+      <c r="D528">
+        <v>19881.65</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>542</v>
-      </c>
-      <c r="D529" t="s">
-        <v>548</v>
+      <c r="C529">
+        <v>173473.5</v>
+      </c>
+      <c r="D529">
+        <v>19868.6</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9450,10 +9453,10 @@
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D530" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9464,10 +9467,10 @@
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D531" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9478,38 +9481,38 @@
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D532" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533">
-        <v>142722</v>
-      </c>
-      <c r="D533">
-        <v>19656.77</v>
+      <c r="C533" t="s">
+        <v>545</v>
+      </c>
+      <c r="D533" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534">
-        <v>141841</v>
-      </c>
-      <c r="D534">
-        <v>19604.85</v>
+      <c r="C534" t="s">
+        <v>546</v>
+      </c>
+      <c r="D534" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9528,44 +9531,44 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536" t="s">
-        <v>544</v>
-      </c>
-      <c r="D536" t="s">
-        <v>552</v>
+      <c r="C536">
+        <v>170821</v>
+      </c>
+      <c r="D536">
+        <v>19635</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>544</v>
-      </c>
-      <c r="D537" t="s">
-        <v>553</v>
+      <c r="C537">
+        <v>170821</v>
+      </c>
+      <c r="D537">
+        <v>19677.65</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>544</v>
-      </c>
-      <c r="D538" t="s">
-        <v>554</v>
+      <c r="C538">
+        <v>170821</v>
+      </c>
+      <c r="D538">
+        <v>19683.14</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9580,6 +9583,17 @@
       </c>
       <c r="D539">
         <v>20911.11</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4">
+      <c r="A540" s="1">
+        <v>558</v>
+      </c>
+      <c r="B540" t="s">
+        <v>541</v>
+      </c>
+      <c r="C540" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="556">
   <si>
     <t>Date</t>
   </si>
@@ -1642,49 +1642,46 @@
     <t>2026-05-14</t>
   </si>
   <si>
-    <t>177187</t>
-  </si>
-  <si>
-    <t>175595.5</t>
-  </si>
-  <si>
-    <t>173473.5</t>
-  </si>
-  <si>
-    <t>171882</t>
-  </si>
-  <si>
-    <t>170821</t>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>147127</t>
+  </si>
+  <si>
+    <t>144043.5</t>
+  </si>
+  <si>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>141841</t>
   </si>
   <si>
     <t>161000</t>
   </si>
   <si>
-    <t>24467.89</t>
-  </si>
-  <si>
-    <t>24236.34</t>
-  </si>
-  <si>
-    <t>24013.38</t>
-  </si>
-  <si>
-    <t>23693.38</t>
-  </si>
-  <si>
-    <t>23693.73</t>
-  </si>
-  <si>
-    <t>23694.42</t>
-  </si>
-  <si>
-    <t>23428.1</t>
-  </si>
-  <si>
-    <t>23416.83</t>
-  </si>
-  <si>
-    <t>23354.98</t>
+    <t>19229.45</t>
+  </si>
+  <si>
+    <t>19027.15</t>
+  </si>
+  <si>
+    <t>18620.76</t>
+  </si>
+  <si>
+    <t>18613.96</t>
+  </si>
+  <si>
+    <t>18601.74</t>
+  </si>
+  <si>
+    <t>18403.42</t>
+  </si>
+  <si>
+    <t>18391.11</t>
+  </si>
+  <si>
+    <t>18383.03</t>
   </si>
 </sst>
 </file>
@@ -2042,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D540"/>
+  <dimension ref="A1:D541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9310,7 +9307,7 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
@@ -9335,16 +9332,16 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522" s="1">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="B522" t="s">
         <v>523</v>
       </c>
-      <c r="C522" t="s">
-        <v>542</v>
-      </c>
-      <c r="D522" t="s">
-        <v>549</v>
+      <c r="C522">
+        <v>177187</v>
+      </c>
+      <c r="D522">
+        <v>24236.34</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -9363,16 +9360,16 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524">
-        <v>147127</v>
-      </c>
-      <c r="D524">
-        <v>20322.98</v>
+      <c r="C524" t="s">
+        <v>543</v>
+      </c>
+      <c r="D524" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -9391,21 +9388,21 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526" t="s">
-        <v>543</v>
-      </c>
-      <c r="D526" t="s">
-        <v>550</v>
+      <c r="C526">
+        <v>175595.5</v>
+      </c>
+      <c r="D526">
+        <v>24013.38</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
@@ -9414,82 +9411,82 @@
         <v>544</v>
       </c>
       <c r="D527" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>173473.5</v>
-      </c>
-      <c r="D528">
-        <v>19881.65</v>
+      <c r="C528" t="s">
+        <v>544</v>
+      </c>
+      <c r="D528" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529">
-        <v>173473.5</v>
-      </c>
-      <c r="D529">
-        <v>19868.6</v>
+      <c r="C529" t="s">
+        <v>544</v>
+      </c>
+      <c r="D529" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530" t="s">
-        <v>544</v>
-      </c>
-      <c r="D530" t="s">
-        <v>552</v>
+      <c r="C530">
+        <v>173473.5</v>
+      </c>
+      <c r="D530">
+        <v>23693.73</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531" t="s">
-        <v>544</v>
-      </c>
-      <c r="D531" t="s">
-        <v>553</v>
+      <c r="C531">
+        <v>173473.5</v>
+      </c>
+      <c r="D531">
+        <v>23694.42</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532" t="s">
-        <v>545</v>
-      </c>
-      <c r="D532" t="s">
-        <v>554</v>
+      <c r="C532">
+        <v>171882</v>
+      </c>
+      <c r="D532">
+        <v>23428.1</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
@@ -9498,49 +9495,49 @@
         <v>545</v>
       </c>
       <c r="D533" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>546</v>
-      </c>
-      <c r="D534" t="s">
-        <v>556</v>
+      <c r="C534">
+        <v>170821</v>
+      </c>
+      <c r="D534">
+        <v>23354.98</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535">
-        <v>170821</v>
-      </c>
-      <c r="D535">
-        <v>18391.11</v>
+      <c r="C535" t="s">
+        <v>546</v>
+      </c>
+      <c r="D535" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536">
-        <v>170821</v>
-      </c>
-      <c r="D536">
-        <v>19635</v>
+      <c r="C536" t="s">
+        <v>546</v>
+      </c>
+      <c r="D536" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9587,12 +9584,23 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
+      <c r="C540">
+        <v>161000</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
+      <c r="A541" s="1">
+        <v>560</v>
+      </c>
+      <c r="B541" t="s">
+        <v>542</v>
+      </c>
+      <c r="C541" t="s">
         <v>547</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="556">
   <si>
     <t>Date</t>
   </si>
@@ -1645,43 +1645,43 @@
     <t>2026-05-15</t>
   </si>
   <si>
-    <t>147127</t>
-  </si>
-  <si>
-    <t>144043.5</t>
-  </si>
-  <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>161000</t>
-  </si>
-  <si>
-    <t>19229.45</t>
-  </si>
-  <si>
-    <t>19027.15</t>
+    <t>175595.5</t>
+  </si>
+  <si>
+    <t>173473.5</t>
+  </si>
+  <si>
+    <t>171882</t>
+  </si>
+  <si>
+    <t>170821</t>
+  </si>
+  <si>
+    <t>18869.21</t>
+  </si>
+  <si>
+    <t>18872.24</t>
   </si>
   <si>
     <t>18620.76</t>
   </si>
   <si>
-    <t>18613.96</t>
-  </si>
-  <si>
-    <t>18601.74</t>
+    <t>18621.57</t>
+  </si>
+  <si>
+    <t>18412.27</t>
   </si>
   <si>
     <t>18403.42</t>
   </si>
   <si>
-    <t>18391.11</t>
-  </si>
-  <si>
     <t>18383.03</t>
+  </si>
+  <si>
+    <t>18422.96</t>
+  </si>
+  <si>
+    <t>18450.31</t>
   </si>
 </sst>
 </file>
@@ -9307,13 +9307,13 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520" s="1">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="B520" t="s">
         <v>521</v>
       </c>
-      <c r="D520" t="s">
-        <v>548</v>
+      <c r="D520">
+        <v>19229.45</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -9360,49 +9360,49 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524" s="1">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B524" t="s">
         <v>525</v>
       </c>
-      <c r="C524" t="s">
-        <v>543</v>
-      </c>
-      <c r="D524" t="s">
-        <v>549</v>
+      <c r="C524">
+        <v>147127</v>
+      </c>
+      <c r="D524">
+        <v>19027.15</v>
       </c>
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525">
-        <v>175595.5</v>
-      </c>
-      <c r="D525">
-        <v>20154.28</v>
+      <c r="C525" t="s">
+        <v>543</v>
+      </c>
+      <c r="D525" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526">
-        <v>175595.5</v>
-      </c>
-      <c r="D526">
-        <v>24013.38</v>
+      <c r="C526" t="s">
+        <v>543</v>
+      </c>
+      <c r="D526" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
@@ -9411,35 +9411,35 @@
         <v>544</v>
       </c>
       <c r="D527" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>544</v>
-      </c>
-      <c r="D528" t="s">
-        <v>551</v>
+      <c r="C528">
+        <v>144043.5</v>
+      </c>
+      <c r="D528">
+        <v>18613.96</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>544</v>
-      </c>
-      <c r="D529" t="s">
-        <v>552</v>
+      <c r="C529">
+        <v>144043.5</v>
+      </c>
+      <c r="D529">
+        <v>18601.74</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9458,35 +9458,35 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531">
-        <v>173473.5</v>
-      </c>
-      <c r="D531">
-        <v>23694.42</v>
+      <c r="C531" t="s">
+        <v>544</v>
+      </c>
+      <c r="D531" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532">
-        <v>171882</v>
-      </c>
-      <c r="D532">
-        <v>23428.1</v>
+      <c r="C532" t="s">
+        <v>545</v>
+      </c>
+      <c r="D532" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
@@ -9495,7 +9495,7 @@
         <v>545</v>
       </c>
       <c r="D533" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9506,29 +9506,29 @@
         <v>535</v>
       </c>
       <c r="C534">
-        <v>170821</v>
+        <v>141841</v>
       </c>
       <c r="D534">
-        <v>23354.98</v>
+        <v>18354.81</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535" t="s">
-        <v>546</v>
-      </c>
-      <c r="D535" t="s">
-        <v>554</v>
+      <c r="C535">
+        <v>141841</v>
+      </c>
+      <c r="D535">
+        <v>18391.11</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
@@ -9537,21 +9537,21 @@
         <v>546</v>
       </c>
       <c r="D536" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537">
-        <v>170821</v>
-      </c>
-      <c r="D537">
-        <v>19677.65</v>
+      <c r="C537" t="s">
+        <v>546</v>
+      </c>
+      <c r="D537" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9562,10 +9562,10 @@
         <v>539</v>
       </c>
       <c r="C538">
-        <v>170821</v>
+        <v>141841</v>
       </c>
       <c r="D538">
-        <v>19683.14</v>
+        <v>18428.1</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9576,7 +9576,7 @@
         <v>540</v>
       </c>
       <c r="C539">
-        <v>161000</v>
+        <v>141841</v>
       </c>
       <c r="D539">
         <v>20911.11</v>
@@ -9584,24 +9584,30 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540">
-        <v>161000</v>
+      <c r="C540" t="s">
+        <v>546</v>
+      </c>
+      <c r="D540" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541" t="s">
-        <v>547</v>
+      <c r="C541">
+        <v>161000</v>
+      </c>
+      <c r="D541">
+        <v>20929.85</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="561">
   <si>
     <t>Date</t>
   </si>
@@ -1645,43 +1645,58 @@
     <t>2026-05-15</t>
   </si>
   <si>
-    <t>175595.5</t>
-  </si>
-  <si>
-    <t>173473.5</t>
-  </si>
-  <si>
-    <t>171882</t>
-  </si>
-  <si>
-    <t>170821</t>
-  </si>
-  <si>
-    <t>18869.21</t>
-  </si>
-  <si>
-    <t>18872.24</t>
-  </si>
-  <si>
-    <t>18620.76</t>
-  </si>
-  <si>
-    <t>18621.57</t>
-  </si>
-  <si>
-    <t>18412.27</t>
-  </si>
-  <si>
-    <t>18403.42</t>
-  </si>
-  <si>
-    <t>18383.03</t>
-  </si>
-  <si>
-    <t>18422.96</t>
-  </si>
-  <si>
-    <t>18450.31</t>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>145805.5</t>
+  </si>
+  <si>
+    <t>144043.5</t>
+  </si>
+  <si>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>141841</t>
+  </si>
+  <si>
+    <t>159000</t>
+  </si>
+  <si>
+    <t>20154.28</t>
+  </si>
+  <si>
+    <t>20157.53</t>
+  </si>
+  <si>
+    <t>19888.91</t>
+  </si>
+  <si>
+    <t>19881.65</t>
+  </si>
+  <si>
+    <t>19868.6</t>
+  </si>
+  <si>
+    <t>19889.2</t>
+  </si>
+  <si>
+    <t>19889.79</t>
+  </si>
+  <si>
+    <t>19666.23</t>
+  </si>
+  <si>
+    <t>19677.65</t>
+  </si>
+  <si>
+    <t>19683.14</t>
+  </si>
+  <si>
+    <t>19677.36</t>
+  </si>
+  <si>
+    <t>20593.02</t>
   </si>
 </sst>
 </file>
@@ -2039,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D541"/>
+  <dimension ref="A1:D542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9374,128 +9389,128 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
       <c r="C525" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D525" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
       <c r="C526" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D526" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
       <c r="C527" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D527" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>526</v>
+        <v>543</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528">
-        <v>144043.5</v>
-      </c>
-      <c r="D528">
-        <v>18613.96</v>
+      <c r="C528" t="s">
+        <v>545</v>
+      </c>
+      <c r="D528" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529">
-        <v>144043.5</v>
-      </c>
-      <c r="D529">
-        <v>18601.74</v>
+      <c r="C529" t="s">
+        <v>545</v>
+      </c>
+      <c r="D529" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530">
-        <v>173473.5</v>
-      </c>
-      <c r="D530">
-        <v>23693.73</v>
+      <c r="C530" t="s">
+        <v>545</v>
+      </c>
+      <c r="D530" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D531" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D532" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>545</v>
-      </c>
-      <c r="D533" t="s">
-        <v>552</v>
+      <c r="C533">
+        <v>171882</v>
+      </c>
+      <c r="D533">
+        <v>18403.42</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9528,72 +9543,72 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536" t="s">
-        <v>546</v>
-      </c>
-      <c r="D536" t="s">
-        <v>553</v>
+      <c r="C536">
+        <v>170821</v>
+      </c>
+      <c r="D536">
+        <v>18383.03</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
       <c r="C537" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D537" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538">
-        <v>141841</v>
-      </c>
-      <c r="D538">
-        <v>18428.1</v>
+      <c r="C538" t="s">
+        <v>547</v>
+      </c>
+      <c r="D538" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539">
-        <v>141841</v>
-      </c>
-      <c r="D539">
-        <v>20911.11</v>
+      <c r="C539" t="s">
+        <v>547</v>
+      </c>
+      <c r="D539" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
-        <v>546</v>
-      </c>
-      <c r="D540" t="s">
-        <v>555</v>
+      <c r="C540">
+        <v>170821</v>
+      </c>
+      <c r="D540">
+        <v>18450.31</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9608,6 +9623,20 @@
       </c>
       <c r="D541">
         <v>20929.85</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
+      <c r="A542" s="1">
+        <v>557</v>
+      </c>
+      <c r="B542" t="s">
+        <v>543</v>
+      </c>
+      <c r="C542" t="s">
+        <v>548</v>
+      </c>
+      <c r="D542" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="561">
   <si>
     <t>Date</t>
   </si>
@@ -1648,6 +1648,9 @@
     <t>2026-05-18</t>
   </si>
   <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
     <t>145805.5</t>
   </si>
   <si>
@@ -1663,40 +1666,37 @@
     <t>159000</t>
   </si>
   <si>
-    <t>20154.28</t>
-  </si>
-  <si>
-    <t>20157.53</t>
-  </si>
-  <si>
-    <t>19888.91</t>
-  </si>
-  <si>
-    <t>19881.65</t>
-  </si>
-  <si>
-    <t>19868.6</t>
-  </si>
-  <si>
-    <t>19889.2</t>
-  </si>
-  <si>
-    <t>19889.79</t>
-  </si>
-  <si>
-    <t>19666.23</t>
-  </si>
-  <si>
-    <t>19677.65</t>
-  </si>
-  <si>
-    <t>19683.14</t>
-  </si>
-  <si>
-    <t>19677.36</t>
-  </si>
-  <si>
-    <t>20593.02</t>
+    <t>22728.09</t>
+  </si>
+  <si>
+    <t>22425.23</t>
+  </si>
+  <si>
+    <t>22417.04</t>
+  </si>
+  <si>
+    <t>22402.32</t>
+  </si>
+  <si>
+    <t>22425.55</t>
+  </si>
+  <si>
+    <t>22426.21</t>
+  </si>
+  <si>
+    <t>22174.14</t>
+  </si>
+  <si>
+    <t>22163.48</t>
+  </si>
+  <si>
+    <t>22104.94</t>
+  </si>
+  <si>
+    <t>22148.66</t>
+  </si>
+  <si>
+    <t>20632.88</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D542"/>
+  <dimension ref="A1:D543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9389,27 +9389,27 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525" s="1">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B525" t="s">
         <v>526</v>
       </c>
-      <c r="C525" t="s">
-        <v>544</v>
-      </c>
-      <c r="D525" t="s">
-        <v>549</v>
+      <c r="C525">
+        <v>145805.5</v>
+      </c>
+      <c r="D525">
+        <v>20154.28</v>
       </c>
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
       <c r="C526" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D526" t="s">
         <v>550</v>
@@ -9417,13 +9417,13 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
       <c r="C527" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D527" t="s">
         <v>551</v>
@@ -9431,13 +9431,13 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
       <c r="C528" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D528" t="s">
         <v>552</v>
@@ -9445,13 +9445,13 @@
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
       <c r="C529" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D529" t="s">
         <v>553</v>
@@ -9459,13 +9459,13 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D530" t="s">
         <v>554</v>
@@ -9473,13 +9473,13 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D531" t="s">
         <v>555</v>
@@ -9487,13 +9487,13 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D532" t="s">
         <v>556</v>
@@ -9501,44 +9501,44 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533">
-        <v>171882</v>
-      </c>
-      <c r="D533">
-        <v>18403.42</v>
+      <c r="C533" t="s">
+        <v>547</v>
+      </c>
+      <c r="D533" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534">
-        <v>141841</v>
-      </c>
-      <c r="D534">
-        <v>18354.81</v>
+      <c r="C534" t="s">
+        <v>548</v>
+      </c>
+      <c r="D534" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535">
-        <v>141841</v>
-      </c>
-      <c r="D535">
-        <v>18391.11</v>
+      <c r="C535" t="s">
+        <v>548</v>
+      </c>
+      <c r="D535" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9557,44 +9557,44 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>547</v>
-      </c>
-      <c r="D537" t="s">
-        <v>557</v>
+      <c r="C537">
+        <v>141841</v>
+      </c>
+      <c r="D537">
+        <v>19677.65</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>547</v>
-      </c>
-      <c r="D538" t="s">
-        <v>558</v>
+      <c r="C538">
+        <v>141841</v>
+      </c>
+      <c r="D538">
+        <v>19683.14</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>547</v>
-      </c>
-      <c r="D539" t="s">
-        <v>559</v>
+      <c r="C539">
+        <v>141841</v>
+      </c>
+      <c r="D539">
+        <v>19677.36</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9627,15 +9627,29 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>548</v>
-      </c>
-      <c r="D542" t="s">
+      <c r="C542">
+        <v>159000</v>
+      </c>
+      <c r="D542">
+        <v>20593.02</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4">
+      <c r="A543" s="1">
+        <v>559</v>
+      </c>
+      <c r="B543" t="s">
+        <v>544</v>
+      </c>
+      <c r="C543" t="s">
+        <v>549</v>
+      </c>
+      <c r="D543" t="s">
         <v>560</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="563">
   <si>
     <t>Date</t>
   </si>
@@ -1651,7 +1651,7 @@
     <t>2026-05-19</t>
   </si>
   <si>
-    <t>145805.5</t>
+    <t>2026-05-20</t>
   </si>
   <si>
     <t>144043.5</t>
@@ -1663,40 +1663,46 @@
     <t>141841</t>
   </si>
   <si>
-    <t>159000</t>
-  </si>
-  <si>
-    <t>22728.09</t>
-  </si>
-  <si>
-    <t>22425.23</t>
-  </si>
-  <si>
-    <t>22417.04</t>
-  </si>
-  <si>
-    <t>22402.32</t>
-  </si>
-  <si>
-    <t>22425.55</t>
-  </si>
-  <si>
-    <t>22426.21</t>
-  </si>
-  <si>
-    <t>22174.14</t>
-  </si>
-  <si>
-    <t>22163.48</t>
-  </si>
-  <si>
-    <t>22104.94</t>
-  </si>
-  <si>
-    <t>22148.66</t>
-  </si>
-  <si>
-    <t>20632.88</t>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>155500</t>
+  </si>
+  <si>
+    <t>23684.73</t>
+  </si>
+  <si>
+    <t>23669.18</t>
+  </si>
+  <si>
+    <t>23693.73</t>
+  </si>
+  <si>
+    <t>23694.42</t>
+  </si>
+  <si>
+    <t>23428.1</t>
+  </si>
+  <si>
+    <t>23416.83</t>
+  </si>
+  <si>
+    <t>23354.98</t>
+  </si>
+  <si>
+    <t>23401.17</t>
+  </si>
+  <si>
+    <t>23441.36</t>
+  </si>
+  <si>
+    <t>23476.5</t>
+  </si>
+  <si>
+    <t>23084.77</t>
+  </si>
+  <si>
+    <t>20138.83</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:D544"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9403,35 +9409,35 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526" s="1">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="B526" t="s">
         <v>527</v>
       </c>
-      <c r="C526" t="s">
-        <v>545</v>
-      </c>
-      <c r="D526" t="s">
-        <v>550</v>
+      <c r="C526">
+        <v>145805.5</v>
+      </c>
+      <c r="D526">
+        <v>22728.09</v>
       </c>
     </row>
     <row r="527" spans="1:4">
       <c r="A527" s="1">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B527" t="s">
         <v>528</v>
       </c>
-      <c r="C527" t="s">
-        <v>546</v>
-      </c>
-      <c r="D527" t="s">
-        <v>551</v>
+      <c r="C527">
+        <v>144043.5</v>
+      </c>
+      <c r="D527">
+        <v>22425.23</v>
       </c>
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
@@ -9440,12 +9446,12 @@
         <v>546</v>
       </c>
       <c r="D528" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
@@ -9454,12 +9460,12 @@
         <v>546</v>
       </c>
       <c r="D529" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
@@ -9468,12 +9474,12 @@
         <v>546</v>
       </c>
       <c r="D530" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
@@ -9482,12 +9488,12 @@
         <v>546</v>
       </c>
       <c r="D531" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
@@ -9496,12 +9502,12 @@
         <v>547</v>
       </c>
       <c r="D532" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
@@ -9510,12 +9516,12 @@
         <v>547</v>
       </c>
       <c r="D533" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
@@ -9524,12 +9530,12 @@
         <v>548</v>
       </c>
       <c r="D534" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
@@ -9538,7 +9544,7 @@
         <v>548</v>
       </c>
       <c r="D535" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9585,30 +9591,30 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539">
-        <v>141841</v>
-      </c>
-      <c r="D539">
-        <v>19677.36</v>
+      <c r="C539" t="s">
+        <v>548</v>
+      </c>
+      <c r="D539" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540">
-        <v>170821</v>
-      </c>
-      <c r="D540">
-        <v>18450.31</v>
+      <c r="C540" t="s">
+        <v>548</v>
+      </c>
+      <c r="D540" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9627,30 +9633,44 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>159000</v>
-      </c>
-      <c r="D542">
-        <v>20593.02</v>
+      <c r="C542" t="s">
+        <v>549</v>
+      </c>
+      <c r="D542" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>549</v>
-      </c>
-      <c r="D543" t="s">
-        <v>560</v>
+      <c r="C543">
+        <v>159000</v>
+      </c>
+      <c r="D543">
+        <v>20632.88</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
+      <c r="A544" s="1">
+        <v>561</v>
+      </c>
+      <c r="B544" t="s">
+        <v>545</v>
+      </c>
+      <c r="C544" t="s">
+        <v>550</v>
+      </c>
+      <c r="D544" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="564">
   <si>
     <t>Date</t>
   </si>
@@ -1654,22 +1654,22 @@
     <t>2026-05-20</t>
   </si>
   <si>
-    <t>144043.5</t>
-  </si>
-  <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>155500</t>
-  </si>
-  <si>
-    <t>23684.73</t>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>153853.5</t>
+  </si>
+  <si>
+    <t>152442</t>
+  </si>
+  <si>
+    <t>151501</t>
+  </si>
+  <si>
+    <t>149619</t>
+  </si>
+  <si>
+    <t>154000</t>
   </si>
   <si>
     <t>23669.18</t>
@@ -1693,16 +1693,19 @@
     <t>23401.17</t>
   </si>
   <si>
-    <t>23441.36</t>
+    <t>23390.89</t>
   </si>
   <si>
     <t>23476.5</t>
   </si>
   <si>
-    <t>23084.77</t>
-  </si>
-  <si>
-    <t>20138.83</t>
+    <t>23462.36</t>
+  </si>
+  <si>
+    <t>23129.45</t>
+  </si>
+  <si>
+    <t>19984.63</t>
   </si>
 </sst>
 </file>
@@ -2060,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D544"/>
+  <dimension ref="A1:D545"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9437,16 +9440,16 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528" s="1">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="B528" t="s">
         <v>529</v>
       </c>
-      <c r="C528" t="s">
-        <v>546</v>
-      </c>
-      <c r="D528" t="s">
-        <v>551</v>
+      <c r="C528">
+        <v>144043.5</v>
+      </c>
+      <c r="D528">
+        <v>23684.73</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -9457,7 +9460,7 @@
         <v>530</v>
       </c>
       <c r="C529" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D529" t="s">
         <v>552</v>
@@ -9471,7 +9474,7 @@
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D530" t="s">
         <v>553</v>
@@ -9485,7 +9488,7 @@
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D531" t="s">
         <v>554</v>
@@ -9499,7 +9502,7 @@
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D532" t="s">
         <v>555</v>
@@ -9513,7 +9516,7 @@
         <v>534</v>
       </c>
       <c r="C533" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D533" t="s">
         <v>556</v>
@@ -9527,7 +9530,7 @@
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D534" t="s">
         <v>557</v>
@@ -9541,7 +9544,7 @@
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D535" t="s">
         <v>558</v>
@@ -9549,16 +9552,16 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536">
-        <v>170821</v>
-      </c>
-      <c r="D536">
-        <v>18383.03</v>
+      <c r="C536" t="s">
+        <v>549</v>
+      </c>
+      <c r="D536" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9591,16 +9594,16 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>556</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>548</v>
-      </c>
-      <c r="D539" t="s">
-        <v>559</v>
+      <c r="C539">
+        <v>141841</v>
+      </c>
+      <c r="D539">
+        <v>23441.36</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9611,7 +9614,7 @@
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D540" t="s">
         <v>560</v>
@@ -9619,58 +9622,72 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541">
-        <v>161000</v>
-      </c>
-      <c r="D541">
-        <v>20929.85</v>
+      <c r="C541" t="s">
+        <v>549</v>
+      </c>
+      <c r="D541" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>549</v>
-      </c>
-      <c r="D542" t="s">
-        <v>561</v>
+      <c r="C542">
+        <v>140079</v>
+      </c>
+      <c r="D542">
+        <v>23084.77</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>159000</v>
-      </c>
-      <c r="D543">
-        <v>20632.88</v>
+      <c r="C543" t="s">
+        <v>550</v>
+      </c>
+      <c r="D543" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>550</v>
-      </c>
-      <c r="D544" t="s">
+      <c r="C544">
+        <v>155500</v>
+      </c>
+      <c r="D544">
+        <v>20138.83</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4">
+      <c r="A545" s="1">
         <v>562</v>
+      </c>
+      <c r="B545" t="s">
+        <v>546</v>
+      </c>
+      <c r="C545" t="s">
+        <v>551</v>
+      </c>
+      <c r="D545" t="s">
+        <v>563</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="566">
   <si>
     <t>Date</t>
   </si>
@@ -1657,55 +1657,61 @@
     <t>2026-05-21</t>
   </si>
   <si>
-    <t>153853.5</t>
-  </si>
-  <si>
-    <t>152442</t>
-  </si>
-  <si>
-    <t>151501</t>
-  </si>
-  <si>
-    <t>149619</t>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>144043.5</t>
+  </si>
+  <si>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>141841</t>
+  </si>
+  <si>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>136995.5</t>
   </si>
   <si>
     <t>154000</t>
   </si>
   <si>
-    <t>23669.18</t>
-  </si>
-  <si>
-    <t>23693.73</t>
-  </si>
-  <si>
-    <t>23694.42</t>
-  </si>
-  <si>
-    <t>23428.1</t>
-  </si>
-  <si>
-    <t>23416.83</t>
-  </si>
-  <si>
-    <t>23354.98</t>
-  </si>
-  <si>
-    <t>23401.17</t>
-  </si>
-  <si>
-    <t>23390.89</t>
-  </si>
-  <si>
-    <t>23476.5</t>
-  </si>
-  <si>
-    <t>23462.36</t>
-  </si>
-  <si>
-    <t>23129.45</t>
-  </si>
-  <si>
-    <t>19984.63</t>
+    <t>19889.2</t>
+  </si>
+  <si>
+    <t>19889.79</t>
+  </si>
+  <si>
+    <t>19666.23</t>
+  </si>
+  <si>
+    <t>19656.77</t>
+  </si>
+  <si>
+    <t>19604.85</t>
+  </si>
+  <si>
+    <t>19643.63</t>
+  </si>
+  <si>
+    <t>19635</t>
+  </si>
+  <si>
+    <t>19677.65</t>
+  </si>
+  <si>
+    <t>19694.99</t>
+  </si>
+  <si>
+    <t>19378.03</t>
+  </si>
+  <si>
+    <t>18950.64</t>
+  </si>
+  <si>
+    <t>19986.68</t>
   </si>
 </sst>
 </file>
@@ -2063,7 +2069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D545"/>
+  <dimension ref="A1:D546"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9454,16 +9460,16 @@
     </row>
     <row r="529" spans="1:4">
       <c r="A529" s="1">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="B529" t="s">
         <v>530</v>
       </c>
-      <c r="C529" t="s">
-        <v>547</v>
-      </c>
-      <c r="D529" t="s">
-        <v>552</v>
+      <c r="C529">
+        <v>153853.5</v>
+      </c>
+      <c r="D529">
+        <v>23669.18</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -9474,10 +9480,10 @@
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D530" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9488,10 +9494,10 @@
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D531" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -9502,10 +9508,10 @@
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D532" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9516,10 +9522,10 @@
         <v>534</v>
       </c>
       <c r="C533" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D533" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -9530,10 +9536,10 @@
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D534" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9544,10 +9550,10 @@
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D535" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9558,24 +9564,24 @@
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D536" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537">
-        <v>141841</v>
-      </c>
-      <c r="D537">
-        <v>19677.65</v>
+      <c r="C537" t="s">
+        <v>550</v>
+      </c>
+      <c r="D537" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9608,16 +9614,16 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
-        <v>549</v>
-      </c>
-      <c r="D540" t="s">
-        <v>560</v>
+      <c r="C540">
+        <v>151501</v>
+      </c>
+      <c r="D540">
+        <v>23476.5</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9628,66 +9634,80 @@
         <v>542</v>
       </c>
       <c r="C541" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D541" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>140079</v>
-      </c>
-      <c r="D542">
-        <v>23084.77</v>
+      <c r="C542" t="s">
+        <v>551</v>
+      </c>
+      <c r="D542" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>550</v>
-      </c>
-      <c r="D543" t="s">
-        <v>562</v>
+      <c r="C543">
+        <v>149619</v>
+      </c>
+      <c r="D543">
+        <v>23129.45</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>155500</v>
-      </c>
-      <c r="D544">
-        <v>20138.83</v>
+      <c r="C544" t="s">
+        <v>552</v>
+      </c>
+      <c r="D544" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545" t="s">
-        <v>551</v>
-      </c>
-      <c r="D545" t="s">
+      <c r="C545">
+        <v>154000</v>
+      </c>
+      <c r="D545">
+        <v>19984.63</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4">
+      <c r="A546" s="1">
         <v>563</v>
+      </c>
+      <c r="B546" t="s">
+        <v>547</v>
+      </c>
+      <c r="C546" t="s">
+        <v>553</v>
+      </c>
+      <c r="D546" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="561">
   <si>
     <t>Date</t>
   </si>
@@ -1660,58 +1660,43 @@
     <t>2026-05-22</t>
   </si>
   <si>
-    <t>144043.5</t>
-  </si>
-  <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>136995.5</t>
-  </si>
-  <si>
-    <t>154000</t>
-  </si>
-  <si>
-    <t>19889.2</t>
-  </si>
-  <si>
-    <t>19889.79</t>
-  </si>
-  <si>
-    <t>19666.23</t>
-  </si>
-  <si>
-    <t>19656.77</t>
-  </si>
-  <si>
-    <t>19604.85</t>
-  </si>
-  <si>
-    <t>19643.63</t>
-  </si>
-  <si>
-    <t>19635</t>
-  </si>
-  <si>
-    <t>19677.65</t>
-  </si>
-  <si>
-    <t>19694.99</t>
-  </si>
-  <si>
-    <t>19378.03</t>
-  </si>
-  <si>
-    <t>18950.64</t>
-  </si>
-  <si>
-    <t>19986.68</t>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>183283.5</t>
+  </si>
+  <si>
+    <t>180481</t>
+  </si>
+  <si>
+    <t>178239</t>
+  </si>
+  <si>
+    <t>172634</t>
+  </si>
+  <si>
+    <t>22425.55</t>
+  </si>
+  <si>
+    <t>22426.21</t>
+  </si>
+  <si>
+    <t>22187.02</t>
+  </si>
+  <si>
+    <t>22193.21</t>
+  </si>
+  <si>
+    <t>22186.69</t>
+  </si>
+  <si>
+    <t>21849.19</t>
+  </si>
+  <si>
+    <t>21891.48</t>
+  </si>
+  <si>
+    <t>21205.87</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D546"/>
+  <dimension ref="A1:D547"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9474,105 +9459,105 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
       <c r="C530" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D530" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D531" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532" t="s">
-        <v>549</v>
-      </c>
-      <c r="D532" t="s">
-        <v>556</v>
+      <c r="C532">
+        <v>152442</v>
+      </c>
+      <c r="D532">
+        <v>19666.23</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>549</v>
-      </c>
-      <c r="D533" t="s">
-        <v>557</v>
+      <c r="C533">
+        <v>152442</v>
+      </c>
+      <c r="D533">
+        <v>19656.77</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>550</v>
-      </c>
-      <c r="D534" t="s">
-        <v>558</v>
+      <c r="C534">
+        <v>151501</v>
+      </c>
+      <c r="D534">
+        <v>19604.85</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535" t="s">
-        <v>550</v>
-      </c>
-      <c r="D535" t="s">
-        <v>559</v>
+      <c r="C535">
+        <v>151501</v>
+      </c>
+      <c r="D535">
+        <v>19643.63</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536" t="s">
-        <v>550</v>
-      </c>
-      <c r="D536" t="s">
-        <v>560</v>
+      <c r="C536">
+        <v>151501</v>
+      </c>
+      <c r="D536">
+        <v>19635</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
@@ -9581,35 +9566,35 @@
         <v>550</v>
       </c>
       <c r="D537" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538">
-        <v>141841</v>
-      </c>
-      <c r="D538">
-        <v>19683.14</v>
+      <c r="C538" t="s">
+        <v>550</v>
+      </c>
+      <c r="D538" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539">
-        <v>141841</v>
-      </c>
-      <c r="D539">
-        <v>23441.36</v>
+      <c r="C539" t="s">
+        <v>550</v>
+      </c>
+      <c r="D539" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9628,21 +9613,21 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541" t="s">
-        <v>550</v>
-      </c>
-      <c r="D541" t="s">
-        <v>562</v>
+      <c r="C541">
+        <v>141841</v>
+      </c>
+      <c r="D541">
+        <v>19694.99</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
@@ -9651,35 +9636,35 @@
         <v>551</v>
       </c>
       <c r="D542" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>149619</v>
-      </c>
-      <c r="D543">
-        <v>23129.45</v>
+      <c r="C543" t="s">
+        <v>551</v>
+      </c>
+      <c r="D543" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>552</v>
-      </c>
-      <c r="D544" t="s">
-        <v>564</v>
+      <c r="C544">
+        <v>146325.5</v>
+      </c>
+      <c r="D544">
+        <v>18950.64</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9698,16 +9683,30 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D546" t="s">
-        <v>565</v>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4">
+      <c r="A547" s="1">
+        <v>545</v>
+      </c>
+      <c r="B547" t="s">
+        <v>548</v>
+      </c>
+      <c r="C547">
+        <v>154000</v>
+      </c>
+      <c r="D547">
+        <v>20035.46</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="565">
   <si>
     <t>Date</t>
   </si>
@@ -1663,40 +1663,52 @@
     <t>2026-05-25</t>
   </si>
   <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
     <t>183283.5</t>
   </si>
   <si>
+    <t>181602</t>
+  </si>
+  <si>
     <t>180481</t>
   </si>
   <si>
-    <t>178239</t>
-  </si>
-  <si>
-    <t>172634</t>
-  </si>
-  <si>
-    <t>22425.55</t>
-  </si>
-  <si>
-    <t>22426.21</t>
-  </si>
-  <si>
-    <t>22187.02</t>
-  </si>
-  <si>
-    <t>22193.21</t>
-  </si>
-  <si>
-    <t>22186.69</t>
-  </si>
-  <si>
-    <t>21849.19</t>
-  </si>
-  <si>
-    <t>21891.48</t>
-  </si>
-  <si>
-    <t>21205.87</t>
+    <t>154000</t>
+  </si>
+  <si>
+    <t>19889.79</t>
+  </si>
+  <si>
+    <t>19666.23</t>
+  </si>
+  <si>
+    <t>19656.77</t>
+  </si>
+  <si>
+    <t>19604.85</t>
+  </si>
+  <si>
+    <t>19643.63</t>
+  </si>
+  <si>
+    <t>19635</t>
+  </si>
+  <si>
+    <t>19677.65</t>
+  </si>
+  <si>
+    <t>19683.14</t>
+  </si>
+  <si>
+    <t>19677.36</t>
+  </si>
+  <si>
+    <t>19706.86</t>
+  </si>
+  <si>
+    <t>20033.98</t>
   </si>
 </sst>
 </file>
@@ -2054,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D547"/>
+  <dimension ref="A1:D548"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9459,16 +9471,16 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530" s="1">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="B530" t="s">
         <v>531</v>
       </c>
-      <c r="C530" t="s">
-        <v>549</v>
-      </c>
-      <c r="D530" t="s">
-        <v>553</v>
+      <c r="C530">
+        <v>183283.5</v>
+      </c>
+      <c r="D530">
+        <v>22425.55</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -9479,7 +9491,7 @@
         <v>532</v>
       </c>
       <c r="C531" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D531" t="s">
         <v>554</v>
@@ -9487,72 +9499,72 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532">
-        <v>152442</v>
-      </c>
-      <c r="D532">
-        <v>19666.23</v>
+      <c r="C532" t="s">
+        <v>551</v>
+      </c>
+      <c r="D532" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533">
-        <v>152442</v>
-      </c>
-      <c r="D533">
-        <v>19656.77</v>
+      <c r="C533" t="s">
+        <v>551</v>
+      </c>
+      <c r="D533" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534">
-        <v>151501</v>
-      </c>
-      <c r="D534">
-        <v>19604.85</v>
+      <c r="C534" t="s">
+        <v>552</v>
+      </c>
+      <c r="D534" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535">
-        <v>151501</v>
-      </c>
-      <c r="D535">
-        <v>19643.63</v>
+      <c r="C535" t="s">
+        <v>552</v>
+      </c>
+      <c r="D535" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536">
-        <v>151501</v>
-      </c>
-      <c r="D536">
-        <v>19635</v>
+      <c r="C536" t="s">
+        <v>552</v>
+      </c>
+      <c r="D536" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -9563,10 +9575,10 @@
         <v>538</v>
       </c>
       <c r="C537" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D537" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9577,10 +9589,10 @@
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D538" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9591,24 +9603,24 @@
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D539" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540">
-        <v>151501</v>
-      </c>
-      <c r="D540">
-        <v>23476.5</v>
+      <c r="C540" t="s">
+        <v>552</v>
+      </c>
+      <c r="D540" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9627,30 +9639,30 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>551</v>
-      </c>
-      <c r="D542" t="s">
-        <v>558</v>
+      <c r="C542">
+        <v>178239</v>
+      </c>
+      <c r="D542">
+        <v>21849.19</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>551</v>
-      </c>
-      <c r="D543" t="s">
-        <v>559</v>
+      <c r="C543">
+        <v>178239</v>
+      </c>
+      <c r="D543">
+        <v>21891.48</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9683,16 +9695,16 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546" t="s">
-        <v>552</v>
-      </c>
-      <c r="D546" t="s">
-        <v>560</v>
+      <c r="C546">
+        <v>172634</v>
+      </c>
+      <c r="D546">
+        <v>21205.87</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9707,6 +9719,20 @@
       </c>
       <c r="D547">
         <v>20035.46</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4">
+      <c r="A548" s="1">
+        <v>564</v>
+      </c>
+      <c r="B548" t="s">
+        <v>549</v>
+      </c>
+      <c r="C548" t="s">
+        <v>553</v>
+      </c>
+      <c r="D548" t="s">
+        <v>564</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="564">
   <si>
     <t>Date</t>
   </si>
@@ -1666,49 +1666,46 @@
     <t>2026-05-26</t>
   </si>
   <si>
-    <t>183283.5</t>
-  </si>
-  <si>
-    <t>181602</t>
-  </si>
-  <si>
-    <t>180481</t>
-  </si>
-  <si>
-    <t>154000</t>
-  </si>
-  <si>
-    <t>19889.79</t>
-  </si>
-  <si>
-    <t>19666.23</t>
-  </si>
-  <si>
-    <t>19656.77</t>
-  </si>
-  <si>
-    <t>19604.85</t>
-  </si>
-  <si>
-    <t>19643.63</t>
-  </si>
-  <si>
-    <t>19635</t>
-  </si>
-  <si>
-    <t>19677.65</t>
-  </si>
-  <si>
-    <t>19683.14</t>
-  </si>
-  <si>
-    <t>19677.36</t>
-  </si>
-  <si>
-    <t>19706.86</t>
-  </si>
-  <si>
-    <t>20033.98</t>
+    <t>142722</t>
+  </si>
+  <si>
+    <t>141841</t>
+  </si>
+  <si>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>135674</t>
+  </si>
+  <si>
+    <t>18412.27</t>
+  </si>
+  <si>
+    <t>18403.42</t>
+  </si>
+  <si>
+    <t>18391.11</t>
+  </si>
+  <si>
+    <t>18383.03</t>
+  </si>
+  <si>
+    <t>18450.31</t>
+  </si>
+  <si>
+    <t>18439.2</t>
+  </si>
+  <si>
+    <t>18142.45</t>
+  </si>
+  <si>
+    <t>18177.56</t>
+  </si>
+  <si>
+    <t>17608.27</t>
+  </si>
+  <si>
+    <t>17651.24</t>
   </si>
 </sst>
 </file>
@@ -9485,184 +9482,184 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531" s="1">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="B531" t="s">
         <v>532</v>
       </c>
-      <c r="C531" t="s">
-        <v>550</v>
-      </c>
-      <c r="D531" t="s">
-        <v>554</v>
+      <c r="C531">
+        <v>183283.5</v>
+      </c>
+      <c r="D531">
+        <v>19889.79</v>
       </c>
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
       <c r="C532" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D532" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
       <c r="C533" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D533" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>552</v>
-      </c>
-      <c r="D534" t="s">
-        <v>557</v>
+      <c r="C534">
+        <v>180481</v>
+      </c>
+      <c r="D534">
+        <v>19604.85</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D535" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D536" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>552</v>
-      </c>
-      <c r="D537" t="s">
-        <v>560</v>
+      <c r="C537">
+        <v>180481</v>
+      </c>
+      <c r="D537">
+        <v>19677.65</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>552</v>
-      </c>
-      <c r="D538" t="s">
-        <v>561</v>
+      <c r="C538">
+        <v>180481</v>
+      </c>
+      <c r="D538">
+        <v>19683.14</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>552</v>
-      </c>
-      <c r="D539" t="s">
-        <v>562</v>
+      <c r="C539">
+        <v>180481</v>
+      </c>
+      <c r="D539">
+        <v>19677.36</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D540" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541">
-        <v>141841</v>
-      </c>
-      <c r="D541">
-        <v>19694.99</v>
+      <c r="C541" t="s">
+        <v>551</v>
+      </c>
+      <c r="D541" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>178239</v>
-      </c>
-      <c r="D542">
-        <v>21849.19</v>
+      <c r="C542" t="s">
+        <v>552</v>
+      </c>
+      <c r="D542" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>178239</v>
-      </c>
-      <c r="D543">
-        <v>21891.48</v>
+      <c r="C543" t="s">
+        <v>552</v>
+      </c>
+      <c r="D543" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9695,44 +9692,44 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546">
-        <v>172634</v>
-      </c>
-      <c r="D546">
-        <v>21205.87</v>
+      <c r="C546" t="s">
+        <v>553</v>
+      </c>
+      <c r="D546" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547">
-        <v>154000</v>
-      </c>
-      <c r="D547">
-        <v>20035.46</v>
+      <c r="C547" t="s">
+        <v>553</v>
+      </c>
+      <c r="D547" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548" t="s">
-        <v>553</v>
-      </c>
-      <c r="D548" t="s">
-        <v>564</v>
+      <c r="C548">
+        <v>154000</v>
+      </c>
+      <c r="D548">
+        <v>20033.98</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="568">
   <si>
     <t>Date</t>
   </si>
@@ -1666,46 +1666,58 @@
     <t>2026-05-26</t>
   </si>
   <si>
-    <t>142722</t>
-  </si>
-  <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>135674</t>
-  </si>
-  <si>
-    <t>18412.27</t>
-  </si>
-  <si>
-    <t>18403.42</t>
-  </si>
-  <si>
-    <t>18391.11</t>
-  </si>
-  <si>
-    <t>18383.03</t>
-  </si>
-  <si>
-    <t>18450.31</t>
-  </si>
-  <si>
-    <t>18439.2</t>
-  </si>
-  <si>
-    <t>18142.45</t>
-  </si>
-  <si>
-    <t>18177.56</t>
-  </si>
-  <si>
-    <t>17608.27</t>
-  </si>
-  <si>
-    <t>17651.24</t>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>181602</t>
+  </si>
+  <si>
+    <t>180481</t>
+  </si>
+  <si>
+    <t>174315.5</t>
+  </si>
+  <si>
+    <t>172634</t>
+  </si>
+  <si>
+    <t>154000</t>
+  </si>
+  <si>
+    <t>22163.48</t>
+  </si>
+  <si>
+    <t>22104.94</t>
+  </si>
+  <si>
+    <t>22148.66</t>
+  </si>
+  <si>
+    <t>22138.93</t>
+  </si>
+  <si>
+    <t>22187.02</t>
+  </si>
+  <si>
+    <t>22193.21</t>
+  </si>
+  <si>
+    <t>22186.69</t>
+  </si>
+  <si>
+    <t>22219.96</t>
+  </si>
+  <si>
+    <t>21367.3</t>
+  </si>
+  <si>
+    <t>21203.69</t>
+  </si>
+  <si>
+    <t>21257.62</t>
+  </si>
+  <si>
+    <t>20037.52</t>
   </si>
 </sst>
 </file>
@@ -2063,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D548"/>
+  <dimension ref="A1:D549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9496,16 +9508,16 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532" s="1">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="B532" t="s">
         <v>533</v>
       </c>
-      <c r="C532" t="s">
-        <v>550</v>
-      </c>
-      <c r="D532" t="s">
-        <v>554</v>
+      <c r="C532">
+        <v>142722</v>
+      </c>
+      <c r="D532">
+        <v>18412.27</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -9516,24 +9528,24 @@
         <v>534</v>
       </c>
       <c r="C533" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D533" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534">
-        <v>180481</v>
-      </c>
-      <c r="D534">
-        <v>19604.85</v>
+      <c r="C534" t="s">
+        <v>552</v>
+      </c>
+      <c r="D534" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9544,10 +9556,10 @@
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D535" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -9558,52 +9570,52 @@
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D536" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537">
-        <v>180481</v>
-      </c>
-      <c r="D537">
-        <v>19677.65</v>
+      <c r="C537" t="s">
+        <v>552</v>
+      </c>
+      <c r="D537" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538">
-        <v>180481</v>
-      </c>
-      <c r="D538">
-        <v>19683.14</v>
+      <c r="C538" t="s">
+        <v>552</v>
+      </c>
+      <c r="D538" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539">
-        <v>180481</v>
-      </c>
-      <c r="D539">
-        <v>19677.36</v>
+      <c r="C539" t="s">
+        <v>552</v>
+      </c>
+      <c r="D539" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9614,94 +9626,94 @@
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D540" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541" t="s">
-        <v>551</v>
-      </c>
-      <c r="D541" t="s">
-        <v>559</v>
+      <c r="C541">
+        <v>141841</v>
+      </c>
+      <c r="D541">
+        <v>18439.2</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>552</v>
-      </c>
-      <c r="D542" t="s">
-        <v>560</v>
+      <c r="C542">
+        <v>140079</v>
+      </c>
+      <c r="D542">
+        <v>18142.45</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>552</v>
-      </c>
-      <c r="D543" t="s">
-        <v>561</v>
+      <c r="C543">
+        <v>140079</v>
+      </c>
+      <c r="D543">
+        <v>18177.56</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>146325.5</v>
-      </c>
-      <c r="D544">
-        <v>18950.64</v>
+      <c r="C544" t="s">
+        <v>553</v>
+      </c>
+      <c r="D544" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545">
-        <v>154000</v>
-      </c>
-      <c r="D545">
-        <v>19984.63</v>
+      <c r="C545" t="s">
+        <v>554</v>
+      </c>
+      <c r="D545" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546" t="s">
-        <v>553</v>
-      </c>
-      <c r="D546" t="s">
-        <v>562</v>
+      <c r="C546">
+        <v>135674</v>
+      </c>
+      <c r="D546">
+        <v>17608.27</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9712,10 +9724,10 @@
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D547" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9730,6 +9742,20 @@
       </c>
       <c r="D548">
         <v>20033.98</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4">
+      <c r="A549" s="1">
+        <v>566</v>
+      </c>
+      <c r="B549" t="s">
+        <v>550</v>
+      </c>
+      <c r="C549" t="s">
+        <v>555</v>
+      </c>
+      <c r="D549" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="570">
   <si>
     <t>Date</t>
   </si>
@@ -1669,55 +1669,61 @@
     <t>2026-05-27</t>
   </si>
   <si>
-    <t>181602</t>
-  </si>
-  <si>
-    <t>180481</t>
-  </si>
-  <si>
-    <t>174315.5</t>
-  </si>
-  <si>
-    <t>172634</t>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>171882</t>
+  </si>
+  <si>
+    <t>170821</t>
+  </si>
+  <si>
+    <t>163394</t>
   </si>
   <si>
     <t>154000</t>
   </si>
   <si>
-    <t>22163.48</t>
-  </si>
-  <si>
-    <t>22104.94</t>
-  </si>
-  <si>
-    <t>22148.66</t>
-  </si>
-  <si>
-    <t>22138.93</t>
-  </si>
-  <si>
-    <t>22187.02</t>
-  </si>
-  <si>
-    <t>22193.21</t>
-  </si>
-  <si>
-    <t>22186.69</t>
-  </si>
-  <si>
-    <t>22219.96</t>
-  </si>
-  <si>
-    <t>21367.3</t>
-  </si>
-  <si>
-    <t>21203.69</t>
-  </si>
-  <si>
-    <t>21257.62</t>
-  </si>
-  <si>
-    <t>20037.52</t>
+    <t>18403.42</t>
+  </si>
+  <si>
+    <t>18354.81</t>
+  </si>
+  <si>
+    <t>18391.11</t>
+  </si>
+  <si>
+    <t>18383.03</t>
+  </si>
+  <si>
+    <t>18422.96</t>
+  </si>
+  <si>
+    <t>18428.1</t>
+  </si>
+  <si>
+    <t>18422.69</t>
+  </si>
+  <si>
+    <t>18450.31</t>
+  </si>
+  <si>
+    <t>17606.46</t>
+  </si>
+  <si>
+    <t>17608.27</t>
+  </si>
+  <si>
+    <t>17651.24</t>
+  </si>
+  <si>
+    <t>17658.25</t>
+  </si>
+  <si>
+    <t>20054.03</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D549"/>
+  <dimension ref="A1:D551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9514,122 +9520,122 @@
         <v>533</v>
       </c>
       <c r="C532">
-        <v>142722</v>
+        <v>162000</v>
       </c>
       <c r="D532">
-        <v>18412.27</v>
+        <v>20899.29</v>
       </c>
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
       <c r="C533" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D533" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D534" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D535" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D536" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
       <c r="C537" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D537" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D538" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D539" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D540" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9676,27 +9682,27 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>553</v>
-      </c>
-      <c r="D544" t="s">
-        <v>564</v>
+      <c r="C544">
+        <v>174315.5</v>
+      </c>
+      <c r="D544">
+        <v>21367.3</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
       <c r="C545" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D545" t="s">
         <v>565</v>
@@ -9704,30 +9710,30 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>544</v>
+        <v>561</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546">
-        <v>135674</v>
-      </c>
-      <c r="D546">
-        <v>17608.27</v>
+      <c r="C546" t="s">
+        <v>555</v>
+      </c>
+      <c r="D546" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D547" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9746,16 +9752,44 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
+      <c r="C549">
+        <v>154000</v>
+      </c>
+      <c r="D549">
+        <v>20037.52</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4">
+      <c r="A550" s="1">
+        <v>565</v>
+      </c>
+      <c r="B550" t="s">
+        <v>551</v>
+      </c>
+      <c r="C550" t="s">
         <v>555</v>
       </c>
-      <c r="D549" t="s">
-        <v>567</v>
+      <c r="D550" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4">
+      <c r="A551" s="1">
+        <v>566</v>
+      </c>
+      <c r="B551" t="s">
+        <v>552</v>
+      </c>
+      <c r="C551" t="s">
+        <v>556</v>
+      </c>
+      <c r="D551" t="s">
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="567">
   <si>
     <t>Date</t>
   </si>
@@ -1675,22 +1675,16 @@
     <t>2026-05-29</t>
   </si>
   <si>
-    <t>171882</t>
-  </si>
-  <si>
-    <t>170821</t>
-  </si>
-  <si>
-    <t>163394</t>
-  </si>
-  <si>
-    <t>154000</t>
-  </si>
-  <si>
-    <t>18403.42</t>
-  </si>
-  <si>
-    <t>18354.81</t>
+    <t>151501</t>
+  </si>
+  <si>
+    <t>149619</t>
+  </si>
+  <si>
+    <t>146325.5</t>
+  </si>
+  <si>
+    <t>144914</t>
   </si>
   <si>
     <t>18391.11</t>
@@ -1699,16 +1693,16 @@
     <t>18383.03</t>
   </si>
   <si>
-    <t>18422.96</t>
-  </si>
-  <si>
     <t>18428.1</t>
   </si>
   <si>
     <t>18422.69</t>
   </si>
   <si>
-    <t>18450.31</t>
+    <t>18177.56</t>
+  </si>
+  <si>
+    <t>17742.31</t>
   </si>
   <si>
     <t>17606.46</t>
@@ -1717,13 +1711,10 @@
     <t>17608.27</t>
   </si>
   <si>
-    <t>17651.24</t>
+    <t>17653.05</t>
   </si>
   <si>
     <t>17658.25</t>
-  </si>
-  <si>
-    <t>20054.03</t>
   </si>
 </sst>
 </file>
@@ -9528,114 +9519,114 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533" s="1">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B533" t="s">
         <v>534</v>
       </c>
-      <c r="C533" t="s">
-        <v>553</v>
-      </c>
-      <c r="D533" t="s">
-        <v>557</v>
+      <c r="C533">
+        <v>171882</v>
+      </c>
+      <c r="D533">
+        <v>18403.42</v>
       </c>
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>554</v>
-      </c>
-      <c r="D534" t="s">
-        <v>558</v>
+      <c r="C534">
+        <v>170821</v>
+      </c>
+      <c r="D534">
+        <v>18354.81</v>
       </c>
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D535" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D536" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>554</v>
-      </c>
-      <c r="D537" t="s">
-        <v>561</v>
+      <c r="C537">
+        <v>170821</v>
+      </c>
+      <c r="D537">
+        <v>18422.96</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D538" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D539" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
-        <v>554</v>
-      </c>
-      <c r="D540" t="s">
-        <v>564</v>
+      <c r="C540">
+        <v>170821</v>
+      </c>
+      <c r="D540">
+        <v>18450.31</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9668,72 +9659,72 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>140079</v>
-      </c>
-      <c r="D543">
-        <v>18177.56</v>
+      <c r="C543" t="s">
+        <v>554</v>
+      </c>
+      <c r="D543" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>174315.5</v>
-      </c>
-      <c r="D544">
-        <v>21367.3</v>
+      <c r="C544" t="s">
+        <v>555</v>
+      </c>
+      <c r="D544" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
       <c r="C545" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D545" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D546" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547" t="s">
-        <v>555</v>
-      </c>
-      <c r="D547" t="s">
-        <v>567</v>
+      <c r="C547">
+        <v>163394</v>
+      </c>
+      <c r="D547">
+        <v>17651.24</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9752,44 +9743,44 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>154000</v>
-      </c>
-      <c r="D549">
-        <v>20037.52</v>
+      <c r="C549" t="s">
+        <v>556</v>
+      </c>
+      <c r="D549" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
       <c r="C550" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D550" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
-      <c r="C551" t="s">
-        <v>556</v>
-      </c>
-      <c r="D551" t="s">
-        <v>569</v>
+      <c r="C551">
+        <v>154000</v>
+      </c>
+      <c r="D551">
+        <v>20054.03</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="569">
   <si>
     <t>Date</t>
   </si>
@@ -1675,46 +1675,52 @@
     <t>2026-05-29</t>
   </si>
   <si>
-    <t>151501</t>
-  </si>
-  <si>
-    <t>149619</t>
-  </si>
-  <si>
-    <t>146325.5</t>
-  </si>
-  <si>
-    <t>144914</t>
-  </si>
-  <si>
-    <t>18391.11</t>
-  </si>
-  <si>
-    <t>18383.03</t>
-  </si>
-  <si>
-    <t>18428.1</t>
-  </si>
-  <si>
-    <t>18422.69</t>
-  </si>
-  <si>
-    <t>18177.56</t>
-  </si>
-  <si>
-    <t>17742.31</t>
-  </si>
-  <si>
-    <t>17606.46</t>
-  </si>
-  <si>
-    <t>17608.27</t>
-  </si>
-  <si>
-    <t>17653.05</t>
-  </si>
-  <si>
-    <t>17658.25</t>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>170821</t>
+  </si>
+  <si>
+    <t>168699</t>
+  </si>
+  <si>
+    <t>164985.5</t>
+  </si>
+  <si>
+    <t>154000</t>
+  </si>
+  <si>
+    <t>19643.63</t>
+  </si>
+  <si>
+    <t>19635</t>
+  </si>
+  <si>
+    <t>19677.65</t>
+  </si>
+  <si>
+    <t>19683.14</t>
+  </si>
+  <si>
+    <t>19677.36</t>
+  </si>
+  <si>
+    <t>19706.86</t>
+  </si>
+  <si>
+    <t>19694.99</t>
+  </si>
+  <si>
+    <t>19378.03</t>
+  </si>
+  <si>
+    <t>19415.54</t>
+  </si>
+  <si>
+    <t>18950.64</t>
+  </si>
+  <si>
+    <t>20085.06</t>
   </si>
 </sst>
 </file>
@@ -2072,7 +2078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D551"/>
+  <dimension ref="A1:D552"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9547,170 +9553,170 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
       <c r="C535" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D535" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
       <c r="C536" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D536" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537">
-        <v>170821</v>
-      </c>
-      <c r="D537">
-        <v>18422.96</v>
+      <c r="C537" t="s">
+        <v>554</v>
+      </c>
+      <c r="D537" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D538" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D539" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540">
-        <v>170821</v>
-      </c>
-      <c r="D540">
-        <v>18450.31</v>
+      <c r="C540" t="s">
+        <v>554</v>
+      </c>
+      <c r="D540" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541">
-        <v>141841</v>
-      </c>
-      <c r="D541">
-        <v>18439.2</v>
+      <c r="C541" t="s">
+        <v>554</v>
+      </c>
+      <c r="D541" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>140079</v>
-      </c>
-      <c r="D542">
-        <v>18142.45</v>
+      <c r="C542" t="s">
+        <v>555</v>
+      </c>
+      <c r="D542" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D543" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
       <c r="C544" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D544" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545" t="s">
-        <v>556</v>
-      </c>
-      <c r="D545" t="s">
-        <v>563</v>
+      <c r="C545">
+        <v>144914</v>
+      </c>
+      <c r="D545">
+        <v>17606.46</v>
       </c>
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546" t="s">
-        <v>556</v>
-      </c>
-      <c r="D546" t="s">
-        <v>564</v>
+      <c r="C546">
+        <v>144914</v>
+      </c>
+      <c r="D546">
+        <v>17608.27</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9743,30 +9749,30 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>556</v>
-      </c>
-      <c r="D549" t="s">
-        <v>565</v>
+      <c r="C549">
+        <v>144914</v>
+      </c>
+      <c r="D549">
+        <v>17653.05</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550" t="s">
-        <v>556</v>
-      </c>
-      <c r="D550" t="s">
-        <v>566</v>
+      <c r="C550">
+        <v>144914</v>
+      </c>
+      <c r="D550">
+        <v>17658.25</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9781,6 +9787,20 @@
       </c>
       <c r="D551">
         <v>20054.03</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4">
+      <c r="A552" s="1">
+        <v>568</v>
+      </c>
+      <c r="B552" t="s">
+        <v>553</v>
+      </c>
+      <c r="C552" t="s">
+        <v>557</v>
+      </c>
+      <c r="D552" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="572">
   <si>
     <t>Date</t>
   </si>
@@ -1678,49 +1678,58 @@
     <t>2026-06-01</t>
   </si>
   <si>
-    <t>170821</t>
-  </si>
-  <si>
-    <t>168699</t>
-  </si>
-  <si>
-    <t>164985.5</t>
-  </si>
-  <si>
-    <t>154000</t>
-  </si>
-  <si>
-    <t>19643.63</t>
-  </si>
-  <si>
-    <t>19635</t>
-  </si>
-  <si>
-    <t>19677.65</t>
-  </si>
-  <si>
-    <t>19683.14</t>
-  </si>
-  <si>
-    <t>19677.36</t>
-  </si>
-  <si>
-    <t>19706.86</t>
-  </si>
-  <si>
-    <t>19694.99</t>
-  </si>
-  <si>
-    <t>19378.03</t>
-  </si>
-  <si>
-    <t>19415.54</t>
-  </si>
-  <si>
-    <t>18950.64</t>
-  </si>
-  <si>
-    <t>20085.06</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>180481</t>
+  </si>
+  <si>
+    <t>178239</t>
+  </si>
+  <si>
+    <t>174315.5</t>
+  </si>
+  <si>
+    <t>172634</t>
+  </si>
+  <si>
+    <t>152000</t>
+  </si>
+  <si>
+    <t>18422.96</t>
+  </si>
+  <si>
+    <t>18428.1</t>
+  </si>
+  <si>
+    <t>18422.69</t>
+  </si>
+  <si>
+    <t>18450.31</t>
+  </si>
+  <si>
+    <t>18439.2</t>
+  </si>
+  <si>
+    <t>18142.45</t>
+  </si>
+  <si>
+    <t>18177.56</t>
+  </si>
+  <si>
+    <t>17742.31</t>
+  </si>
+  <si>
+    <t>17649.94</t>
+  </si>
+  <si>
+    <t>17653.05</t>
+  </si>
+  <si>
+    <t>17667.6</t>
+  </si>
+  <si>
+    <t>19821.01</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D552"/>
+  <dimension ref="A1:D553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9553,41 +9562,41 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535" s="1">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="B535" t="s">
         <v>536</v>
       </c>
-      <c r="C535" t="s">
-        <v>554</v>
-      </c>
-      <c r="D535" t="s">
-        <v>558</v>
+      <c r="C535">
+        <v>170821</v>
+      </c>
+      <c r="D535">
+        <v>19643.63</v>
       </c>
     </row>
     <row r="536" spans="1:4">
       <c r="A536" s="1">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="B536" t="s">
         <v>537</v>
       </c>
-      <c r="C536" t="s">
-        <v>554</v>
-      </c>
-      <c r="D536" t="s">
-        <v>559</v>
+      <c r="C536">
+        <v>170821</v>
+      </c>
+      <c r="D536">
+        <v>19635</v>
       </c>
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
       <c r="C537" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D537" t="s">
         <v>560</v>
@@ -9595,13 +9604,13 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
       <c r="C538" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D538" t="s">
         <v>561</v>
@@ -9609,13 +9618,13 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D539" t="s">
         <v>562</v>
@@ -9623,13 +9632,13 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D540" t="s">
         <v>563</v>
@@ -9637,13 +9646,13 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
       <c r="C541" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D541" t="s">
         <v>564</v>
@@ -9651,13 +9660,13 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D542" t="s">
         <v>565</v>
@@ -9665,13 +9674,13 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D543" t="s">
         <v>566</v>
@@ -9679,13 +9688,13 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
       <c r="C544" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D544" t="s">
         <v>567</v>
@@ -9735,30 +9744,30 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548">
-        <v>154000</v>
-      </c>
-      <c r="D548">
-        <v>20033.98</v>
+      <c r="C548" t="s">
+        <v>558</v>
+      </c>
+      <c r="D548" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>144914</v>
-      </c>
-      <c r="D549">
-        <v>17653.05</v>
+      <c r="C549" t="s">
+        <v>558</v>
+      </c>
+      <c r="D549" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9777,30 +9786,44 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
-      <c r="C551">
-        <v>154000</v>
-      </c>
-      <c r="D551">
-        <v>20054.03</v>
+      <c r="C551" t="s">
+        <v>558</v>
+      </c>
+      <c r="D551" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>557</v>
-      </c>
-      <c r="D552" t="s">
-        <v>568</v>
+      <c r="C552">
+        <v>154000</v>
+      </c>
+      <c r="D552">
+        <v>20085.06</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4">
+      <c r="A553" s="1">
+        <v>570</v>
+      </c>
+      <c r="B553" t="s">
+        <v>554</v>
+      </c>
+      <c r="C553" t="s">
+        <v>559</v>
+      </c>
+      <c r="D553" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="570">
   <si>
     <t>Date</t>
   </si>
@@ -1681,55 +1681,49 @@
     <t>2026-06-02</t>
   </si>
   <si>
-    <t>180481</t>
-  </si>
-  <si>
-    <t>178239</t>
-  </si>
-  <si>
-    <t>174315.5</t>
-  </si>
-  <si>
-    <t>172634</t>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>141841</t>
+  </si>
+  <si>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>136995.5</t>
+  </si>
+  <si>
+    <t>135674</t>
   </si>
   <si>
     <t>152000</t>
   </si>
   <si>
-    <t>18422.96</t>
-  </si>
-  <si>
-    <t>18428.1</t>
-  </si>
-  <si>
-    <t>18422.69</t>
-  </si>
-  <si>
-    <t>18450.31</t>
-  </si>
-  <si>
-    <t>18439.2</t>
-  </si>
-  <si>
-    <t>18142.45</t>
-  </si>
-  <si>
-    <t>18177.56</t>
-  </si>
-  <si>
-    <t>17742.31</t>
-  </si>
-  <si>
-    <t>17649.94</t>
-  </si>
-  <si>
-    <t>17653.05</t>
-  </si>
-  <si>
-    <t>17667.6</t>
-  </si>
-  <si>
-    <t>19821.01</t>
+    <t>23441.36</t>
+  </si>
+  <si>
+    <t>23476.5</t>
+  </si>
+  <si>
+    <t>23462.36</t>
+  </si>
+  <si>
+    <t>23084.77</t>
+  </si>
+  <si>
+    <t>23129.45</t>
+  </si>
+  <si>
+    <t>22575.63</t>
+  </si>
+  <si>
+    <t>22402.77</t>
+  </si>
+  <si>
+    <t>22405.07</t>
+  </si>
+  <si>
+    <t>19829.77</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D553"/>
+  <dimension ref="A1:D554"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9590,142 +9584,142 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>555</v>
-      </c>
-      <c r="D537" t="s">
-        <v>560</v>
+      <c r="C537">
+        <v>180481</v>
+      </c>
+      <c r="D537">
+        <v>18422.96</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>555</v>
-      </c>
-      <c r="D538" t="s">
-        <v>561</v>
+      <c r="C538">
+        <v>180481</v>
+      </c>
+      <c r="D538">
+        <v>18428.1</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
       <c r="C539" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D539" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
       <c r="C540" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D540" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
       <c r="C541" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D541" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D542" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D543" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
       <c r="C544" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D544" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545">
-        <v>144914</v>
-      </c>
-      <c r="D545">
-        <v>17606.46</v>
+      <c r="C545" t="s">
+        <v>559</v>
+      </c>
+      <c r="D545" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546">
-        <v>144914</v>
-      </c>
-      <c r="D546">
-        <v>17608.27</v>
+      <c r="C546" t="s">
+        <v>559</v>
+      </c>
+      <c r="D546" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9744,30 +9738,30 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548" t="s">
-        <v>558</v>
-      </c>
-      <c r="D548" t="s">
-        <v>568</v>
+      <c r="C548">
+        <v>172634</v>
+      </c>
+      <c r="D548">
+        <v>17649.94</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>558</v>
-      </c>
-      <c r="D549" t="s">
-        <v>569</v>
+      <c r="C549">
+        <v>172634</v>
+      </c>
+      <c r="D549">
+        <v>17653.05</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9786,16 +9780,16 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
-      <c r="C551" t="s">
-        <v>558</v>
-      </c>
-      <c r="D551" t="s">
-        <v>570</v>
+      <c r="C551">
+        <v>172634</v>
+      </c>
+      <c r="D551">
+        <v>17667.6</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9814,16 +9808,30 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553" t="s">
-        <v>559</v>
-      </c>
-      <c r="D553" t="s">
-        <v>571</v>
+      <c r="C553">
+        <v>152000</v>
+      </c>
+      <c r="D553">
+        <v>19821.01</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4">
+      <c r="A554" s="1">
+        <v>572</v>
+      </c>
+      <c r="B554" t="s">
+        <v>555</v>
+      </c>
+      <c r="C554" t="s">
+        <v>560</v>
+      </c>
+      <c r="D554" t="s">
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="570">
   <si>
     <t>Date</t>
   </si>
@@ -1684,46 +1684,46 @@
     <t>2026-06-03</t>
   </si>
   <si>
-    <t>141841</t>
-  </si>
-  <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>136995.5</t>
-  </si>
-  <si>
-    <t>135674</t>
-  </si>
-  <si>
-    <t>152000</t>
-  </si>
-  <si>
-    <t>23441.36</t>
-  </si>
-  <si>
-    <t>23476.5</t>
-  </si>
-  <si>
-    <t>23462.36</t>
-  </si>
-  <si>
-    <t>23084.77</t>
-  </si>
-  <si>
-    <t>23129.45</t>
-  </si>
-  <si>
-    <t>22575.63</t>
-  </si>
-  <si>
-    <t>22402.77</t>
-  </si>
-  <si>
-    <t>22405.07</t>
-  </si>
-  <si>
-    <t>19829.77</t>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>151501</t>
+  </si>
+  <si>
+    <t>149619</t>
+  </si>
+  <si>
+    <t>144914</t>
+  </si>
+  <si>
+    <t>148500</t>
+  </si>
+  <si>
+    <t>18354.81</t>
+  </si>
+  <si>
+    <t>18428.1</t>
+  </si>
+  <si>
+    <t>18439.2</t>
+  </si>
+  <si>
+    <t>18142.45</t>
+  </si>
+  <si>
+    <t>18177.56</t>
+  </si>
+  <si>
+    <t>17651.24</t>
+  </si>
+  <si>
+    <t>17653.05</t>
+  </si>
+  <si>
+    <t>17658.25</t>
+  </si>
+  <si>
+    <t>19345.22</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D554"/>
+  <dimension ref="A1:D555"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9542,16 +9542,16 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>532</v>
+        <v>553</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534">
-        <v>170821</v>
-      </c>
-      <c r="D534">
-        <v>18354.81</v>
+      <c r="C534" t="s">
+        <v>557</v>
+      </c>
+      <c r="D534" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9598,55 +9598,55 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>536</v>
+        <v>557</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538">
-        <v>180481</v>
-      </c>
-      <c r="D538">
-        <v>18428.1</v>
+      <c r="C538" t="s">
+        <v>557</v>
+      </c>
+      <c r="D538" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>556</v>
-      </c>
-      <c r="D539" t="s">
-        <v>561</v>
+      <c r="C539">
+        <v>141841</v>
+      </c>
+      <c r="D539">
+        <v>23441.36</v>
       </c>
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
-        <v>556</v>
-      </c>
-      <c r="D540" t="s">
-        <v>562</v>
+      <c r="C540">
+        <v>141841</v>
+      </c>
+      <c r="D540">
+        <v>23476.5</v>
       </c>
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
       <c r="C541" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D541" t="s">
         <v>563</v>
@@ -9654,13 +9654,13 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D542" t="s">
         <v>564</v>
@@ -9668,13 +9668,13 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D543" t="s">
         <v>565</v>
@@ -9682,58 +9682,58 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>558</v>
-      </c>
-      <c r="D544" t="s">
-        <v>566</v>
+      <c r="C544">
+        <v>136995.5</v>
+      </c>
+      <c r="D544">
+        <v>22575.63</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545" t="s">
-        <v>559</v>
-      </c>
-      <c r="D545" t="s">
-        <v>567</v>
+      <c r="C545">
+        <v>135674</v>
+      </c>
+      <c r="D545">
+        <v>22402.77</v>
       </c>
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546" t="s">
-        <v>559</v>
-      </c>
-      <c r="D546" t="s">
-        <v>568</v>
+      <c r="C546">
+        <v>135674</v>
+      </c>
+      <c r="D546">
+        <v>22405.07</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547">
-        <v>163394</v>
-      </c>
-      <c r="D547">
-        <v>17651.24</v>
+      <c r="C547" t="s">
+        <v>559</v>
+      </c>
+      <c r="D547" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9752,30 +9752,30 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>172634</v>
-      </c>
-      <c r="D549">
-        <v>17653.05</v>
+      <c r="C549" t="s">
+        <v>559</v>
+      </c>
+      <c r="D549" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550">
-        <v>144914</v>
-      </c>
-      <c r="D550">
-        <v>17658.25</v>
+      <c r="C550" t="s">
+        <v>559</v>
+      </c>
+      <c r="D550" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9822,15 +9822,29 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554" t="s">
+      <c r="C554">
+        <v>152000</v>
+      </c>
+      <c r="D554">
+        <v>19829.77</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4">
+      <c r="A555" s="1">
+        <v>574</v>
+      </c>
+      <c r="B555" t="s">
+        <v>556</v>
+      </c>
+      <c r="C555" t="s">
         <v>560</v>
       </c>
-      <c r="D554" t="s">
+      <c r="D555" t="s">
         <v>569</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="572">
   <si>
     <t>Date</t>
   </si>
@@ -1687,43 +1687,49 @@
     <t>2026-06-04</t>
   </si>
   <si>
-    <t>151501</t>
-  </si>
-  <si>
-    <t>149619</t>
-  </si>
-  <si>
-    <t>144914</t>
-  </si>
-  <si>
-    <t>148500</t>
-  </si>
-  <si>
-    <t>18354.81</t>
-  </si>
-  <si>
-    <t>18428.1</t>
-  </si>
-  <si>
-    <t>18439.2</t>
-  </si>
-  <si>
-    <t>18142.45</t>
-  </si>
-  <si>
-    <t>18177.56</t>
-  </si>
-  <si>
-    <t>17651.24</t>
-  </si>
-  <si>
-    <t>17653.05</t>
-  </si>
-  <si>
-    <t>17658.25</t>
-  </si>
-  <si>
-    <t>19345.22</t>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>141841</t>
+  </si>
+  <si>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>136995.5</t>
+  </si>
+  <si>
+    <t>135674</t>
+  </si>
+  <si>
+    <t>145000</t>
+  </si>
+  <si>
+    <t>19604.85</t>
+  </si>
+  <si>
+    <t>19677.36</t>
+  </si>
+  <si>
+    <t>19378.03</t>
+  </si>
+  <si>
+    <t>19415.54</t>
+  </si>
+  <si>
+    <t>18950.64</t>
+  </si>
+  <si>
+    <t>18805.54</t>
+  </si>
+  <si>
+    <t>18855.31</t>
+  </si>
+  <si>
+    <t>18900.05</t>
+  </si>
+  <si>
+    <t>18885.1</t>
   </si>
 </sst>
 </file>
@@ -2081,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D555"/>
+  <dimension ref="A1:D556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9542,16 +9548,16 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
       <c r="C534" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D534" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9598,30 +9604,30 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>557</v>
-      </c>
-      <c r="D538" t="s">
-        <v>562</v>
+      <c r="C538">
+        <v>151501</v>
+      </c>
+      <c r="D538">
+        <v>18428.1</v>
       </c>
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539">
-        <v>141841</v>
-      </c>
-      <c r="D539">
-        <v>23441.36</v>
+      <c r="C539" t="s">
+        <v>558</v>
+      </c>
+      <c r="D539" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9640,72 +9646,72 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541" s="1">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="B541" t="s">
         <v>542</v>
       </c>
-      <c r="C541" t="s">
-        <v>557</v>
-      </c>
-      <c r="D541" t="s">
-        <v>563</v>
+      <c r="C541">
+        <v>151501</v>
+      </c>
+      <c r="D541">
+        <v>18439.2</v>
       </c>
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D542" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D543" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>136995.5</v>
-      </c>
-      <c r="D544">
-        <v>22575.63</v>
+      <c r="C544" t="s">
+        <v>560</v>
+      </c>
+      <c r="D544" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545">
-        <v>135674</v>
-      </c>
-      <c r="D545">
-        <v>22402.77</v>
+      <c r="C545" t="s">
+        <v>561</v>
+      </c>
+      <c r="D545" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9724,16 +9730,16 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547" t="s">
-        <v>559</v>
-      </c>
-      <c r="D547" t="s">
-        <v>566</v>
+      <c r="C547">
+        <v>144914</v>
+      </c>
+      <c r="D547">
+        <v>17651.24</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9752,30 +9758,30 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D549" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550" t="s">
-        <v>559</v>
-      </c>
-      <c r="D550" t="s">
-        <v>568</v>
+      <c r="C550">
+        <v>144914</v>
+      </c>
+      <c r="D550">
+        <v>17658.25</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9794,16 +9800,16 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>154000</v>
-      </c>
-      <c r="D552">
-        <v>20085.06</v>
+      <c r="C552" t="s">
+        <v>561</v>
+      </c>
+      <c r="D552" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9836,16 +9842,30 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>560</v>
-      </c>
-      <c r="D555" t="s">
-        <v>569</v>
+      <c r="C555">
+        <v>148500</v>
+      </c>
+      <c r="D555">
+        <v>19345.22</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4">
+      <c r="A556" s="1">
+        <v>576</v>
+      </c>
+      <c r="B556" t="s">
+        <v>557</v>
+      </c>
+      <c r="C556" t="s">
+        <v>562</v>
+      </c>
+      <c r="D556" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="575">
   <si>
     <t>Date</t>
   </si>
@@ -1690,7 +1690,10 @@
     <t>2026-06-05</t>
   </si>
   <si>
-    <t>141841</t>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
   </si>
   <si>
     <t>140079</t>
@@ -1702,34 +1705,40 @@
     <t>135674</t>
   </si>
   <si>
-    <t>145000</t>
-  </si>
-  <si>
-    <t>19604.85</t>
-  </si>
-  <si>
-    <t>19677.36</t>
-  </si>
-  <si>
-    <t>19378.03</t>
-  </si>
-  <si>
-    <t>19415.54</t>
-  </si>
-  <si>
-    <t>18950.64</t>
-  </si>
-  <si>
-    <t>18805.54</t>
-  </si>
-  <si>
-    <t>18855.31</t>
-  </si>
-  <si>
-    <t>18900.05</t>
-  </si>
-  <si>
-    <t>18885.1</t>
+    <t>127745</t>
+  </si>
+  <si>
+    <t>141500</t>
+  </si>
+  <si>
+    <t>18142.45</t>
+  </si>
+  <si>
+    <t>18177.56</t>
+  </si>
+  <si>
+    <t>17742.31</t>
+  </si>
+  <si>
+    <t>17606.46</t>
+  </si>
+  <si>
+    <t>17608.27</t>
+  </si>
+  <si>
+    <t>17651.24</t>
+  </si>
+  <si>
+    <t>17649.94</t>
+  </si>
+  <si>
+    <t>17653.05</t>
+  </si>
+  <si>
+    <t>16622.36</t>
+  </si>
+  <si>
+    <t>18407.31</t>
   </si>
 </sst>
 </file>
@@ -2087,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D556"/>
+  <dimension ref="A1:D558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9548,16 +9557,16 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534" s="1">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="B534" t="s">
         <v>535</v>
       </c>
-      <c r="C534" t="s">
-        <v>558</v>
-      </c>
-      <c r="D534" t="s">
-        <v>563</v>
+      <c r="C534">
+        <v>141841</v>
+      </c>
+      <c r="D534">
+        <v>19604.85</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -9618,16 +9627,16 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539" s="1">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="B539" t="s">
         <v>540</v>
       </c>
-      <c r="C539" t="s">
-        <v>558</v>
-      </c>
-      <c r="D539" t="s">
-        <v>564</v>
+      <c r="C539">
+        <v>141841</v>
+      </c>
+      <c r="D539">
+        <v>19677.36</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -9660,13 +9669,13 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D542" t="s">
         <v>565</v>
@@ -9674,13 +9683,13 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
       <c r="C543" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D543" t="s">
         <v>566</v>
@@ -9688,13 +9697,13 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
       <c r="C544" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D544" t="s">
         <v>567</v>
@@ -9702,13 +9711,13 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
       <c r="C545" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D545" t="s">
         <v>568</v>
@@ -9716,58 +9725,58 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546">
-        <v>135674</v>
-      </c>
-      <c r="D546">
-        <v>22405.07</v>
+      <c r="C546" t="s">
+        <v>562</v>
+      </c>
+      <c r="D546" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547">
-        <v>144914</v>
-      </c>
-      <c r="D547">
-        <v>17651.24</v>
+      <c r="C547" t="s">
+        <v>562</v>
+      </c>
+      <c r="D547" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548">
-        <v>172634</v>
-      </c>
-      <c r="D548">
-        <v>17649.94</v>
+      <c r="C548" t="s">
+        <v>562</v>
+      </c>
+      <c r="D548" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D549" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9800,16 +9809,16 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>561</v>
-      </c>
-      <c r="D552" t="s">
-        <v>570</v>
+      <c r="C552">
+        <v>135674</v>
+      </c>
+      <c r="D552">
+        <v>18900.05</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9856,16 +9865,44 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556" t="s">
-        <v>562</v>
-      </c>
-      <c r="D556" t="s">
-        <v>571</v>
+      <c r="C556">
+        <v>145000</v>
+      </c>
+      <c r="D556">
+        <v>18885.1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4">
+      <c r="A557" s="1">
+        <v>575</v>
+      </c>
+      <c r="B557" t="s">
+        <v>558</v>
+      </c>
+      <c r="C557" t="s">
+        <v>563</v>
+      </c>
+      <c r="D557" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4">
+      <c r="A558" s="1">
+        <v>576</v>
+      </c>
+      <c r="B558" t="s">
+        <v>559</v>
+      </c>
+      <c r="C558" t="s">
+        <v>564</v>
+      </c>
+      <c r="D558" t="s">
+        <v>574</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="575">
   <si>
     <t>Date</t>
   </si>
@@ -1696,49 +1696,49 @@
     <t>2026-06-09</t>
   </si>
   <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>136995.5</t>
-  </si>
-  <si>
-    <t>135674</t>
-  </si>
-  <si>
-    <t>127745</t>
-  </si>
-  <si>
-    <t>141500</t>
-  </si>
-  <si>
-    <t>18142.45</t>
-  </si>
-  <si>
-    <t>18177.56</t>
-  </si>
-  <si>
-    <t>17742.31</t>
-  </si>
-  <si>
-    <t>17606.46</t>
-  </si>
-  <si>
-    <t>17608.27</t>
-  </si>
-  <si>
-    <t>17651.24</t>
-  </si>
-  <si>
-    <t>17649.94</t>
-  </si>
-  <si>
-    <t>17653.05</t>
-  </si>
-  <si>
-    <t>16622.36</t>
-  </si>
-  <si>
-    <t>18407.31</t>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>170821</t>
+  </si>
+  <si>
+    <t>168699</t>
+  </si>
+  <si>
+    <t>163394</t>
+  </si>
+  <si>
+    <t>157558.5</t>
+  </si>
+  <si>
+    <t>136500</t>
+  </si>
+  <si>
+    <t>23441.7</t>
+  </si>
+  <si>
+    <t>23084.77</t>
+  </si>
+  <si>
+    <t>22402.77</t>
+  </si>
+  <si>
+    <t>22405.07</t>
+  </si>
+  <si>
+    <t>22459.75</t>
+  </si>
+  <si>
+    <t>22458.1</t>
+  </si>
+  <si>
+    <t>22515.36</t>
+  </si>
+  <si>
+    <t>21685.99</t>
+  </si>
+  <si>
+    <t>17790.61</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D558"/>
+  <dimension ref="A1:D559"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9599,16 +9599,16 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537">
-        <v>180481</v>
-      </c>
-      <c r="D537">
-        <v>18422.96</v>
+      <c r="C537" t="s">
+        <v>561</v>
+      </c>
+      <c r="D537" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -9669,55 +9669,55 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D542" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>560</v>
-      </c>
-      <c r="D543" t="s">
-        <v>566</v>
+      <c r="C543">
+        <v>140079</v>
+      </c>
+      <c r="D543">
+        <v>18177.56</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>561</v>
-      </c>
-      <c r="D544" t="s">
-        <v>567</v>
+      <c r="C544">
+        <v>136995.5</v>
+      </c>
+      <c r="D544">
+        <v>17742.31</v>
       </c>
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
       <c r="C545" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D545" t="s">
         <v>568</v>
@@ -9725,13 +9725,13 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D546" t="s">
         <v>569</v>
@@ -9739,13 +9739,13 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D547" t="s">
         <v>570</v>
@@ -9753,13 +9753,13 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
       <c r="C548" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D548" t="s">
         <v>571</v>
@@ -9767,16 +9767,16 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>562</v>
-      </c>
-      <c r="D549" t="s">
-        <v>572</v>
+      <c r="C549">
+        <v>135674</v>
+      </c>
+      <c r="D549">
+        <v>17653.05</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9809,16 +9809,16 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>135674</v>
-      </c>
-      <c r="D552">
-        <v>18900.05</v>
+      <c r="C552" t="s">
+        <v>563</v>
+      </c>
+      <c r="D552" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9851,16 +9851,16 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555">
-        <v>148500</v>
-      </c>
-      <c r="D555">
-        <v>19345.22</v>
+      <c r="C555" t="s">
+        <v>564</v>
+      </c>
+      <c r="D555" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9879,29 +9879,43 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
-      <c r="C557" t="s">
-        <v>563</v>
-      </c>
-      <c r="D557" t="s">
-        <v>573</v>
+      <c r="C557">
+        <v>127745</v>
+      </c>
+      <c r="D557">
+        <v>16622.36</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558" t="s">
-        <v>564</v>
-      </c>
-      <c r="D558" t="s">
+      <c r="C558">
+        <v>141500</v>
+      </c>
+      <c r="D558">
+        <v>18407.31</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4">
+      <c r="A559" s="1">
+        <v>579</v>
+      </c>
+      <c r="B559" t="s">
+        <v>560</v>
+      </c>
+      <c r="C559" t="s">
+        <v>565</v>
+      </c>
+      <c r="D559" t="s">
         <v>574</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="577">
   <si>
     <t>Date</t>
   </si>
@@ -1699,46 +1699,52 @@
     <t>2026-06-10</t>
   </si>
   <si>
-    <t>170821</t>
-  </si>
-  <si>
-    <t>168699</t>
-  </si>
-  <si>
-    <t>163394</t>
-  </si>
-  <si>
-    <t>157558.5</t>
-  </si>
-  <si>
-    <t>136500</t>
-  </si>
-  <si>
-    <t>23441.7</t>
-  </si>
-  <si>
-    <t>23084.77</t>
-  </si>
-  <si>
-    <t>22402.77</t>
-  </si>
-  <si>
-    <t>22405.07</t>
-  </si>
-  <si>
-    <t>22459.75</t>
-  </si>
-  <si>
-    <t>22458.1</t>
-  </si>
-  <si>
-    <t>22515.36</t>
-  </si>
-  <si>
-    <t>21685.99</t>
-  </si>
-  <si>
-    <t>17790.61</t>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>180481</t>
+  </si>
+  <si>
+    <t>178239</t>
+  </si>
+  <si>
+    <t>172634</t>
+  </si>
+  <si>
+    <t>170392</t>
+  </si>
+  <si>
+    <t>162545</t>
+  </si>
+  <si>
+    <t>134500</t>
+  </si>
+  <si>
+    <t>19683.14</t>
+  </si>
+  <si>
+    <t>19415.54</t>
+  </si>
+  <si>
+    <t>18807.47</t>
+  </si>
+  <si>
+    <t>18853.37</t>
+  </si>
+  <si>
+    <t>18851.98</t>
+  </si>
+  <si>
+    <t>18855.31</t>
+  </si>
+  <si>
+    <t>18651.57</t>
+  </si>
+  <si>
+    <t>17770.88</t>
+  </si>
+  <si>
+    <t>17515.24</t>
   </si>
 </sst>
 </file>
@@ -2096,7 +2102,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D559"/>
+  <dimension ref="A1:D560"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9599,30 +9605,30 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537" s="1">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="B537" t="s">
         <v>538</v>
       </c>
-      <c r="C537" t="s">
-        <v>561</v>
-      </c>
-      <c r="D537" t="s">
-        <v>566</v>
+      <c r="C537">
+        <v>170821</v>
+      </c>
+      <c r="D537">
+        <v>23441.7</v>
       </c>
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>536</v>
+        <v>558</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538">
-        <v>151501</v>
-      </c>
-      <c r="D538">
-        <v>18428.1</v>
+      <c r="C538" t="s">
+        <v>562</v>
+      </c>
+      <c r="D538" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9669,30 +9675,30 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>562</v>
-      </c>
-      <c r="D542" t="s">
-        <v>567</v>
+      <c r="C542">
+        <v>168699</v>
+      </c>
+      <c r="D542">
+        <v>23084.77</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>140079</v>
-      </c>
-      <c r="D543">
-        <v>18177.56</v>
+      <c r="C543" t="s">
+        <v>563</v>
+      </c>
+      <c r="D543" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9711,16 +9717,16 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545" s="1">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="B545" t="s">
         <v>546</v>
       </c>
-      <c r="C545" t="s">
-        <v>563</v>
-      </c>
-      <c r="D545" t="s">
-        <v>568</v>
+      <c r="C545">
+        <v>163394</v>
+      </c>
+      <c r="D545">
+        <v>22402.77</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9731,10 +9737,10 @@
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D546" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9745,10 +9751,10 @@
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D547" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9759,24 +9765,24 @@
         <v>549</v>
       </c>
       <c r="C548" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D548" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>135674</v>
-      </c>
-      <c r="D549">
-        <v>17653.05</v>
+      <c r="C549" t="s">
+        <v>564</v>
+      </c>
+      <c r="D549" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9809,30 +9815,30 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>563</v>
-      </c>
-      <c r="D552" t="s">
-        <v>572</v>
+      <c r="C552">
+        <v>163394</v>
+      </c>
+      <c r="D552">
+        <v>22515.36</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553">
-        <v>152000</v>
-      </c>
-      <c r="D553">
-        <v>19821.01</v>
+      <c r="C553" t="s">
+        <v>565</v>
+      </c>
+      <c r="D553" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9851,30 +9857,30 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>564</v>
-      </c>
-      <c r="D555" t="s">
-        <v>573</v>
+      <c r="C555">
+        <v>157558.5</v>
+      </c>
+      <c r="D555">
+        <v>21685.99</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556">
-        <v>145000</v>
-      </c>
-      <c r="D556">
-        <v>18885.1</v>
+      <c r="C556" t="s">
+        <v>566</v>
+      </c>
+      <c r="D556" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9907,16 +9913,30 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559" t="s">
-        <v>565</v>
-      </c>
-      <c r="D559" t="s">
-        <v>574</v>
+      <c r="C559">
+        <v>136500</v>
+      </c>
+      <c r="D559">
+        <v>17790.61</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4">
+      <c r="A560" s="1">
+        <v>580</v>
+      </c>
+      <c r="B560" t="s">
+        <v>561</v>
+      </c>
+      <c r="C560" t="s">
+        <v>567</v>
+      </c>
+      <c r="D560" t="s">
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="579">
   <si>
     <t>Date</t>
   </si>
@@ -1702,6 +1702,9 @@
     <t>2026-06-11</t>
   </si>
   <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
     <t>180481</t>
   </si>
   <si>
@@ -1714,37 +1717,40 @@
     <t>170392</t>
   </si>
   <si>
-    <t>162545</t>
-  </si>
-  <si>
-    <t>134500</t>
-  </si>
-  <si>
-    <t>19683.14</t>
-  </si>
-  <si>
-    <t>19415.54</t>
-  </si>
-  <si>
-    <t>18807.47</t>
-  </si>
-  <si>
-    <t>18853.37</t>
-  </si>
-  <si>
-    <t>18851.98</t>
-  </si>
-  <si>
-    <t>18855.31</t>
-  </si>
-  <si>
-    <t>18651.57</t>
-  </si>
-  <si>
-    <t>17770.88</t>
-  </si>
-  <si>
-    <t>17515.24</t>
+    <t>133000</t>
+  </si>
+  <si>
+    <t>23476.5</t>
+  </si>
+  <si>
+    <t>23084.77</t>
+  </si>
+  <si>
+    <t>22405.07</t>
+  </si>
+  <si>
+    <t>22459.75</t>
+  </si>
+  <si>
+    <t>22462.06</t>
+  </si>
+  <si>
+    <t>22468.67</t>
+  </si>
+  <si>
+    <t>22480.57</t>
+  </si>
+  <si>
+    <t>22515.36</t>
+  </si>
+  <si>
+    <t>22219.35</t>
+  </si>
+  <si>
+    <t>22229.17</t>
+  </si>
+  <si>
+    <t>17353.61</t>
   </si>
 </sst>
 </file>
@@ -2102,7 +2108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D560"/>
+  <dimension ref="A1:D561"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9619,16 +9625,16 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538" s="1">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="B538" t="s">
         <v>539</v>
       </c>
-      <c r="C538" t="s">
-        <v>562</v>
-      </c>
-      <c r="D538" t="s">
-        <v>568</v>
+      <c r="C538">
+        <v>180481</v>
+      </c>
+      <c r="D538">
+        <v>19683.14</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -9647,16 +9653,16 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>538</v>
+        <v>559</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540">
-        <v>141841</v>
-      </c>
-      <c r="D540">
-        <v>23476.5</v>
+      <c r="C540" t="s">
+        <v>563</v>
+      </c>
+      <c r="D540" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9675,30 +9681,30 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>168699</v>
-      </c>
-      <c r="D542">
-        <v>23084.77</v>
+      <c r="C542" t="s">
+        <v>564</v>
+      </c>
+      <c r="D542" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>563</v>
-      </c>
-      <c r="D543" t="s">
-        <v>569</v>
+      <c r="C543">
+        <v>178239</v>
+      </c>
+      <c r="D543">
+        <v>19415.54</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9731,13 +9737,13 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D546" t="s">
         <v>570</v>
@@ -9745,13 +9751,13 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D547" t="s">
         <v>571</v>
@@ -9759,100 +9765,100 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548" t="s">
-        <v>564</v>
-      </c>
-      <c r="D548" t="s">
-        <v>572</v>
+      <c r="C548">
+        <v>172634</v>
+      </c>
+      <c r="D548">
+        <v>18851.98</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D549" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550">
-        <v>144914</v>
-      </c>
-      <c r="D550">
-        <v>17658.25</v>
+      <c r="C550" t="s">
+        <v>565</v>
+      </c>
+      <c r="D550" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
-      <c r="C551">
-        <v>172634</v>
-      </c>
-      <c r="D551">
-        <v>17667.6</v>
+      <c r="C551" t="s">
+        <v>565</v>
+      </c>
+      <c r="D551" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>163394</v>
-      </c>
-      <c r="D552">
-        <v>22515.36</v>
+      <c r="C552" t="s">
+        <v>565</v>
+      </c>
+      <c r="D552" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
       <c r="C553" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D553" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554">
-        <v>152000</v>
-      </c>
-      <c r="D554">
-        <v>19829.77</v>
+      <c r="C554" t="s">
+        <v>566</v>
+      </c>
+      <c r="D554" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9871,16 +9877,16 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556" t="s">
-        <v>566</v>
-      </c>
-      <c r="D556" t="s">
-        <v>575</v>
+      <c r="C556">
+        <v>162545</v>
+      </c>
+      <c r="D556">
+        <v>17770.88</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9927,16 +9933,30 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560" t="s">
+      <c r="C560">
+        <v>134500</v>
+      </c>
+      <c r="D560">
+        <v>17515.24</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4">
+      <c r="A561" s="1">
+        <v>580</v>
+      </c>
+      <c r="B561" t="s">
+        <v>562</v>
+      </c>
+      <c r="C561" t="s">
         <v>567</v>
       </c>
-      <c r="D560" t="s">
-        <v>576</v>
+      <c r="D561" t="s">
+        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="580">
   <si>
     <t>Date</t>
   </si>
@@ -1705,52 +1705,55 @@
     <t>2026-06-12</t>
   </si>
   <si>
-    <t>180481</t>
-  </si>
-  <si>
-    <t>178239</t>
-  </si>
-  <si>
-    <t>172634</t>
-  </si>
-  <si>
-    <t>170392</t>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>163394</t>
+  </si>
+  <si>
+    <t>161272</t>
+  </si>
+  <si>
+    <t>142704.5</t>
+  </si>
+  <si>
+    <t>141113</t>
   </si>
   <si>
     <t>133000</t>
   </si>
   <si>
-    <t>23476.5</t>
-  </si>
-  <si>
-    <t>23084.77</t>
-  </si>
-  <si>
-    <t>22405.07</t>
-  </si>
-  <si>
-    <t>22459.75</t>
-  </si>
-  <si>
-    <t>22462.06</t>
-  </si>
-  <si>
-    <t>22468.67</t>
-  </si>
-  <si>
-    <t>22480.57</t>
-  </si>
-  <si>
-    <t>22515.36</t>
-  </si>
-  <si>
-    <t>22219.35</t>
-  </si>
-  <si>
-    <t>22229.17</t>
-  </si>
-  <si>
-    <t>17353.61</t>
+    <t>18807.47</t>
+  </si>
+  <si>
+    <t>18853.37</t>
+  </si>
+  <si>
+    <t>18851.98</t>
+  </si>
+  <si>
+    <t>18855.31</t>
+  </si>
+  <si>
+    <t>18860.85</t>
+  </si>
+  <si>
+    <t>18870.84</t>
+  </si>
+  <si>
+    <t>18900.05</t>
+  </si>
+  <si>
+    <t>18651.57</t>
+  </si>
+  <si>
+    <t>16481.84</t>
+  </si>
+  <si>
+    <t>16329.75</t>
+  </si>
+  <si>
+    <t>17373.85</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D561"/>
+  <dimension ref="A1:D562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9653,16 +9656,16 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540" s="1">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="B540" t="s">
         <v>541</v>
       </c>
-      <c r="C540" t="s">
-        <v>563</v>
-      </c>
-      <c r="D540" t="s">
-        <v>568</v>
+      <c r="C540">
+        <v>180481</v>
+      </c>
+      <c r="D540">
+        <v>23476.5</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -9681,16 +9684,16 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>564</v>
-      </c>
-      <c r="D542" t="s">
-        <v>569</v>
+      <c r="C542">
+        <v>178239</v>
+      </c>
+      <c r="D542">
+        <v>23084.77</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9737,55 +9740,55 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
       <c r="C546" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D546" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D547" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548">
-        <v>172634</v>
-      </c>
-      <c r="D548">
-        <v>18851.98</v>
+      <c r="C548" t="s">
+        <v>564</v>
+      </c>
+      <c r="D548" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D549" t="s">
         <v>572</v>
@@ -9793,13 +9796,13 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
       <c r="C550" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D550" t="s">
         <v>573</v>
@@ -9807,13 +9810,13 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
       <c r="C551" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D551" t="s">
         <v>574</v>
@@ -9821,13 +9824,13 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
       <c r="C552" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D552" t="s">
         <v>575</v>
@@ -9835,13 +9838,13 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
       <c r="C553" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D553" t="s">
         <v>576</v>
@@ -9849,16 +9852,16 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554" t="s">
-        <v>566</v>
-      </c>
-      <c r="D554" t="s">
-        <v>577</v>
+      <c r="C554">
+        <v>170392</v>
+      </c>
+      <c r="D554">
+        <v>22229.17</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9933,21 +9936,21 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560">
-        <v>134500</v>
-      </c>
-      <c r="D560">
-        <v>17515.24</v>
+      <c r="C560" t="s">
+        <v>566</v>
+      </c>
+      <c r="D560" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
@@ -9957,6 +9960,20 @@
       </c>
       <c r="D561" t="s">
         <v>578</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4">
+      <c r="A562" s="1">
+        <v>580</v>
+      </c>
+      <c r="B562" t="s">
+        <v>563</v>
+      </c>
+      <c r="C562" t="s">
+        <v>568</v>
+      </c>
+      <c r="D562" t="s">
+        <v>579</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="583">
   <si>
     <t>Date</t>
   </si>
@@ -1708,52 +1708,61 @@
     <t>2026-06-15</t>
   </si>
   <si>
-    <t>163394</t>
-  </si>
-  <si>
-    <t>161272</t>
-  </si>
-  <si>
-    <t>142704.5</t>
-  </si>
-  <si>
-    <t>141113</t>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>140079</t>
+  </si>
+  <si>
+    <t>136995.5</t>
+  </si>
+  <si>
+    <t>135674</t>
+  </si>
+  <si>
+    <t>133912</t>
+  </si>
+  <si>
+    <t>130828.5</t>
+  </si>
+  <si>
+    <t>127745</t>
   </si>
   <si>
     <t>133000</t>
   </si>
   <si>
-    <t>18807.47</t>
-  </si>
-  <si>
-    <t>18853.37</t>
-  </si>
-  <si>
-    <t>18851.98</t>
-  </si>
-  <si>
-    <t>18855.31</t>
-  </si>
-  <si>
-    <t>18860.85</t>
-  </si>
-  <si>
-    <t>18870.84</t>
-  </si>
-  <si>
-    <t>18900.05</t>
-  </si>
-  <si>
-    <t>18651.57</t>
-  </si>
-  <si>
-    <t>16481.84</t>
-  </si>
-  <si>
-    <t>16329.75</t>
-  </si>
-  <si>
-    <t>17373.85</t>
+    <t>21849.19</t>
+  </si>
+  <si>
+    <t>21367.3</t>
+  </si>
+  <si>
+    <t>21256.06</t>
+  </si>
+  <si>
+    <t>21259.81</t>
+  </si>
+  <si>
+    <t>21277.33</t>
+  </si>
+  <si>
+    <t>21310.25</t>
+  </si>
+  <si>
+    <t>21030.09</t>
+  </si>
+  <si>
+    <t>21039.39</t>
+  </si>
+  <si>
+    <t>20525.28</t>
+  </si>
+  <si>
+    <t>20037.09</t>
+  </si>
+  <si>
+    <t>17367.18</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D562"/>
+  <dimension ref="A1:D563"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9684,16 +9693,16 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542">
-        <v>178239</v>
-      </c>
-      <c r="D542">
-        <v>23084.77</v>
+      <c r="C542" t="s">
+        <v>565</v>
+      </c>
+      <c r="D542" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9712,16 +9721,16 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>136995.5</v>
-      </c>
-      <c r="D544">
-        <v>17742.31</v>
+      <c r="C544" t="s">
+        <v>566</v>
+      </c>
+      <c r="D544" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9740,156 +9749,156 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546" s="1">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="B546" t="s">
         <v>547</v>
       </c>
-      <c r="C546" t="s">
-        <v>564</v>
-      </c>
-      <c r="D546" t="s">
-        <v>569</v>
+      <c r="C546">
+        <v>163394</v>
+      </c>
+      <c r="D546">
+        <v>18807.47</v>
       </c>
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547" t="s">
-        <v>564</v>
-      </c>
-      <c r="D547" t="s">
-        <v>570</v>
+      <c r="C547">
+        <v>163394</v>
+      </c>
+      <c r="D547">
+        <v>18853.37</v>
       </c>
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
       <c r="C548" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D548" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
       <c r="C549" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D549" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550" t="s">
-        <v>564</v>
-      </c>
-      <c r="D550" t="s">
-        <v>573</v>
+      <c r="C550">
+        <v>163394</v>
+      </c>
+      <c r="D550">
+        <v>18860.85</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
       <c r="C551" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D551" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
       <c r="C552" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D552" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
       <c r="C553" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D553" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554">
-        <v>170392</v>
-      </c>
-      <c r="D554">
-        <v>22229.17</v>
+      <c r="C554" t="s">
+        <v>568</v>
+      </c>
+      <c r="D554" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555">
-        <v>157558.5</v>
-      </c>
-      <c r="D555">
-        <v>21685.99</v>
+      <c r="C555" t="s">
+        <v>569</v>
+      </c>
+      <c r="D555" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556">
-        <v>162545</v>
-      </c>
-      <c r="D556">
-        <v>17770.88</v>
+      <c r="C556" t="s">
+        <v>570</v>
+      </c>
+      <c r="D556" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9936,44 +9945,58 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560" t="s">
-        <v>566</v>
-      </c>
-      <c r="D560" t="s">
-        <v>577</v>
+      <c r="C560">
+        <v>142704.5</v>
+      </c>
+      <c r="D560">
+        <v>16481.84</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561" t="s">
-        <v>567</v>
-      </c>
-      <c r="D561" t="s">
-        <v>578</v>
+      <c r="C561">
+        <v>141113</v>
+      </c>
+      <c r="D561">
+        <v>16329.75</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562" t="s">
-        <v>568</v>
-      </c>
-      <c r="D562" t="s">
-        <v>579</v>
+      <c r="C562">
+        <v>133000</v>
+      </c>
+      <c r="D562">
+        <v>17373.85</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4">
+      <c r="A563" s="1">
+        <v>582</v>
+      </c>
+      <c r="B563" t="s">
+        <v>564</v>
+      </c>
+      <c r="C563" t="s">
+        <v>571</v>
+      </c>
+      <c r="D563" t="s">
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="578">
   <si>
     <t>Date</t>
   </si>
@@ -1711,37 +1711,28 @@
     <t>2026-06-16</t>
   </si>
   <si>
-    <t>140079</t>
-  </si>
-  <si>
-    <t>136995.5</t>
-  </si>
-  <si>
-    <t>135674</t>
-  </si>
-  <si>
-    <t>133912</t>
-  </si>
-  <si>
-    <t>130828.5</t>
-  </si>
-  <si>
-    <t>127745</t>
-  </si>
-  <si>
-    <t>133000</t>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>178239</t>
+  </si>
+  <si>
+    <t>172634</t>
+  </si>
+  <si>
+    <t>149093</t>
+  </si>
+  <si>
+    <t>131500</t>
   </si>
   <si>
     <t>21849.19</t>
   </si>
   <si>
-    <t>21367.3</t>
-  </si>
-  <si>
-    <t>21256.06</t>
-  </si>
-  <si>
-    <t>21259.81</t>
+    <t>21266.06</t>
   </si>
   <si>
     <t>21277.33</t>
@@ -1750,19 +1741,13 @@
     <t>21310.25</t>
   </si>
   <si>
-    <t>21030.09</t>
-  </si>
-  <si>
-    <t>21039.39</t>
-  </si>
-  <si>
-    <t>20525.28</t>
-  </si>
-  <si>
-    <t>20037.09</t>
-  </si>
-  <si>
-    <t>17367.18</t>
+    <t>18433.65</t>
+  </si>
+  <si>
+    <t>18426.03</t>
+  </si>
+  <si>
+    <t>17149.8</t>
   </si>
 </sst>
 </file>
@@ -2120,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D563"/>
+  <dimension ref="A1:D565"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9693,16 +9678,16 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
       <c r="C542" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D542" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9721,16 +9706,16 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>566</v>
-      </c>
-      <c r="D544" t="s">
-        <v>573</v>
+      <c r="C544">
+        <v>136995.5</v>
+      </c>
+      <c r="D544">
+        <v>21367.3</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9777,128 +9762,128 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548" t="s">
-        <v>567</v>
-      </c>
-      <c r="D548" t="s">
-        <v>574</v>
+      <c r="C548">
+        <v>135674</v>
+      </c>
+      <c r="D548">
+        <v>21256.06</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>567</v>
-      </c>
-      <c r="D549" t="s">
-        <v>575</v>
+      <c r="C549">
+        <v>135674</v>
+      </c>
+      <c r="D549">
+        <v>21259.81</v>
       </c>
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550">
-        <v>163394</v>
-      </c>
-      <c r="D550">
-        <v>18860.85</v>
+      <c r="C550" t="s">
+        <v>568</v>
+      </c>
+      <c r="D550" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
       <c r="C551" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D551" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
       <c r="C552" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D552" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553" t="s">
-        <v>568</v>
-      </c>
-      <c r="D553" t="s">
-        <v>578</v>
+      <c r="C553">
+        <v>133912</v>
+      </c>
+      <c r="D553">
+        <v>21030.09</v>
       </c>
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554" t="s">
-        <v>568</v>
-      </c>
-      <c r="D554" t="s">
-        <v>579</v>
+      <c r="C554">
+        <v>133912</v>
+      </c>
+      <c r="D554">
+        <v>21039.39</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>569</v>
-      </c>
-      <c r="D555" t="s">
-        <v>580</v>
+      <c r="C555">
+        <v>130828.5</v>
+      </c>
+      <c r="D555">
+        <v>20525.28</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556" t="s">
-        <v>570</v>
-      </c>
-      <c r="D556" t="s">
-        <v>581</v>
+      <c r="C556">
+        <v>127745</v>
+      </c>
+      <c r="D556">
+        <v>20037.09</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9973,30 +9958,58 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562">
-        <v>133000</v>
-      </c>
-      <c r="D562">
-        <v>17373.85</v>
+      <c r="C562" t="s">
+        <v>569</v>
+      </c>
+      <c r="D562" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563" t="s">
-        <v>571</v>
-      </c>
-      <c r="D563" t="s">
-        <v>582</v>
+      <c r="C563">
+        <v>133000</v>
+      </c>
+      <c r="D563">
+        <v>17367.18</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4">
+      <c r="A564" s="1">
+        <v>584</v>
+      </c>
+      <c r="B564" t="s">
+        <v>565</v>
+      </c>
+      <c r="C564" t="s">
+        <v>569</v>
+      </c>
+      <c r="D564" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4">
+      <c r="A565" s="1">
+        <v>585</v>
+      </c>
+      <c r="B565" t="s">
+        <v>566</v>
+      </c>
+      <c r="C565" t="s">
+        <v>570</v>
+      </c>
+      <c r="D565" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="583">
   <si>
     <t>Date</t>
   </si>
@@ -1723,31 +1723,46 @@
     <t>172634</t>
   </si>
   <si>
+    <t>162545</t>
+  </si>
+  <si>
+    <t>158621.5</t>
+  </si>
+  <si>
+    <t>153016.5</t>
+  </si>
+  <si>
     <t>149093</t>
   </si>
   <si>
-    <t>131500</t>
-  </si>
-  <si>
-    <t>21849.19</t>
-  </si>
-  <si>
-    <t>21266.06</t>
-  </si>
-  <si>
-    <t>21277.33</t>
-  </si>
-  <si>
-    <t>21310.25</t>
-  </si>
-  <si>
-    <t>18433.65</t>
-  </si>
-  <si>
-    <t>18426.03</t>
-  </si>
-  <si>
-    <t>17149.8</t>
+    <t>19415.54</t>
+  </si>
+  <si>
+    <t>18870.84</t>
+  </si>
+  <si>
+    <t>18900.05</t>
+  </si>
+  <si>
+    <t>17754.42</t>
+  </si>
+  <si>
+    <t>17321.28</t>
+  </si>
+  <si>
+    <t>16740.96</t>
+  </si>
+  <si>
+    <t>16329.75</t>
+  </si>
+  <si>
+    <t>16348.79</t>
+  </si>
+  <si>
+    <t>16342.52</t>
+  </si>
+  <si>
+    <t>16342.03</t>
   </si>
 </sst>
 </file>
@@ -9678,30 +9693,30 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542" s="1">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
       </c>
-      <c r="C542" t="s">
-        <v>567</v>
-      </c>
-      <c r="D542" t="s">
-        <v>571</v>
+      <c r="C542">
+        <v>178239</v>
+      </c>
+      <c r="D542">
+        <v>21849.19</v>
       </c>
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543">
-        <v>178239</v>
-      </c>
-      <c r="D543">
-        <v>19415.54</v>
+      <c r="C543" t="s">
+        <v>567</v>
+      </c>
+      <c r="D543" t="s">
+        <v>573</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9790,21 +9805,21 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550" s="1">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="B550" t="s">
         <v>551</v>
       </c>
-      <c r="C550" t="s">
-        <v>568</v>
-      </c>
-      <c r="D550" t="s">
-        <v>572</v>
+      <c r="C550">
+        <v>172634</v>
+      </c>
+      <c r="D550">
+        <v>21266.06</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
@@ -9813,12 +9828,12 @@
         <v>568</v>
       </c>
       <c r="D551" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
@@ -9827,7 +9842,7 @@
         <v>568</v>
       </c>
       <c r="D552" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9888,44 +9903,44 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>555</v>
+        <v>578</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
-      <c r="C557">
-        <v>127745</v>
-      </c>
-      <c r="D557">
-        <v>16622.36</v>
+      <c r="C557" t="s">
+        <v>569</v>
+      </c>
+      <c r="D557" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558">
-        <v>141500</v>
-      </c>
-      <c r="D558">
-        <v>18407.31</v>
+      <c r="C558" t="s">
+        <v>570</v>
+      </c>
+      <c r="D558" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>557</v>
+        <v>580</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559">
-        <v>136500</v>
-      </c>
-      <c r="D559">
-        <v>17790.61</v>
+      <c r="C559" t="s">
+        <v>571</v>
+      </c>
+      <c r="D559" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9944,72 +9959,72 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>559</v>
+        <v>582</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561">
-        <v>141113</v>
-      </c>
-      <c r="D561">
-        <v>16329.75</v>
+      <c r="C561" t="s">
+        <v>572</v>
+      </c>
+      <c r="D561" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D562" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>561</v>
+        <v>584</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563">
-        <v>133000</v>
-      </c>
-      <c r="D563">
-        <v>17367.18</v>
+      <c r="C563" t="s">
+        <v>572</v>
+      </c>
+      <c r="D563" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D564" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565" t="s">
-        <v>570</v>
-      </c>
-      <c r="D565" t="s">
-        <v>577</v>
+      <c r="C565">
+        <v>131500</v>
+      </c>
+      <c r="D565">
+        <v>17149.8</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="585">
   <si>
     <t>Date</t>
   </si>
@@ -1717,52 +1717,58 @@
     <t>2026-06-18</t>
   </si>
   <si>
-    <t>178239</t>
-  </si>
-  <si>
-    <t>172634</t>
-  </si>
-  <si>
-    <t>162545</t>
-  </si>
-  <si>
-    <t>158621.5</t>
-  </si>
-  <si>
-    <t>153016.5</t>
-  </si>
-  <si>
-    <t>149093</t>
-  </si>
-  <si>
-    <t>19415.54</t>
-  </si>
-  <si>
-    <t>18870.84</t>
-  </si>
-  <si>
-    <t>18900.05</t>
-  </si>
-  <si>
-    <t>17754.42</t>
-  </si>
-  <si>
-    <t>17321.28</t>
-  </si>
-  <si>
-    <t>16740.96</t>
-  </si>
-  <si>
-    <t>16329.75</t>
-  </si>
-  <si>
-    <t>16348.79</t>
-  </si>
-  <si>
-    <t>16342.52</t>
-  </si>
-  <si>
-    <t>16342.03</t>
+    <t>146325.5</t>
+  </si>
+  <si>
+    <t>144914</t>
+  </si>
+  <si>
+    <t>139738.5</t>
+  </si>
+  <si>
+    <t>136445</t>
+  </si>
+  <si>
+    <t>133151.5</t>
+  </si>
+  <si>
+    <t>128446.5</t>
+  </si>
+  <si>
+    <t>125153</t>
+  </si>
+  <si>
+    <t>22575.63</t>
+  </si>
+  <si>
+    <t>22459.75</t>
+  </si>
+  <si>
+    <t>22480.57</t>
+  </si>
+  <si>
+    <t>21685.99</t>
+  </si>
+  <si>
+    <t>21170.2</t>
+  </si>
+  <si>
+    <t>21150.59</t>
+  </si>
+  <si>
+    <t>20634.59</t>
+  </si>
+  <si>
+    <t>19943.27</t>
+  </si>
+  <si>
+    <t>19476.08</t>
+  </si>
+  <si>
+    <t>19468.61</t>
+  </si>
+  <si>
+    <t>19468.03</t>
   </si>
 </sst>
 </file>
@@ -9707,30 +9713,30 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543" s="1">
-        <v>564</v>
+        <v>541</v>
       </c>
       <c r="B543" t="s">
         <v>544</v>
       </c>
-      <c r="C543" t="s">
-        <v>567</v>
-      </c>
-      <c r="D543" t="s">
-        <v>573</v>
+      <c r="C543">
+        <v>178239</v>
+      </c>
+      <c r="D543">
+        <v>19415.54</v>
       </c>
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>542</v>
+        <v>564</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544">
-        <v>136995.5</v>
-      </c>
-      <c r="D544">
-        <v>21367.3</v>
+      <c r="C544" t="s">
+        <v>567</v>
+      </c>
+      <c r="D544" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9763,16 +9769,16 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547">
-        <v>163394</v>
-      </c>
-      <c r="D547">
-        <v>18853.37</v>
+      <c r="C547" t="s">
+        <v>568</v>
+      </c>
+      <c r="D547" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9819,7 +9825,7 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
@@ -9828,21 +9834,21 @@
         <v>568</v>
       </c>
       <c r="D551" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>573</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>568</v>
-      </c>
-      <c r="D552" t="s">
-        <v>575</v>
+      <c r="C552">
+        <v>172634</v>
+      </c>
+      <c r="D552">
+        <v>18900.05</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9875,72 +9881,72 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555">
-        <v>130828.5</v>
-      </c>
-      <c r="D555">
-        <v>20525.28</v>
+      <c r="C555" t="s">
+        <v>569</v>
+      </c>
+      <c r="D555" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556">
-        <v>127745</v>
-      </c>
-      <c r="D556">
-        <v>20037.09</v>
+      <c r="C556" t="s">
+        <v>570</v>
+      </c>
+      <c r="D556" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D557" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D558" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D559" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9959,58 +9965,58 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561" t="s">
-        <v>572</v>
-      </c>
-      <c r="D561" t="s">
-        <v>579</v>
+      <c r="C561">
+        <v>149093</v>
+      </c>
+      <c r="D561">
+        <v>16329.75</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D562" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D563" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D564" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="565" spans="1:4">

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="588">
   <si>
     <t>Date</t>
   </si>
@@ -1717,58 +1717,67 @@
     <t>2026-06-18</t>
   </si>
   <si>
-    <t>146325.5</t>
-  </si>
-  <si>
-    <t>144914</t>
-  </si>
-  <si>
-    <t>139738.5</t>
-  </si>
-  <si>
-    <t>136445</t>
-  </si>
-  <si>
-    <t>133151.5</t>
-  </si>
-  <si>
-    <t>128446.5</t>
-  </si>
-  <si>
-    <t>125153</t>
-  </si>
-  <si>
-    <t>22575.63</t>
-  </si>
-  <si>
-    <t>22459.75</t>
-  </si>
-  <si>
-    <t>22480.57</t>
-  </si>
-  <si>
-    <t>21685.99</t>
-  </si>
-  <si>
-    <t>21170.2</t>
-  </si>
-  <si>
-    <t>21150.59</t>
-  </si>
-  <si>
-    <t>20634.59</t>
-  </si>
-  <si>
-    <t>19943.27</t>
-  </si>
-  <si>
-    <t>19476.08</t>
-  </si>
-  <si>
-    <t>19468.61</t>
-  </si>
-  <si>
-    <t>19468.03</t>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>163394</t>
+  </si>
+  <si>
+    <t>161272</t>
+  </si>
+  <si>
+    <t>157558.5</t>
+  </si>
+  <si>
+    <t>153845</t>
+  </si>
+  <si>
+    <t>150131.5</t>
+  </si>
+  <si>
+    <t>144826.5</t>
+  </si>
+  <si>
+    <t>141113</t>
+  </si>
+  <si>
+    <t>139521.5</t>
+  </si>
+  <si>
+    <t>137399.5</t>
+  </si>
+  <si>
+    <t>17694.94</t>
+  </si>
+  <si>
+    <t>17462.31</t>
+  </si>
+  <si>
+    <t>17043.14</t>
+  </si>
+  <si>
+    <t>16637.77</t>
+  </si>
+  <si>
+    <t>16622.36</t>
+  </si>
+  <si>
+    <t>16216.84</t>
+  </si>
+  <si>
+    <t>15673.53</t>
+  </si>
+  <si>
+    <t>15300.03</t>
+  </si>
+  <si>
+    <t>15108.97</t>
+  </si>
+  <si>
+    <t>14866.47</t>
   </si>
 </sst>
 </file>
@@ -2126,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D565"/>
+  <dimension ref="A1:D567"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9727,16 +9736,16 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544" s="1">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="B544" t="s">
         <v>545</v>
       </c>
-      <c r="C544" t="s">
-        <v>567</v>
-      </c>
-      <c r="D544" t="s">
-        <v>574</v>
+      <c r="C544">
+        <v>146325.5</v>
+      </c>
+      <c r="D544">
+        <v>22575.63</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9769,16 +9778,16 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547" t="s">
-        <v>568</v>
-      </c>
-      <c r="D547" t="s">
-        <v>575</v>
+      <c r="C547">
+        <v>144914</v>
+      </c>
+      <c r="D547">
+        <v>22459.75</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9817,52 +9826,52 @@
         <v>551</v>
       </c>
       <c r="C550">
-        <v>172634</v>
+        <v>163394</v>
       </c>
       <c r="D550">
-        <v>21266.06</v>
+        <v>22468.67</v>
       </c>
     </row>
     <row r="551" spans="1:4">
       <c r="A551" s="1">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="B551" t="s">
         <v>552</v>
       </c>
-      <c r="C551" t="s">
-        <v>568</v>
-      </c>
-      <c r="D551" t="s">
-        <v>576</v>
+      <c r="C551">
+        <v>163394</v>
+      </c>
+      <c r="D551">
+        <v>22480.57</v>
       </c>
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>571</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>172634</v>
-      </c>
-      <c r="D552">
-        <v>18900.05</v>
+      <c r="C552" t="s">
+        <v>569</v>
+      </c>
+      <c r="D552" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>551</v>
+        <v>572</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553">
-        <v>133912</v>
-      </c>
-      <c r="D553">
-        <v>21030.09</v>
+      <c r="C553" t="s">
+        <v>570</v>
+      </c>
+      <c r="D553" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9873,80 +9882,80 @@
         <v>555</v>
       </c>
       <c r="C554">
-        <v>133912</v>
+        <v>161272</v>
       </c>
       <c r="D554">
-        <v>21039.39</v>
+        <v>22229.17</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
       <c r="C555" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D555" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D556" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D557" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D558" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D559" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9979,58 +9988,86 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562" t="s">
-        <v>573</v>
-      </c>
-      <c r="D562" t="s">
-        <v>582</v>
+      <c r="C562">
+        <v>125153</v>
+      </c>
+      <c r="D562">
+        <v>19476.08</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563" t="s">
-        <v>573</v>
-      </c>
-      <c r="D563" t="s">
-        <v>583</v>
+      <c r="C563">
+        <v>141113</v>
+      </c>
+      <c r="D563">
+        <v>19468.61</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D564" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565">
-        <v>131500</v>
-      </c>
-      <c r="D565">
-        <v>17149.8</v>
+      <c r="C565" t="s">
+        <v>576</v>
+      </c>
+      <c r="D565" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4">
+      <c r="A566" s="1">
+        <v>585</v>
+      </c>
+      <c r="B566" t="s">
+        <v>567</v>
+      </c>
+      <c r="C566" t="s">
+        <v>577</v>
+      </c>
+      <c r="D566" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4">
+      <c r="A567" s="1">
+        <v>565</v>
+      </c>
+      <c r="B567" t="s">
+        <v>568</v>
+      </c>
+      <c r="C567">
+        <v>129500</v>
+      </c>
+      <c r="D567">
+        <v>16879.27</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="589">
   <si>
     <t>Date</t>
   </si>
@@ -1723,61 +1723,64 @@
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>163394</t>
-  </si>
-  <si>
-    <t>161272</t>
-  </si>
-  <si>
-    <t>157558.5</t>
-  </si>
-  <si>
-    <t>153845</t>
-  </si>
-  <si>
-    <t>150131.5</t>
-  </si>
-  <si>
-    <t>144826.5</t>
-  </si>
-  <si>
-    <t>141113</t>
-  </si>
-  <si>
-    <t>139521.5</t>
-  </si>
-  <si>
-    <t>137399.5</t>
-  </si>
-  <si>
-    <t>17694.94</t>
-  </si>
-  <si>
-    <t>17462.31</t>
-  </si>
-  <si>
-    <t>17043.14</t>
-  </si>
-  <si>
-    <t>16637.77</t>
-  </si>
-  <si>
-    <t>16622.36</t>
-  </si>
-  <si>
-    <t>16216.84</t>
-  </si>
-  <si>
-    <t>15673.53</t>
-  </si>
-  <si>
-    <t>15300.03</t>
-  </si>
-  <si>
-    <t>15108.97</t>
-  </si>
-  <si>
-    <t>14866.47</t>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>144914</t>
+  </si>
+  <si>
+    <t>143032</t>
+  </si>
+  <si>
+    <t>136445</t>
+  </si>
+  <si>
+    <t>133151.5</t>
+  </si>
+  <si>
+    <t>128446.5</t>
+  </si>
+  <si>
+    <t>126564.5</t>
+  </si>
+  <si>
+    <t>125153</t>
+  </si>
+  <si>
+    <t>126500</t>
+  </si>
+  <si>
+    <t>18853.37</t>
+  </si>
+  <si>
+    <t>18855.31</t>
+  </si>
+  <si>
+    <t>18651.57</t>
+  </si>
+  <si>
+    <t>18659.82</t>
+  </si>
+  <si>
+    <t>17770.88</t>
+  </si>
+  <si>
+    <t>17754.42</t>
+  </si>
+  <si>
+    <t>17321.28</t>
+  </si>
+  <si>
+    <t>16740.96</t>
+  </si>
+  <si>
+    <t>16481.84</t>
+  </si>
+  <si>
+    <t>16329.75</t>
+  </si>
+  <si>
+    <t>16451.17</t>
   </si>
 </sst>
 </file>
@@ -2135,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D567"/>
+  <dimension ref="A1:D568"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9778,16 +9781,16 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547">
-        <v>144914</v>
-      </c>
-      <c r="D547">
-        <v>22459.75</v>
+      <c r="C547" t="s">
+        <v>570</v>
+      </c>
+      <c r="D547" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9806,16 +9809,16 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>135674</v>
-      </c>
-      <c r="D549">
-        <v>21259.81</v>
+      <c r="C549" t="s">
+        <v>570</v>
+      </c>
+      <c r="D549" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9848,16 +9851,16 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>569</v>
-      </c>
-      <c r="D552" t="s">
-        <v>578</v>
+      <c r="C552">
+        <v>163394</v>
+      </c>
+      <c r="D552">
+        <v>17694.94</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9868,38 +9871,38 @@
         <v>554</v>
       </c>
       <c r="C553" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D553" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554">
-        <v>161272</v>
-      </c>
-      <c r="D554">
-        <v>22229.17</v>
+      <c r="C554" t="s">
+        <v>571</v>
+      </c>
+      <c r="D554" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>571</v>
-      </c>
-      <c r="D555" t="s">
-        <v>580</v>
+      <c r="C555">
+        <v>157558.5</v>
+      </c>
+      <c r="D555">
+        <v>17043.14</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9913,7 +9916,7 @@
         <v>572</v>
       </c>
       <c r="D556" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9927,7 +9930,7 @@
         <v>572</v>
       </c>
       <c r="D557" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9941,7 +9944,7 @@
         <v>573</v>
       </c>
       <c r="D558" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9955,35 +9958,35 @@
         <v>574</v>
       </c>
       <c r="D559" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560">
-        <v>142704.5</v>
-      </c>
-      <c r="D560">
-        <v>16481.84</v>
+      <c r="C560" t="s">
+        <v>575</v>
+      </c>
+      <c r="D560" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561">
-        <v>149093</v>
-      </c>
-      <c r="D561">
-        <v>16329.75</v>
+      <c r="C561" t="s">
+        <v>576</v>
+      </c>
+      <c r="D561" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -10016,44 +10019,44 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
-      <c r="C564" t="s">
-        <v>575</v>
-      </c>
-      <c r="D564" t="s">
-        <v>585</v>
+      <c r="C564">
+        <v>141113</v>
+      </c>
+      <c r="D564">
+        <v>15300.03</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565" t="s">
-        <v>576</v>
-      </c>
-      <c r="D565" t="s">
-        <v>586</v>
+      <c r="C565">
+        <v>139521.5</v>
+      </c>
+      <c r="D565">
+        <v>15108.97</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566" t="s">
-        <v>577</v>
-      </c>
-      <c r="D566" t="s">
-        <v>587</v>
+      <c r="C566">
+        <v>137399.5</v>
+      </c>
+      <c r="D566">
+        <v>14866.47</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10068,6 +10071,20 @@
       </c>
       <c r="D567">
         <v>16879.27</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4">
+      <c r="A568" s="1">
+        <v>587</v>
+      </c>
+      <c r="B568" t="s">
+        <v>569</v>
+      </c>
+      <c r="C568" t="s">
+        <v>577</v>
+      </c>
+      <c r="D568" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="587">
   <si>
     <t>Date</t>
   </si>
@@ -1726,61 +1726,55 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>144914</t>
-  </si>
-  <si>
-    <t>143032</t>
-  </si>
-  <si>
-    <t>136445</t>
-  </si>
-  <si>
-    <t>133151.5</t>
-  </si>
-  <si>
-    <t>128446.5</t>
-  </si>
-  <si>
-    <t>126564.5</t>
-  </si>
-  <si>
-    <t>125153</t>
-  </si>
-  <si>
-    <t>126500</t>
-  </si>
-  <si>
-    <t>18853.37</t>
-  </si>
-  <si>
-    <t>18855.31</t>
-  </si>
-  <si>
-    <t>18651.57</t>
-  </si>
-  <si>
-    <t>18659.82</t>
-  </si>
-  <si>
-    <t>17770.88</t>
-  </si>
-  <si>
-    <t>17754.42</t>
-  </si>
-  <si>
-    <t>17321.28</t>
-  </si>
-  <si>
-    <t>16740.96</t>
-  </si>
-  <si>
-    <t>16481.84</t>
-  </si>
-  <si>
-    <t>16329.75</t>
-  </si>
-  <si>
-    <t>16451.17</t>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>135674</t>
+  </si>
+  <si>
+    <t>130828.5</t>
+  </si>
+  <si>
+    <t>127745</t>
+  </si>
+  <si>
+    <t>124661.5</t>
+  </si>
+  <si>
+    <t>117173</t>
+  </si>
+  <si>
+    <t>115851.5</t>
+  </si>
+  <si>
+    <t>123500</t>
+  </si>
+  <si>
+    <t>17651.24</t>
+  </si>
+  <si>
+    <t>17694.94</t>
+  </si>
+  <si>
+    <t>17043.14</t>
+  </si>
+  <si>
+    <t>16637.77</t>
+  </si>
+  <si>
+    <t>16622.36</t>
+  </si>
+  <si>
+    <t>16216.84</t>
+  </si>
+  <si>
+    <t>15306.36</t>
+  </si>
+  <si>
+    <t>15108.97</t>
+  </si>
+  <si>
+    <t>16014.42</t>
   </si>
 </sst>
 </file>
@@ -2138,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D568"/>
+  <dimension ref="A1:D569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9781,13 +9775,13 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
       <c r="C547" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D547" t="s">
         <v>578</v>
@@ -9809,16 +9803,16 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>570</v>
-      </c>
-      <c r="D549" t="s">
-        <v>579</v>
+      <c r="C549">
+        <v>144914</v>
+      </c>
+      <c r="D549">
+        <v>18855.31</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9851,156 +9845,156 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>163394</v>
-      </c>
-      <c r="D552">
-        <v>17694.94</v>
+      <c r="C552" t="s">
+        <v>571</v>
+      </c>
+      <c r="D552" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553" t="s">
-        <v>571</v>
-      </c>
-      <c r="D553" t="s">
-        <v>580</v>
+      <c r="C553">
+        <v>143032</v>
+      </c>
+      <c r="D553">
+        <v>18651.57</v>
       </c>
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554" t="s">
-        <v>571</v>
-      </c>
-      <c r="D554" t="s">
-        <v>581</v>
+      <c r="C554">
+        <v>143032</v>
+      </c>
+      <c r="D554">
+        <v>18659.82</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555">
-        <v>157558.5</v>
-      </c>
-      <c r="D555">
-        <v>17043.14</v>
+      <c r="C555" t="s">
+        <v>572</v>
+      </c>
+      <c r="D555" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D556" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D557" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D558" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559" t="s">
-        <v>574</v>
-      </c>
-      <c r="D559" t="s">
-        <v>585</v>
+      <c r="C559">
+        <v>128446.5</v>
+      </c>
+      <c r="D559">
+        <v>16740.96</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560" t="s">
-        <v>575</v>
-      </c>
-      <c r="D560" t="s">
-        <v>586</v>
+      <c r="C560">
+        <v>126564.5</v>
+      </c>
+      <c r="D560">
+        <v>16481.84</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561" t="s">
-        <v>576</v>
-      </c>
-      <c r="D561" t="s">
-        <v>587</v>
+      <c r="C561">
+        <v>125153</v>
+      </c>
+      <c r="D561">
+        <v>16329.75</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562">
-        <v>125153</v>
-      </c>
-      <c r="D562">
-        <v>19476.08</v>
+      <c r="C562" t="s">
+        <v>575</v>
+      </c>
+      <c r="D562" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -10033,16 +10027,16 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565">
-        <v>139521.5</v>
-      </c>
-      <c r="D565">
-        <v>15108.97</v>
+      <c r="C565" t="s">
+        <v>576</v>
+      </c>
+      <c r="D565" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10075,16 +10069,30 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
+      <c r="C568">
+        <v>126500</v>
+      </c>
+      <c r="D568">
+        <v>16451.17</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4">
+      <c r="A569" s="1">
+        <v>589</v>
+      </c>
+      <c r="B569" t="s">
+        <v>570</v>
+      </c>
+      <c r="C569" t="s">
         <v>577</v>
       </c>
-      <c r="D568" t="s">
-        <v>588</v>
+      <c r="D569" t="s">
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="589">
   <si>
     <t>Date</t>
   </si>
@@ -1729,10 +1729,13 @@
     <t>2026-06-25</t>
   </si>
   <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
     <t>135674</t>
   </si>
   <si>
-    <t>130828.5</t>
+    <t>133912</t>
   </si>
   <si>
     <t>127745</t>
@@ -1741,40 +1744,43 @@
     <t>124661.5</t>
   </si>
   <si>
+    <t>120256.5</t>
+  </si>
+  <si>
     <t>117173</t>
   </si>
   <si>
-    <t>115851.5</t>
-  </si>
-  <si>
-    <t>123500</t>
-  </si>
-  <si>
-    <t>17651.24</t>
-  </si>
-  <si>
-    <t>17694.94</t>
-  </si>
-  <si>
-    <t>17043.14</t>
-  </si>
-  <si>
-    <t>16637.77</t>
-  </si>
-  <si>
-    <t>16622.36</t>
-  </si>
-  <si>
-    <t>16216.84</t>
-  </si>
-  <si>
-    <t>15306.36</t>
-  </si>
-  <si>
-    <t>15108.97</t>
-  </si>
-  <si>
-    <t>16014.42</t>
+    <t>114089.5</t>
+  </si>
+  <si>
+    <t>121500</t>
+  </si>
+  <si>
+    <t>21302.74</t>
+  </si>
+  <si>
+    <t>21076.27</t>
+  </si>
+  <si>
+    <t>20081.09</t>
+  </si>
+  <si>
+    <t>20062.49</t>
+  </si>
+  <si>
+    <t>19573.04</t>
+  </si>
+  <si>
+    <t>18917.29</t>
+  </si>
+  <si>
+    <t>18467.04</t>
+  </si>
+  <si>
+    <t>17943.21</t>
+  </si>
+  <si>
+    <t>17828.06</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D569"/>
+  <dimension ref="A1:D570"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9775,30 +9781,30 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547" s="1">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B547" t="s">
         <v>548</v>
       </c>
-      <c r="C547" t="s">
-        <v>571</v>
-      </c>
-      <c r="D547" t="s">
-        <v>578</v>
+      <c r="C547">
+        <v>135674</v>
+      </c>
+      <c r="D547">
+        <v>17651.24</v>
       </c>
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548">
-        <v>135674</v>
-      </c>
-      <c r="D548">
-        <v>21256.06</v>
+      <c r="C548" t="s">
+        <v>572</v>
+      </c>
+      <c r="D548" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9845,30 +9851,30 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>571</v>
-      </c>
-      <c r="D552" t="s">
-        <v>579</v>
+      <c r="C552">
+        <v>135674</v>
+      </c>
+      <c r="D552">
+        <v>17694.94</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553">
-        <v>143032</v>
-      </c>
-      <c r="D553">
-        <v>18651.57</v>
+      <c r="C553" t="s">
+        <v>573</v>
+      </c>
+      <c r="D553" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9887,16 +9893,16 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>572</v>
-      </c>
-      <c r="D555" t="s">
-        <v>580</v>
+      <c r="C555">
+        <v>130828.5</v>
+      </c>
+      <c r="D555">
+        <v>17043.14</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9907,10 +9913,10 @@
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D556" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9921,10 +9927,10 @@
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D557" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9935,24 +9941,24 @@
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D558" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559">
-        <v>128446.5</v>
-      </c>
-      <c r="D559">
-        <v>16740.96</v>
+      <c r="C559" t="s">
+        <v>576</v>
+      </c>
+      <c r="D559" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9985,30 +9991,30 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562" t="s">
-        <v>575</v>
-      </c>
-      <c r="D562" t="s">
-        <v>584</v>
+      <c r="C562">
+        <v>117173</v>
+      </c>
+      <c r="D562">
+        <v>15306.36</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>561</v>
+        <v>583</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563">
-        <v>141113</v>
-      </c>
-      <c r="D563">
-        <v>19468.61</v>
+      <c r="C563" t="s">
+        <v>577</v>
+      </c>
+      <c r="D563" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10027,30 +10033,30 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565" t="s">
-        <v>576</v>
-      </c>
-      <c r="D565" t="s">
-        <v>585</v>
+      <c r="C565">
+        <v>115851.5</v>
+      </c>
+      <c r="D565">
+        <v>15108.97</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566">
-        <v>137399.5</v>
-      </c>
-      <c r="D566">
-        <v>14866.47</v>
+      <c r="C566" t="s">
+        <v>578</v>
+      </c>
+      <c r="D566" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10083,16 +10089,30 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569" t="s">
-        <v>577</v>
-      </c>
-      <c r="D569" t="s">
-        <v>586</v>
+      <c r="C569">
+        <v>123500</v>
+      </c>
+      <c r="D569">
+        <v>16014.42</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4">
+      <c r="A570" s="1">
+        <v>590</v>
+      </c>
+      <c r="B570" t="s">
+        <v>571</v>
+      </c>
+      <c r="C570" t="s">
+        <v>579</v>
+      </c>
+      <c r="D570" t="s">
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="590">
   <si>
     <t>Date</t>
   </si>
@@ -1732,55 +1732,58 @@
     <t>2026-06-26</t>
   </si>
   <si>
-    <t>135674</t>
-  </si>
-  <si>
-    <t>133912</t>
-  </si>
-  <si>
-    <t>127745</t>
-  </si>
-  <si>
-    <t>124661.5</t>
-  </si>
-  <si>
-    <t>120256.5</t>
-  </si>
-  <si>
-    <t>117173</t>
-  </si>
-  <si>
-    <t>114089.5</t>
-  </si>
-  <si>
-    <t>121500</t>
-  </si>
-  <si>
-    <t>21302.74</t>
-  </si>
-  <si>
-    <t>21076.27</t>
+    <t>144914</t>
+  </si>
+  <si>
+    <t>136445</t>
+  </si>
+  <si>
+    <t>126564.5</t>
+  </si>
+  <si>
+    <t>125153</t>
+  </si>
+  <si>
+    <t>121859.5</t>
+  </si>
+  <si>
+    <t>119036.5</t>
+  </si>
+  <si>
+    <t>116213.5</t>
+  </si>
+  <si>
+    <t>21306.5</t>
+  </si>
+  <si>
+    <t>21357.05</t>
   </si>
   <si>
     <t>20081.09</t>
   </si>
   <si>
-    <t>20062.49</t>
-  </si>
-  <si>
-    <t>19573.04</t>
-  </si>
-  <si>
-    <t>18917.29</t>
+    <t>18624.48</t>
+  </si>
+  <si>
+    <t>18452.61</t>
+  </si>
+  <si>
+    <t>18474.13</t>
   </si>
   <si>
     <t>18467.04</t>
   </si>
   <si>
-    <t>17943.21</t>
-  </si>
-  <si>
-    <t>17828.06</t>
+    <t>18466.5</t>
+  </si>
+  <si>
+    <t>17948.23</t>
+  </si>
+  <si>
+    <t>17493.02</t>
+  </si>
+  <si>
+    <t>17028.62</t>
   </si>
 </sst>
 </file>
@@ -9795,30 +9798,30 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548" s="1">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B548" t="s">
         <v>549</v>
       </c>
-      <c r="C548" t="s">
-        <v>572</v>
-      </c>
-      <c r="D548" t="s">
-        <v>580</v>
+      <c r="C548">
+        <v>135674</v>
+      </c>
+      <c r="D548">
+        <v>21302.74</v>
       </c>
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549">
-        <v>144914</v>
-      </c>
-      <c r="D549">
-        <v>18855.31</v>
+      <c r="C549" t="s">
+        <v>572</v>
+      </c>
+      <c r="D549" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9851,30 +9854,30 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552">
-        <v>135674</v>
-      </c>
-      <c r="D552">
-        <v>17694.94</v>
+      <c r="C552" t="s">
+        <v>572</v>
+      </c>
+      <c r="D552" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="553" spans="1:4">
       <c r="A553" s="1">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="B553" t="s">
         <v>554</v>
       </c>
-      <c r="C553" t="s">
-        <v>573</v>
-      </c>
-      <c r="D553" t="s">
-        <v>581</v>
+      <c r="C553">
+        <v>133912</v>
+      </c>
+      <c r="D553">
+        <v>21076.27</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9913,94 +9916,94 @@
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D556" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
-      <c r="C557" t="s">
-        <v>574</v>
-      </c>
-      <c r="D557" t="s">
-        <v>583</v>
+      <c r="C557">
+        <v>127745</v>
+      </c>
+      <c r="D557">
+        <v>20062.49</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558" t="s">
-        <v>575</v>
-      </c>
-      <c r="D558" t="s">
-        <v>584</v>
+      <c r="C558">
+        <v>124661.5</v>
+      </c>
+      <c r="D558">
+        <v>19573.04</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559" t="s">
-        <v>576</v>
-      </c>
-      <c r="D559" t="s">
-        <v>585</v>
+      <c r="C559">
+        <v>120256.5</v>
+      </c>
+      <c r="D559">
+        <v>18917.29</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560">
-        <v>126564.5</v>
-      </c>
-      <c r="D560">
-        <v>16481.84</v>
+      <c r="C560" t="s">
+        <v>574</v>
+      </c>
+      <c r="D560" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>559</v>
+        <v>581</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561">
-        <v>125153</v>
-      </c>
-      <c r="D561">
-        <v>16329.75</v>
+      <c r="C561" t="s">
+        <v>575</v>
+      </c>
+      <c r="D561" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>560</v>
+        <v>582</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562">
-        <v>117173</v>
-      </c>
-      <c r="D562">
-        <v>15306.36</v>
+      <c r="C562" t="s">
+        <v>575</v>
+      </c>
+      <c r="D562" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -10011,24 +10014,24 @@
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D563" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
-      <c r="C564">
-        <v>141113</v>
-      </c>
-      <c r="D564">
-        <v>15300.03</v>
+      <c r="C564" t="s">
+        <v>575</v>
+      </c>
+      <c r="D564" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -10047,72 +10050,72 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566" t="s">
-        <v>578</v>
-      </c>
-      <c r="D566" t="s">
-        <v>587</v>
+      <c r="C566">
+        <v>114089.5</v>
+      </c>
+      <c r="D566">
+        <v>17943.21</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567">
-        <v>129500</v>
-      </c>
-      <c r="D567">
-        <v>16879.27</v>
+      <c r="C567" t="s">
+        <v>576</v>
+      </c>
+      <c r="D567" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568">
-        <v>126500</v>
-      </c>
-      <c r="D568">
-        <v>16451.17</v>
+      <c r="C568" t="s">
+        <v>577</v>
+      </c>
+      <c r="D568" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569">
-        <v>123500</v>
-      </c>
-      <c r="D569">
-        <v>16014.42</v>
+      <c r="C569" t="s">
+        <v>578</v>
+      </c>
+      <c r="D569" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570" t="s">
-        <v>579</v>
-      </c>
-      <c r="D570" t="s">
-        <v>588</v>
+      <c r="C570">
+        <v>121500</v>
+      </c>
+      <c r="D570">
+        <v>17828.06</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="594">
   <si>
     <t>Date</t>
   </si>
@@ -1732,58 +1732,70 @@
     <t>2026-06-26</t>
   </si>
   <si>
-    <t>144914</t>
-  </si>
-  <si>
-    <t>136445</t>
-  </si>
-  <si>
-    <t>126564.5</t>
-  </si>
-  <si>
-    <t>125153</t>
-  </si>
-  <si>
-    <t>121859.5</t>
-  </si>
-  <si>
-    <t>119036.5</t>
-  </si>
-  <si>
-    <t>116213.5</t>
-  </si>
-  <si>
-    <t>21306.5</t>
-  </si>
-  <si>
-    <t>21357.05</t>
-  </si>
-  <si>
-    <t>20081.09</t>
-  </si>
-  <si>
-    <t>18624.48</t>
-  </si>
-  <si>
-    <t>18452.61</t>
-  </si>
-  <si>
-    <t>18474.13</t>
-  </si>
-  <si>
-    <t>18467.04</t>
-  </si>
-  <si>
-    <t>18466.5</t>
-  </si>
-  <si>
-    <t>17948.23</t>
-  </si>
-  <si>
-    <t>17493.02</t>
-  </si>
-  <si>
-    <t>17028.62</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>161272</t>
+  </si>
+  <si>
+    <t>157558.5</t>
+  </si>
+  <si>
+    <t>153845</t>
+  </si>
+  <si>
+    <t>150131.5</t>
+  </si>
+  <si>
+    <t>144826.5</t>
+  </si>
+  <si>
+    <t>141113</t>
+  </si>
+  <si>
+    <t>139521.5</t>
+  </si>
+  <si>
+    <t>137399.5</t>
+  </si>
+  <si>
+    <t>119500</t>
+  </si>
+  <si>
+    <t>25118.97</t>
+  </si>
+  <si>
+    <t>24505.17</t>
+  </si>
+  <si>
+    <t>23922.32</t>
+  </si>
+  <si>
+    <t>23900.16</t>
+  </si>
+  <si>
+    <t>23317.09</t>
+  </si>
+  <si>
+    <t>22535.9</t>
+  </si>
+  <si>
+    <t>22007.97</t>
+  </si>
+  <si>
+    <t>21999.53</t>
+  </si>
+  <si>
+    <t>21998.88</t>
+  </si>
+  <si>
+    <t>21724.17</t>
+  </si>
+  <si>
+    <t>21375.49</t>
+  </si>
+  <si>
+    <t>17526.62</t>
   </si>
 </sst>
 </file>
@@ -2141,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D570"/>
+  <dimension ref="A1:D571"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9812,16 +9824,16 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549" s="1">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="B549" t="s">
         <v>550</v>
       </c>
-      <c r="C549" t="s">
-        <v>572</v>
-      </c>
-      <c r="D549" t="s">
-        <v>579</v>
+      <c r="C549">
+        <v>144914</v>
+      </c>
+      <c r="D549">
+        <v>21306.5</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9854,16 +9866,16 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552" s="1">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="B552" t="s">
         <v>553</v>
       </c>
-      <c r="C552" t="s">
-        <v>572</v>
-      </c>
-      <c r="D552" t="s">
-        <v>580</v>
+      <c r="C552">
+        <v>144914</v>
+      </c>
+      <c r="D552">
+        <v>21357.05</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9882,226 +9894,226 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554">
-        <v>143032</v>
-      </c>
-      <c r="D554">
-        <v>18659.82</v>
+      <c r="C554" t="s">
+        <v>573</v>
+      </c>
+      <c r="D554" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555">
-        <v>130828.5</v>
-      </c>
-      <c r="D555">
-        <v>17043.14</v>
+      <c r="C555" t="s">
+        <v>574</v>
+      </c>
+      <c r="D555" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D556" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
-      <c r="C557">
-        <v>127745</v>
-      </c>
-      <c r="D557">
-        <v>20062.49</v>
+      <c r="C557" t="s">
+        <v>575</v>
+      </c>
+      <c r="D557" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558">
-        <v>124661.5</v>
-      </c>
-      <c r="D558">
-        <v>19573.04</v>
+      <c r="C558" t="s">
+        <v>576</v>
+      </c>
+      <c r="D558" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559">
-        <v>120256.5</v>
-      </c>
-      <c r="D559">
-        <v>18917.29</v>
+      <c r="C559" t="s">
+        <v>577</v>
+      </c>
+      <c r="D559" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560" t="s">
-        <v>574</v>
-      </c>
-      <c r="D560" t="s">
-        <v>582</v>
+      <c r="C560">
+        <v>126564.5</v>
+      </c>
+      <c r="D560">
+        <v>18624.48</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561" t="s">
-        <v>575</v>
-      </c>
-      <c r="D561" t="s">
-        <v>583</v>
+      <c r="C561">
+        <v>125153</v>
+      </c>
+      <c r="D561">
+        <v>18452.61</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D562" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D563" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D564" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565">
-        <v>115851.5</v>
-      </c>
-      <c r="D565">
-        <v>15108.97</v>
+      <c r="C565" t="s">
+        <v>579</v>
+      </c>
+      <c r="D565" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566">
-        <v>114089.5</v>
-      </c>
-      <c r="D566">
-        <v>17943.21</v>
+      <c r="C566" t="s">
+        <v>580</v>
+      </c>
+      <c r="D566" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567" t="s">
-        <v>576</v>
-      </c>
-      <c r="D567" t="s">
-        <v>587</v>
+      <c r="C567">
+        <v>121859.5</v>
+      </c>
+      <c r="D567">
+        <v>17948.23</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
-        <v>577</v>
-      </c>
-      <c r="D568" t="s">
-        <v>588</v>
+      <c r="C568">
+        <v>119036.5</v>
+      </c>
+      <c r="D568">
+        <v>17493.02</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569" t="s">
-        <v>578</v>
-      </c>
-      <c r="D569" t="s">
-        <v>589</v>
+      <c r="C569">
+        <v>116213.5</v>
+      </c>
+      <c r="D569">
+        <v>17028.62</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10116,6 +10128,20 @@
       </c>
       <c r="D570">
         <v>17828.06</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4">
+      <c r="A571" s="1">
+        <v>588</v>
+      </c>
+      <c r="B571" t="s">
+        <v>572</v>
+      </c>
+      <c r="C571" t="s">
+        <v>581</v>
+      </c>
+      <c r="D571" t="s">
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="593">
   <si>
     <t>Date</t>
   </si>
@@ -1735,10 +1735,7 @@
     <t>2026-06-29</t>
   </si>
   <si>
-    <t>161272</t>
-  </si>
-  <si>
-    <t>157558.5</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>153845</t>
@@ -1750,52 +1747,52 @@
     <t>144826.5</t>
   </si>
   <si>
+    <t>142704.5</t>
+  </si>
+  <si>
     <t>141113</t>
   </si>
   <si>
-    <t>139521.5</t>
-  </si>
-  <si>
-    <t>137399.5</t>
-  </si>
-  <si>
-    <t>119500</t>
-  </si>
-  <si>
-    <t>25118.97</t>
-  </si>
-  <si>
-    <t>24505.17</t>
-  </si>
-  <si>
-    <t>23922.32</t>
-  </si>
-  <si>
-    <t>23900.16</t>
-  </si>
-  <si>
-    <t>23317.09</t>
-  </si>
-  <si>
-    <t>22535.9</t>
-  </si>
-  <si>
-    <t>22007.97</t>
-  </si>
-  <si>
-    <t>21999.53</t>
-  </si>
-  <si>
-    <t>21998.88</t>
-  </si>
-  <si>
-    <t>21724.17</t>
-  </si>
-  <si>
-    <t>21375.49</t>
-  </si>
-  <si>
-    <t>17526.62</t>
+    <t>128911.5</t>
+  </si>
+  <si>
+    <t>126789.5</t>
+  </si>
+  <si>
+    <t>118500</t>
+  </si>
+  <si>
+    <t>18800.68</t>
+  </si>
+  <si>
+    <t>18783.27</t>
+  </si>
+  <si>
+    <t>18325.03</t>
+  </si>
+  <si>
+    <t>17711.09</t>
+  </si>
+  <si>
+    <t>17436.94</t>
+  </si>
+  <si>
+    <t>17276.04</t>
+  </si>
+  <si>
+    <t>17296.18</t>
+  </si>
+  <si>
+    <t>17289.55</t>
+  </si>
+  <si>
+    <t>15706.52</t>
+  </si>
+  <si>
+    <t>15440.95</t>
+  </si>
+  <si>
+    <t>17390.67</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D571"/>
+  <dimension ref="A1:D572"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9894,119 +9891,119 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554" s="1">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="B554" t="s">
         <v>555</v>
       </c>
-      <c r="C554" t="s">
-        <v>573</v>
-      </c>
-      <c r="D554" t="s">
-        <v>582</v>
+      <c r="C554">
+        <v>161272</v>
+      </c>
+      <c r="D554">
+        <v>25118.97</v>
       </c>
     </row>
     <row r="555" spans="1:4">
       <c r="A555" s="1">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="B555" t="s">
         <v>556</v>
       </c>
-      <c r="C555" t="s">
-        <v>574</v>
-      </c>
-      <c r="D555" t="s">
-        <v>583</v>
+      <c r="C555">
+        <v>157558.5</v>
+      </c>
+      <c r="D555">
+        <v>24505.17</v>
       </c>
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
       <c r="C556" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D556" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D557" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D558" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D559" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560">
-        <v>126564.5</v>
-      </c>
-      <c r="D560">
-        <v>18624.48</v>
+      <c r="C560" t="s">
+        <v>577</v>
+      </c>
+      <c r="D560" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561">
-        <v>125153</v>
-      </c>
-      <c r="D561">
-        <v>18452.61</v>
+      <c r="C561" t="s">
+        <v>578</v>
+      </c>
+      <c r="D561" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
@@ -10020,7 +10017,7 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
@@ -10034,44 +10031,44 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
-      <c r="C564" t="s">
-        <v>578</v>
-      </c>
-      <c r="D564" t="s">
-        <v>590</v>
+      <c r="C564">
+        <v>141113</v>
+      </c>
+      <c r="D564">
+        <v>21998.88</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565" t="s">
-        <v>579</v>
-      </c>
-      <c r="D565" t="s">
-        <v>591</v>
+      <c r="C565">
+        <v>139521.5</v>
+      </c>
+      <c r="D565">
+        <v>21724.17</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566" t="s">
-        <v>580</v>
-      </c>
-      <c r="D566" t="s">
-        <v>592</v>
+      <c r="C566">
+        <v>137399.5</v>
+      </c>
+      <c r="D566">
+        <v>21375.49</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10118,30 +10115,44 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570">
-        <v>121500</v>
-      </c>
-      <c r="D570">
-        <v>17828.06</v>
+      <c r="C570" t="s">
+        <v>579</v>
+      </c>
+      <c r="D570" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
       <c r="C571" t="s">
+        <v>580</v>
+      </c>
+      <c r="D571" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4">
+      <c r="A572" s="1">
+        <v>590</v>
+      </c>
+      <c r="B572" t="s">
+        <v>573</v>
+      </c>
+      <c r="C572" t="s">
         <v>581</v>
       </c>
-      <c r="D571" t="s">
-        <v>593</v>
+      <c r="D572" t="s">
+        <v>592</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="594">
   <si>
     <t>Date</t>
   </si>
@@ -1738,61 +1738,64 @@
     <t>2026-06-30</t>
   </si>
   <si>
-    <t>153845</t>
-  </si>
-  <si>
-    <t>150131.5</t>
-  </si>
-  <si>
-    <t>144826.5</t>
-  </si>
-  <si>
-    <t>142704.5</t>
-  </si>
-  <si>
-    <t>141113</t>
-  </si>
-  <si>
-    <t>128911.5</t>
-  </si>
-  <si>
-    <t>126789.5</t>
-  </si>
-  <si>
-    <t>118500</t>
-  </si>
-  <si>
-    <t>18800.68</t>
-  </si>
-  <si>
-    <t>18783.27</t>
-  </si>
-  <si>
-    <t>18325.03</t>
-  </si>
-  <si>
-    <t>17711.09</t>
-  </si>
-  <si>
-    <t>17436.94</t>
-  </si>
-  <si>
-    <t>17276.04</t>
-  </si>
-  <si>
-    <t>17296.18</t>
-  </si>
-  <si>
-    <t>17289.55</t>
-  </si>
-  <si>
-    <t>15706.52</t>
-  </si>
-  <si>
-    <t>15440.95</t>
-  </si>
-  <si>
-    <t>17390.67</t>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>136445</t>
+  </si>
+  <si>
+    <t>133151.5</t>
+  </si>
+  <si>
+    <t>128446.5</t>
+  </si>
+  <si>
+    <t>126564.5</t>
+  </si>
+  <si>
+    <t>125153</t>
+  </si>
+  <si>
+    <t>123741.5</t>
+  </si>
+  <si>
+    <t>111508.5</t>
+  </si>
+  <si>
+    <t>117000</t>
+  </si>
+  <si>
+    <t>23900.16</t>
+  </si>
+  <si>
+    <t>23317.09</t>
+  </si>
+  <si>
+    <t>22535.9</t>
+  </si>
+  <si>
+    <t>22187.08</t>
+  </si>
+  <si>
+    <t>21982.34</t>
+  </si>
+  <si>
+    <t>22007.97</t>
+  </si>
+  <si>
+    <t>21999.53</t>
+  </si>
+  <si>
+    <t>21998.88</t>
+  </si>
+  <si>
+    <t>21724.17</t>
+  </si>
+  <si>
+    <t>19494.94</t>
+  </si>
+  <si>
+    <t>17197.03</t>
   </si>
 </sst>
 </file>
@@ -2150,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D572"/>
+  <dimension ref="A1:D573"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9919,27 +9922,27 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556" s="1">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="B556" t="s">
         <v>557</v>
       </c>
-      <c r="C556" t="s">
-        <v>574</v>
-      </c>
-      <c r="D556" t="s">
-        <v>582</v>
+      <c r="C556">
+        <v>153845</v>
+      </c>
+      <c r="D556">
+        <v>18800.68</v>
       </c>
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
       <c r="C557" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D557" t="s">
         <v>583</v>
@@ -9947,13 +9950,13 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
       <c r="C558" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D558" t="s">
         <v>584</v>
@@ -9961,13 +9964,13 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D559" t="s">
         <v>585</v>
@@ -9975,13 +9978,13 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
       <c r="C560" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D560" t="s">
         <v>586</v>
@@ -9989,13 +9992,13 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
       <c r="C561" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D561" t="s">
         <v>587</v>
@@ -10003,13 +10006,13 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D562" t="s">
         <v>588</v>
@@ -10017,13 +10020,13 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D563" t="s">
         <v>589</v>
@@ -10031,30 +10034,30 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
-      <c r="C564">
-        <v>141113</v>
-      </c>
-      <c r="D564">
-        <v>21998.88</v>
+      <c r="C564" t="s">
+        <v>579</v>
+      </c>
+      <c r="D564" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565">
-        <v>139521.5</v>
-      </c>
-      <c r="D565">
-        <v>21724.17</v>
+      <c r="C565" t="s">
+        <v>580</v>
+      </c>
+      <c r="D565" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10115,35 +10118,35 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570" t="s">
-        <v>579</v>
-      </c>
-      <c r="D570" t="s">
-        <v>590</v>
+      <c r="C570">
+        <v>128911.5</v>
+      </c>
+      <c r="D570">
+        <v>15706.52</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>589</v>
+        <v>569</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
-      <c r="C571" t="s">
-        <v>580</v>
-      </c>
-      <c r="D571" t="s">
-        <v>591</v>
+      <c r="C571">
+        <v>126789.5</v>
+      </c>
+      <c r="D571">
+        <v>15440.95</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
@@ -10153,6 +10156,20 @@
       </c>
       <c r="D572" t="s">
         <v>592</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4">
+      <c r="A573" s="1">
+        <v>592</v>
+      </c>
+      <c r="B573" t="s">
+        <v>574</v>
+      </c>
+      <c r="C573" t="s">
+        <v>582</v>
+      </c>
+      <c r="D573" t="s">
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="595">
   <si>
     <t>Date</t>
   </si>
@@ -1741,7 +1741,7 @@
     <t>2026-07-01</t>
   </si>
   <si>
-    <t>136445</t>
+    <t>2026-07-02</t>
   </si>
   <si>
     <t>133151.5</t>
@@ -1759,43 +1759,46 @@
     <t>123741.5</t>
   </si>
   <si>
-    <t>111508.5</t>
-  </si>
-  <si>
-    <t>117000</t>
-  </si>
-  <si>
-    <t>23900.16</t>
-  </si>
-  <si>
-    <t>23317.09</t>
-  </si>
-  <si>
-    <t>22535.9</t>
-  </si>
-  <si>
-    <t>22187.08</t>
-  </si>
-  <si>
-    <t>21982.34</t>
-  </si>
-  <si>
-    <t>22007.97</t>
-  </si>
-  <si>
-    <t>21999.53</t>
-  </si>
-  <si>
-    <t>21998.88</t>
-  </si>
-  <si>
-    <t>21724.17</t>
-  </si>
-  <si>
-    <t>19494.94</t>
-  </si>
-  <si>
-    <t>17197.03</t>
+    <t>121859.5</t>
+  </si>
+  <si>
+    <t>110097</t>
+  </si>
+  <si>
+    <t>115000</t>
+  </si>
+  <si>
+    <t>18325.03</t>
+  </si>
+  <si>
+    <t>17711.09</t>
+  </si>
+  <si>
+    <t>17436.94</t>
+  </si>
+  <si>
+    <t>17276.04</t>
+  </si>
+  <si>
+    <t>17296.18</t>
+  </si>
+  <si>
+    <t>17289.55</t>
+  </si>
+  <si>
+    <t>17289.04</t>
+  </si>
+  <si>
+    <t>17073.14</t>
+  </si>
+  <si>
+    <t>16799.11</t>
+  </si>
+  <si>
+    <t>15150.58</t>
+  </si>
+  <si>
+    <t>16894.62</t>
   </si>
 </sst>
 </file>
@@ -2153,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D573"/>
+  <dimension ref="A1:D574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9936,16 +9939,16 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557" s="1">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B557" t="s">
         <v>558</v>
       </c>
-      <c r="C557" t="s">
-        <v>575</v>
-      </c>
-      <c r="D557" t="s">
-        <v>583</v>
+      <c r="C557">
+        <v>136445</v>
+      </c>
+      <c r="D557">
+        <v>23900.16</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -10062,16 +10065,16 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>564</v>
+        <v>585</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566">
-        <v>137399.5</v>
-      </c>
-      <c r="D566">
-        <v>21375.49</v>
+      <c r="C566" t="s">
+        <v>581</v>
+      </c>
+      <c r="D566" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10146,16 +10149,16 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572" t="s">
-        <v>581</v>
-      </c>
-      <c r="D572" t="s">
-        <v>592</v>
+      <c r="C572">
+        <v>111508.5</v>
+      </c>
+      <c r="D572">
+        <v>19494.94</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10170,6 +10173,20 @@
       </c>
       <c r="D573" t="s">
         <v>593</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4">
+      <c r="A574" s="1">
+        <v>593</v>
+      </c>
+      <c r="B574" t="s">
+        <v>575</v>
+      </c>
+      <c r="C574" t="s">
+        <v>583</v>
+      </c>
+      <c r="D574" t="s">
+        <v>594</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="595">
   <si>
     <t>Date</t>
   </si>
@@ -1744,61 +1744,61 @@
     <t>2026-07-02</t>
   </si>
   <si>
-    <t>133151.5</t>
-  </si>
-  <si>
-    <t>128446.5</t>
-  </si>
-  <si>
-    <t>126564.5</t>
-  </si>
-  <si>
-    <t>125153</t>
-  </si>
-  <si>
-    <t>123741.5</t>
-  </si>
-  <si>
-    <t>121859.5</t>
-  </si>
-  <si>
-    <t>110097</t>
-  </si>
-  <si>
-    <t>115000</t>
-  </si>
-  <si>
-    <t>18325.03</t>
-  </si>
-  <si>
-    <t>17711.09</t>
-  </si>
-  <si>
-    <t>17436.94</t>
-  </si>
-  <si>
-    <t>17276.04</t>
-  </si>
-  <si>
-    <t>17296.18</t>
-  </si>
-  <si>
-    <t>17289.55</t>
-  </si>
-  <si>
-    <t>17289.04</t>
-  </si>
-  <si>
-    <t>17073.14</t>
-  </si>
-  <si>
-    <t>16799.11</t>
-  </si>
-  <si>
-    <t>15150.58</t>
-  </si>
-  <si>
-    <t>16894.62</t>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>153016.5</t>
+  </si>
+  <si>
+    <t>150774.5</t>
+  </si>
+  <si>
+    <t>149093</t>
+  </si>
+  <si>
+    <t>147411.5</t>
+  </si>
+  <si>
+    <t>145169.5</t>
+  </si>
+  <si>
+    <t>128915</t>
+  </si>
+  <si>
+    <t>112500</t>
+  </si>
+  <si>
+    <t>18917.29</t>
+  </si>
+  <si>
+    <t>18624.48</t>
+  </si>
+  <si>
+    <t>18452.61</t>
+  </si>
+  <si>
+    <t>18474.13</t>
+  </si>
+  <si>
+    <t>18467.04</t>
+  </si>
+  <si>
+    <t>18466.5</t>
+  </si>
+  <si>
+    <t>18235.9</t>
+  </si>
+  <si>
+    <t>17943.21</t>
+  </si>
+  <si>
+    <t>17948.23</t>
+  </si>
+  <si>
+    <t>15897.84</t>
+  </si>
+  <si>
+    <t>16539.25</t>
   </si>
 </sst>
 </file>
@@ -2156,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D574"/>
+  <dimension ref="A1:D575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9953,16 +9953,16 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558" t="s">
-        <v>576</v>
-      </c>
-      <c r="D558" t="s">
-        <v>584</v>
+      <c r="C558">
+        <v>133151.5</v>
+      </c>
+      <c r="D558">
+        <v>18325.03</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9976,7 +9976,7 @@
         <v>577</v>
       </c>
       <c r="D559" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9990,7 +9990,7 @@
         <v>578</v>
       </c>
       <c r="D560" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -10004,7 +10004,7 @@
         <v>579</v>
       </c>
       <c r="D561" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -10018,7 +10018,7 @@
         <v>579</v>
       </c>
       <c r="D562" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -10032,7 +10032,7 @@
         <v>579</v>
       </c>
       <c r="D563" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10046,7 +10046,7 @@
         <v>579</v>
       </c>
       <c r="D564" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -10060,7 +10060,7 @@
         <v>580</v>
       </c>
       <c r="D565" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10074,21 +10074,21 @@
         <v>581</v>
       </c>
       <c r="D566" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>565</v>
+        <v>586</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567">
-        <v>121859.5</v>
-      </c>
-      <c r="D567">
-        <v>17948.23</v>
+      <c r="C567" t="s">
+        <v>581</v>
+      </c>
+      <c r="D567" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10163,16 +10163,16 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>582</v>
-      </c>
-      <c r="D573" t="s">
-        <v>593</v>
+      <c r="C573">
+        <v>110097</v>
+      </c>
+      <c r="D573">
+        <v>15150.58</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10183,9 +10183,23 @@
         <v>575</v>
       </c>
       <c r="C574" t="s">
+        <v>582</v>
+      </c>
+      <c r="D574" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4">
+      <c r="A575" s="1">
+        <v>594</v>
+      </c>
+      <c r="B575" t="s">
+        <v>576</v>
+      </c>
+      <c r="C575" t="s">
         <v>583</v>
       </c>
-      <c r="D574" t="s">
+      <c r="D575" t="s">
         <v>594</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="598">
   <si>
     <t>Date</t>
   </si>
@@ -1747,27 +1747,36 @@
     <t>2026-07-03</t>
   </si>
   <si>
-    <t>153016.5</t>
-  </si>
-  <si>
-    <t>150774.5</t>
-  </si>
-  <si>
-    <t>149093</t>
-  </si>
-  <si>
-    <t>147411.5</t>
-  </si>
-  <si>
-    <t>145169.5</t>
-  </si>
-  <si>
-    <t>128915</t>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>124661.5</t>
+  </si>
+  <si>
+    <t>120256.5</t>
+  </si>
+  <si>
+    <t>118494.5</t>
+  </si>
+  <si>
+    <t>117173</t>
+  </si>
+  <si>
+    <t>115851.5</t>
+  </si>
+  <si>
+    <t>114089.5</t>
+  </si>
+  <si>
+    <t>111446.5</t>
   </si>
   <si>
     <t>112500</t>
   </si>
   <si>
+    <t>19573.04</t>
+  </si>
+  <si>
     <t>18917.29</t>
   </si>
   <si>
@@ -1795,10 +1804,10 @@
     <t>17948.23</t>
   </si>
   <si>
-    <t>15897.84</t>
-  </si>
-  <si>
-    <t>16539.25</t>
+    <t>17493.02</t>
+  </si>
+  <si>
+    <t>16547.28</t>
   </si>
 </sst>
 </file>
@@ -2156,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D575"/>
+  <dimension ref="A1:D576"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9953,156 +9962,156 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558">
-        <v>133151.5</v>
-      </c>
-      <c r="D558">
-        <v>18325.03</v>
+      <c r="C558" t="s">
+        <v>578</v>
+      </c>
+      <c r="D558" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
       <c r="C559" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D559" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
       <c r="C560" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D560" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
       <c r="C561" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D561" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D562" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D563" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D564" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D565" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D566" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D567" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568">
-        <v>119036.5</v>
-      </c>
-      <c r="D568">
-        <v>17493.02</v>
+      <c r="C568" t="s">
+        <v>584</v>
+      </c>
+      <c r="D568" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10177,30 +10186,44 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574" t="s">
-        <v>582</v>
-      </c>
-      <c r="D574" t="s">
-        <v>593</v>
+      <c r="C574">
+        <v>128915</v>
+      </c>
+      <c r="D574">
+        <v>15897.84</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575" t="s">
-        <v>583</v>
-      </c>
-      <c r="D575" t="s">
-        <v>594</v>
+      <c r="C575">
+        <v>112500</v>
+      </c>
+      <c r="D575">
+        <v>16539.25</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4">
+      <c r="A576" s="1">
+        <v>593</v>
+      </c>
+      <c r="B576" t="s">
+        <v>577</v>
+      </c>
+      <c r="C576" t="s">
+        <v>585</v>
+      </c>
+      <c r="D576" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="599">
   <si>
     <t>Date</t>
   </si>
@@ -1750,64 +1750,67 @@
     <t>2026-07-06</t>
   </si>
   <si>
-    <t>124661.5</t>
-  </si>
-  <si>
-    <t>120256.5</t>
-  </si>
-  <si>
-    <t>118494.5</t>
-  </si>
-  <si>
-    <t>117173</t>
-  </si>
-  <si>
-    <t>115851.5</t>
-  </si>
-  <si>
-    <t>114089.5</t>
-  </si>
-  <si>
-    <t>111446.5</t>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>126564.5</t>
+  </si>
+  <si>
+    <t>125153</t>
+  </si>
+  <si>
+    <t>123741.5</t>
+  </si>
+  <si>
+    <t>121859.5</t>
+  </si>
+  <si>
+    <t>111508.5</t>
+  </si>
+  <si>
+    <t>108215</t>
+  </si>
+  <si>
+    <t>105862.5</t>
   </si>
   <si>
     <t>112500</t>
   </si>
   <si>
-    <t>19573.04</t>
-  </si>
-  <si>
-    <t>18917.29</t>
-  </si>
-  <si>
-    <t>18624.48</t>
-  </si>
-  <si>
-    <t>18452.61</t>
-  </si>
-  <si>
-    <t>18474.13</t>
-  </si>
-  <si>
-    <t>18467.04</t>
-  </si>
-  <si>
-    <t>18466.5</t>
-  </si>
-  <si>
-    <t>18235.9</t>
-  </si>
-  <si>
-    <t>17943.21</t>
-  </si>
-  <si>
-    <t>17948.23</t>
-  </si>
-  <si>
-    <t>17493.02</t>
-  </si>
-  <si>
-    <t>16547.28</t>
+    <t>20999.54</t>
+  </si>
+  <si>
+    <t>20805.76</t>
+  </si>
+  <si>
+    <t>20830.02</t>
+  </si>
+  <si>
+    <t>20822.03</t>
+  </si>
+  <si>
+    <t>20821.42</t>
+  </si>
+  <si>
+    <t>20561.41</t>
+  </si>
+  <si>
+    <t>20231.4</t>
+  </si>
+  <si>
+    <t>20237.06</t>
+  </si>
+  <si>
+    <t>18451.5</t>
+  </si>
+  <si>
+    <t>17925.19</t>
+  </si>
+  <si>
+    <t>17548.15</t>
+  </si>
+  <si>
+    <t>16514.97</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D576"/>
+  <dimension ref="A1:D577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9962,156 +9965,156 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558" s="1">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="B558" t="s">
         <v>559</v>
       </c>
-      <c r="C558" t="s">
-        <v>578</v>
-      </c>
-      <c r="D558" t="s">
-        <v>586</v>
+      <c r="C558">
+        <v>124661.5</v>
+      </c>
+      <c r="D558">
+        <v>19573.04</v>
       </c>
     </row>
     <row r="559" spans="1:4">
       <c r="A559" s="1">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="B559" t="s">
         <v>560</v>
       </c>
-      <c r="C559" t="s">
-        <v>579</v>
-      </c>
-      <c r="D559" t="s">
-        <v>587</v>
+      <c r="C559">
+        <v>120256.5</v>
+      </c>
+      <c r="D559">
+        <v>18917.29</v>
       </c>
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
       <c r="C560" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D560" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
       <c r="C561" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D561" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
       <c r="C562" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D562" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D563" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D564" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D565" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D566" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D567" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
-        <v>584</v>
-      </c>
-      <c r="D568" t="s">
-        <v>596</v>
+      <c r="C568">
+        <v>111446.5</v>
+      </c>
+      <c r="D568">
+        <v>17493.02</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10158,16 +10161,16 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>570</v>
+        <v>590</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572">
-        <v>111508.5</v>
-      </c>
-      <c r="D572">
-        <v>19494.94</v>
+      <c r="C572" t="s">
+        <v>583</v>
+      </c>
+      <c r="D572" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10186,44 +10189,58 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574">
-        <v>128915</v>
-      </c>
-      <c r="D574">
-        <v>15897.84</v>
+      <c r="C574" t="s">
+        <v>584</v>
+      </c>
+      <c r="D574" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575">
-        <v>112500</v>
-      </c>
-      <c r="D575">
-        <v>16539.25</v>
+      <c r="C575" t="s">
+        <v>585</v>
+      </c>
+      <c r="D575" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576" t="s">
-        <v>585</v>
-      </c>
-      <c r="D576" t="s">
-        <v>597</v>
+      <c r="C576">
+        <v>112500</v>
+      </c>
+      <c r="D576">
+        <v>16547.28</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4">
+      <c r="A577" s="1">
+        <v>595</v>
+      </c>
+      <c r="B577" t="s">
+        <v>578</v>
+      </c>
+      <c r="C577" t="s">
+        <v>586</v>
+      </c>
+      <c r="D577" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="599">
   <si>
     <t>Date</t>
   </si>
@@ -1753,64 +1753,64 @@
     <t>2026-07-07</t>
   </si>
   <si>
-    <t>126564.5</t>
-  </si>
-  <si>
-    <t>125153</t>
-  </si>
-  <si>
-    <t>123741.5</t>
-  </si>
-  <si>
-    <t>121859.5</t>
-  </si>
-  <si>
-    <t>111508.5</t>
-  </si>
-  <si>
-    <t>108215</t>
-  </si>
-  <si>
-    <t>105862.5</t>
-  </si>
-  <si>
-    <t>112500</t>
-  </si>
-  <si>
-    <t>20999.54</t>
-  </si>
-  <si>
-    <t>20805.76</t>
-  </si>
-  <si>
-    <t>20830.02</t>
-  </si>
-  <si>
-    <t>20822.03</t>
-  </si>
-  <si>
-    <t>20821.42</t>
-  </si>
-  <si>
-    <t>20561.41</t>
-  </si>
-  <si>
-    <t>20231.4</t>
-  </si>
-  <si>
-    <t>20237.06</t>
-  </si>
-  <si>
-    <t>18451.5</t>
-  </si>
-  <si>
-    <t>17925.19</t>
-  </si>
-  <si>
-    <t>17548.15</t>
-  </si>
-  <si>
-    <t>16514.97</t>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>149093</t>
+  </si>
+  <si>
+    <t>147411.5</t>
+  </si>
+  <si>
+    <t>145169.5</t>
+  </si>
+  <si>
+    <t>141806.5</t>
+  </si>
+  <si>
+    <t>138443.5</t>
+  </si>
+  <si>
+    <t>136201.5</t>
+  </si>
+  <si>
+    <t>126112.5</t>
+  </si>
+  <si>
+    <t>111500</t>
+  </si>
+  <si>
+    <t>22007.97</t>
+  </si>
+  <si>
+    <t>21999.53</t>
+  </si>
+  <si>
+    <t>21998.88</t>
+  </si>
+  <si>
+    <t>21724.17</t>
+  </si>
+  <si>
+    <t>21375.49</t>
+  </si>
+  <si>
+    <t>21381.47</t>
+  </si>
+  <si>
+    <t>20839.19</t>
+  </si>
+  <si>
+    <t>20285.95</t>
+  </si>
+  <si>
+    <t>19985.25</t>
+  </si>
+  <si>
+    <t>18513.29</t>
+  </si>
+  <si>
+    <t>16368.17</t>
   </si>
 </sst>
 </file>
@@ -2168,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D577"/>
+  <dimension ref="A1:D578"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9993,35 +9993,35 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560" s="1">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="B560" t="s">
         <v>561</v>
       </c>
-      <c r="C560" t="s">
-        <v>579</v>
-      </c>
-      <c r="D560" t="s">
-        <v>587</v>
+      <c r="C560">
+        <v>126564.5</v>
+      </c>
+      <c r="D560">
+        <v>20999.54</v>
       </c>
     </row>
     <row r="561" spans="1:4">
       <c r="A561" s="1">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="B561" t="s">
         <v>562</v>
       </c>
-      <c r="C561" t="s">
-        <v>580</v>
-      </c>
-      <c r="D561" t="s">
-        <v>588</v>
+      <c r="C561">
+        <v>125153</v>
+      </c>
+      <c r="D561">
+        <v>20805.76</v>
       </c>
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
@@ -10030,12 +10030,12 @@
         <v>580</v>
       </c>
       <c r="D562" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
@@ -10044,12 +10044,12 @@
         <v>580</v>
       </c>
       <c r="D563" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
@@ -10058,12 +10058,12 @@
         <v>580</v>
       </c>
       <c r="D564" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
@@ -10072,12 +10072,12 @@
         <v>581</v>
       </c>
       <c r="D565" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
@@ -10086,12 +10086,12 @@
         <v>582</v>
       </c>
       <c r="D566" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
@@ -10100,49 +10100,49 @@
         <v>582</v>
       </c>
       <c r="D567" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568">
-        <v>111446.5</v>
-      </c>
-      <c r="D568">
-        <v>17493.02</v>
+      <c r="C568" t="s">
+        <v>583</v>
+      </c>
+      <c r="D568" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569">
-        <v>116213.5</v>
-      </c>
-      <c r="D569">
-        <v>17028.62</v>
+      <c r="C569" t="s">
+        <v>584</v>
+      </c>
+      <c r="D569" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570">
-        <v>128911.5</v>
-      </c>
-      <c r="D570">
-        <v>15706.52</v>
+      <c r="C570" t="s">
+        <v>585</v>
+      </c>
+      <c r="D570" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10161,16 +10161,16 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572" t="s">
-        <v>583</v>
-      </c>
-      <c r="D572" t="s">
-        <v>595</v>
+      <c r="C572">
+        <v>111508.5</v>
+      </c>
+      <c r="D572">
+        <v>18451.5</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10189,30 +10189,30 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574" t="s">
-        <v>584</v>
-      </c>
-      <c r="D574" t="s">
-        <v>596</v>
+      <c r="C574">
+        <v>108215</v>
+      </c>
+      <c r="D574">
+        <v>17925.19</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575" t="s">
-        <v>585</v>
-      </c>
-      <c r="D575" t="s">
-        <v>597</v>
+      <c r="C575">
+        <v>105862.5</v>
+      </c>
+      <c r="D575">
+        <v>17548.15</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10231,7 +10231,7 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
@@ -10240,6 +10240,20 @@
         <v>586</v>
       </c>
       <c r="D577" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4">
+      <c r="A578" s="1">
+        <v>597</v>
+      </c>
+      <c r="B578" t="s">
+        <v>579</v>
+      </c>
+      <c r="C578" t="s">
+        <v>587</v>
+      </c>
+      <c r="D578" t="s">
         <v>598</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="601">
   <si>
     <t>Date</t>
   </si>
@@ -1756,31 +1756,34 @@
     <t>2026-07-08</t>
   </si>
   <si>
-    <t>149093</t>
-  </si>
-  <si>
-    <t>147411.5</t>
-  </si>
-  <si>
-    <t>145169.5</t>
-  </si>
-  <si>
-    <t>141806.5</t>
-  </si>
-  <si>
-    <t>138443.5</t>
-  </si>
-  <si>
-    <t>136201.5</t>
-  </si>
-  <si>
-    <t>126112.5</t>
-  </si>
-  <si>
-    <t>111500</t>
-  </si>
-  <si>
-    <t>22007.97</t>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>117173</t>
+  </si>
+  <si>
+    <t>115851.5</t>
+  </si>
+  <si>
+    <t>114089.5</t>
+  </si>
+  <si>
+    <t>111446.5</t>
+  </si>
+  <si>
+    <t>108803.5</t>
+  </si>
+  <si>
+    <t>107041.5</t>
+  </si>
+  <si>
+    <t>105279.5</t>
+  </si>
+  <si>
+    <t>98231.5</t>
+  </si>
+  <si>
+    <t>109500</t>
   </si>
   <si>
     <t>21999.53</t>
@@ -1807,10 +1810,13 @@
     <t>19985.25</t>
   </si>
   <si>
-    <t>18513.29</t>
-  </si>
-  <si>
-    <t>16368.17</t>
+    <t>19647.34</t>
+  </si>
+  <si>
+    <t>18348.72</t>
+  </si>
+  <si>
+    <t>16052.89</t>
   </si>
 </sst>
 </file>
@@ -2168,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D578"/>
+  <dimension ref="A1:D579"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10021,16 +10027,16 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562" s="1">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="B562" t="s">
         <v>563</v>
       </c>
-      <c r="C562" t="s">
-        <v>580</v>
-      </c>
-      <c r="D562" t="s">
-        <v>588</v>
+      <c r="C562">
+        <v>149093</v>
+      </c>
+      <c r="D562">
+        <v>22007.97</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -10041,10 +10047,10 @@
         <v>564</v>
       </c>
       <c r="C563" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D563" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10055,10 +10061,10 @@
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D564" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -10069,10 +10075,10 @@
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D565" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10083,10 +10089,10 @@
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D566" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10097,10 +10103,10 @@
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D567" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10111,10 +10117,10 @@
         <v>569</v>
       </c>
       <c r="C568" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D568" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10125,10 +10131,10 @@
         <v>570</v>
       </c>
       <c r="C569" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D569" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10139,24 +10145,24 @@
         <v>571</v>
       </c>
       <c r="C570" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D570" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
-      <c r="C571">
-        <v>126789.5</v>
-      </c>
-      <c r="D571">
-        <v>15440.95</v>
+      <c r="C571" t="s">
+        <v>587</v>
+      </c>
+      <c r="D571" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10231,16 +10237,16 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577" t="s">
-        <v>586</v>
-      </c>
-      <c r="D577" t="s">
-        <v>597</v>
+      <c r="C577">
+        <v>126112.5</v>
+      </c>
+      <c r="D577">
+        <v>18513.29</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10251,10 +10257,24 @@
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D578" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4">
+      <c r="A579" s="1">
         <v>598</v>
+      </c>
+      <c r="B579" t="s">
+        <v>580</v>
+      </c>
+      <c r="C579" t="s">
+        <v>589</v>
+      </c>
+      <c r="D579" t="s">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="603">
   <si>
     <t>Date</t>
   </si>
@@ -1759,64 +1759,70 @@
     <t>2026-07-09</t>
   </si>
   <si>
-    <t>117173</t>
-  </si>
-  <si>
-    <t>115851.5</t>
-  </si>
-  <si>
-    <t>114089.5</t>
-  </si>
-  <si>
-    <t>111446.5</t>
-  </si>
-  <si>
-    <t>108803.5</t>
-  </si>
-  <si>
-    <t>107041.5</t>
-  </si>
-  <si>
-    <t>105279.5</t>
-  </si>
-  <si>
-    <t>98231.5</t>
-  </si>
-  <si>
-    <t>109500</t>
-  </si>
-  <si>
-    <t>21999.53</t>
-  </si>
-  <si>
-    <t>21998.88</t>
-  </si>
-  <si>
-    <t>21724.17</t>
-  </si>
-  <si>
-    <t>21375.49</t>
-  </si>
-  <si>
-    <t>21381.47</t>
-  </si>
-  <si>
-    <t>20839.19</t>
-  </si>
-  <si>
-    <t>20285.95</t>
-  </si>
-  <si>
-    <t>19985.25</t>
-  </si>
-  <si>
-    <t>19647.34</t>
-  </si>
-  <si>
-    <t>18348.72</t>
-  </si>
-  <si>
-    <t>16052.89</t>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>141113</t>
+  </si>
+  <si>
+    <t>139521.5</t>
+  </si>
+  <si>
+    <t>137399.5</t>
+  </si>
+  <si>
+    <t>134216.5</t>
+  </si>
+  <si>
+    <t>131033.5</t>
+  </si>
+  <si>
+    <t>128911.5</t>
+  </si>
+  <si>
+    <t>126789.5</t>
+  </si>
+  <si>
+    <t>125728.5</t>
+  </si>
+  <si>
+    <t>116179.5</t>
+  </si>
+  <si>
+    <t>109000</t>
+  </si>
+  <si>
+    <t>17289.04</t>
+  </si>
+  <si>
+    <t>17073.14</t>
+  </si>
+  <si>
+    <t>16799.11</t>
+  </si>
+  <si>
+    <t>16803.81</t>
+  </si>
+  <si>
+    <t>16377.63</t>
+  </si>
+  <si>
+    <t>15942.84</t>
+  </si>
+  <si>
+    <t>15706.52</t>
+  </si>
+  <si>
+    <t>15440.95</t>
+  </si>
+  <si>
+    <t>15321.18</t>
+  </si>
+  <si>
+    <t>14142.6</t>
+  </si>
+  <si>
+    <t>16006.58</t>
   </si>
 </sst>
 </file>
@@ -2174,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D579"/>
+  <dimension ref="A1:D580"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10041,16 +10047,16 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563" t="s">
-        <v>581</v>
-      </c>
-      <c r="D563" t="s">
-        <v>590</v>
+      <c r="C563">
+        <v>117173</v>
+      </c>
+      <c r="D563">
+        <v>21999.53</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10061,10 +10067,10 @@
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D564" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -10075,10 +10081,10 @@
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D565" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -10089,10 +10095,10 @@
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D566" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10103,10 +10109,10 @@
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D567" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10117,10 +10123,10 @@
         <v>569</v>
       </c>
       <c r="C568" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D568" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10131,10 +10137,10 @@
         <v>570</v>
       </c>
       <c r="C569" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D569" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10145,10 +10151,10 @@
         <v>571</v>
       </c>
       <c r="C570" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D570" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10159,24 +10165,24 @@
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D571" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572">
-        <v>111508.5</v>
-      </c>
-      <c r="D572">
-        <v>18451.5</v>
+      <c r="C572" t="s">
+        <v>589</v>
+      </c>
+      <c r="D572" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10251,16 +10257,16 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578" t="s">
-        <v>588</v>
-      </c>
-      <c r="D578" t="s">
-        <v>599</v>
+      <c r="C578">
+        <v>98231.5</v>
+      </c>
+      <c r="D578">
+        <v>18348.72</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -10271,10 +10277,24 @@
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D579" t="s">
-        <v>600</v>
+        <v>601</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4">
+      <c r="A580" s="1">
+        <v>599</v>
+      </c>
+      <c r="B580" t="s">
+        <v>581</v>
+      </c>
+      <c r="C580" t="s">
+        <v>591</v>
+      </c>
+      <c r="D580" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="605">
   <si>
     <t>Date</t>
   </si>
@@ -1762,6 +1762,9 @@
     <t>2026-07-10</t>
   </si>
   <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
     <t>141113</t>
   </si>
   <si>
@@ -1786,43 +1789,46 @@
     <t>125728.5</t>
   </si>
   <si>
-    <t>116179.5</t>
+    <t>124137</t>
   </si>
   <si>
     <t>109000</t>
   </si>
   <si>
-    <t>17289.04</t>
-  </si>
-  <si>
-    <t>17073.14</t>
-  </si>
-  <si>
-    <t>16799.11</t>
-  </si>
-  <si>
-    <t>16803.81</t>
-  </si>
-  <si>
-    <t>16377.63</t>
-  </si>
-  <si>
-    <t>15942.84</t>
-  </si>
-  <si>
-    <t>15706.52</t>
-  </si>
-  <si>
-    <t>15440.95</t>
-  </si>
-  <si>
-    <t>15321.18</t>
-  </si>
-  <si>
-    <t>14142.6</t>
-  </si>
-  <si>
-    <t>16006.58</t>
+    <t>18426.58</t>
+  </si>
+  <si>
+    <t>18426.03</t>
+  </si>
+  <si>
+    <t>18195.94</t>
+  </si>
+  <si>
+    <t>17903.89</t>
+  </si>
+  <si>
+    <t>17908.9</t>
+  </si>
+  <si>
+    <t>17454.69</t>
+  </si>
+  <si>
+    <t>16991.3</t>
+  </si>
+  <si>
+    <t>16739.44</t>
+  </si>
+  <si>
+    <t>16456.41</t>
+  </si>
+  <si>
+    <t>16328.76</t>
+  </si>
+  <si>
+    <t>16146.95</t>
+  </si>
+  <si>
+    <t>14195.34</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D580"/>
+  <dimension ref="A1:D581"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10047,156 +10053,156 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563">
-        <v>117173</v>
-      </c>
-      <c r="D563">
-        <v>21999.53</v>
+      <c r="C563" t="s">
+        <v>583</v>
+      </c>
+      <c r="D563" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
       <c r="C564" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D564" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
       <c r="C565" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D565" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
       <c r="C566" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D566" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D567" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
       <c r="C568" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D568" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
       <c r="C569" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D569" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
       <c r="C570" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D570" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
       <c r="C572" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573">
-        <v>110097</v>
-      </c>
-      <c r="D573">
-        <v>15150.58</v>
+      <c r="C573" t="s">
+        <v>591</v>
+      </c>
+      <c r="D573" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10271,30 +10277,44 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>590</v>
-      </c>
-      <c r="D579" t="s">
-        <v>601</v>
+      <c r="C579">
+        <v>116179.5</v>
+      </c>
+      <c r="D579">
+        <v>14142.6</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580" t="s">
-        <v>591</v>
-      </c>
-      <c r="D580" t="s">
-        <v>602</v>
+      <c r="C580">
+        <v>109000</v>
+      </c>
+      <c r="D580">
+        <v>16006.58</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4">
+      <c r="A581" s="1">
+        <v>598</v>
+      </c>
+      <c r="B581" t="s">
+        <v>582</v>
+      </c>
+      <c r="C581" t="s">
+        <v>592</v>
+      </c>
+      <c r="D581" t="s">
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="607">
   <si>
     <t>Date</t>
   </si>
@@ -1765,70 +1765,76 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>141113</t>
-  </si>
-  <si>
-    <t>139521.5</t>
-  </si>
-  <si>
-    <t>137399.5</t>
-  </si>
-  <si>
-    <t>134216.5</t>
-  </si>
-  <si>
-    <t>131033.5</t>
-  </si>
-  <si>
-    <t>128911.5</t>
-  </si>
-  <si>
-    <t>126789.5</t>
-  </si>
-  <si>
-    <t>125728.5</t>
-  </si>
-  <si>
-    <t>124137</t>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>115851.5</t>
+  </si>
+  <si>
+    <t>114089.5</t>
+  </si>
+  <si>
+    <t>111446.5</t>
+  </si>
+  <si>
+    <t>108803.5</t>
+  </si>
+  <si>
+    <t>107041.5</t>
+  </si>
+  <si>
+    <t>105279.5</t>
+  </si>
+  <si>
+    <t>104398.5</t>
+  </si>
+  <si>
+    <t>99112.5</t>
+  </si>
+  <si>
+    <t>96469.5</t>
+  </si>
+  <si>
+    <t>96029</t>
   </si>
   <si>
     <t>109000</t>
   </si>
   <si>
-    <t>18426.58</t>
-  </si>
-  <si>
-    <t>18426.03</t>
-  </si>
-  <si>
-    <t>18195.94</t>
-  </si>
-  <si>
-    <t>17903.89</t>
-  </si>
-  <si>
-    <t>17908.9</t>
-  </si>
-  <si>
-    <t>17454.69</t>
-  </si>
-  <si>
-    <t>16991.3</t>
-  </si>
-  <si>
-    <t>16739.44</t>
-  </si>
-  <si>
-    <t>16456.41</t>
-  </si>
-  <si>
-    <t>16328.76</t>
-  </si>
-  <si>
-    <t>16146.95</t>
-  </si>
-  <si>
-    <t>14195.34</t>
+    <t>15108.97</t>
+  </si>
+  <si>
+    <t>14866.47</t>
+  </si>
+  <si>
+    <t>14870.63</t>
+  </si>
+  <si>
+    <t>14493.48</t>
+  </si>
+  <si>
+    <t>14108.71</t>
+  </si>
+  <si>
+    <t>13899.57</t>
+  </si>
+  <si>
+    <t>13664.56</t>
+  </si>
+  <si>
+    <t>13558.56</t>
+  </si>
+  <si>
+    <t>12875.83</t>
+  </si>
+  <si>
+    <t>12515.57</t>
+  </si>
+  <si>
+    <t>12479.47</t>
+  </si>
+  <si>
+    <t>14192</t>
   </si>
 </sst>
 </file>
@@ -2186,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D581"/>
+  <dimension ref="A1:D582"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10053,35 +10059,35 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563" s="1">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="B563" t="s">
         <v>564</v>
       </c>
-      <c r="C563" t="s">
-        <v>583</v>
-      </c>
-      <c r="D563" t="s">
-        <v>593</v>
+      <c r="C563">
+        <v>141113</v>
+      </c>
+      <c r="D563">
+        <v>18426.58</v>
       </c>
     </row>
     <row r="564" spans="1:4">
       <c r="A564" s="1">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="B564" t="s">
         <v>565</v>
       </c>
-      <c r="C564" t="s">
-        <v>583</v>
-      </c>
-      <c r="D564" t="s">
-        <v>594</v>
+      <c r="C564">
+        <v>141113</v>
+      </c>
+      <c r="D564">
+        <v>18426.03</v>
       </c>
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
@@ -10095,7 +10101,7 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
@@ -10109,7 +10115,7 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
@@ -10123,7 +10129,7 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
@@ -10137,7 +10143,7 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
@@ -10151,7 +10157,7 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
@@ -10165,7 +10171,7 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
@@ -10179,7 +10185,7 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
@@ -10193,16 +10199,16 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>591</v>
-      </c>
-      <c r="D573" t="s">
-        <v>603</v>
+      <c r="C573">
+        <v>124137</v>
+      </c>
+      <c r="D573">
+        <v>16146.95</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10249,16 +10255,16 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577">
-        <v>126112.5</v>
-      </c>
-      <c r="D577">
-        <v>18513.29</v>
+      <c r="C577" t="s">
+        <v>591</v>
+      </c>
+      <c r="D577" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10277,44 +10283,58 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579">
-        <v>116179.5</v>
-      </c>
-      <c r="D579">
-        <v>14142.6</v>
+      <c r="C579" t="s">
+        <v>592</v>
+      </c>
+      <c r="D579" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580">
-        <v>109000</v>
-      </c>
-      <c r="D580">
-        <v>16006.58</v>
+      <c r="C580" t="s">
+        <v>593</v>
+      </c>
+      <c r="D580" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>592</v>
-      </c>
-      <c r="D581" t="s">
-        <v>604</v>
+      <c r="C581">
+        <v>109000</v>
+      </c>
+      <c r="D581">
+        <v>14195.34</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4">
+      <c r="A582" s="1">
+        <v>600</v>
+      </c>
+      <c r="B582" t="s">
+        <v>583</v>
+      </c>
+      <c r="C582" t="s">
+        <v>594</v>
+      </c>
+      <c r="D582" t="s">
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
   <si>
     <t>Date</t>
   </si>
@@ -1768,73 +1768,73 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>115851.5</t>
-  </si>
-  <si>
-    <t>114089.5</t>
-  </si>
-  <si>
-    <t>111446.5</t>
-  </si>
-  <si>
-    <t>108803.5</t>
-  </si>
-  <si>
-    <t>107041.5</t>
-  </si>
-  <si>
-    <t>105279.5</t>
-  </si>
-  <si>
-    <t>104398.5</t>
-  </si>
-  <si>
-    <t>99112.5</t>
-  </si>
-  <si>
-    <t>96469.5</t>
-  </si>
-  <si>
-    <t>96029</t>
-  </si>
-  <si>
-    <t>109000</t>
-  </si>
-  <si>
-    <t>15108.97</t>
-  </si>
-  <si>
-    <t>14866.47</t>
-  </si>
-  <si>
-    <t>14870.63</t>
-  </si>
-  <si>
-    <t>14493.48</t>
-  </si>
-  <si>
-    <t>14108.71</t>
-  </si>
-  <si>
-    <t>13899.57</t>
-  </si>
-  <si>
-    <t>13664.56</t>
-  </si>
-  <si>
-    <t>13558.56</t>
-  </si>
-  <si>
-    <t>12875.83</t>
-  </si>
-  <si>
-    <t>12515.57</t>
-  </si>
-  <si>
-    <t>12479.47</t>
-  </si>
-  <si>
-    <t>14192</t>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>137399.5</t>
+  </si>
+  <si>
+    <t>134216.5</t>
+  </si>
+  <si>
+    <t>131033.5</t>
+  </si>
+  <si>
+    <t>128911.5</t>
+  </si>
+  <si>
+    <t>126789.5</t>
+  </si>
+  <si>
+    <t>125728.5</t>
+  </si>
+  <si>
+    <t>124137</t>
+  </si>
+  <si>
+    <t>122015</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>115649</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>18921.66</t>
+  </si>
+  <si>
+    <t>18441.76</t>
+  </si>
+  <si>
+    <t>17952.17</t>
+  </si>
+  <si>
+    <t>17686.06</t>
+  </si>
+  <si>
+    <t>17387.03</t>
+  </si>
+  <si>
+    <t>17252.16</t>
+  </si>
+  <si>
+    <t>17060.06</t>
+  </si>
+  <si>
+    <t>16760.06</t>
+  </si>
+  <si>
+    <t>16407.52</t>
+  </si>
+  <si>
+    <t>15909.23</t>
+  </si>
+  <si>
+    <t>13691.94</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D582"/>
+  <dimension ref="A1:D583"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10087,35 +10087,35 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565" s="1">
-        <v>583</v>
+        <v>563</v>
       </c>
       <c r="B565" t="s">
         <v>566</v>
       </c>
-      <c r="C565" t="s">
-        <v>584</v>
-      </c>
-      <c r="D565" t="s">
-        <v>595</v>
+      <c r="C565">
+        <v>115851.5</v>
+      </c>
+      <c r="D565">
+        <v>15108.97</v>
       </c>
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566" t="s">
-        <v>585</v>
-      </c>
-      <c r="D566" t="s">
-        <v>596</v>
+      <c r="C566">
+        <v>114089.5</v>
+      </c>
+      <c r="D566">
+        <v>14866.47</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
@@ -10124,12 +10124,12 @@
         <v>585</v>
       </c>
       <c r="D567" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
@@ -10138,12 +10138,12 @@
         <v>586</v>
       </c>
       <c r="D568" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
@@ -10152,12 +10152,12 @@
         <v>587</v>
       </c>
       <c r="D569" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
@@ -10166,12 +10166,12 @@
         <v>588</v>
       </c>
       <c r="D570" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
@@ -10180,12 +10180,12 @@
         <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
@@ -10194,49 +10194,49 @@
         <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573">
-        <v>124137</v>
-      </c>
-      <c r="D573">
-        <v>16146.95</v>
+      <c r="C573" t="s">
+        <v>591</v>
+      </c>
+      <c r="D573" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574">
-        <v>108215</v>
-      </c>
-      <c r="D574">
-        <v>17925.19</v>
+      <c r="C574" t="s">
+        <v>592</v>
+      </c>
+      <c r="D574" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>573</v>
+        <v>594</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575">
-        <v>105862.5</v>
-      </c>
-      <c r="D575">
-        <v>17548.15</v>
+      <c r="C575" t="s">
+        <v>593</v>
+      </c>
+      <c r="D575" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10255,16 +10255,16 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577" t="s">
-        <v>591</v>
-      </c>
-      <c r="D577" t="s">
-        <v>603</v>
+      <c r="C577">
+        <v>99112.5</v>
+      </c>
+      <c r="D577">
+        <v>12875.83</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10283,30 +10283,30 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>592</v>
-      </c>
-      <c r="D579" t="s">
-        <v>604</v>
+      <c r="C579">
+        <v>96469.5</v>
+      </c>
+      <c r="D579">
+        <v>12515.57</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580" t="s">
-        <v>593</v>
-      </c>
-      <c r="D580" t="s">
-        <v>605</v>
+      <c r="C580">
+        <v>96029</v>
+      </c>
+      <c r="D580">
+        <v>12479.47</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10325,7 +10325,7 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
@@ -10334,6 +10334,20 @@
         <v>594</v>
       </c>
       <c r="D582" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4">
+      <c r="A583" s="1">
+        <v>602</v>
+      </c>
+      <c r="B583" t="s">
+        <v>584</v>
+      </c>
+      <c r="C583" t="s">
+        <v>595</v>
+      </c>
+      <c r="D583" t="s">
         <v>606</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="607">
   <si>
     <t>Date</t>
   </si>
@@ -1771,40 +1771,37 @@
     <t>2026-07-15</t>
   </si>
   <si>
-    <t>137399.5</t>
-  </si>
-  <si>
-    <t>134216.5</t>
-  </si>
-  <si>
-    <t>131033.5</t>
-  </si>
-  <si>
-    <t>128911.5</t>
-  </si>
-  <si>
-    <t>126789.5</t>
-  </si>
-  <si>
-    <t>125728.5</t>
-  </si>
-  <si>
-    <t>124137</t>
-  </si>
-  <si>
-    <t>122015</t>
-  </si>
-  <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>115649</t>
-  </si>
-  <si>
-    <t>105000</t>
-  </si>
-  <si>
-    <t>18921.66</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>141806.5</t>
+  </si>
+  <si>
+    <t>138443.5</t>
+  </si>
+  <si>
+    <t>136201.5</t>
+  </si>
+  <si>
+    <t>133959.5</t>
+  </si>
+  <si>
+    <t>132838.5</t>
+  </si>
+  <si>
+    <t>131157</t>
+  </si>
+  <si>
+    <t>128915</t>
+  </si>
+  <si>
+    <t>126112.5</t>
+  </si>
+  <si>
+    <t>117705</t>
+  </si>
+  <si>
+    <t>103000</t>
   </si>
   <si>
     <t>18441.76</t>
@@ -1831,10 +1828,13 @@
     <t>16407.52</t>
   </si>
   <si>
-    <t>15909.23</t>
-  </si>
-  <si>
-    <t>13691.94</t>
+    <t>16415.49</t>
+  </si>
+  <si>
+    <t>15348.67</t>
+  </si>
+  <si>
+    <t>13433.71</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D583"/>
+  <dimension ref="A1:D584"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10115,16 +10115,16 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567" t="s">
-        <v>585</v>
-      </c>
-      <c r="D567" t="s">
-        <v>596</v>
+      <c r="C567">
+        <v>137399.5</v>
+      </c>
+      <c r="D567">
+        <v>18921.66</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10138,7 +10138,7 @@
         <v>586</v>
       </c>
       <c r="D568" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10152,7 +10152,7 @@
         <v>587</v>
       </c>
       <c r="D569" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10166,7 +10166,7 @@
         <v>588</v>
       </c>
       <c r="D570" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10180,7 +10180,7 @@
         <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10194,7 +10194,7 @@
         <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10208,7 +10208,7 @@
         <v>591</v>
       </c>
       <c r="D573" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10222,7 +10222,7 @@
         <v>592</v>
       </c>
       <c r="D574" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10236,21 +10236,21 @@
         <v>593</v>
       </c>
       <c r="D575" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576">
-        <v>112500</v>
-      </c>
-      <c r="D576">
-        <v>16547.28</v>
+      <c r="C576" t="s">
+        <v>593</v>
+      </c>
+      <c r="D576" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10325,16 +10325,16 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582" t="s">
-        <v>594</v>
-      </c>
-      <c r="D582" t="s">
-        <v>605</v>
+      <c r="C582">
+        <v>115649</v>
+      </c>
+      <c r="D582">
+        <v>15909.23</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -10345,9 +10345,23 @@
         <v>584</v>
       </c>
       <c r="C583" t="s">
+        <v>594</v>
+      </c>
+      <c r="D583" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4">
+      <c r="A584" s="1">
+        <v>603</v>
+      </c>
+      <c r="B584" t="s">
+        <v>585</v>
+      </c>
+      <c r="C584" t="s">
         <v>595</v>
       </c>
-      <c r="D583" t="s">
+      <c r="D584" t="s">
         <v>606</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="607">
   <si>
     <t>Date</t>
   </si>
@@ -1774,67 +1774,67 @@
     <t>2026-07-16</t>
   </si>
   <si>
-    <t>141806.5</t>
-  </si>
-  <si>
-    <t>138443.5</t>
-  </si>
-  <si>
-    <t>136201.5</t>
-  </si>
-  <si>
-    <t>133959.5</t>
-  </si>
-  <si>
-    <t>132838.5</t>
-  </si>
-  <si>
-    <t>131157</t>
-  </si>
-  <si>
-    <t>128915</t>
-  </si>
-  <si>
-    <t>126112.5</t>
-  </si>
-  <si>
-    <t>117705</t>
-  </si>
-  <si>
-    <t>103000</t>
-  </si>
-  <si>
-    <t>18441.76</t>
-  </si>
-  <si>
-    <t>17952.17</t>
-  </si>
-  <si>
-    <t>17686.06</t>
-  </si>
-  <si>
-    <t>17387.03</t>
-  </si>
-  <si>
-    <t>17252.16</t>
-  </si>
-  <si>
-    <t>17060.06</t>
-  </si>
-  <si>
-    <t>16760.06</t>
-  </si>
-  <si>
-    <t>16407.52</t>
-  </si>
-  <si>
-    <t>16415.49</t>
-  </si>
-  <si>
-    <t>15348.67</t>
-  </si>
-  <si>
-    <t>13433.71</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>131033.5</t>
+  </si>
+  <si>
+    <t>128911.5</t>
+  </si>
+  <si>
+    <t>126789.5</t>
+  </si>
+  <si>
+    <t>125728.5</t>
+  </si>
+  <si>
+    <t>124137</t>
+  </si>
+  <si>
+    <t>122015</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>101000</t>
+  </si>
+  <si>
+    <t>15069.57</t>
+  </si>
+  <si>
+    <t>14846.2</t>
+  </si>
+  <si>
+    <t>14595.18</t>
+  </si>
+  <si>
+    <t>14481.96</t>
+  </si>
+  <si>
+    <t>14320.71</t>
+  </si>
+  <si>
+    <t>14068.88</t>
+  </si>
+  <si>
+    <t>13772.95</t>
+  </si>
+  <si>
+    <t>13779.64</t>
+  </si>
+  <si>
+    <t>13752.73</t>
+  </si>
+  <si>
+    <t>12641.13</t>
+  </si>
+  <si>
+    <t>13165.49</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D584"/>
+  <dimension ref="A1:D585"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10129,16 +10129,16 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
-        <v>586</v>
-      </c>
-      <c r="D568" t="s">
-        <v>596</v>
+      <c r="C568">
+        <v>141806.5</v>
+      </c>
+      <c r="D568">
+        <v>18441.76</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10152,7 +10152,7 @@
         <v>587</v>
       </c>
       <c r="D569" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10166,7 +10166,7 @@
         <v>588</v>
       </c>
       <c r="D570" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10180,7 +10180,7 @@
         <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10194,7 +10194,7 @@
         <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10208,7 +10208,7 @@
         <v>591</v>
       </c>
       <c r="D573" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10222,7 +10222,7 @@
         <v>592</v>
       </c>
       <c r="D574" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10236,7 +10236,7 @@
         <v>593</v>
       </c>
       <c r="D575" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10250,21 +10250,21 @@
         <v>593</v>
       </c>
       <c r="D576" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577">
-        <v>99112.5</v>
-      </c>
-      <c r="D577">
-        <v>12875.83</v>
+      <c r="C577" t="s">
+        <v>593</v>
+      </c>
+      <c r="D577" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10339,16 +10339,16 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583" t="s">
-        <v>594</v>
-      </c>
-      <c r="D583" t="s">
-        <v>605</v>
+      <c r="C583">
+        <v>117705</v>
+      </c>
+      <c r="D583">
+        <v>15348.67</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -10359,9 +10359,23 @@
         <v>585</v>
       </c>
       <c r="C584" t="s">
+        <v>594</v>
+      </c>
+      <c r="D584" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4">
+      <c r="A585" s="1">
+        <v>604</v>
+      </c>
+      <c r="B585" t="s">
+        <v>586</v>
+      </c>
+      <c r="C585" t="s">
         <v>595</v>
       </c>
-      <c r="D584" t="s">
+      <c r="D585" t="s">
         <v>606</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="610">
   <si>
     <t>Date</t>
   </si>
@@ -1777,64 +1777,73 @@
     <t>2026-07-17</t>
   </si>
   <si>
+    <t>134216.5</t>
+  </si>
+  <si>
     <t>131033.5</t>
   </si>
   <si>
-    <t>128911.5</t>
-  </si>
-  <si>
     <t>126789.5</t>
   </si>
   <si>
     <t>125728.5</t>
   </si>
   <si>
-    <t>124137</t>
-  </si>
-  <si>
     <t>122015</t>
   </si>
   <si>
     <t>119362.5</t>
   </si>
   <si>
+    <t>118301.5</t>
+  </si>
+  <si>
+    <t>116179.5</t>
+  </si>
+  <si>
+    <t>115649</t>
+  </si>
+  <si>
+    <t>111405</t>
+  </si>
+  <si>
     <t>109283</t>
   </si>
   <si>
-    <t>101000</t>
-  </si>
-  <si>
-    <t>15069.57</t>
-  </si>
-  <si>
-    <t>14846.2</t>
-  </si>
-  <si>
-    <t>14595.18</t>
-  </si>
-  <si>
-    <t>14481.96</t>
-  </si>
-  <si>
-    <t>14320.71</t>
-  </si>
-  <si>
-    <t>14068.88</t>
-  </si>
-  <si>
-    <t>13772.95</t>
-  </si>
-  <si>
-    <t>13779.64</t>
-  </si>
-  <si>
-    <t>13752.73</t>
-  </si>
-  <si>
-    <t>12641.13</t>
-  </si>
-  <si>
-    <t>13165.49</t>
+    <t>18441.76</t>
+  </si>
+  <si>
+    <t>17952.17</t>
+  </si>
+  <si>
+    <t>17387.03</t>
+  </si>
+  <si>
+    <t>17252.16</t>
+  </si>
+  <si>
+    <t>16760.06</t>
+  </si>
+  <si>
+    <t>16415.49</t>
+  </si>
+  <si>
+    <t>16383.44</t>
+  </si>
+  <si>
+    <t>16237.81</t>
+  </si>
+  <si>
+    <t>15925.04</t>
+  </si>
+  <si>
+    <t>15909.23</t>
+  </si>
+  <si>
+    <t>15348.67</t>
+  </si>
+  <si>
+    <t>15059.19</t>
   </si>
 </sst>
 </file>
@@ -10129,49 +10138,49 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>586</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568">
-        <v>141806.5</v>
-      </c>
-      <c r="D568">
-        <v>18441.76</v>
+      <c r="C568" t="s">
+        <v>587</v>
+      </c>
+      <c r="D568" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
       <c r="C569" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D569" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570" t="s">
-        <v>588</v>
-      </c>
-      <c r="D570" t="s">
-        <v>597</v>
+      <c r="C570">
+        <v>128911.5</v>
+      </c>
+      <c r="D570">
+        <v>14846.2</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
@@ -10180,12 +10189,12 @@
         <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
@@ -10194,60 +10203,60 @@
         <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>591</v>
-      </c>
-      <c r="D573" t="s">
-        <v>600</v>
+      <c r="C573">
+        <v>124137</v>
+      </c>
+      <c r="D573">
+        <v>14320.71</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
       <c r="C574" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D574" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575" t="s">
-        <v>593</v>
-      </c>
-      <c r="D575" t="s">
-        <v>602</v>
+      <c r="C575">
+        <v>119362.5</v>
+      </c>
+      <c r="D575">
+        <v>13772.95</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D576" t="s">
         <v>603</v>
@@ -10255,13 +10264,13 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D577" t="s">
         <v>604</v>
@@ -10269,30 +10278,30 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578">
-        <v>98231.5</v>
-      </c>
-      <c r="D578">
-        <v>18348.72</v>
+      <c r="C578" t="s">
+        <v>593</v>
+      </c>
+      <c r="D578" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579">
-        <v>96469.5</v>
-      </c>
-      <c r="D579">
-        <v>12515.57</v>
+      <c r="C579" t="s">
+        <v>594</v>
+      </c>
+      <c r="D579" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -10325,58 +10334,58 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582">
-        <v>115649</v>
-      </c>
-      <c r="D582">
-        <v>15909.23</v>
+      <c r="C582" t="s">
+        <v>595</v>
+      </c>
+      <c r="D582" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583">
-        <v>117705</v>
-      </c>
-      <c r="D583">
-        <v>15348.67</v>
+      <c r="C583" t="s">
+        <v>596</v>
+      </c>
+      <c r="D583" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
       <c r="C584" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D584" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
-      <c r="C585" t="s">
-        <v>595</v>
-      </c>
-      <c r="D585" t="s">
-        <v>606</v>
+      <c r="C585">
+        <v>101000</v>
+      </c>
+      <c r="D585">
+        <v>13165.49</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="611">
   <si>
     <t>Date</t>
   </si>
@@ -1777,73 +1777,76 @@
     <t>2026-07-17</t>
   </si>
   <si>
-    <t>134216.5</t>
-  </si>
-  <si>
-    <t>131033.5</t>
-  </si>
-  <si>
-    <t>126789.5</t>
-  </si>
-  <si>
-    <t>125728.5</t>
-  </si>
-  <si>
-    <t>122015</t>
-  </si>
-  <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>118301.5</t>
-  </si>
-  <si>
-    <t>116179.5</t>
-  </si>
-  <si>
-    <t>115649</t>
-  </si>
-  <si>
-    <t>111405</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>18441.76</t>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>138443.5</t>
+  </si>
+  <si>
+    <t>136201.5</t>
+  </si>
+  <si>
+    <t>133959.5</t>
+  </si>
+  <si>
+    <t>132838.5</t>
+  </si>
+  <si>
+    <t>131157</t>
+  </si>
+  <si>
+    <t>128915</t>
+  </si>
+  <si>
+    <t>126112.5</t>
+  </si>
+  <si>
+    <t>122189</t>
+  </si>
+  <si>
+    <t>117705</t>
+  </si>
+  <si>
+    <t>115463</t>
+  </si>
+  <si>
+    <t>99000</t>
   </si>
   <si>
     <t>17952.17</t>
   </si>
   <si>
+    <t>17686.06</t>
+  </si>
+  <si>
     <t>17387.03</t>
   </si>
   <si>
     <t>17252.16</t>
   </si>
   <si>
+    <t>17060.06</t>
+  </si>
+  <si>
     <t>16760.06</t>
   </si>
   <si>
+    <t>16407.52</t>
+  </si>
+  <si>
     <t>16415.49</t>
   </si>
   <si>
-    <t>16383.44</t>
-  </si>
-  <si>
-    <t>16237.81</t>
-  </si>
-  <si>
-    <t>15925.04</t>
-  </si>
-  <si>
-    <t>15909.23</t>
+    <t>15912.98</t>
   </si>
   <si>
     <t>15348.67</t>
   </si>
   <si>
     <t>15059.19</t>
+  </si>
+  <si>
+    <t>12895.48</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D585"/>
+  <dimension ref="A1:D586"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10138,16 +10141,16 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
-        <v>587</v>
-      </c>
-      <c r="D568" t="s">
-        <v>598</v>
+      <c r="C568">
+        <v>134216.5</v>
+      </c>
+      <c r="D568">
+        <v>18441.76</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10166,16 +10169,16 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570">
-        <v>128911.5</v>
-      </c>
-      <c r="D570">
-        <v>14846.2</v>
+      <c r="C570" t="s">
+        <v>589</v>
+      </c>
+      <c r="D570" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -10186,10 +10189,10 @@
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D571" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10200,24 +10203,24 @@
         <v>573</v>
       </c>
       <c r="C572" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D572" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573">
-        <v>124137</v>
-      </c>
-      <c r="D573">
-        <v>14320.71</v>
+      <c r="C573" t="s">
+        <v>592</v>
+      </c>
+      <c r="D573" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10228,24 +10231,24 @@
         <v>575</v>
       </c>
       <c r="C574" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D574" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575">
-        <v>119362.5</v>
-      </c>
-      <c r="D575">
-        <v>13772.95</v>
+      <c r="C575" t="s">
+        <v>594</v>
+      </c>
+      <c r="D575" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10256,52 +10259,52 @@
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D576" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577" t="s">
-        <v>592</v>
-      </c>
-      <c r="D577" t="s">
-        <v>604</v>
+      <c r="C577">
+        <v>119362.5</v>
+      </c>
+      <c r="D577">
+        <v>16383.44</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578" t="s">
-        <v>593</v>
-      </c>
-      <c r="D578" t="s">
-        <v>605</v>
+      <c r="C578">
+        <v>118301.5</v>
+      </c>
+      <c r="D578">
+        <v>16237.81</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>594</v>
-      </c>
-      <c r="D579" t="s">
-        <v>606</v>
+      <c r="C579">
+        <v>116179.5</v>
+      </c>
+      <c r="D579">
+        <v>15925.04</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -10320,30 +10323,30 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581">
-        <v>109000</v>
-      </c>
-      <c r="D581">
-        <v>14195.34</v>
+      <c r="C581" t="s">
+        <v>595</v>
+      </c>
+      <c r="D581" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582" t="s">
-        <v>595</v>
-      </c>
-      <c r="D582" t="s">
-        <v>607</v>
+      <c r="C582">
+        <v>115649</v>
+      </c>
+      <c r="D582">
+        <v>15909.23</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -10386,6 +10389,20 @@
       </c>
       <c r="D585">
         <v>13165.49</v>
+      </c>
+    </row>
+    <row r="586" spans="1:4">
+      <c r="A586" s="1">
+        <v>604</v>
+      </c>
+      <c r="B586" t="s">
+        <v>587</v>
+      </c>
+      <c r="C586" t="s">
+        <v>598</v>
+      </c>
+      <c r="D586" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="609">
   <si>
     <t>Date</t>
   </si>
@@ -1780,73 +1780,67 @@
     <t>2026-07-20</t>
   </si>
   <si>
-    <t>138443.5</t>
-  </si>
-  <si>
-    <t>136201.5</t>
-  </si>
-  <si>
-    <t>133959.5</t>
-  </si>
-  <si>
-    <t>132838.5</t>
-  </si>
-  <si>
-    <t>131157</t>
-  </si>
-  <si>
-    <t>128915</t>
-  </si>
-  <si>
-    <t>126112.5</t>
-  </si>
-  <si>
-    <t>122189</t>
-  </si>
-  <si>
-    <t>117705</t>
-  </si>
-  <si>
-    <t>115463</t>
-  </si>
-  <si>
-    <t>99000</t>
-  </si>
-  <si>
-    <t>17952.17</t>
-  </si>
-  <si>
-    <t>17686.06</t>
-  </si>
-  <si>
-    <t>17387.03</t>
-  </si>
-  <si>
-    <t>17252.16</t>
-  </si>
-  <si>
-    <t>17060.06</t>
-  </si>
-  <si>
-    <t>16760.06</t>
-  </si>
-  <si>
-    <t>16407.52</t>
-  </si>
-  <si>
-    <t>16415.49</t>
-  </si>
-  <si>
-    <t>15912.98</t>
-  </si>
-  <si>
-    <t>15348.67</t>
-  </si>
-  <si>
-    <t>15059.19</t>
-  </si>
-  <si>
-    <t>12895.48</t>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>105279.5</t>
+  </si>
+  <si>
+    <t>104398.5</t>
+  </si>
+  <si>
+    <t>103077</t>
+  </si>
+  <si>
+    <t>101315</t>
+  </si>
+  <si>
+    <t>99112.5</t>
+  </si>
+  <si>
+    <t>98231.5</t>
+  </si>
+  <si>
+    <t>96469.5</t>
+  </si>
+  <si>
+    <t>87219</t>
+  </si>
+  <si>
+    <t>97000</t>
+  </si>
+  <si>
+    <t>16456.41</t>
+  </si>
+  <si>
+    <t>16328.76</t>
+  </si>
+  <si>
+    <t>16146.95</t>
+  </si>
+  <si>
+    <t>15863</t>
+  </si>
+  <si>
+    <t>15529.33</t>
+  </si>
+  <si>
+    <t>15536.87</t>
+  </si>
+  <si>
+    <t>15506.54</t>
+  </si>
+  <si>
+    <t>15368.7</t>
+  </si>
+  <si>
+    <t>15072.67</t>
+  </si>
+  <si>
+    <t>13682.11</t>
+  </si>
+  <si>
+    <t>12651.73</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D586"/>
+  <dimension ref="A1:D587"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10155,156 +10149,156 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569" t="s">
-        <v>588</v>
-      </c>
-      <c r="D569" t="s">
-        <v>599</v>
+      <c r="C569">
+        <v>138443.5</v>
+      </c>
+      <c r="D569">
+        <v>17952.17</v>
       </c>
     </row>
     <row r="570" spans="1:4">
       <c r="A570" s="1">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="B570" t="s">
         <v>571</v>
       </c>
-      <c r="C570" t="s">
-        <v>589</v>
-      </c>
-      <c r="D570" t="s">
-        <v>600</v>
+      <c r="C570">
+        <v>136201.5</v>
+      </c>
+      <c r="D570">
+        <v>17686.06</v>
       </c>
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D571" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
       <c r="C572" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D572" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
       <c r="C573" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D573" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
       <c r="C574" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D574" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
       <c r="C575" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D575" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D576" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577">
-        <v>119362.5</v>
-      </c>
-      <c r="D577">
-        <v>16383.44</v>
+      <c r="C577" t="s">
+        <v>593</v>
+      </c>
+      <c r="D577" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578">
-        <v>118301.5</v>
-      </c>
-      <c r="D578">
-        <v>16237.81</v>
+      <c r="C578" t="s">
+        <v>594</v>
+      </c>
+      <c r="D578" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579">
-        <v>116179.5</v>
-      </c>
-      <c r="D579">
-        <v>15925.04</v>
+      <c r="C579" t="s">
+        <v>595</v>
+      </c>
+      <c r="D579" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -10323,16 +10317,16 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>595</v>
-      </c>
-      <c r="D581" t="s">
-        <v>607</v>
+      <c r="C581">
+        <v>122189</v>
+      </c>
+      <c r="D581">
+        <v>15912.98</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10351,30 +10345,30 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583" t="s">
-        <v>596</v>
-      </c>
-      <c r="D583" t="s">
-        <v>608</v>
+      <c r="C583">
+        <v>117705</v>
+      </c>
+      <c r="D583">
+        <v>15348.67</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>597</v>
-      </c>
-      <c r="D584" t="s">
-        <v>609</v>
+      <c r="C584">
+        <v>115463</v>
+      </c>
+      <c r="D584">
+        <v>15059.19</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -10393,16 +10387,30 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D586" t="s">
-        <v>610</v>
+        <v>607</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4">
+      <c r="A587" s="1">
+        <v>606</v>
+      </c>
+      <c r="B587" t="s">
+        <v>588</v>
+      </c>
+      <c r="C587" t="s">
+        <v>597</v>
+      </c>
+      <c r="D587" t="s">
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="611">
   <si>
     <t>Date</t>
   </si>
@@ -1783,7 +1783,10 @@
     <t>2026-07-21</t>
   </si>
   <si>
-    <t>105279.5</t>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>114089.5</t>
   </si>
   <si>
     <t>104398.5</t>
@@ -1804,43 +1807,46 @@
     <t>96469.5</t>
   </si>
   <si>
-    <t>87219</t>
-  </si>
-  <si>
-    <t>97000</t>
-  </si>
-  <si>
-    <t>16456.41</t>
-  </si>
-  <si>
-    <t>16328.76</t>
-  </si>
-  <si>
-    <t>16146.95</t>
-  </si>
-  <si>
-    <t>15863</t>
-  </si>
-  <si>
-    <t>15529.33</t>
-  </si>
-  <si>
-    <t>15536.87</t>
-  </si>
-  <si>
-    <t>15506.54</t>
-  </si>
-  <si>
-    <t>15368.7</t>
-  </si>
-  <si>
-    <t>15072.67</t>
-  </si>
-  <si>
-    <t>13682.11</t>
-  </si>
-  <si>
-    <t>12651.73</t>
+    <t>96029</t>
+  </si>
+  <si>
+    <t>95000</t>
+  </si>
+  <si>
+    <t>15878.94</t>
+  </si>
+  <si>
+    <t>15883.39</t>
+  </si>
+  <si>
+    <t>14481.96</t>
+  </si>
+  <si>
+    <t>14320.71</t>
+  </si>
+  <si>
+    <t>14068.88</t>
+  </si>
+  <si>
+    <t>13772.95</t>
+  </si>
+  <si>
+    <t>13779.64</t>
+  </si>
+  <si>
+    <t>13752.73</t>
+  </si>
+  <si>
+    <t>13630.49</t>
+  </si>
+  <si>
+    <t>13367.94</t>
+  </si>
+  <si>
+    <t>13329.37</t>
+  </si>
+  <si>
+    <t>12393.42</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D587"/>
+  <dimension ref="A1:D588"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10107,30 +10113,30 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566">
-        <v>114089.5</v>
-      </c>
-      <c r="D566">
-        <v>14866.47</v>
+      <c r="C566" t="s">
+        <v>590</v>
+      </c>
+      <c r="D566" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567">
-        <v>137399.5</v>
-      </c>
-      <c r="D567">
-        <v>18921.66</v>
+      <c r="C567" t="s">
+        <v>590</v>
+      </c>
+      <c r="D567" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10177,142 +10183,142 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
-      <c r="C571" t="s">
-        <v>589</v>
-      </c>
-      <c r="D571" t="s">
-        <v>598</v>
+      <c r="C571">
+        <v>105279.5</v>
+      </c>
+      <c r="D571">
+        <v>16456.41</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
       <c r="C572" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D572" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
       <c r="C573" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D573" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
       <c r="C574" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D574" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
       <c r="C575" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D575" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D576" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D577" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D578" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D579" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580">
-        <v>96029</v>
-      </c>
-      <c r="D580">
-        <v>12479.47</v>
+      <c r="C580" t="s">
+        <v>597</v>
+      </c>
+      <c r="D580" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10387,30 +10393,44 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586" t="s">
-        <v>596</v>
-      </c>
-      <c r="D586" t="s">
-        <v>607</v>
+      <c r="C586">
+        <v>87219</v>
+      </c>
+      <c r="D586">
+        <v>13682.11</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>597</v>
-      </c>
-      <c r="D587" t="s">
+      <c r="C587">
+        <v>97000</v>
+      </c>
+      <c r="D587">
+        <v>12651.73</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4">
+      <c r="A588" s="1">
         <v>608</v>
+      </c>
+      <c r="B588" t="s">
+        <v>589</v>
+      </c>
+      <c r="C588" t="s">
+        <v>598</v>
+      </c>
+      <c r="D588" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="612">
   <si>
     <t>Date</t>
   </si>
@@ -1786,40 +1786,40 @@
     <t>2026-07-22</t>
   </si>
   <si>
-    <t>114089.5</t>
-  </si>
-  <si>
-    <t>104398.5</t>
-  </si>
-  <si>
-    <t>103077</t>
-  </si>
-  <si>
-    <t>101315</t>
-  </si>
-  <si>
-    <t>99112.5</t>
-  </si>
-  <si>
-    <t>98231.5</t>
-  </si>
-  <si>
-    <t>96469.5</t>
-  </si>
-  <si>
-    <t>96029</t>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>121859.5</t>
+  </si>
+  <si>
+    <t>119036.5</t>
+  </si>
+  <si>
+    <t>110097</t>
+  </si>
+  <si>
+    <t>108215</t>
+  </si>
+  <si>
+    <t>105862.5</t>
+  </si>
+  <si>
+    <t>104921.5</t>
+  </si>
+  <si>
+    <t>103039.5</t>
+  </si>
+  <si>
+    <t>102569</t>
   </si>
   <si>
     <t>95000</t>
   </si>
   <si>
-    <t>15878.94</t>
-  </si>
-  <si>
     <t>15883.39</t>
   </si>
   <si>
-    <t>14481.96</t>
+    <t>15480.55</t>
   </si>
   <si>
     <t>14320.71</t>
@@ -1846,7 +1846,10 @@
     <t>13329.37</t>
   </si>
   <si>
-    <t>12393.42</t>
+    <t>13357.82</t>
+  </si>
+  <si>
+    <t>12383.2</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D588"/>
+  <dimension ref="A1:D589"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10113,16 +10116,16 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566" s="1">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="B566" t="s">
         <v>567</v>
       </c>
-      <c r="C566" t="s">
-        <v>590</v>
-      </c>
-      <c r="D566" t="s">
-        <v>599</v>
+      <c r="C566">
+        <v>114089.5</v>
+      </c>
+      <c r="D566">
+        <v>15878.94</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10133,7 +10136,7 @@
         <v>568</v>
       </c>
       <c r="C567" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D567" t="s">
         <v>600</v>
@@ -10141,16 +10144,16 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>566</v>
+        <v>588</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568">
-        <v>134216.5</v>
-      </c>
-      <c r="D568">
-        <v>18441.76</v>
+      <c r="C568" t="s">
+        <v>592</v>
+      </c>
+      <c r="D568" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10197,16 +10200,16 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572" t="s">
-        <v>591</v>
-      </c>
-      <c r="D572" t="s">
-        <v>601</v>
+      <c r="C572">
+        <v>104398.5</v>
+      </c>
+      <c r="D572">
+        <v>14481.96</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10217,7 +10220,7 @@
         <v>574</v>
       </c>
       <c r="C573" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D573" t="s">
         <v>602</v>
@@ -10231,7 +10234,7 @@
         <v>575</v>
       </c>
       <c r="C574" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D574" t="s">
         <v>603</v>
@@ -10245,7 +10248,7 @@
         <v>576</v>
       </c>
       <c r="C575" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D575" t="s">
         <v>604</v>
@@ -10259,7 +10262,7 @@
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D576" t="s">
         <v>605</v>
@@ -10273,7 +10276,7 @@
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D577" t="s">
         <v>606</v>
@@ -10287,7 +10290,7 @@
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D578" t="s">
         <v>607</v>
@@ -10301,7 +10304,7 @@
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D579" t="s">
         <v>608</v>
@@ -10315,7 +10318,7 @@
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D580" t="s">
         <v>609</v>
@@ -10323,16 +10326,16 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581">
-        <v>122189</v>
-      </c>
-      <c r="D581">
-        <v>15912.98</v>
+      <c r="C581" t="s">
+        <v>598</v>
+      </c>
+      <c r="D581" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10421,16 +10424,30 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588" t="s">
-        <v>598</v>
-      </c>
-      <c r="D588" t="s">
-        <v>610</v>
+      <c r="C588">
+        <v>95000</v>
+      </c>
+      <c r="D588">
+        <v>12393.42</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4">
+      <c r="A589" s="1">
+        <v>609</v>
+      </c>
+      <c r="B589" t="s">
+        <v>590</v>
+      </c>
+      <c r="C589" t="s">
+        <v>599</v>
+      </c>
+      <c r="D589" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="612">
   <si>
     <t>Date</t>
   </si>
@@ -1789,67 +1789,67 @@
     <t>2026-07-23</t>
   </si>
   <si>
-    <t>121859.5</t>
-  </si>
-  <si>
-    <t>119036.5</t>
-  </si>
-  <si>
-    <t>110097</t>
-  </si>
-  <si>
-    <t>108215</t>
-  </si>
-  <si>
-    <t>105862.5</t>
-  </si>
-  <si>
-    <t>104921.5</t>
-  </si>
-  <si>
-    <t>103039.5</t>
-  </si>
-  <si>
-    <t>102569</t>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>134216.5</t>
+  </si>
+  <si>
+    <t>131033.5</t>
+  </si>
+  <si>
+    <t>122015</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>118301.5</t>
+  </si>
+  <si>
+    <t>116179.5</t>
+  </si>
+  <si>
+    <t>115649</t>
   </si>
   <si>
     <t>95000</t>
   </si>
   <si>
-    <t>15883.39</t>
-  </si>
-  <si>
-    <t>15480.55</t>
-  </si>
-  <si>
-    <t>14320.71</t>
-  </si>
-  <si>
-    <t>14068.88</t>
-  </si>
-  <si>
-    <t>13772.95</t>
-  </si>
-  <si>
-    <t>13779.64</t>
-  </si>
-  <si>
-    <t>13752.73</t>
-  </si>
-  <si>
-    <t>13630.49</t>
-  </si>
-  <si>
-    <t>13367.94</t>
-  </si>
-  <si>
-    <t>13329.37</t>
-  </si>
-  <si>
-    <t>13357.82</t>
-  </si>
-  <si>
-    <t>12383.2</t>
+    <t>17454.69</t>
+  </si>
+  <si>
+    <t>16991.3</t>
+  </si>
+  <si>
+    <t>15863</t>
+  </si>
+  <si>
+    <t>15529.33</t>
+  </si>
+  <si>
+    <t>15536.87</t>
+  </si>
+  <si>
+    <t>15506.54</t>
+  </si>
+  <si>
+    <t>15368.7</t>
+  </si>
+  <si>
+    <t>15072.67</t>
+  </si>
+  <si>
+    <t>15029.19</t>
+  </si>
+  <si>
+    <t>15061.26</t>
+  </si>
+  <si>
+    <t>15057.71</t>
+  </si>
+  <si>
+    <t>12373.54</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D589"/>
+  <dimension ref="A1:D590"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10130,16 +10130,16 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567" s="1">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="B567" t="s">
         <v>568</v>
       </c>
-      <c r="C567" t="s">
-        <v>591</v>
-      </c>
-      <c r="D567" t="s">
-        <v>600</v>
+      <c r="C567">
+        <v>121859.5</v>
+      </c>
+      <c r="D567">
+        <v>15883.39</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10153,21 +10153,21 @@
         <v>592</v>
       </c>
       <c r="D568" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569">
-        <v>138443.5</v>
-      </c>
-      <c r="D569">
-        <v>17952.17</v>
+      <c r="C569" t="s">
+        <v>593</v>
+      </c>
+      <c r="D569" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10214,16 +10214,16 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>593</v>
-      </c>
-      <c r="D573" t="s">
-        <v>602</v>
+      <c r="C573">
+        <v>110097</v>
+      </c>
+      <c r="D573">
+        <v>14320.71</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10237,7 +10237,7 @@
         <v>594</v>
       </c>
       <c r="D574" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10251,7 +10251,7 @@
         <v>595</v>
       </c>
       <c r="D575" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10265,7 +10265,7 @@
         <v>595</v>
       </c>
       <c r="D576" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10279,7 +10279,7 @@
         <v>595</v>
       </c>
       <c r="D577" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10293,7 +10293,7 @@
         <v>596</v>
       </c>
       <c r="D578" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -10307,7 +10307,7 @@
         <v>597</v>
       </c>
       <c r="D579" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -10321,7 +10321,7 @@
         <v>598</v>
       </c>
       <c r="D580" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10335,21 +10335,21 @@
         <v>598</v>
       </c>
       <c r="D581" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582">
-        <v>115649</v>
-      </c>
-      <c r="D582">
-        <v>15909.23</v>
+      <c r="C582" t="s">
+        <v>598</v>
+      </c>
+      <c r="D582" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -10438,15 +10438,29 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
+      <c r="C589">
+        <v>95000</v>
+      </c>
+      <c r="D589">
+        <v>12383.2</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4">
+      <c r="A590" s="1">
+        <v>610</v>
+      </c>
+      <c r="B590" t="s">
+        <v>591</v>
+      </c>
+      <c r="C590" t="s">
         <v>599</v>
       </c>
-      <c r="D589" t="s">
+      <c r="D590" t="s">
         <v>611</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="615">
   <si>
     <t>Date</t>
   </si>
@@ -1792,10 +1792,10 @@
     <t>2026-07-24</t>
   </si>
   <si>
-    <t>134216.5</t>
-  </si>
-  <si>
-    <t>131033.5</t>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>124137</t>
   </si>
   <si>
     <t>122015</t>
@@ -1807,49 +1807,58 @@
     <t>118301.5</t>
   </si>
   <si>
-    <t>116179.5</t>
-  </si>
-  <si>
     <t>115649</t>
   </si>
   <si>
+    <t>111405</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>107161</t>
+  </si>
+  <si>
     <t>95000</t>
   </si>
   <si>
-    <t>17454.69</t>
-  </si>
-  <si>
-    <t>16991.3</t>
-  </si>
-  <si>
-    <t>15863</t>
-  </si>
-  <si>
-    <t>15529.33</t>
-  </si>
-  <si>
-    <t>15536.87</t>
-  </si>
-  <si>
-    <t>15506.54</t>
-  </si>
-  <si>
-    <t>15368.7</t>
-  </si>
-  <si>
-    <t>15072.67</t>
-  </si>
-  <si>
-    <t>15029.19</t>
-  </si>
-  <si>
-    <t>15061.26</t>
-  </si>
-  <si>
-    <t>15057.71</t>
-  </si>
-  <si>
-    <t>12373.54</t>
+    <t>17060.06</t>
+  </si>
+  <si>
+    <t>16760.06</t>
+  </si>
+  <si>
+    <t>16407.52</t>
+  </si>
+  <si>
+    <t>16415.49</t>
+  </si>
+  <si>
+    <t>16383.44</t>
+  </si>
+  <si>
+    <t>16237.81</t>
+  </si>
+  <si>
+    <t>15879.09</t>
+  </si>
+  <si>
+    <t>15912.98</t>
+  </si>
+  <si>
+    <t>15909.23</t>
+  </si>
+  <si>
+    <t>15348.67</t>
+  </si>
+  <si>
+    <t>15059.19</t>
+  </si>
+  <si>
+    <t>14758.52</t>
+  </si>
+  <si>
+    <t>12385.76</t>
   </si>
 </sst>
 </file>
@@ -2207,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D590"/>
+  <dimension ref="A1:D591"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10144,30 +10153,30 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568" s="1">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="B568" t="s">
         <v>569</v>
       </c>
-      <c r="C568" t="s">
-        <v>592</v>
-      </c>
-      <c r="D568" t="s">
-        <v>600</v>
+      <c r="C568">
+        <v>134216.5</v>
+      </c>
+      <c r="D568">
+        <v>17454.69</v>
       </c>
     </row>
     <row r="569" spans="1:4">
       <c r="A569" s="1">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="B569" t="s">
         <v>570</v>
       </c>
-      <c r="C569" t="s">
-        <v>593</v>
-      </c>
-      <c r="D569" t="s">
-        <v>601</v>
+      <c r="C569">
+        <v>131033.5</v>
+      </c>
+      <c r="D569">
+        <v>16991.3</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -10214,21 +10223,21 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573">
-        <v>110097</v>
-      </c>
-      <c r="D573">
-        <v>14320.71</v>
+      <c r="C573" t="s">
+        <v>593</v>
+      </c>
+      <c r="D573" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
@@ -10237,12 +10246,12 @@
         <v>594</v>
       </c>
       <c r="D574" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
@@ -10251,12 +10260,12 @@
         <v>595</v>
       </c>
       <c r="D575" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
@@ -10265,12 +10274,12 @@
         <v>595</v>
       </c>
       <c r="D576" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
@@ -10279,12 +10288,12 @@
         <v>595</v>
       </c>
       <c r="D577" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
@@ -10293,32 +10302,32 @@
         <v>596</v>
       </c>
       <c r="D578" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>597</v>
-      </c>
-      <c r="D579" t="s">
-        <v>607</v>
+      <c r="C579">
+        <v>116179.5</v>
+      </c>
+      <c r="D579">
+        <v>15072.67</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D580" t="s">
         <v>608</v>
@@ -10326,13 +10335,13 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
       <c r="C581" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D581" t="s">
         <v>609</v>
@@ -10340,13 +10349,13 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
       <c r="C582" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D582" t="s">
         <v>610</v>
@@ -10354,44 +10363,44 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583">
-        <v>117705</v>
-      </c>
-      <c r="D583">
-        <v>15348.67</v>
+      <c r="C583" t="s">
+        <v>598</v>
+      </c>
+      <c r="D583" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584">
-        <v>115463</v>
-      </c>
-      <c r="D584">
-        <v>15059.19</v>
+      <c r="C584" t="s">
+        <v>599</v>
+      </c>
+      <c r="D584" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
-      <c r="C585">
-        <v>101000</v>
-      </c>
-      <c r="D585">
-        <v>13165.49</v>
+      <c r="C585" t="s">
+        <v>600</v>
+      </c>
+      <c r="D585" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10452,16 +10461,30 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>599</v>
-      </c>
-      <c r="D590" t="s">
-        <v>611</v>
+      <c r="C590">
+        <v>95000</v>
+      </c>
+      <c r="D590">
+        <v>12373.54</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4">
+      <c r="A591" s="1">
+        <v>609</v>
+      </c>
+      <c r="B591" t="s">
+        <v>592</v>
+      </c>
+      <c r="C591" t="s">
+        <v>601</v>
+      </c>
+      <c r="D591" t="s">
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="614">
   <si>
     <t>Date</t>
   </si>
@@ -1795,39 +1795,30 @@
     <t>2026-07-27</t>
   </si>
   <si>
-    <t>124137</t>
-  </si>
-  <si>
-    <t>122015</t>
-  </si>
-  <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>118301.5</t>
-  </si>
-  <si>
-    <t>115649</t>
-  </si>
-  <si>
-    <t>111405</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>107161</t>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>105862.5</t>
+  </si>
+  <si>
+    <t>104921.5</t>
+  </si>
+  <si>
+    <t>103039.5</t>
+  </si>
+  <si>
+    <t>102569</t>
+  </si>
+  <si>
+    <t>98805</t>
+  </si>
+  <si>
+    <t>89395</t>
   </si>
   <si>
     <t>95000</t>
   </si>
   <si>
-    <t>17060.06</t>
-  </si>
-  <si>
-    <t>16760.06</t>
-  </si>
-  <si>
     <t>16407.52</t>
   </si>
   <si>
@@ -1840,6 +1831,9 @@
     <t>16237.81</t>
   </si>
   <si>
+    <t>15925.04</t>
+  </si>
+  <si>
     <t>15879.09</t>
   </si>
   <si>
@@ -1852,13 +1846,16 @@
     <t>15348.67</t>
   </si>
   <si>
-    <t>15059.19</t>
-  </si>
-  <si>
-    <t>14758.52</t>
-  </si>
-  <si>
-    <t>12385.76</t>
+    <t>13881.57</t>
+  </si>
+  <si>
+    <t>13870.74</t>
+  </si>
+  <si>
+    <t>13884.43</t>
+  </si>
+  <si>
+    <t>12398.18</t>
   </si>
 </sst>
 </file>
@@ -2216,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D591"/>
+  <dimension ref="A1:D592"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10223,105 +10220,105 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>593</v>
-      </c>
-      <c r="D573" t="s">
-        <v>602</v>
+      <c r="C573">
+        <v>124137</v>
+      </c>
+      <c r="D573">
+        <v>17060.06</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574" t="s">
-        <v>594</v>
-      </c>
-      <c r="D574" t="s">
-        <v>603</v>
+      <c r="C574">
+        <v>122015</v>
+      </c>
+      <c r="D574">
+        <v>16760.06</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
       <c r="C575" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D575" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
       <c r="C576" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D576" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D577" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D578" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579">
-        <v>116179.5</v>
-      </c>
-      <c r="D579">
-        <v>15072.67</v>
+      <c r="C579" t="s">
+        <v>596</v>
+      </c>
+      <c r="D579" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
@@ -10330,12 +10327,12 @@
         <v>597</v>
       </c>
       <c r="D580" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
@@ -10344,12 +10341,12 @@
         <v>597</v>
       </c>
       <c r="D581" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
@@ -10358,12 +10355,12 @@
         <v>597</v>
       </c>
       <c r="D582" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
@@ -10372,35 +10369,35 @@
         <v>598</v>
       </c>
       <c r="D583" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>599</v>
-      </c>
-      <c r="D584" t="s">
-        <v>612</v>
+      <c r="C584">
+        <v>109283</v>
+      </c>
+      <c r="D584">
+        <v>15059.19</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
-      <c r="C585" t="s">
-        <v>600</v>
-      </c>
-      <c r="D585" t="s">
-        <v>613</v>
+      <c r="C585">
+        <v>107161</v>
+      </c>
+      <c r="D585">
+        <v>14758.52</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10447,44 +10444,58 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>95000</v>
-      </c>
-      <c r="D589">
-        <v>12383.2</v>
+      <c r="C589" t="s">
+        <v>599</v>
+      </c>
+      <c r="D589" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590">
-        <v>95000</v>
-      </c>
-      <c r="D590">
-        <v>12373.54</v>
+      <c r="C590" t="s">
+        <v>599</v>
+      </c>
+      <c r="D590" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
       <c r="C591" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D591" t="s">
-        <v>614</v>
+        <v>612</v>
+      </c>
+    </row>
+    <row r="592" spans="1:4">
+      <c r="A592" s="1">
+        <v>611</v>
+      </c>
+      <c r="B592" t="s">
+        <v>593</v>
+      </c>
+      <c r="C592" t="s">
+        <v>600</v>
+      </c>
+      <c r="D592" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="617">
   <si>
     <t>Date</t>
   </si>
@@ -1798,64 +1798,73 @@
     <t>2026-07-28</t>
   </si>
   <si>
-    <t>105862.5</t>
-  </si>
-  <si>
-    <t>104921.5</t>
-  </si>
-  <si>
-    <t>103039.5</t>
-  </si>
-  <si>
-    <t>102569</t>
-  </si>
-  <si>
-    <t>98805</t>
-  </si>
-  <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>95000</t>
-  </si>
-  <si>
-    <t>16407.52</t>
-  </si>
-  <si>
-    <t>16415.49</t>
-  </si>
-  <si>
-    <t>16383.44</t>
-  </si>
-  <si>
-    <t>16237.81</t>
-  </si>
-  <si>
-    <t>15925.04</t>
-  </si>
-  <si>
-    <t>15879.09</t>
-  </si>
-  <si>
-    <t>15912.98</t>
-  </si>
-  <si>
-    <t>15909.23</t>
-  </si>
-  <si>
-    <t>15348.67</t>
-  </si>
-  <si>
-    <t>13881.57</t>
-  </si>
-  <si>
-    <t>13870.74</t>
-  </si>
-  <si>
-    <t>13884.43</t>
-  </si>
-  <si>
-    <t>12398.18</t>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>126789.5</t>
+  </si>
+  <si>
+    <t>125728.5</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>118301.5</t>
+  </si>
+  <si>
+    <t>116179.5</t>
+  </si>
+  <si>
+    <t>115649</t>
+  </si>
+  <si>
+    <t>111405</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>107161</t>
+  </si>
+  <si>
+    <t>93500</t>
+  </si>
+  <si>
+    <t>16456.41</t>
+  </si>
+  <si>
+    <t>16328.76</t>
+  </si>
+  <si>
+    <t>15506.54</t>
+  </si>
+  <si>
+    <t>15368.7</t>
+  </si>
+  <si>
+    <t>15072.67</t>
+  </si>
+  <si>
+    <t>15029.19</t>
+  </si>
+  <si>
+    <t>15061.26</t>
+  </si>
+  <si>
+    <t>15057.71</t>
+  </si>
+  <si>
+    <t>14527.15</t>
+  </si>
+  <si>
+    <t>14253.17</t>
+  </si>
+  <si>
+    <t>13968.59</t>
+  </si>
+  <si>
+    <t>12195.94</t>
   </si>
 </sst>
 </file>
@@ -2213,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D592"/>
+  <dimension ref="A1:D593"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10192,30 +10201,30 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
-      <c r="C571">
-        <v>105279.5</v>
-      </c>
-      <c r="D571">
-        <v>16456.41</v>
+      <c r="C571" t="s">
+        <v>595</v>
+      </c>
+      <c r="D571" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572">
-        <v>104398.5</v>
-      </c>
-      <c r="D572">
-        <v>14481.96</v>
+      <c r="C572" t="s">
+        <v>596</v>
+      </c>
+      <c r="D572" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10248,156 +10257,156 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575" t="s">
-        <v>594</v>
-      </c>
-      <c r="D575" t="s">
-        <v>601</v>
+      <c r="C575">
+        <v>105862.5</v>
+      </c>
+      <c r="D575">
+        <v>16407.52</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576" t="s">
-        <v>594</v>
-      </c>
-      <c r="D576" t="s">
-        <v>602</v>
+      <c r="C576">
+        <v>105862.5</v>
+      </c>
+      <c r="D576">
+        <v>16415.49</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D577" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
       <c r="C578" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="D578" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D579" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D580" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
       <c r="C581" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D581" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
       <c r="C582" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D582" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D583" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584">
-        <v>109283</v>
-      </c>
-      <c r="D584">
-        <v>15059.19</v>
+      <c r="C584" t="s">
+        <v>602</v>
+      </c>
+      <c r="D584" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
-      <c r="C585">
-        <v>107161</v>
-      </c>
-      <c r="D585">
-        <v>14758.52</v>
+      <c r="C585" t="s">
+        <v>603</v>
+      </c>
+      <c r="D585" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10444,58 +10453,72 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>599</v>
-      </c>
-      <c r="D589" t="s">
-        <v>610</v>
+      <c r="C589">
+        <v>89395</v>
+      </c>
+      <c r="D589">
+        <v>13881.57</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>599</v>
-      </c>
-      <c r="D590" t="s">
-        <v>611</v>
+      <c r="C590">
+        <v>89395</v>
+      </c>
+      <c r="D590">
+        <v>13870.74</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
-      <c r="C591" t="s">
-        <v>599</v>
-      </c>
-      <c r="D591" t="s">
-        <v>612</v>
+      <c r="C591">
+        <v>89395</v>
+      </c>
+      <c r="D591">
+        <v>13884.43</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>600</v>
-      </c>
-      <c r="D592" t="s">
+      <c r="C592">
+        <v>95000</v>
+      </c>
+      <c r="D592">
+        <v>12398.18</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4">
+      <c r="A593" s="1">
         <v>613</v>
+      </c>
+      <c r="B593" t="s">
+        <v>594</v>
+      </c>
+      <c r="C593" t="s">
+        <v>604</v>
+      </c>
+      <c r="D593" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="614">
   <si>
     <t>Date</t>
   </si>
@@ -1801,70 +1801,61 @@
     <t>2026-07-29</t>
   </si>
   <si>
-    <t>126789.5</t>
-  </si>
-  <si>
-    <t>125728.5</t>
-  </si>
-  <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>118301.5</t>
-  </si>
-  <si>
-    <t>116179.5</t>
-  </si>
-  <si>
-    <t>115649</t>
-  </si>
-  <si>
-    <t>111405</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>107161</t>
-  </si>
-  <si>
-    <t>93500</t>
-  </si>
-  <si>
-    <t>16456.41</t>
-  </si>
-  <si>
-    <t>16328.76</t>
-  </si>
-  <si>
-    <t>15506.54</t>
-  </si>
-  <si>
-    <t>15368.7</t>
-  </si>
-  <si>
-    <t>15072.67</t>
-  </si>
-  <si>
-    <t>15029.19</t>
-  </si>
-  <si>
-    <t>15061.26</t>
-  </si>
-  <si>
-    <t>15057.71</t>
-  </si>
-  <si>
-    <t>14527.15</t>
-  </si>
-  <si>
-    <t>14253.17</t>
-  </si>
-  <si>
-    <t>13968.59</t>
-  </si>
-  <si>
-    <t>12195.94</t>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>133959.5</t>
+  </si>
+  <si>
+    <t>126112.5</t>
+  </si>
+  <si>
+    <t>122749.5</t>
+  </si>
+  <si>
+    <t>122189</t>
+  </si>
+  <si>
+    <t>117705</t>
+  </si>
+  <si>
+    <t>113221</t>
+  </si>
+  <si>
+    <t>106495</t>
+  </si>
+  <si>
+    <t>90500</t>
+  </si>
+  <si>
+    <t>13664.56</t>
+  </si>
+  <si>
+    <t>12901.02</t>
+  </si>
+  <si>
+    <t>12515.57</t>
+  </si>
+  <si>
+    <t>12479.47</t>
+  </si>
+  <si>
+    <t>12506.09</t>
+  </si>
+  <si>
+    <t>12503.15</t>
+  </si>
+  <si>
+    <t>12062.6</t>
+  </si>
+  <si>
+    <t>11598.8</t>
+  </si>
+  <si>
+    <t>10909.6</t>
+  </si>
+  <si>
+    <t>11802.19</t>
   </si>
 </sst>
 </file>
@@ -2222,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D593"/>
+  <dimension ref="A1:D594"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10201,30 +10192,30 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
       <c r="C571" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D571" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572" t="s">
-        <v>596</v>
-      </c>
-      <c r="D572" t="s">
-        <v>606</v>
+      <c r="C572">
+        <v>125728.5</v>
+      </c>
+      <c r="D572">
+        <v>16328.76</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10271,142 +10262,142 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576">
-        <v>105862.5</v>
-      </c>
-      <c r="D576">
-        <v>16415.49</v>
+      <c r="C576" t="s">
+        <v>597</v>
+      </c>
+      <c r="D576" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577" t="s">
-        <v>597</v>
-      </c>
-      <c r="D577" t="s">
-        <v>607</v>
+      <c r="C577">
+        <v>119362.5</v>
+      </c>
+      <c r="D577">
+        <v>15506.54</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578" t="s">
-        <v>598</v>
-      </c>
-      <c r="D578" t="s">
-        <v>608</v>
+      <c r="C578">
+        <v>118301.5</v>
+      </c>
+      <c r="D578">
+        <v>15368.7</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D579" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D580" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
       <c r="C581" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D581" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
       <c r="C582" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D582" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D583" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>602</v>
-      </c>
-      <c r="D584" t="s">
-        <v>614</v>
+      <c r="C584">
+        <v>109283</v>
+      </c>
+      <c r="D584">
+        <v>14253.17</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D585" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10453,16 +10444,16 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>89395</v>
-      </c>
-      <c r="D589">
-        <v>13881.57</v>
+      <c r="C589" t="s">
+        <v>602</v>
+      </c>
+      <c r="D589" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10509,16 +10500,30 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>613</v>
+        <v>591</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593" t="s">
-        <v>604</v>
-      </c>
-      <c r="D593" t="s">
-        <v>616</v>
+      <c r="C593">
+        <v>93500</v>
+      </c>
+      <c r="D593">
+        <v>12195.94</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4">
+      <c r="A594" s="1">
+        <v>615</v>
+      </c>
+      <c r="B594" t="s">
+        <v>595</v>
+      </c>
+      <c r="C594" t="s">
+        <v>603</v>
+      </c>
+      <c r="D594" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="616">
   <si>
     <t>Date</t>
   </si>
@@ -1804,58 +1804,64 @@
     <t>2026-07-30</t>
   </si>
   <si>
-    <t>133959.5</t>
-  </si>
-  <si>
-    <t>126112.5</t>
-  </si>
-  <si>
-    <t>122749.5</t>
-  </si>
-  <si>
-    <t>122189</t>
-  </si>
-  <si>
-    <t>117705</t>
-  </si>
-  <si>
-    <t>113221</t>
-  </si>
-  <si>
-    <t>106495</t>
-  </si>
-  <si>
-    <t>90500</t>
-  </si>
-  <si>
-    <t>13664.56</t>
-  </si>
-  <si>
-    <t>12901.02</t>
+    <t>125728.5</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>116179.5</t>
+  </si>
+  <si>
+    <t>111405</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>107161</t>
+  </si>
+  <si>
+    <t>102917</t>
+  </si>
+  <si>
+    <t>100795</t>
+  </si>
+  <si>
+    <t>99203.5</t>
+  </si>
+  <si>
+    <t>13558.56</t>
+  </si>
+  <si>
+    <t>12894.76</t>
   </si>
   <si>
     <t>12515.57</t>
   </si>
   <si>
-    <t>12479.47</t>
-  </si>
-  <si>
-    <t>12506.09</t>
-  </si>
-  <si>
-    <t>12503.15</t>
-  </si>
-  <si>
     <t>12062.6</t>
   </si>
   <si>
+    <t>11835.1</t>
+  </si>
+  <si>
     <t>11598.8</t>
   </si>
   <si>
-    <t>10909.6</t>
-  </si>
-  <si>
-    <t>11802.19</t>
+    <t>11146.17</t>
+  </si>
+  <si>
+    <t>10918.61</t>
+  </si>
+  <si>
+    <t>10911.85</t>
+  </si>
+  <si>
+    <t>10922.79</t>
+  </si>
+  <si>
+    <t>10744.62</t>
   </si>
 </sst>
 </file>
@@ -10192,30 +10198,30 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571" s="1">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="B571" t="s">
         <v>572</v>
       </c>
-      <c r="C571" t="s">
-        <v>596</v>
-      </c>
-      <c r="D571" t="s">
-        <v>604</v>
+      <c r="C571">
+        <v>133959.5</v>
+      </c>
+      <c r="D571">
+        <v>13664.56</v>
       </c>
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572">
-        <v>125728.5</v>
-      </c>
-      <c r="D572">
-        <v>16328.76</v>
+      <c r="C572" t="s">
+        <v>596</v>
+      </c>
+      <c r="D572" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10248,30 +10254,30 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575">
-        <v>105862.5</v>
-      </c>
-      <c r="D575">
-        <v>16407.52</v>
+      <c r="C575" t="s">
+        <v>597</v>
+      </c>
+      <c r="D575" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576" t="s">
-        <v>597</v>
-      </c>
-      <c r="D576" t="s">
-        <v>605</v>
+      <c r="C576">
+        <v>126112.5</v>
+      </c>
+      <c r="D576">
+        <v>12901.02</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10313,49 +10319,49 @@
         <v>598</v>
       </c>
       <c r="D579" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580" t="s">
-        <v>599</v>
-      </c>
-      <c r="D580" t="s">
-        <v>607</v>
+      <c r="C580">
+        <v>122189</v>
+      </c>
+      <c r="D580">
+        <v>12479.47</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>599</v>
-      </c>
-      <c r="D581" t="s">
-        <v>608</v>
+      <c r="C581">
+        <v>122189</v>
+      </c>
+      <c r="D581">
+        <v>12506.09</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>603</v>
+        <v>580</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582" t="s">
-        <v>599</v>
-      </c>
-      <c r="D582" t="s">
-        <v>609</v>
+      <c r="C582">
+        <v>122189</v>
+      </c>
+      <c r="D582">
+        <v>12503.15</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -10366,24 +10372,24 @@
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D583" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584">
-        <v>109283</v>
-      </c>
-      <c r="D584">
-        <v>14253.17</v>
+      <c r="C584" t="s">
+        <v>600</v>
+      </c>
+      <c r="D584" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -10397,7 +10403,7 @@
         <v>601</v>
       </c>
       <c r="D585" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10416,44 +10422,44 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587">
-        <v>97000</v>
-      </c>
-      <c r="D587">
-        <v>12651.73</v>
+      <c r="C587" t="s">
+        <v>602</v>
+      </c>
+      <c r="D587" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588">
-        <v>95000</v>
-      </c>
-      <c r="D588">
-        <v>12393.42</v>
+      <c r="C588" t="s">
+        <v>603</v>
+      </c>
+      <c r="D588" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>602</v>
-      </c>
-      <c r="D589" t="s">
-        <v>612</v>
+      <c r="C589">
+        <v>106495</v>
+      </c>
+      <c r="D589">
+        <v>10909.6</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10472,58 +10478,58 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
-      <c r="C591">
-        <v>89395</v>
-      </c>
-      <c r="D591">
-        <v>13884.43</v>
+      <c r="C591" t="s">
+        <v>603</v>
+      </c>
+      <c r="D591" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592">
-        <v>95000</v>
-      </c>
-      <c r="D592">
-        <v>12398.18</v>
+      <c r="C592" t="s">
+        <v>603</v>
+      </c>
+      <c r="D592" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593">
-        <v>93500</v>
-      </c>
-      <c r="D593">
-        <v>12195.94</v>
+      <c r="C593" t="s">
+        <v>604</v>
+      </c>
+      <c r="D593" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>603</v>
-      </c>
-      <c r="D594" t="s">
-        <v>613</v>
+      <c r="C594">
+        <v>90500</v>
+      </c>
+      <c r="D594">
+        <v>11802.19</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="619">
   <si>
     <t>Date</t>
   </si>
@@ -1804,42 +1804,57 @@
     <t>2026-07-30</t>
   </si>
   <si>
-    <t>125728.5</t>
-  </si>
-  <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>116179.5</t>
-  </si>
-  <si>
-    <t>111405</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>107161</t>
-  </si>
-  <si>
-    <t>102917</t>
-  </si>
-  <si>
-    <t>100795</t>
-  </si>
-  <si>
-    <t>99203.5</t>
-  </si>
-  <si>
-    <t>13558.56</t>
-  </si>
-  <si>
-    <t>12894.76</t>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>131157</t>
+  </si>
+  <si>
+    <t>128915</t>
+  </si>
+  <si>
+    <t>122749.5</t>
+  </si>
+  <si>
+    <t>122189</t>
+  </si>
+  <si>
+    <t>117705</t>
+  </si>
+  <si>
+    <t>115463</t>
+  </si>
+  <si>
+    <t>113221</t>
+  </si>
+  <si>
+    <t>110979</t>
+  </si>
+  <si>
+    <t>108737</t>
+  </si>
+  <si>
+    <t>90500</t>
+  </si>
+  <si>
+    <t>13407.6</t>
+  </si>
+  <si>
+    <t>13171.82</t>
   </si>
   <si>
     <t>12515.57</t>
   </si>
   <si>
+    <t>12479.47</t>
+  </si>
+  <si>
+    <t>12506.09</t>
+  </si>
+  <si>
+    <t>12503.15</t>
+  </si>
+  <si>
     <t>12062.6</t>
   </si>
   <si>
@@ -1849,19 +1864,13 @@
     <t>11598.8</t>
   </si>
   <si>
+    <t>11360.92</t>
+  </si>
+  <si>
     <t>11146.17</t>
   </si>
   <si>
-    <t>10918.61</t>
-  </si>
-  <si>
-    <t>10911.85</t>
-  </si>
-  <si>
-    <t>10922.79</t>
-  </si>
-  <si>
-    <t>10744.62</t>
+    <t>11830.61</t>
   </si>
 </sst>
 </file>
@@ -2219,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D594"/>
+  <dimension ref="A1:D595"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10212,58 +10221,58 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572" s="1">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="B572" t="s">
         <v>573</v>
       </c>
-      <c r="C572" t="s">
-        <v>596</v>
-      </c>
-      <c r="D572" t="s">
-        <v>605</v>
+      <c r="C572">
+        <v>125728.5</v>
+      </c>
+      <c r="D572">
+        <v>13558.56</v>
       </c>
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573">
-        <v>124137</v>
-      </c>
-      <c r="D573">
-        <v>17060.06</v>
+      <c r="C573" t="s">
+        <v>597</v>
+      </c>
+      <c r="D573" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574">
-        <v>122015</v>
-      </c>
-      <c r="D574">
-        <v>16760.06</v>
+      <c r="C574" t="s">
+        <v>598</v>
+      </c>
+      <c r="D574" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="575" spans="1:4">
       <c r="A575" s="1">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="B575" t="s">
         <v>576</v>
       </c>
-      <c r="C575" t="s">
-        <v>597</v>
-      </c>
-      <c r="D575" t="s">
-        <v>606</v>
+      <c r="C575">
+        <v>119362.5</v>
+      </c>
+      <c r="D575">
+        <v>12894.76</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10310,142 +10319,142 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
       <c r="C579" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D579" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580">
-        <v>122189</v>
-      </c>
-      <c r="D580">
-        <v>12479.47</v>
+      <c r="C580" t="s">
+        <v>600</v>
+      </c>
+      <c r="D580" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581">
-        <v>122189</v>
-      </c>
-      <c r="D581">
-        <v>12506.09</v>
+      <c r="C581" t="s">
+        <v>600</v>
+      </c>
+      <c r="D581" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582">
-        <v>122189</v>
-      </c>
-      <c r="D582">
-        <v>12503.15</v>
+      <c r="C582" t="s">
+        <v>600</v>
+      </c>
+      <c r="D582" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D583" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
       <c r="C584" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D584" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D585" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586">
-        <v>87219</v>
-      </c>
-      <c r="D586">
-        <v>13682.11</v>
+      <c r="C586" t="s">
+        <v>604</v>
+      </c>
+      <c r="D586" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
       <c r="C587" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D587" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588" t="s">
-        <v>603</v>
-      </c>
-      <c r="D588" t="s">
-        <v>612</v>
+      <c r="C588">
+        <v>100795</v>
+      </c>
+      <c r="D588">
+        <v>10918.61</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -10478,44 +10487,44 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
-      <c r="C591" t="s">
-        <v>603</v>
-      </c>
-      <c r="D591" t="s">
-        <v>613</v>
+      <c r="C591">
+        <v>100795</v>
+      </c>
+      <c r="D591">
+        <v>10911.85</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>603</v>
-      </c>
-      <c r="D592" t="s">
-        <v>614</v>
+      <c r="C592">
+        <v>100795</v>
+      </c>
+      <c r="D592">
+        <v>10922.79</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593" t="s">
-        <v>604</v>
-      </c>
-      <c r="D593" t="s">
-        <v>615</v>
+      <c r="C593">
+        <v>99203.5</v>
+      </c>
+      <c r="D593">
+        <v>10744.62</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -10530,6 +10539,20 @@
       </c>
       <c r="D594">
         <v>11802.19</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4">
+      <c r="A595" s="1">
+        <v>615</v>
+      </c>
+      <c r="B595" t="s">
+        <v>596</v>
+      </c>
+      <c r="C595" t="s">
+        <v>606</v>
+      </c>
+      <c r="D595" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="617">
   <si>
     <t>Date</t>
   </si>
@@ -1807,70 +1807,64 @@
     <t>2026-07-31</t>
   </si>
   <si>
-    <t>131157</t>
-  </si>
-  <si>
-    <t>128915</t>
-  </si>
-  <si>
-    <t>122749.5</t>
-  </si>
-  <si>
-    <t>122189</t>
-  </si>
-  <si>
-    <t>117705</t>
-  </si>
-  <si>
-    <t>115463</t>
-  </si>
-  <si>
-    <t>113221</t>
-  </si>
-  <si>
-    <t>110979</t>
-  </si>
-  <si>
-    <t>108737</t>
-  </si>
-  <si>
-    <t>90500</t>
-  </si>
-  <si>
-    <t>13407.6</t>
-  </si>
-  <si>
-    <t>13171.82</t>
-  </si>
-  <si>
-    <t>12515.57</t>
-  </si>
-  <si>
-    <t>12479.47</t>
-  </si>
-  <si>
-    <t>12506.09</t>
-  </si>
-  <si>
-    <t>12503.15</t>
-  </si>
-  <si>
-    <t>12062.6</t>
-  </si>
-  <si>
-    <t>11835.1</t>
-  </si>
-  <si>
-    <t>11598.8</t>
-  </si>
-  <si>
-    <t>11360.92</t>
-  </si>
-  <si>
-    <t>11146.17</t>
-  </si>
-  <si>
-    <t>11830.61</t>
+    <t>110097</t>
+  </si>
+  <si>
+    <t>105862.5</t>
+  </si>
+  <si>
+    <t>102569</t>
+  </si>
+  <si>
+    <t>96923</t>
+  </si>
+  <si>
+    <t>95041</t>
+  </si>
+  <si>
+    <t>93159</t>
+  </si>
+  <si>
+    <t>89395</t>
+  </si>
+  <si>
+    <t>87983.5</t>
+  </si>
+  <si>
+    <t>85160.5</t>
+  </si>
+  <si>
+    <t>17060.06</t>
+  </si>
+  <si>
+    <t>16415.49</t>
+  </si>
+  <si>
+    <t>15879.09</t>
+  </si>
+  <si>
+    <t>15059.19</t>
+  </si>
+  <si>
+    <t>14758.52</t>
+  </si>
+  <si>
+    <t>14455.84</t>
+  </si>
+  <si>
+    <t>13893.03</t>
+  </si>
+  <si>
+    <t>13881.57</t>
+  </si>
+  <si>
+    <t>13898.36</t>
+  </si>
+  <si>
+    <t>13671.65</t>
+  </si>
+  <si>
+    <t>13230.26</t>
   </si>
 </sst>
 </file>
@@ -10235,7 +10229,7 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
@@ -10244,21 +10238,21 @@
         <v>597</v>
       </c>
       <c r="D573" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="574" spans="1:4">
       <c r="A574" s="1">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="B574" t="s">
         <v>575</v>
       </c>
-      <c r="C574" t="s">
-        <v>598</v>
-      </c>
-      <c r="D574" t="s">
-        <v>608</v>
+      <c r="C574">
+        <v>128915</v>
+      </c>
+      <c r="D574">
+        <v>13171.82</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10277,16 +10271,16 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576">
-        <v>126112.5</v>
-      </c>
-      <c r="D576">
-        <v>12901.02</v>
+      <c r="C576" t="s">
+        <v>598</v>
+      </c>
+      <c r="D576" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10319,156 +10313,156 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>599</v>
-      </c>
-      <c r="D579" t="s">
-        <v>609</v>
+      <c r="C579">
+        <v>122749.5</v>
+      </c>
+      <c r="D579">
+        <v>12515.57</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D580" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>600</v>
-      </c>
-      <c r="D581" t="s">
-        <v>611</v>
+      <c r="C581">
+        <v>122189</v>
+      </c>
+      <c r="D581">
+        <v>12506.09</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582" t="s">
-        <v>600</v>
-      </c>
-      <c r="D582" t="s">
-        <v>612</v>
+      <c r="C582">
+        <v>122189</v>
+      </c>
+      <c r="D582">
+        <v>12503.15</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583" t="s">
-        <v>601</v>
-      </c>
-      <c r="D583" t="s">
-        <v>613</v>
+      <c r="C583">
+        <v>117705</v>
+      </c>
+      <c r="D583">
+        <v>12062.6</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
       <c r="C584" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D584" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D585" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D586" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>605</v>
-      </c>
-      <c r="D587" t="s">
-        <v>617</v>
+      <c r="C587">
+        <v>108737</v>
+      </c>
+      <c r="D587">
+        <v>11146.17</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588">
-        <v>100795</v>
-      </c>
-      <c r="D588">
-        <v>10918.61</v>
+      <c r="C588" t="s">
+        <v>603</v>
+      </c>
+      <c r="D588" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>106495</v>
-      </c>
-      <c r="D589">
-        <v>10909.6</v>
+      <c r="C589" t="s">
+        <v>603</v>
+      </c>
+      <c r="D589" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10501,58 +10495,58 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>613</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592">
-        <v>100795</v>
-      </c>
-      <c r="D592">
-        <v>10922.79</v>
+      <c r="C592" t="s">
+        <v>603</v>
+      </c>
+      <c r="D592" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593">
-        <v>99203.5</v>
-      </c>
-      <c r="D593">
-        <v>10744.62</v>
+      <c r="C593" t="s">
+        <v>604</v>
+      </c>
+      <c r="D593" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594">
-        <v>90500</v>
-      </c>
-      <c r="D594">
-        <v>11802.19</v>
+      <c r="C594" t="s">
+        <v>605</v>
+      </c>
+      <c r="D594" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595" t="s">
-        <v>606</v>
-      </c>
-      <c r="D595" t="s">
-        <v>618</v>
+      <c r="C595">
+        <v>90500</v>
+      </c>
+      <c r="D595">
+        <v>11830.61</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="620">
   <si>
     <t>Date</t>
   </si>
@@ -1807,16 +1807,19 @@
     <t>2026-07-31</t>
   </si>
   <si>
-    <t>110097</t>
-  </si>
-  <si>
-    <t>105862.5</t>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>104921.5</t>
+  </si>
+  <si>
+    <t>103039.5</t>
   </si>
   <si>
     <t>102569</t>
   </si>
   <si>
-    <t>96923</t>
+    <t>98805</t>
   </si>
   <si>
     <t>95041</t>
@@ -1825,46 +1828,52 @@
     <t>93159</t>
   </si>
   <si>
+    <t>91277</t>
+  </si>
+  <si>
     <t>89395</t>
   </si>
   <si>
-    <t>87983.5</t>
-  </si>
-  <si>
-    <t>85160.5</t>
-  </si>
-  <si>
-    <t>17060.06</t>
-  </si>
-  <si>
-    <t>16415.49</t>
-  </si>
-  <si>
-    <t>15879.09</t>
-  </si>
-  <si>
-    <t>15059.19</t>
-  </si>
-  <si>
-    <t>14758.52</t>
-  </si>
-  <si>
-    <t>14455.84</t>
-  </si>
-  <si>
-    <t>13893.03</t>
-  </si>
-  <si>
-    <t>13881.57</t>
-  </si>
-  <si>
-    <t>13898.36</t>
-  </si>
-  <si>
-    <t>13671.65</t>
-  </si>
-  <si>
-    <t>13230.26</t>
+    <t>90500</t>
+  </si>
+  <si>
+    <t>12761.38</t>
+  </si>
+  <si>
+    <t>12515.57</t>
+  </si>
+  <si>
+    <t>12479.47</t>
+  </si>
+  <si>
+    <t>12506.09</t>
+  </si>
+  <si>
+    <t>12503.15</t>
+  </si>
+  <si>
+    <t>12062.6</t>
+  </si>
+  <si>
+    <t>11598.8</t>
+  </si>
+  <si>
+    <t>11360.92</t>
+  </si>
+  <si>
+    <t>11146.17</t>
+  </si>
+  <si>
+    <t>10918.61</t>
+  </si>
+  <si>
+    <t>10909.6</t>
+  </si>
+  <si>
+    <t>10901.09</t>
+  </si>
+  <si>
+    <t>11829.04</t>
   </si>
 </sst>
 </file>
@@ -2222,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D595"/>
+  <dimension ref="A1:D596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10229,16 +10238,16 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573" s="1">
-        <v>594</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
         <v>574</v>
       </c>
-      <c r="C573" t="s">
-        <v>597</v>
-      </c>
-      <c r="D573" t="s">
-        <v>606</v>
+      <c r="C573">
+        <v>110097</v>
+      </c>
+      <c r="D573">
+        <v>17060.06</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10271,16 +10280,16 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576" t="s">
-        <v>598</v>
-      </c>
-      <c r="D576" t="s">
-        <v>607</v>
+      <c r="C576">
+        <v>105862.5</v>
+      </c>
+      <c r="D576">
+        <v>16415.49</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10299,184 +10308,184 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578">
-        <v>118301.5</v>
-      </c>
-      <c r="D578">
-        <v>15368.7</v>
+      <c r="C578" t="s">
+        <v>598</v>
+      </c>
+      <c r="D578" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579">
-        <v>122749.5</v>
-      </c>
-      <c r="D579">
-        <v>12515.57</v>
+      <c r="C579" t="s">
+        <v>599</v>
+      </c>
+      <c r="D579" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D580" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581">
-        <v>122189</v>
-      </c>
-      <c r="D581">
-        <v>12506.09</v>
+      <c r="C581" t="s">
+        <v>600</v>
+      </c>
+      <c r="D581" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582">
-        <v>122189</v>
-      </c>
-      <c r="D582">
-        <v>12503.15</v>
+      <c r="C582" t="s">
+        <v>600</v>
+      </c>
+      <c r="D582" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583">
-        <v>117705</v>
-      </c>
-      <c r="D583">
-        <v>12062.6</v>
+      <c r="C583" t="s">
+        <v>601</v>
+      </c>
+      <c r="D583" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>605</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>600</v>
-      </c>
-      <c r="D584" t="s">
-        <v>609</v>
+      <c r="C584">
+        <v>96923</v>
+      </c>
+      <c r="D584">
+        <v>15059.19</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D585" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D586" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587">
-        <v>108737</v>
-      </c>
-      <c r="D587">
-        <v>11146.17</v>
+      <c r="C587" t="s">
+        <v>604</v>
+      </c>
+      <c r="D587" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
       <c r="C588" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D588" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
       <c r="C589" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D589" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590">
-        <v>89395</v>
-      </c>
-      <c r="D590">
-        <v>13870.74</v>
+      <c r="C590" t="s">
+        <v>605</v>
+      </c>
+      <c r="D590" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10495,44 +10504,44 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>603</v>
-      </c>
-      <c r="D592" t="s">
-        <v>614</v>
+      <c r="C592">
+        <v>89395</v>
+      </c>
+      <c r="D592">
+        <v>13898.36</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593" t="s">
-        <v>604</v>
-      </c>
-      <c r="D593" t="s">
-        <v>615</v>
+      <c r="C593">
+        <v>87983.5</v>
+      </c>
+      <c r="D593">
+        <v>13671.65</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>615</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>605</v>
-      </c>
-      <c r="D594" t="s">
-        <v>616</v>
+      <c r="C594">
+        <v>85160.5</v>
+      </c>
+      <c r="D594">
+        <v>13230.26</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -10547,6 +10556,20 @@
       </c>
       <c r="D595">
         <v>11830.61</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4">
+      <c r="A596" s="1">
+        <v>614</v>
+      </c>
+      <c r="B596" t="s">
+        <v>597</v>
+      </c>
+      <c r="C596" t="s">
+        <v>606</v>
+      </c>
+      <c r="D596" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="621">
   <si>
     <t>Date</t>
   </si>
@@ -1810,39 +1810,36 @@
     <t>2026-08-03</t>
   </si>
   <si>
-    <t>104921.5</t>
-  </si>
-  <si>
-    <t>103039.5</t>
-  </si>
-  <si>
-    <t>102569</t>
-  </si>
-  <si>
-    <t>98805</t>
-  </si>
-  <si>
-    <t>95041</t>
-  </si>
-  <si>
-    <t>93159</t>
-  </si>
-  <si>
-    <t>91277</t>
-  </si>
-  <si>
-    <t>89395</t>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>96029</t>
+  </si>
+  <si>
+    <t>92505</t>
+  </si>
+  <si>
+    <t>90743</t>
+  </si>
+  <si>
+    <t>88981</t>
+  </si>
+  <si>
+    <t>87219</t>
+  </si>
+  <si>
+    <t>85457</t>
+  </si>
+  <si>
+    <t>83695</t>
+  </si>
+  <si>
+    <t>79730.5</t>
   </si>
   <si>
     <t>90500</t>
   </si>
   <si>
-    <t>12761.38</t>
-  </si>
-  <si>
-    <t>12515.57</t>
-  </si>
-  <si>
     <t>12479.47</t>
   </si>
   <si>
@@ -1855,6 +1852,9 @@
     <t>12062.6</t>
   </si>
   <si>
+    <t>11835.1</t>
+  </si>
+  <si>
     <t>11598.8</t>
   </si>
   <si>
@@ -1867,13 +1867,16 @@
     <t>10918.61</t>
   </si>
   <si>
-    <t>10909.6</t>
-  </si>
-  <si>
-    <t>10901.09</t>
-  </si>
-  <si>
-    <t>11829.04</t>
+    <t>10397.73</t>
+  </si>
+  <si>
+    <t>10422.77</t>
+  </si>
+  <si>
+    <t>10421.38</t>
+  </si>
+  <si>
+    <t>11823.97</t>
   </si>
 </sst>
 </file>
@@ -2231,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D596"/>
+  <dimension ref="A1:D597"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10308,105 +10311,105 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578" t="s">
-        <v>598</v>
-      </c>
-      <c r="D578" t="s">
-        <v>607</v>
+      <c r="C578">
+        <v>104921.5</v>
+      </c>
+      <c r="D578">
+        <v>12761.38</v>
       </c>
     </row>
     <row r="579" spans="1:4">
       <c r="A579" s="1">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="B579" t="s">
         <v>580</v>
       </c>
-      <c r="C579" t="s">
-        <v>599</v>
-      </c>
-      <c r="D579" t="s">
-        <v>608</v>
+      <c r="C579">
+        <v>103039.5</v>
+      </c>
+      <c r="D579">
+        <v>12515.57</v>
       </c>
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
       <c r="C580" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D580" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
       <c r="C581" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D581" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
       <c r="C582" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D582" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D583" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584">
-        <v>96923</v>
-      </c>
-      <c r="D584">
-        <v>15059.19</v>
+      <c r="C584" t="s">
+        <v>601</v>
+      </c>
+      <c r="D584" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
@@ -10420,7 +10423,7 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
@@ -10434,7 +10437,7 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
@@ -10448,7 +10451,7 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
@@ -10462,30 +10465,30 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>605</v>
-      </c>
-      <c r="D589" t="s">
-        <v>617</v>
+      <c r="C589">
+        <v>89395</v>
+      </c>
+      <c r="D589">
+        <v>10909.6</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>605</v>
-      </c>
-      <c r="D590" t="s">
-        <v>618</v>
+      <c r="C590">
+        <v>89395</v>
+      </c>
+      <c r="D590">
+        <v>10901.09</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10532,35 +10535,35 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>613</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594">
-        <v>85160.5</v>
-      </c>
-      <c r="D594">
-        <v>13230.26</v>
+      <c r="C594" t="s">
+        <v>606</v>
+      </c>
+      <c r="D594" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>593</v>
+        <v>614</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595">
-        <v>90500</v>
-      </c>
-      <c r="D595">
-        <v>11830.61</v>
+      <c r="C595" t="s">
+        <v>606</v>
+      </c>
+      <c r="D595" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
@@ -10570,6 +10573,20 @@
       </c>
       <c r="D596" t="s">
         <v>619</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4">
+      <c r="A597" s="1">
+        <v>616</v>
+      </c>
+      <c r="B597" t="s">
+        <v>598</v>
+      </c>
+      <c r="C597" t="s">
+        <v>607</v>
+      </c>
+      <c r="D597" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="621">
   <si>
     <t>Date</t>
   </si>
@@ -1813,70 +1813,70 @@
     <t>2026-08-04</t>
   </si>
   <si>
-    <t>96029</t>
-  </si>
-  <si>
-    <t>92505</t>
-  </si>
-  <si>
-    <t>90743</t>
-  </si>
-  <si>
-    <t>88981</t>
-  </si>
-  <si>
-    <t>87219</t>
-  </si>
-  <si>
-    <t>85457</t>
-  </si>
-  <si>
-    <t>83695</t>
-  </si>
-  <si>
-    <t>79730.5</t>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>105862.5</t>
+  </si>
+  <si>
+    <t>102569</t>
+  </si>
+  <si>
+    <t>98805</t>
+  </si>
+  <si>
+    <t>96923</t>
+  </si>
+  <si>
+    <t>95041</t>
+  </si>
+  <si>
+    <t>93159</t>
+  </si>
+  <si>
+    <t>91277</t>
+  </si>
+  <si>
+    <t>89395</t>
   </si>
   <si>
     <t>90500</t>
   </si>
   <si>
-    <t>12479.47</t>
-  </si>
-  <si>
-    <t>12506.09</t>
-  </si>
-  <si>
-    <t>12503.15</t>
-  </si>
-  <si>
-    <t>12062.6</t>
-  </si>
-  <si>
-    <t>11835.1</t>
-  </si>
-  <si>
-    <t>11598.8</t>
-  </si>
-  <si>
-    <t>11360.92</t>
-  </si>
-  <si>
-    <t>11146.17</t>
-  </si>
-  <si>
-    <t>10918.61</t>
-  </si>
-  <si>
-    <t>10397.73</t>
-  </si>
-  <si>
-    <t>10422.77</t>
-  </si>
-  <si>
-    <t>10421.38</t>
-  </si>
-  <si>
-    <t>11823.97</t>
+    <t>15536.87</t>
+  </si>
+  <si>
+    <t>15506.54</t>
+  </si>
+  <si>
+    <t>15057.71</t>
+  </si>
+  <si>
+    <t>14527.15</t>
+  </si>
+  <si>
+    <t>14253.17</t>
+  </si>
+  <si>
+    <t>13968.59</t>
+  </si>
+  <si>
+    <t>13682.11</t>
+  </si>
+  <si>
+    <t>13423.48</t>
+  </si>
+  <si>
+    <t>13149.42</t>
+  </si>
+  <si>
+    <t>13138.58</t>
+  </si>
+  <si>
+    <t>13128.33</t>
+  </si>
+  <si>
+    <t>11840.23</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D597"/>
+  <dimension ref="A1:D598"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10283,30 +10283,30 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>574</v>
+        <v>596</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576">
-        <v>105862.5</v>
-      </c>
-      <c r="D576">
-        <v>16415.49</v>
+      <c r="C576" t="s">
+        <v>600</v>
+      </c>
+      <c r="D576" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577">
-        <v>119362.5</v>
-      </c>
-      <c r="D577">
-        <v>15506.54</v>
+      <c r="C577" t="s">
+        <v>600</v>
+      </c>
+      <c r="D577" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10339,156 +10339,156 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580" t="s">
-        <v>599</v>
-      </c>
-      <c r="D580" t="s">
-        <v>608</v>
+      <c r="C580">
+        <v>96029</v>
+      </c>
+      <c r="D580">
+        <v>12479.47</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>599</v>
-      </c>
-      <c r="D581" t="s">
-        <v>609</v>
+      <c r="C581">
+        <v>96029</v>
+      </c>
+      <c r="D581">
+        <v>12506.09</v>
       </c>
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
       <c r="C582" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D582" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
       <c r="C583" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D583" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
       <c r="C584" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D584" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D585" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D586" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
       <c r="C587" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D587" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
       <c r="C588" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D588" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>609</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>89395</v>
-      </c>
-      <c r="D589">
-        <v>10909.6</v>
+      <c r="C589" t="s">
+        <v>607</v>
+      </c>
+      <c r="D589" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590">
-        <v>89395</v>
-      </c>
-      <c r="D590">
-        <v>10901.09</v>
+      <c r="C590" t="s">
+        <v>607</v>
+      </c>
+      <c r="D590" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10535,57 +10535,71 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>606</v>
-      </c>
-      <c r="D594" t="s">
-        <v>617</v>
+      <c r="C594">
+        <v>79730.5</v>
+      </c>
+      <c r="D594">
+        <v>10397.73</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595" t="s">
-        <v>606</v>
-      </c>
-      <c r="D595" t="s">
-        <v>618</v>
+      <c r="C595">
+        <v>79730.5</v>
+      </c>
+      <c r="D595">
+        <v>10422.77</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
-      <c r="C596" t="s">
-        <v>606</v>
-      </c>
-      <c r="D596" t="s">
-        <v>619</v>
+      <c r="C596">
+        <v>79730.5</v>
+      </c>
+      <c r="D596">
+        <v>10421.38</v>
       </c>
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597" t="s">
-        <v>607</v>
-      </c>
-      <c r="D597" t="s">
+      <c r="C597">
+        <v>90500</v>
+      </c>
+      <c r="D597">
+        <v>11823.97</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4">
+      <c r="A598" s="1">
+        <v>618</v>
+      </c>
+      <c r="B598" t="s">
+        <v>599</v>
+      </c>
+      <c r="C598" t="s">
+        <v>608</v>
+      </c>
+      <c r="D598" t="s">
         <v>620</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="619">
   <si>
     <t>Date</t>
   </si>
@@ -1816,43 +1816,40 @@
     <t>2026-08-05</t>
   </si>
   <si>
-    <t>105862.5</t>
-  </si>
-  <si>
-    <t>102569</t>
-  </si>
-  <si>
-    <t>98805</t>
-  </si>
-  <si>
-    <t>96923</t>
-  </si>
-  <si>
-    <t>95041</t>
-  </si>
-  <si>
-    <t>93159</t>
-  </si>
-  <si>
-    <t>91277</t>
-  </si>
-  <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>90500</t>
-  </si>
-  <si>
-    <t>15536.87</t>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>119362.5</t>
+  </si>
+  <si>
+    <t>115649</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>107161</t>
+  </si>
+  <si>
+    <t>100795</t>
+  </si>
+  <si>
+    <t>99203.5</t>
+  </si>
+  <si>
+    <t>97612</t>
+  </si>
+  <si>
+    <t>92000</t>
   </si>
   <si>
     <t>15506.54</t>
   </si>
   <si>
-    <t>15057.71</t>
-  </si>
-  <si>
-    <t>14527.15</t>
+    <t>15029.19</t>
   </si>
   <si>
     <t>14253.17</t>
@@ -1861,22 +1858,19 @@
     <t>13968.59</t>
   </si>
   <si>
-    <t>13682.11</t>
-  </si>
-  <si>
-    <t>13423.48</t>
-  </si>
-  <si>
-    <t>13149.42</t>
-  </si>
-  <si>
     <t>13138.58</t>
   </si>
   <si>
-    <t>13128.33</t>
-  </si>
-  <si>
-    <t>11840.23</t>
+    <t>13154.47</t>
+  </si>
+  <si>
+    <t>12939.89</t>
+  </si>
+  <si>
+    <t>12768.44</t>
+  </si>
+  <si>
+    <t>12031.14</t>
   </si>
 </sst>
 </file>
@@ -2234,7 +2228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D598"/>
+  <dimension ref="A1:D600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10283,16 +10277,16 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576" s="1">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="B576" t="s">
         <v>577</v>
       </c>
-      <c r="C576" t="s">
-        <v>600</v>
-      </c>
-      <c r="D576" t="s">
-        <v>609</v>
+      <c r="C576">
+        <v>105862.5</v>
+      </c>
+      <c r="D576">
+        <v>15536.87</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10303,7 +10297,7 @@
         <v>578</v>
       </c>
       <c r="C577" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D577" t="s">
         <v>610</v>
@@ -10339,16 +10333,16 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580">
-        <v>96029</v>
-      </c>
-      <c r="D580">
-        <v>12479.47</v>
+      <c r="C580" t="s">
+        <v>603</v>
+      </c>
+      <c r="D580" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -10367,30 +10361,30 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582" s="1">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="B582" t="s">
         <v>583</v>
       </c>
-      <c r="C582" t="s">
-        <v>601</v>
-      </c>
-      <c r="D582" t="s">
-        <v>611</v>
+      <c r="C582">
+        <v>102569</v>
+      </c>
+      <c r="D582">
+        <v>15057.71</v>
       </c>
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583" t="s">
-        <v>602</v>
-      </c>
-      <c r="D583" t="s">
-        <v>612</v>
+      <c r="C583">
+        <v>98805</v>
+      </c>
+      <c r="D583">
+        <v>14527.15</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -10401,10 +10395,10 @@
         <v>585</v>
       </c>
       <c r="C584" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D584" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -10415,52 +10409,52 @@
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D585" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586" t="s">
-        <v>605</v>
-      </c>
-      <c r="D586" t="s">
-        <v>615</v>
+      <c r="C586">
+        <v>93159</v>
+      </c>
+      <c r="D586">
+        <v>13682.11</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>606</v>
-      </c>
-      <c r="D587" t="s">
-        <v>616</v>
+      <c r="C587">
+        <v>91277</v>
+      </c>
+      <c r="D587">
+        <v>13423.48</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588" t="s">
-        <v>607</v>
-      </c>
-      <c r="D588" t="s">
-        <v>617</v>
+      <c r="C588">
+        <v>89395</v>
+      </c>
+      <c r="D588">
+        <v>13149.42</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -10471,24 +10465,24 @@
         <v>590</v>
       </c>
       <c r="C589" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D589" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>607</v>
-      </c>
-      <c r="D590" t="s">
-        <v>619</v>
+      <c r="C590">
+        <v>89395</v>
+      </c>
+      <c r="D590">
+        <v>13128.33</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10507,30 +10501,30 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>612</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592">
-        <v>89395</v>
-      </c>
-      <c r="D592">
-        <v>13898.36</v>
+      <c r="C592" t="s">
+        <v>606</v>
+      </c>
+      <c r="D592" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>591</v>
+        <v>613</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593">
-        <v>87983.5</v>
-      </c>
-      <c r="D593">
-        <v>13671.65</v>
+      <c r="C593" t="s">
+        <v>607</v>
+      </c>
+      <c r="D593" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -10591,16 +10585,44 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
-      <c r="C598" t="s">
+      <c r="C598">
+        <v>90500</v>
+      </c>
+      <c r="D598">
+        <v>11840.23</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4">
+      <c r="A599" s="1">
+        <v>619</v>
+      </c>
+      <c r="B599" t="s">
+        <v>600</v>
+      </c>
+      <c r="C599" t="s">
         <v>608</v>
       </c>
-      <c r="D598" t="s">
+      <c r="D599" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4">
+      <c r="A600" s="1">
         <v>620</v>
+      </c>
+      <c r="B600" t="s">
+        <v>601</v>
+      </c>
+      <c r="C600" t="s">
+        <v>609</v>
+      </c>
+      <c r="D600" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="620">
   <si>
     <t>Date</t>
   </si>
@@ -1822,37 +1822,31 @@
     <t>2026-08-07</t>
   </si>
   <si>
-    <t>119362.5</t>
-  </si>
-  <si>
-    <t>115649</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>107161</t>
-  </si>
-  <si>
-    <t>100795</t>
-  </si>
-  <si>
-    <t>99203.5</t>
-  </si>
-  <si>
-    <t>97612</t>
-  </si>
-  <si>
-    <t>92000</t>
-  </si>
-  <si>
-    <t>15506.54</t>
-  </si>
-  <si>
-    <t>15029.19</t>
-  </si>
-  <si>
-    <t>14253.17</t>
+    <t>104921.5</t>
+  </si>
+  <si>
+    <t>102569</t>
+  </si>
+  <si>
+    <t>95041</t>
+  </si>
+  <si>
+    <t>89395</t>
+  </si>
+  <si>
+    <t>87983.5</t>
+  </si>
+  <si>
+    <t>85160.5</t>
+  </si>
+  <si>
+    <t>86572</t>
+  </si>
+  <si>
+    <t>15368.7</t>
+  </si>
+  <si>
+    <t>15061.26</t>
   </si>
   <si>
     <t>13968.59</t>
@@ -1861,16 +1855,25 @@
     <t>13138.58</t>
   </si>
   <si>
-    <t>13154.47</t>
+    <t>13128.33</t>
+  </si>
+  <si>
+    <t>13141.29</t>
   </si>
   <si>
     <t>12939.89</t>
   </si>
   <si>
+    <t>12522.13</t>
+  </si>
+  <si>
+    <t>12545.23</t>
+  </si>
+  <si>
+    <t>12562.48</t>
+  </si>
+  <si>
     <t>12768.44</t>
-  </si>
-  <si>
-    <t>12031.14</t>
   </si>
 </sst>
 </file>
@@ -10291,30 +10294,30 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577" s="1">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="B577" t="s">
         <v>578</v>
       </c>
-      <c r="C577" t="s">
-        <v>602</v>
-      </c>
-      <c r="D577" t="s">
-        <v>610</v>
+      <c r="C577">
+        <v>119362.5</v>
+      </c>
+      <c r="D577">
+        <v>15506.54</v>
       </c>
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>576</v>
+        <v>599</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578">
-        <v>104921.5</v>
-      </c>
-      <c r="D578">
-        <v>12761.38</v>
+      <c r="C578" t="s">
+        <v>602</v>
+      </c>
+      <c r="D578" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -10333,30 +10336,30 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580" s="1">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="B580" t="s">
         <v>581</v>
       </c>
-      <c r="C580" t="s">
-        <v>603</v>
-      </c>
-      <c r="D580" t="s">
-        <v>611</v>
+      <c r="C580">
+        <v>115649</v>
+      </c>
+      <c r="D580">
+        <v>15029.19</v>
       </c>
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>579</v>
+        <v>602</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581">
-        <v>96029</v>
-      </c>
-      <c r="D581">
-        <v>12506.09</v>
+      <c r="C581" t="s">
+        <v>603</v>
+      </c>
+      <c r="D581" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10389,30 +10392,30 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>604</v>
-      </c>
-      <c r="D584" t="s">
-        <v>612</v>
+      <c r="C584">
+        <v>109283</v>
+      </c>
+      <c r="D584">
+        <v>14253.17</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D585" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -10459,86 +10462,86 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
       <c r="C589" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D589" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590">
-        <v>89395</v>
-      </c>
-      <c r="D590">
-        <v>13128.33</v>
+      <c r="C590" t="s">
+        <v>605</v>
+      </c>
+      <c r="D590" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
-      <c r="C591">
-        <v>100795</v>
-      </c>
-      <c r="D591">
-        <v>10911.85</v>
+      <c r="C591" t="s">
+        <v>605</v>
+      </c>
+      <c r="D591" t="s">
+        <v>614</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>606</v>
-      </c>
-      <c r="D592" t="s">
-        <v>615</v>
+      <c r="C592">
+        <v>100795</v>
+      </c>
+      <c r="D592">
+        <v>13154.47</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
       <c r="C593" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D593" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594">
-        <v>79730.5</v>
-      </c>
-      <c r="D594">
-        <v>10397.73</v>
+      <c r="C594" t="s">
+        <v>607</v>
+      </c>
+      <c r="D594" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -10571,35 +10574,35 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597">
-        <v>90500</v>
-      </c>
-      <c r="D597">
-        <v>11823.97</v>
+      <c r="C597" t="s">
+        <v>607</v>
+      </c>
+      <c r="D597" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
-      <c r="C598">
-        <v>90500</v>
-      </c>
-      <c r="D598">
-        <v>11840.23</v>
+      <c r="C598" t="s">
+        <v>607</v>
+      </c>
+      <c r="D598" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
@@ -10608,21 +10611,21 @@
         <v>608</v>
       </c>
       <c r="D599" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600" t="s">
-        <v>609</v>
-      </c>
-      <c r="D600" t="s">
-        <v>618</v>
+      <c r="C600">
+        <v>92000</v>
+      </c>
+      <c r="D600">
+        <v>12031.14</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="625">
   <si>
     <t>Date</t>
   </si>
@@ -1822,58 +1822,73 @@
     <t>2026-08-07</t>
   </si>
   <si>
-    <t>104921.5</t>
-  </si>
-  <si>
-    <t>102569</t>
-  </si>
-  <si>
-    <t>95041</t>
-  </si>
-  <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>87983.5</t>
-  </si>
-  <si>
-    <t>85160.5</t>
-  </si>
-  <si>
-    <t>86572</t>
-  </si>
-  <si>
-    <t>15368.7</t>
-  </si>
-  <si>
-    <t>15061.26</t>
-  </si>
-  <si>
-    <t>13968.59</t>
-  </si>
-  <si>
-    <t>13138.58</t>
-  </si>
-  <si>
-    <t>13128.33</t>
-  </si>
-  <si>
-    <t>13141.29</t>
-  </si>
-  <si>
-    <t>12939.89</t>
-  </si>
-  <si>
-    <t>12522.13</t>
-  </si>
-  <si>
-    <t>12545.23</t>
-  </si>
-  <si>
-    <t>12562.48</t>
-  </si>
-  <si>
-    <t>12768.44</t>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>111405</t>
+  </si>
+  <si>
+    <t>109283</t>
+  </si>
+  <si>
+    <t>107161</t>
+  </si>
+  <si>
+    <t>105039</t>
+  </si>
+  <si>
+    <t>102917</t>
+  </si>
+  <si>
+    <t>100795</t>
+  </si>
+  <si>
+    <t>99203.5</t>
+  </si>
+  <si>
+    <t>96020.5</t>
+  </si>
+  <si>
+    <t>94000</t>
+  </si>
+  <si>
+    <t>15348.67</t>
+  </si>
+  <si>
+    <t>15059.19</t>
+  </si>
+  <si>
+    <t>14758.52</t>
+  </si>
+  <si>
+    <t>14455.84</t>
+  </si>
+  <si>
+    <t>14182.59</t>
+  </si>
+  <si>
+    <t>13893.03</t>
+  </si>
+  <si>
+    <t>13870.74</t>
+  </si>
+  <si>
+    <t>13884.43</t>
+  </si>
+  <si>
+    <t>13898.36</t>
+  </si>
+  <si>
+    <t>13671.65</t>
+  </si>
+  <si>
+    <t>13230.26</t>
+  </si>
+  <si>
+    <t>13262.11</t>
+  </si>
+  <si>
+    <t>12301.05</t>
   </si>
 </sst>
 </file>
@@ -2231,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D600"/>
+  <dimension ref="A1:D601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10308,16 +10323,16 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578" s="1">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="B578" t="s">
         <v>579</v>
       </c>
-      <c r="C578" t="s">
-        <v>602</v>
-      </c>
-      <c r="D578" t="s">
-        <v>609</v>
+      <c r="C578">
+        <v>104921.5</v>
+      </c>
+      <c r="D578">
+        <v>15368.7</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -10350,16 +10365,16 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581" s="1">
-        <v>602</v>
+        <v>579</v>
       </c>
       <c r="B581" t="s">
         <v>582</v>
       </c>
-      <c r="C581" t="s">
-        <v>603</v>
-      </c>
-      <c r="D581" t="s">
-        <v>610</v>
+      <c r="C581">
+        <v>102569</v>
+      </c>
+      <c r="D581">
+        <v>15061.26</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -10378,184 +10393,184 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583">
-        <v>98805</v>
-      </c>
-      <c r="D583">
-        <v>14527.15</v>
+      <c r="C583" t="s">
+        <v>603</v>
+      </c>
+      <c r="D583" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584">
-        <v>109283</v>
-      </c>
-      <c r="D584">
-        <v>14253.17</v>
+      <c r="C584" t="s">
+        <v>604</v>
+      </c>
+      <c r="D584" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D585" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586">
-        <v>93159</v>
-      </c>
-      <c r="D586">
-        <v>13682.11</v>
+      <c r="C586" t="s">
+        <v>606</v>
+      </c>
+      <c r="D586" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587">
-        <v>91277</v>
-      </c>
-      <c r="D587">
-        <v>13423.48</v>
+      <c r="C587" t="s">
+        <v>607</v>
+      </c>
+      <c r="D587" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588">
-        <v>89395</v>
-      </c>
-      <c r="D588">
-        <v>13149.42</v>
+      <c r="C588" t="s">
+        <v>608</v>
+      </c>
+      <c r="D588" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>605</v>
-      </c>
-      <c r="D589" t="s">
-        <v>612</v>
+      <c r="C589">
+        <v>89395</v>
+      </c>
+      <c r="D589">
+        <v>13138.58</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
       <c r="C590" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D590" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
       <c r="C591" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D591" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592">
-        <v>100795</v>
-      </c>
-      <c r="D592">
-        <v>13154.47</v>
+      <c r="C592" t="s">
+        <v>608</v>
+      </c>
+      <c r="D592" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
       <c r="C593" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D593" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
       <c r="C594" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="D594" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595">
-        <v>79730.5</v>
-      </c>
-      <c r="D595">
-        <v>10422.77</v>
+      <c r="C595" t="s">
+        <v>610</v>
+      </c>
+      <c r="D595" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -10574,44 +10589,44 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597" t="s">
-        <v>607</v>
-      </c>
-      <c r="D597" t="s">
-        <v>617</v>
+      <c r="C597">
+        <v>85160.5</v>
+      </c>
+      <c r="D597">
+        <v>12545.23</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
-      <c r="C598" t="s">
-        <v>607</v>
-      </c>
-      <c r="D598" t="s">
-        <v>618</v>
+      <c r="C598">
+        <v>85160.5</v>
+      </c>
+      <c r="D598">
+        <v>12562.48</v>
       </c>
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>620</v>
+        <v>597</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
-      <c r="C599" t="s">
-        <v>608</v>
-      </c>
-      <c r="D599" t="s">
-        <v>619</v>
+      <c r="C599">
+        <v>86572</v>
+      </c>
+      <c r="D599">
+        <v>12768.44</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10626,6 +10641,20 @@
       </c>
       <c r="D600">
         <v>12031.14</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4">
+      <c r="A601" s="1">
+        <v>619</v>
+      </c>
+      <c r="B601" t="s">
+        <v>602</v>
+      </c>
+      <c r="C601" t="s">
+        <v>611</v>
+      </c>
+      <c r="D601" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="625">
   <si>
     <t>Date</t>
   </si>
@@ -1825,70 +1825,70 @@
     <t>2026-08-10</t>
   </si>
   <si>
-    <t>111405</t>
-  </si>
-  <si>
-    <t>109283</t>
-  </si>
-  <si>
-    <t>107161</t>
-  </si>
-  <si>
-    <t>105039</t>
-  </si>
-  <si>
-    <t>102917</t>
-  </si>
-  <si>
-    <t>100795</t>
-  </si>
-  <si>
-    <t>99203.5</t>
-  </si>
-  <si>
-    <t>96020.5</t>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>113221</t>
+  </si>
+  <si>
+    <t>110979</t>
+  </si>
+  <si>
+    <t>108737</t>
+  </si>
+  <si>
+    <t>106495</t>
+  </si>
+  <si>
+    <t>104813.5</t>
+  </si>
+  <si>
+    <t>103132</t>
+  </si>
+  <si>
+    <t>105374</t>
   </si>
   <si>
     <t>94000</t>
   </si>
   <si>
-    <t>15348.67</t>
-  </si>
-  <si>
-    <t>15059.19</t>
-  </si>
-  <si>
-    <t>14758.52</t>
-  </si>
-  <si>
-    <t>14455.84</t>
-  </si>
-  <si>
-    <t>14182.59</t>
-  </si>
-  <si>
-    <t>13893.03</t>
-  </si>
-  <si>
-    <t>13870.74</t>
-  </si>
-  <si>
-    <t>13884.43</t>
-  </si>
-  <si>
-    <t>13898.36</t>
-  </si>
-  <si>
-    <t>13671.65</t>
-  </si>
-  <si>
-    <t>13230.26</t>
-  </si>
-  <si>
-    <t>13262.11</t>
-  </si>
-  <si>
-    <t>12301.05</t>
+    <t>13968.59</t>
+  </si>
+  <si>
+    <t>13682.11</t>
+  </si>
+  <si>
+    <t>13423.48</t>
+  </si>
+  <si>
+    <t>13149.42</t>
+  </si>
+  <si>
+    <t>13138.58</t>
+  </si>
+  <si>
+    <t>13128.33</t>
+  </si>
+  <si>
+    <t>13141.29</t>
+  </si>
+  <si>
+    <t>13154.47</t>
+  </si>
+  <si>
+    <t>12939.89</t>
+  </si>
+  <si>
+    <t>12768.44</t>
+  </si>
+  <si>
+    <t>12765.04</t>
+  </si>
+  <si>
+    <t>13051.41</t>
+  </si>
+  <si>
+    <t>12303.05</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D601"/>
+  <dimension ref="A1:D602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10393,184 +10393,184 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583" s="1">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="B583" t="s">
         <v>584</v>
       </c>
-      <c r="C583" t="s">
-        <v>603</v>
-      </c>
-      <c r="D583" t="s">
-        <v>612</v>
+      <c r="C583">
+        <v>111405</v>
+      </c>
+      <c r="D583">
+        <v>15348.67</v>
       </c>
     </row>
     <row r="584" spans="1:4">
       <c r="A584" s="1">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B584" t="s">
         <v>585</v>
       </c>
-      <c r="C584" t="s">
-        <v>604</v>
-      </c>
-      <c r="D584" t="s">
-        <v>613</v>
+      <c r="C584">
+        <v>109283</v>
+      </c>
+      <c r="D584">
+        <v>15059.19</v>
       </c>
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
       <c r="C585" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D585" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D586" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
       <c r="C587" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D587" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
       <c r="C588" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D588" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>89395</v>
-      </c>
-      <c r="D589">
-        <v>13138.58</v>
+      <c r="C589" t="s">
+        <v>607</v>
+      </c>
+      <c r="D589" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
       <c r="C590" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D590" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
       <c r="C591" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D591" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
       <c r="C592" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D592" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
       <c r="C593" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D593" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>610</v>
-      </c>
-      <c r="D594" t="s">
-        <v>622</v>
+      <c r="C594">
+        <v>96020.5</v>
+      </c>
+      <c r="D594">
+        <v>13230.26</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595" t="s">
-        <v>610</v>
-      </c>
-      <c r="D595" t="s">
-        <v>623</v>
+      <c r="C595">
+        <v>96020.5</v>
+      </c>
+      <c r="D595">
+        <v>13262.11</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -10617,43 +10617,57 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
-      <c r="C599">
-        <v>86572</v>
-      </c>
-      <c r="D599">
-        <v>12768.44</v>
+      <c r="C599" t="s">
+        <v>609</v>
+      </c>
+      <c r="D599" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>598</v>
+        <v>619</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600">
-        <v>92000</v>
-      </c>
-      <c r="D600">
-        <v>12031.14</v>
+      <c r="C600" t="s">
+        <v>609</v>
+      </c>
+      <c r="D600" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
       <c r="C601" t="s">
+        <v>610</v>
+      </c>
+      <c r="D601" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4">
+      <c r="A602" s="1">
+        <v>621</v>
+      </c>
+      <c r="B602" t="s">
+        <v>603</v>
+      </c>
+      <c r="C602" t="s">
         <v>611</v>
       </c>
-      <c r="D601" t="s">
+      <c r="D602" t="s">
         <v>624</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="624">
   <si>
     <t>Date</t>
   </si>
@@ -1828,67 +1828,64 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>113221</t>
-  </si>
-  <si>
-    <t>110979</t>
-  </si>
-  <si>
-    <t>108737</t>
-  </si>
-  <si>
-    <t>106495</t>
-  </si>
-  <si>
-    <t>104813.5</t>
-  </si>
-  <si>
-    <t>103132</t>
-  </si>
-  <si>
-    <t>105374</t>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>105039</t>
+  </si>
+  <si>
+    <t>102917</t>
+  </si>
+  <si>
+    <t>100795</t>
+  </si>
+  <si>
+    <t>99203.5</t>
+  </si>
+  <si>
+    <t>96020.5</t>
+  </si>
+  <si>
+    <t>99734</t>
   </si>
   <si>
     <t>94000</t>
   </si>
   <si>
-    <t>13968.59</t>
-  </si>
-  <si>
-    <t>13682.11</t>
-  </si>
-  <si>
-    <t>13423.48</t>
-  </si>
-  <si>
-    <t>13149.42</t>
-  </si>
-  <si>
-    <t>13138.58</t>
-  </si>
-  <si>
-    <t>13128.33</t>
-  </si>
-  <si>
-    <t>13141.29</t>
-  </si>
-  <si>
-    <t>13154.47</t>
-  </si>
-  <si>
-    <t>12939.89</t>
-  </si>
-  <si>
-    <t>12768.44</t>
-  </si>
-  <si>
-    <t>12765.04</t>
-  </si>
-  <si>
-    <t>13051.41</t>
-  </si>
-  <si>
-    <t>12303.05</t>
+    <t>14455.84</t>
+  </si>
+  <si>
+    <t>14182.59</t>
+  </si>
+  <si>
+    <t>13893.03</t>
+  </si>
+  <si>
+    <t>13881.57</t>
+  </si>
+  <si>
+    <t>13870.74</t>
+  </si>
+  <si>
+    <t>13884.43</t>
+  </si>
+  <si>
+    <t>13898.36</t>
+  </si>
+  <si>
+    <t>13671.65</t>
+  </si>
+  <si>
+    <t>13230.26</t>
+  </si>
+  <si>
+    <t>13789.48</t>
+  </si>
+  <si>
+    <t>13791.72</t>
+  </si>
+  <si>
+    <t>12303.78</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:D603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10421,21 +10418,21 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585" s="1">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="B585" t="s">
         <v>586</v>
       </c>
-      <c r="C585" t="s">
-        <v>604</v>
-      </c>
-      <c r="D585" t="s">
-        <v>612</v>
+      <c r="C585">
+        <v>113221</v>
+      </c>
+      <c r="D585">
+        <v>13968.59</v>
       </c>
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
@@ -10444,12 +10441,12 @@
         <v>605</v>
       </c>
       <c r="D586" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
@@ -10458,12 +10455,12 @@
         <v>606</v>
       </c>
       <c r="D587" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
@@ -10472,12 +10469,12 @@
         <v>607</v>
       </c>
       <c r="D588" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
@@ -10486,12 +10483,12 @@
         <v>607</v>
       </c>
       <c r="D589" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
@@ -10500,12 +10497,12 @@
         <v>607</v>
       </c>
       <c r="D590" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
@@ -10514,12 +10511,12 @@
         <v>607</v>
       </c>
       <c r="D591" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
@@ -10528,12 +10525,12 @@
         <v>607</v>
       </c>
       <c r="D592" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
@@ -10542,21 +10539,21 @@
         <v>608</v>
       </c>
       <c r="D593" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594">
-        <v>96020.5</v>
-      </c>
-      <c r="D594">
-        <v>13230.26</v>
+      <c r="C594" t="s">
+        <v>609</v>
+      </c>
+      <c r="D594" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -10617,35 +10614,35 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
-      <c r="C599" t="s">
-        <v>609</v>
-      </c>
-      <c r="D599" t="s">
-        <v>621</v>
+      <c r="C599">
+        <v>103132</v>
+      </c>
+      <c r="D599">
+        <v>12768.44</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600" t="s">
-        <v>609</v>
-      </c>
-      <c r="D600" t="s">
-        <v>622</v>
+      <c r="C600">
+        <v>103132</v>
+      </c>
+      <c r="D600">
+        <v>12765.04</v>
       </c>
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
@@ -10654,21 +10651,35 @@
         <v>610</v>
       </c>
       <c r="D601" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
       <c r="C602" t="s">
+        <v>610</v>
+      </c>
+      <c r="D602" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4">
+      <c r="A603" s="1">
+        <v>623</v>
+      </c>
+      <c r="B603" t="s">
+        <v>604</v>
+      </c>
+      <c r="C603" t="s">
         <v>611</v>
       </c>
-      <c r="D602" t="s">
-        <v>624</v>
+      <c r="D603" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="624">
   <si>
     <t>Date</t>
   </si>
@@ -1831,61 +1831,61 @@
     <t>2026-08-12</t>
   </si>
   <si>
-    <t>105039</t>
-  </si>
-  <si>
-    <t>102917</t>
-  </si>
-  <si>
-    <t>100795</t>
-  </si>
-  <si>
-    <t>99203.5</t>
-  </si>
-  <si>
-    <t>96020.5</t>
-  </si>
-  <si>
-    <t>99734</t>
-  </si>
-  <si>
-    <t>94000</t>
-  </si>
-  <si>
-    <t>14455.84</t>
-  </si>
-  <si>
-    <t>14182.59</t>
-  </si>
-  <si>
-    <t>13893.03</t>
-  </si>
-  <si>
-    <t>13881.57</t>
-  </si>
-  <si>
-    <t>13870.74</t>
-  </si>
-  <si>
-    <t>13884.43</t>
-  </si>
-  <si>
-    <t>13898.36</t>
-  </si>
-  <si>
-    <t>13671.65</t>
-  </si>
-  <si>
-    <t>13230.26</t>
-  </si>
-  <si>
-    <t>13789.48</t>
-  </si>
-  <si>
-    <t>13791.72</t>
-  </si>
-  <si>
-    <t>12303.78</t>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>108737</t>
+  </si>
+  <si>
+    <t>106495</t>
+  </si>
+  <si>
+    <t>104813.5</t>
+  </si>
+  <si>
+    <t>101450.5</t>
+  </si>
+  <si>
+    <t>105374</t>
+  </si>
+  <si>
+    <t>95500</t>
+  </si>
+  <si>
+    <t>11146.17</t>
+  </si>
+  <si>
+    <t>10918.61</t>
+  </si>
+  <si>
+    <t>10909.6</t>
+  </si>
+  <si>
+    <t>10901.09</t>
+  </si>
+  <si>
+    <t>10911.85</t>
+  </si>
+  <si>
+    <t>10922.79</t>
+  </si>
+  <si>
+    <t>10744.62</t>
+  </si>
+  <si>
+    <t>10397.73</t>
+  </si>
+  <si>
+    <t>10422.77</t>
+  </si>
+  <si>
+    <t>10838.99</t>
+  </si>
+  <si>
+    <t>10839.63</t>
+  </si>
+  <si>
+    <t>12501.22</t>
   </si>
 </sst>
 </file>
@@ -2243,7 +2243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D603"/>
+  <dimension ref="A1:D604"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10432,16 +10432,16 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586" t="s">
-        <v>605</v>
-      </c>
-      <c r="D586" t="s">
-        <v>612</v>
+      <c r="C586">
+        <v>105039</v>
+      </c>
+      <c r="D586">
+        <v>14455.84</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -10455,7 +10455,7 @@
         <v>606</v>
       </c>
       <c r="D587" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -10469,7 +10469,7 @@
         <v>607</v>
       </c>
       <c r="D588" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -10483,7 +10483,7 @@
         <v>607</v>
       </c>
       <c r="D589" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10497,7 +10497,7 @@
         <v>607</v>
       </c>
       <c r="D590" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10511,7 +10511,7 @@
         <v>607</v>
       </c>
       <c r="D591" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -10525,7 +10525,7 @@
         <v>607</v>
       </c>
       <c r="D592" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -10539,7 +10539,7 @@
         <v>608</v>
       </c>
       <c r="D593" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -10553,21 +10553,21 @@
         <v>609</v>
       </c>
       <c r="D594" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595">
-        <v>96020.5</v>
-      </c>
-      <c r="D595">
-        <v>13262.11</v>
+      <c r="C595" t="s">
+        <v>609</v>
+      </c>
+      <c r="D595" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -10642,16 +10642,16 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
-      <c r="C601" t="s">
-        <v>610</v>
-      </c>
-      <c r="D601" t="s">
-        <v>621</v>
+      <c r="C601">
+        <v>99734</v>
+      </c>
+      <c r="D601">
+        <v>13789.48</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -10665,7 +10665,7 @@
         <v>610</v>
       </c>
       <c r="D602" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10676,9 +10676,23 @@
         <v>604</v>
       </c>
       <c r="C603" t="s">
+        <v>610</v>
+      </c>
+      <c r="D603" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4">
+      <c r="A604" s="1">
+        <v>624</v>
+      </c>
+      <c r="B604" t="s">
+        <v>605</v>
+      </c>
+      <c r="C604" t="s">
         <v>611</v>
       </c>
-      <c r="D603" t="s">
+      <c r="D604" t="s">
         <v>623</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="625">
   <si>
     <t>Date</t>
   </si>
@@ -1834,27 +1834,27 @@
     <t>2026-08-13</t>
   </si>
   <si>
-    <t>108737</t>
-  </si>
-  <si>
-    <t>106495</t>
-  </si>
-  <si>
-    <t>104813.5</t>
-  </si>
-  <si>
-    <t>101450.5</t>
-  </si>
-  <si>
-    <t>105374</t>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>89395</t>
+  </si>
+  <si>
+    <t>87983.5</t>
+  </si>
+  <si>
+    <t>85160.5</t>
+  </si>
+  <si>
+    <t>88454</t>
+  </si>
+  <si>
+    <t>89865.5</t>
   </si>
   <si>
     <t>95500</t>
   </si>
   <si>
-    <t>11146.17</t>
-  </si>
-  <si>
     <t>10918.61</t>
   </si>
   <si>
@@ -1879,13 +1879,16 @@
     <t>10422.77</t>
   </si>
   <si>
-    <t>10838.99</t>
+    <t>10421.38</t>
   </si>
   <si>
     <t>10839.63</t>
   </si>
   <si>
-    <t>12501.22</t>
+    <t>11013.58</t>
+  </si>
+  <si>
+    <t>12501.59</t>
   </si>
 </sst>
 </file>
@@ -2243,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D604"/>
+  <dimension ref="A1:D605"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10446,16 +10449,16 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>606</v>
-      </c>
-      <c r="D587" t="s">
-        <v>612</v>
+      <c r="C587">
+        <v>108737</v>
+      </c>
+      <c r="D587">
+        <v>11146.17</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -10572,16 +10575,16 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>594</v>
+        <v>616</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
-      <c r="C596">
-        <v>79730.5</v>
-      </c>
-      <c r="D596">
-        <v>10421.38</v>
+      <c r="C596" t="s">
+        <v>609</v>
+      </c>
+      <c r="D596" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -10656,16 +10659,16 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
-      <c r="C602" t="s">
-        <v>610</v>
-      </c>
-      <c r="D602" t="s">
-        <v>621</v>
+      <c r="C602">
+        <v>105374</v>
+      </c>
+      <c r="D602">
+        <v>10838.99</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10694,6 +10697,20 @@
       </c>
       <c r="D604" t="s">
         <v>623</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4">
+      <c r="A605" s="1">
+        <v>625</v>
+      </c>
+      <c r="B605" t="s">
+        <v>606</v>
+      </c>
+      <c r="C605" t="s">
+        <v>612</v>
+      </c>
+      <c r="D605" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="629">
   <si>
     <t>Date</t>
   </si>
@@ -1837,22 +1837,28 @@
     <t>2026-08-14</t>
   </si>
   <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>87983.5</t>
-  </si>
-  <si>
-    <t>85160.5</t>
-  </si>
-  <si>
-    <t>88454</t>
-  </si>
-  <si>
-    <t>89865.5</t>
-  </si>
-  <si>
-    <t>95500</t>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>100795</t>
+  </si>
+  <si>
+    <t>99203.5</t>
+  </si>
+  <si>
+    <t>96020.5</t>
+  </si>
+  <si>
+    <t>97612</t>
+  </si>
+  <si>
+    <t>102917</t>
+  </si>
+  <si>
+    <t>97000</t>
   </si>
   <si>
     <t>10918.61</t>
@@ -1873,22 +1879,28 @@
     <t>10744.62</t>
   </si>
   <si>
-    <t>10397.73</t>
-  </si>
-  <si>
     <t>10422.77</t>
   </si>
   <si>
     <t>10421.38</t>
   </si>
   <si>
-    <t>10839.63</t>
-  </si>
-  <si>
-    <t>11013.58</t>
-  </si>
-  <si>
-    <t>12501.59</t>
+    <t>10416.92</t>
+  </si>
+  <si>
+    <t>10431.24</t>
+  </si>
+  <si>
+    <t>10602.25</t>
+  </si>
+  <si>
+    <t>10599.43</t>
+  </si>
+  <si>
+    <t>11189.55</t>
+  </si>
+  <si>
+    <t>12704.16</t>
   </si>
 </sst>
 </file>
@@ -2246,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D605"/>
+  <dimension ref="A1:D607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10463,184 +10475,184 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
       <c r="C588" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D588" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
       <c r="C589" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D589" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
       <c r="C590" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D590" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
       <c r="C591" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D591" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
       <c r="C592" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D592" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
       <c r="C593" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D593" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>614</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>609</v>
-      </c>
-      <c r="D594" t="s">
-        <v>619</v>
+      <c r="C594">
+        <v>85160.5</v>
+      </c>
+      <c r="D594">
+        <v>10397.73</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
       <c r="C595" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D595" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
       <c r="C596" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D596" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597">
-        <v>85160.5</v>
-      </c>
-      <c r="D597">
-        <v>12545.23</v>
+      <c r="C597" t="s">
+        <v>611</v>
+      </c>
+      <c r="D597" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
-      <c r="C598">
-        <v>85160.5</v>
-      </c>
-      <c r="D598">
-        <v>12562.48</v>
+      <c r="C598" t="s">
+        <v>611</v>
+      </c>
+      <c r="D598" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
-      <c r="C599">
-        <v>103132</v>
-      </c>
-      <c r="D599">
-        <v>12768.44</v>
+      <c r="C599" t="s">
+        <v>612</v>
+      </c>
+      <c r="D599" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600">
-        <v>103132</v>
-      </c>
-      <c r="D600">
-        <v>12765.04</v>
+      <c r="C600" t="s">
+        <v>612</v>
+      </c>
+      <c r="D600" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10673,44 +10685,72 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603" s="1">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="B603" t="s">
         <v>604</v>
       </c>
-      <c r="C603" t="s">
-        <v>610</v>
-      </c>
-      <c r="D603" t="s">
-        <v>622</v>
+      <c r="C603">
+        <v>88454</v>
+      </c>
+      <c r="D603">
+        <v>10839.63</v>
       </c>
     </row>
     <row r="604" spans="1:4">
       <c r="A604" s="1">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="B604" t="s">
         <v>605</v>
       </c>
-      <c r="C604" t="s">
-        <v>611</v>
-      </c>
-      <c r="D604" t="s">
-        <v>623</v>
+      <c r="C604">
+        <v>89865.5</v>
+      </c>
+      <c r="D604">
+        <v>11013.58</v>
       </c>
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605" t="s">
-        <v>612</v>
-      </c>
-      <c r="D605" t="s">
+      <c r="C605">
+        <v>95500</v>
+      </c>
+      <c r="D605">
+        <v>12501.59</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4">
+      <c r="A606" s="1">
         <v>624</v>
+      </c>
+      <c r="B606" t="s">
+        <v>607</v>
+      </c>
+      <c r="C606" t="s">
+        <v>613</v>
+      </c>
+      <c r="D606" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4">
+      <c r="A607" s="1">
+        <v>625</v>
+      </c>
+      <c r="B607" t="s">
+        <v>608</v>
+      </c>
+      <c r="C607" t="s">
+        <v>614</v>
+      </c>
+      <c r="D607" t="s">
+        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="630">
   <si>
     <t>Date</t>
   </si>
@@ -1843,64 +1843,67 @@
     <t>2026-08-18</t>
   </si>
   <si>
-    <t>100795</t>
-  </si>
-  <si>
-    <t>99203.5</t>
-  </si>
-  <si>
-    <t>96020.5</t>
-  </si>
-  <si>
-    <t>97612</t>
-  </si>
-  <si>
-    <t>102917</t>
-  </si>
-  <si>
-    <t>97000</t>
-  </si>
-  <si>
-    <t>10918.61</t>
-  </si>
-  <si>
-    <t>10909.6</t>
-  </si>
-  <si>
-    <t>10901.09</t>
-  </si>
-  <si>
-    <t>10911.85</t>
-  </si>
-  <si>
-    <t>10922.79</t>
-  </si>
-  <si>
-    <t>10744.62</t>
-  </si>
-  <si>
-    <t>10422.77</t>
-  </si>
-  <si>
-    <t>10421.38</t>
-  </si>
-  <si>
-    <t>10416.92</t>
-  </si>
-  <si>
-    <t>10431.24</t>
-  </si>
-  <si>
-    <t>10602.25</t>
-  </si>
-  <si>
-    <t>10599.43</t>
-  </si>
-  <si>
-    <t>11189.55</t>
-  </si>
-  <si>
-    <t>12704.16</t>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>93159</t>
+  </si>
+  <si>
+    <t>91277</t>
+  </si>
+  <si>
+    <t>89395</t>
+  </si>
+  <si>
+    <t>87983.5</t>
+  </si>
+  <si>
+    <t>85160.5</t>
+  </si>
+  <si>
+    <t>86572</t>
+  </si>
+  <si>
+    <t>89865.5</t>
+  </si>
+  <si>
+    <t>14455.84</t>
+  </si>
+  <si>
+    <t>14182.59</t>
+  </si>
+  <si>
+    <t>13898.36</t>
+  </si>
+  <si>
+    <t>13671.65</t>
+  </si>
+  <si>
+    <t>13262.11</t>
+  </si>
+  <si>
+    <t>13260.35</t>
+  </si>
+  <si>
+    <t>13254.67</t>
+  </si>
+  <si>
+    <t>13272.9</t>
+  </si>
+  <si>
+    <t>13490.5</t>
+  </si>
+  <si>
+    <t>13486.91</t>
+  </si>
+  <si>
+    <t>14014.29</t>
+  </si>
+  <si>
+    <t>14237.78</t>
+  </si>
+  <si>
+    <t>14241.36</t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D607"/>
+  <dimension ref="A1:D608"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10447,97 +10450,97 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>584</v>
+        <v>607</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586">
-        <v>105039</v>
-      </c>
-      <c r="D586">
-        <v>14455.84</v>
+      <c r="C586" t="s">
+        <v>610</v>
+      </c>
+      <c r="D586" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587">
-        <v>108737</v>
-      </c>
-      <c r="D587">
-        <v>11146.17</v>
+      <c r="C587" t="s">
+        <v>611</v>
+      </c>
+      <c r="D587" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588" t="s">
-        <v>609</v>
-      </c>
-      <c r="D588" t="s">
-        <v>615</v>
+      <c r="C588">
+        <v>100795</v>
+      </c>
+      <c r="D588">
+        <v>10918.61</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>609</v>
-      </c>
-      <c r="D589" t="s">
-        <v>616</v>
+      <c r="C589">
+        <v>100795</v>
+      </c>
+      <c r="D589">
+        <v>10909.6</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>609</v>
-      </c>
-      <c r="D590" t="s">
-        <v>617</v>
+      <c r="C590">
+        <v>100795</v>
+      </c>
+      <c r="D590">
+        <v>10901.09</v>
       </c>
     </row>
     <row r="591" spans="1:4">
       <c r="A591" s="1">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="B591" t="s">
         <v>592</v>
       </c>
-      <c r="C591" t="s">
-        <v>609</v>
-      </c>
-      <c r="D591" t="s">
-        <v>618</v>
+      <c r="C591">
+        <v>89395</v>
+      </c>
+      <c r="D591">
+        <v>10911.85</v>
       </c>
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
       <c r="C592" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="D592" t="s">
         <v>619</v>
@@ -10545,13 +10548,13 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
       <c r="C593" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D593" t="s">
         <v>620</v>
@@ -10573,13 +10576,13 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
       <c r="C595" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D595" t="s">
         <v>621</v>
@@ -10587,13 +10590,13 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
       <c r="C596" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D596" t="s">
         <v>622</v>
@@ -10601,13 +10604,13 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
       <c r="C597" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D597" t="s">
         <v>623</v>
@@ -10615,13 +10618,13 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D598" t="s">
         <v>624</v>
@@ -10629,13 +10632,13 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D599" t="s">
         <v>625</v>
@@ -10643,13 +10646,13 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D600" t="s">
         <v>626</v>
@@ -10713,44 +10716,58 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605">
-        <v>95500</v>
-      </c>
-      <c r="D605">
-        <v>12501.59</v>
+      <c r="C605" t="s">
+        <v>616</v>
+      </c>
+      <c r="D605" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="606" spans="1:4">
       <c r="A606" s="1">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B606" t="s">
         <v>607</v>
       </c>
       <c r="C606" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D606" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
       <c r="C607" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D607" t="s">
-        <v>628</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4">
+      <c r="A608" s="1">
+        <v>606</v>
+      </c>
+      <c r="B608" t="s">
+        <v>609</v>
+      </c>
+      <c r="C608">
+        <v>98000</v>
+      </c>
+      <c r="D608">
+        <v>12828.67</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="627">
   <si>
     <t>Date</t>
   </si>
@@ -1846,64 +1846,55 @@
     <t>2026-08-19</t>
   </si>
   <si>
-    <t>93159</t>
-  </si>
-  <si>
-    <t>91277</t>
-  </si>
-  <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>87983.5</t>
-  </si>
-  <si>
-    <t>85160.5</t>
-  </si>
-  <si>
-    <t>86572</t>
-  </si>
-  <si>
-    <t>89865.5</t>
-  </si>
-  <si>
-    <t>14455.84</t>
-  </si>
-  <si>
-    <t>14182.59</t>
-  </si>
-  <si>
-    <t>13898.36</t>
-  </si>
-  <si>
-    <t>13671.65</t>
-  </si>
-  <si>
-    <t>13262.11</t>
-  </si>
-  <si>
-    <t>13260.35</t>
-  </si>
-  <si>
-    <t>13254.67</t>
-  </si>
-  <si>
-    <t>13272.9</t>
-  </si>
-  <si>
-    <t>13490.5</t>
-  </si>
-  <si>
-    <t>13486.91</t>
-  </si>
-  <si>
-    <t>14014.29</t>
-  </si>
-  <si>
-    <t>14237.78</t>
-  </si>
-  <si>
-    <t>14241.36</t>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>110979</t>
+  </si>
+  <si>
+    <t>106495</t>
+  </si>
+  <si>
+    <t>104813.5</t>
+  </si>
+  <si>
+    <t>101450.5</t>
+  </si>
+  <si>
+    <t>103132</t>
+  </si>
+  <si>
+    <t>105374</t>
+  </si>
+  <si>
+    <t>99500</t>
+  </si>
+  <si>
+    <t>12134.65</t>
+  </si>
+  <si>
+    <t>11652.59</t>
+  </si>
+  <si>
+    <t>11476.38</t>
+  </si>
+  <si>
+    <t>11105.86</t>
+  </si>
+  <si>
+    <t>11126.36</t>
+  </si>
+  <si>
+    <t>11141.66</t>
+  </si>
+  <si>
+    <t>11324.32</t>
+  </si>
+  <si>
+    <t>11577.17</t>
+  </si>
+  <si>
+    <t>13053.22</t>
   </si>
 </sst>
 </file>
@@ -2261,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D608"/>
+  <dimension ref="A1:D609"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10456,24 +10447,24 @@
         <v>587</v>
       </c>
       <c r="C586" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D586" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>611</v>
-      </c>
-      <c r="D587" t="s">
-        <v>618</v>
+      <c r="C587">
+        <v>91277</v>
+      </c>
+      <c r="D587">
+        <v>14182.59</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -10492,16 +10483,16 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>100795</v>
-      </c>
-      <c r="D589">
-        <v>10909.6</v>
+      <c r="C589" t="s">
+        <v>612</v>
+      </c>
+      <c r="D589" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10534,16 +10525,16 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>613</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>612</v>
-      </c>
-      <c r="D592" t="s">
-        <v>619</v>
+      <c r="C592">
+        <v>89395</v>
+      </c>
+      <c r="D592">
+        <v>13898.36</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -10562,44 +10553,44 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>592</v>
+        <v>615</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594">
-        <v>85160.5</v>
-      </c>
-      <c r="D594">
-        <v>10397.73</v>
+      <c r="C594" t="s">
+        <v>614</v>
+      </c>
+      <c r="D594" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>616</v>
+        <v>593</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595" t="s">
-        <v>614</v>
-      </c>
-      <c r="D595" t="s">
-        <v>621</v>
+      <c r="C595">
+        <v>85160.5</v>
+      </c>
+      <c r="D595">
+        <v>13262.11</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
-      <c r="C596" t="s">
-        <v>614</v>
-      </c>
-      <c r="D596" t="s">
-        <v>622</v>
+      <c r="C596">
+        <v>85160.5</v>
+      </c>
+      <c r="D596">
+        <v>13260.35</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -10613,7 +10604,7 @@
         <v>614</v>
       </c>
       <c r="D597" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -10627,7 +10618,7 @@
         <v>614</v>
       </c>
       <c r="D598" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -10641,21 +10632,21 @@
         <v>615</v>
       </c>
       <c r="D599" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>621</v>
+        <v>598</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600" t="s">
-        <v>615</v>
-      </c>
-      <c r="D600" t="s">
-        <v>626</v>
+      <c r="C600">
+        <v>86572</v>
+      </c>
+      <c r="D600">
+        <v>13486.91</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10674,16 +10665,16 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
-      <c r="C602">
-        <v>105374</v>
-      </c>
-      <c r="D602">
-        <v>10838.99</v>
+      <c r="C602" t="s">
+        <v>616</v>
+      </c>
+      <c r="D602" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10716,44 +10707,44 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>626</v>
+        <v>603</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605" t="s">
-        <v>616</v>
-      </c>
-      <c r="D605" t="s">
-        <v>627</v>
+      <c r="C605">
+        <v>89865.5</v>
+      </c>
+      <c r="D605">
+        <v>14014.29</v>
       </c>
     </row>
     <row r="606" spans="1:4">
       <c r="A606" s="1">
-        <v>627</v>
+        <v>604</v>
       </c>
       <c r="B606" t="s">
         <v>607</v>
       </c>
-      <c r="C606" t="s">
-        <v>611</v>
-      </c>
-      <c r="D606" t="s">
-        <v>628</v>
+      <c r="C606">
+        <v>91277</v>
+      </c>
+      <c r="D606">
+        <v>14237.78</v>
       </c>
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
-      <c r="C607" t="s">
-        <v>611</v>
-      </c>
-      <c r="D607" t="s">
-        <v>629</v>
+      <c r="C607">
+        <v>91277</v>
+      </c>
+      <c r="D607">
+        <v>14241.36</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10768,6 +10759,20 @@
       </c>
       <c r="D608">
         <v>12828.67</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4">
+      <c r="A609" s="1">
+        <v>630</v>
+      </c>
+      <c r="B609" t="s">
+        <v>610</v>
+      </c>
+      <c r="C609" t="s">
+        <v>617</v>
+      </c>
+      <c r="D609" t="s">
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="627">
   <si>
     <t>Date</t>
   </si>
@@ -1849,52 +1849,52 @@
     <t>2026-08-20</t>
   </si>
   <si>
-    <t>110979</t>
-  </si>
-  <si>
-    <t>106495</t>
-  </si>
-  <si>
-    <t>104813.5</t>
-  </si>
-  <si>
-    <t>101450.5</t>
-  </si>
-  <si>
-    <t>103132</t>
-  </si>
-  <si>
-    <t>105374</t>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>85457</t>
+  </si>
+  <si>
+    <t>83695</t>
+  </si>
+  <si>
+    <t>79730.5</t>
+  </si>
+  <si>
+    <t>81052</t>
+  </si>
+  <si>
+    <t>82814</t>
   </si>
   <si>
     <t>99500</t>
   </si>
   <si>
-    <t>12134.65</t>
-  </si>
-  <si>
-    <t>11652.59</t>
-  </si>
-  <si>
-    <t>11476.38</t>
-  </si>
-  <si>
-    <t>11105.86</t>
-  </si>
-  <si>
-    <t>11126.36</t>
-  </si>
-  <si>
-    <t>11141.66</t>
-  </si>
-  <si>
-    <t>11324.32</t>
-  </si>
-  <si>
-    <t>11577.17</t>
-  </si>
-  <si>
-    <t>13053.22</t>
+    <t>14182.59</t>
+  </si>
+  <si>
+    <t>13870.74</t>
+  </si>
+  <si>
+    <t>13230.26</t>
+  </si>
+  <si>
+    <t>13262.11</t>
+  </si>
+  <si>
+    <t>13272.9</t>
+  </si>
+  <si>
+    <t>13490.5</t>
+  </si>
+  <si>
+    <t>13486.91</t>
+  </si>
+  <si>
+    <t>13792.53</t>
+  </si>
+  <si>
+    <t>13063.09</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D609"/>
+  <dimension ref="A1:D610"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10441,30 +10441,30 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586" s="1">
-        <v>607</v>
+        <v>584</v>
       </c>
       <c r="B586" t="s">
         <v>587</v>
       </c>
-      <c r="C586" t="s">
-        <v>611</v>
-      </c>
-      <c r="D586" t="s">
-        <v>618</v>
+      <c r="C586">
+        <v>110979</v>
+      </c>
+      <c r="D586">
+        <v>12134.65</v>
       </c>
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587">
-        <v>91277</v>
-      </c>
-      <c r="D587">
-        <v>14182.59</v>
+      <c r="C587" t="s">
+        <v>612</v>
+      </c>
+      <c r="D587" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -10483,30 +10483,30 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>612</v>
-      </c>
-      <c r="D589" t="s">
-        <v>619</v>
+      <c r="C589">
+        <v>106495</v>
+      </c>
+      <c r="D589">
+        <v>11652.59</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590">
-        <v>100795</v>
-      </c>
-      <c r="D590">
-        <v>10901.09</v>
+      <c r="C590" t="s">
+        <v>613</v>
+      </c>
+      <c r="D590" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10539,16 +10539,16 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593" t="s">
-        <v>613</v>
-      </c>
-      <c r="D593" t="s">
-        <v>620</v>
+      <c r="C593">
+        <v>104813.5</v>
+      </c>
+      <c r="D593">
+        <v>11476.38</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -10562,21 +10562,21 @@
         <v>614</v>
       </c>
       <c r="D594" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595">
-        <v>85160.5</v>
-      </c>
-      <c r="D595">
-        <v>13262.11</v>
+      <c r="C595" t="s">
+        <v>614</v>
+      </c>
+      <c r="D595" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -10595,16 +10595,16 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>618</v>
+        <v>595</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597" t="s">
-        <v>614</v>
-      </c>
-      <c r="D597" t="s">
-        <v>622</v>
+      <c r="C597">
+        <v>101450.5</v>
+      </c>
+      <c r="D597">
+        <v>11126.36</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -10618,7 +10618,7 @@
         <v>614</v>
       </c>
       <c r="D598" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -10632,21 +10632,21 @@
         <v>615</v>
       </c>
       <c r="D599" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>598</v>
+        <v>621</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
-      <c r="C600">
-        <v>86572</v>
-      </c>
-      <c r="D600">
-        <v>13486.91</v>
+      <c r="C600" t="s">
+        <v>615</v>
+      </c>
+      <c r="D600" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -10665,30 +10665,30 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>623</v>
+        <v>600</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
-      <c r="C602" t="s">
-        <v>616</v>
-      </c>
-      <c r="D602" t="s">
-        <v>625</v>
+      <c r="C602">
+        <v>105374</v>
+      </c>
+      <c r="D602">
+        <v>11577.17</v>
       </c>
     </row>
     <row r="603" spans="1:4">
       <c r="A603" s="1">
-        <v>601</v>
+        <v>624</v>
       </c>
       <c r="B603" t="s">
         <v>604</v>
       </c>
-      <c r="C603">
-        <v>88454</v>
-      </c>
-      <c r="D603">
-        <v>10839.63</v>
+      <c r="C603" t="s">
+        <v>616</v>
+      </c>
+      <c r="D603" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10763,15 +10763,29 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="1">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="B609" t="s">
         <v>610</v>
       </c>
-      <c r="C609" t="s">
+      <c r="C609">
+        <v>99500</v>
+      </c>
+      <c r="D609">
+        <v>13053.22</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4">
+      <c r="A610" s="1">
+        <v>631</v>
+      </c>
+      <c r="B610" t="s">
+        <v>611</v>
+      </c>
+      <c r="C610" t="s">
         <v>617</v>
       </c>
-      <c r="D609" t="s">
+      <c r="D610" t="s">
         <v>626</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="632">
   <si>
     <t>Date</t>
   </si>
@@ -1852,49 +1852,64 @@
     <t>2026-08-21</t>
   </si>
   <si>
-    <t>85457</t>
-  </si>
-  <si>
-    <t>83695</t>
-  </si>
-  <si>
-    <t>79730.5</t>
-  </si>
-  <si>
-    <t>81052</t>
-  </si>
-  <si>
-    <t>82814</t>
-  </si>
-  <si>
-    <t>99500</t>
-  </si>
-  <si>
-    <t>14182.59</t>
-  </si>
-  <si>
-    <t>13870.74</t>
-  </si>
-  <si>
-    <t>13230.26</t>
-  </si>
-  <si>
-    <t>13262.11</t>
-  </si>
-  <si>
-    <t>13272.9</t>
-  </si>
-  <si>
-    <t>13490.5</t>
-  </si>
-  <si>
-    <t>13486.91</t>
-  </si>
-  <si>
-    <t>13792.53</t>
-  </si>
-  <si>
-    <t>13063.09</t>
+    <t>89395</t>
+  </si>
+  <si>
+    <t>85160.5</t>
+  </si>
+  <si>
+    <t>86572</t>
+  </si>
+  <si>
+    <t>88454</t>
+  </si>
+  <si>
+    <t>91277</t>
+  </si>
+  <si>
+    <t>92218</t>
+  </si>
+  <si>
+    <t>93629.5</t>
+  </si>
+  <si>
+    <t>11662.21</t>
+  </si>
+  <si>
+    <t>11652.59</t>
+  </si>
+  <si>
+    <t>11105.86</t>
+  </si>
+  <si>
+    <t>11132.6</t>
+  </si>
+  <si>
+    <t>11126.36</t>
+  </si>
+  <si>
+    <t>11141.66</t>
+  </si>
+  <si>
+    <t>11324.32</t>
+  </si>
+  <si>
+    <t>11321.3</t>
+  </si>
+  <si>
+    <t>11575.29</t>
+  </si>
+  <si>
+    <t>11577.17</t>
+  </si>
+  <si>
+    <t>11954.61</t>
+  </si>
+  <si>
+    <t>12071.78</t>
+  </si>
+  <si>
+    <t>12283.08</t>
   </si>
 </sst>
 </file>
@@ -10455,58 +10470,58 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587" s="1">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="B587" t="s">
         <v>588</v>
       </c>
-      <c r="C587" t="s">
-        <v>612</v>
-      </c>
-      <c r="D587" t="s">
-        <v>618</v>
+      <c r="C587">
+        <v>85457</v>
+      </c>
+      <c r="D587">
+        <v>14182.59</v>
       </c>
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>586</v>
+        <v>609</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588">
-        <v>100795</v>
-      </c>
-      <c r="D588">
-        <v>10918.61</v>
+      <c r="C588" t="s">
+        <v>612</v>
+      </c>
+      <c r="D588" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589">
-        <v>106495</v>
-      </c>
-      <c r="D589">
-        <v>11652.59</v>
+      <c r="C589" t="s">
+        <v>612</v>
+      </c>
+      <c r="D589" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="590" spans="1:4">
       <c r="A590" s="1">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="B590" t="s">
         <v>591</v>
       </c>
-      <c r="C590" t="s">
-        <v>613</v>
-      </c>
-      <c r="D590" t="s">
-        <v>619</v>
+      <c r="C590">
+        <v>83695</v>
+      </c>
+      <c r="D590">
+        <v>13870.74</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -10559,10 +10574,10 @@
         <v>595</v>
       </c>
       <c r="C594" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D594" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -10573,10 +10588,10 @@
         <v>596</v>
       </c>
       <c r="C595" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D595" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -10595,16 +10610,16 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597">
-        <v>101450.5</v>
-      </c>
-      <c r="D597">
-        <v>11126.36</v>
+      <c r="C597" t="s">
+        <v>613</v>
+      </c>
+      <c r="D597" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -10615,10 +10630,10 @@
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D598" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -10629,10 +10644,10 @@
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D599" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -10643,52 +10658,52 @@
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D600" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>599</v>
+        <v>622</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
-      <c r="C601">
-        <v>99734</v>
-      </c>
-      <c r="D601">
-        <v>13789.48</v>
+      <c r="C601" t="s">
+        <v>615</v>
+      </c>
+      <c r="D601" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>600</v>
+        <v>623</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
-      <c r="C602">
-        <v>105374</v>
-      </c>
-      <c r="D602">
-        <v>11577.17</v>
+      <c r="C602" t="s">
+        <v>615</v>
+      </c>
+      <c r="D602" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="603" spans="1:4">
       <c r="A603" s="1">
-        <v>624</v>
+        <v>601</v>
       </c>
       <c r="B603" t="s">
         <v>604</v>
       </c>
-      <c r="C603" t="s">
-        <v>616</v>
-      </c>
-      <c r="D603" t="s">
-        <v>625</v>
+      <c r="C603">
+        <v>82814</v>
+      </c>
+      <c r="D603">
+        <v>13792.53</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -10735,58 +10750,58 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>605</v>
+        <v>628</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
-      <c r="C607">
-        <v>91277</v>
-      </c>
-      <c r="D607">
-        <v>14241.36</v>
+      <c r="C607" t="s">
+        <v>616</v>
+      </c>
+      <c r="D607" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="608" spans="1:4">
       <c r="A608" s="1">
-        <v>606</v>
+        <v>629</v>
       </c>
       <c r="B608" t="s">
         <v>609</v>
       </c>
-      <c r="C608">
-        <v>98000</v>
-      </c>
-      <c r="D608">
-        <v>12828.67</v>
+      <c r="C608" t="s">
+        <v>617</v>
+      </c>
+      <c r="D608" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="1">
-        <v>607</v>
+        <v>630</v>
       </c>
       <c r="B609" t="s">
         <v>610</v>
       </c>
-      <c r="C609">
-        <v>99500</v>
-      </c>
-      <c r="D609">
-        <v>13053.22</v>
+      <c r="C609" t="s">
+        <v>618</v>
+      </c>
+      <c r="D609" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="610" spans="1:4">
       <c r="A610" s="1">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="B610" t="s">
         <v>611</v>
       </c>
-      <c r="C610" t="s">
-        <v>617</v>
-      </c>
-      <c r="D610" t="s">
-        <v>626</v>
+      <c r="C610">
+        <v>99500</v>
+      </c>
+      <c r="D610">
+        <v>13063.09</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="631">
   <si>
     <t>Date</t>
   </si>
@@ -1852,64 +1852,61 @@
     <t>2026-08-21</t>
   </si>
   <si>
-    <t>89395</t>
-  </si>
-  <si>
-    <t>85160.5</t>
-  </si>
-  <si>
-    <t>86572</t>
-  </si>
-  <si>
-    <t>88454</t>
-  </si>
-  <si>
-    <t>91277</t>
-  </si>
-  <si>
-    <t>92218</t>
-  </si>
-  <si>
-    <t>93629.5</t>
-  </si>
-  <si>
-    <t>11662.21</t>
-  </si>
-  <si>
-    <t>11652.59</t>
-  </si>
-  <si>
-    <t>11105.86</t>
-  </si>
-  <si>
-    <t>11132.6</t>
-  </si>
-  <si>
-    <t>11126.36</t>
-  </si>
-  <si>
-    <t>11141.66</t>
-  </si>
-  <si>
-    <t>11324.32</t>
-  </si>
-  <si>
-    <t>11321.3</t>
-  </si>
-  <si>
-    <t>11575.29</t>
-  </si>
-  <si>
-    <t>11577.17</t>
-  </si>
-  <si>
-    <t>11954.61</t>
-  </si>
-  <si>
-    <t>12071.78</t>
-  </si>
-  <si>
-    <t>12283.08</t>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>106495</t>
+  </si>
+  <si>
+    <t>104813.5</t>
+  </si>
+  <si>
+    <t>101450.5</t>
+  </si>
+  <si>
+    <t>103132</t>
+  </si>
+  <si>
+    <t>105374</t>
+  </si>
+  <si>
+    <t>100500</t>
+  </si>
+  <si>
+    <t>13898.36</t>
+  </si>
+  <si>
+    <t>13671.65</t>
+  </si>
+  <si>
+    <t>13230.26</t>
+  </si>
+  <si>
+    <t>13262.11</t>
+  </si>
+  <si>
+    <t>13260.35</t>
+  </si>
+  <si>
+    <t>13254.67</t>
+  </si>
+  <si>
+    <t>13272.9</t>
+  </si>
+  <si>
+    <t>13490.5</t>
+  </si>
+  <si>
+    <t>13486.91</t>
+  </si>
+  <si>
+    <t>13789.48</t>
+  </si>
+  <si>
+    <t>13791.72</t>
+  </si>
+  <si>
+    <t>13198.69</t>
   </si>
 </sst>
 </file>
@@ -2267,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D611"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10484,30 +10481,30 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588" s="1">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="B588" t="s">
         <v>589</v>
       </c>
-      <c r="C588" t="s">
-        <v>612</v>
-      </c>
-      <c r="D588" t="s">
-        <v>619</v>
+      <c r="C588">
+        <v>89395</v>
+      </c>
+      <c r="D588">
+        <v>11662.21</v>
       </c>
     </row>
     <row r="589" spans="1:4">
       <c r="A589" s="1">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B589" t="s">
         <v>590</v>
       </c>
-      <c r="C589" t="s">
-        <v>612</v>
-      </c>
-      <c r="D589" t="s">
-        <v>620</v>
+      <c r="C589">
+        <v>89395</v>
+      </c>
+      <c r="D589">
+        <v>11652.59</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -10540,41 +10537,41 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592">
-        <v>89395</v>
-      </c>
-      <c r="D592">
-        <v>13898.36</v>
+      <c r="C592" t="s">
+        <v>613</v>
+      </c>
+      <c r="D592" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593">
-        <v>104813.5</v>
-      </c>
-      <c r="D593">
-        <v>11476.38</v>
+      <c r="C593" t="s">
+        <v>614</v>
+      </c>
+      <c r="D593" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
       <c r="C594" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D594" t="s">
         <v>621</v>
@@ -10582,13 +10579,13 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
       <c r="C595" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D595" t="s">
         <v>622</v>
@@ -10596,100 +10593,100 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
-      <c r="C596">
-        <v>85160.5</v>
-      </c>
-      <c r="D596">
-        <v>13260.35</v>
+      <c r="C596" t="s">
+        <v>615</v>
+      </c>
+      <c r="D596" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
       <c r="C597" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D597" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D598" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D599" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D600" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
       <c r="C601" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D601" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
       <c r="C602" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D602" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -10750,44 +10747,44 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
-      <c r="C607" t="s">
-        <v>616</v>
-      </c>
-      <c r="D607" t="s">
-        <v>629</v>
+      <c r="C607">
+        <v>91277</v>
+      </c>
+      <c r="D607">
+        <v>11954.61</v>
       </c>
     </row>
     <row r="608" spans="1:4">
       <c r="A608" s="1">
-        <v>629</v>
+        <v>606</v>
       </c>
       <c r="B608" t="s">
         <v>609</v>
       </c>
-      <c r="C608" t="s">
-        <v>617</v>
-      </c>
-      <c r="D608" t="s">
-        <v>630</v>
+      <c r="C608">
+        <v>92218</v>
+      </c>
+      <c r="D608">
+        <v>12071.78</v>
       </c>
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="1">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="B609" t="s">
         <v>610</v>
       </c>
-      <c r="C609" t="s">
-        <v>618</v>
-      </c>
-      <c r="D609" t="s">
-        <v>631</v>
+      <c r="C609">
+        <v>93629.5</v>
+      </c>
+      <c r="D609">
+        <v>12283.08</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10802,6 +10799,20 @@
       </c>
       <c r="D610">
         <v>13063.09</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4">
+      <c r="A611" s="1">
+        <v>629</v>
+      </c>
+      <c r="B611" t="s">
+        <v>612</v>
+      </c>
+      <c r="C611" t="s">
+        <v>618</v>
+      </c>
+      <c r="D611" t="s">
+        <v>630</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="634">
   <si>
     <t>Date</t>
   </si>
@@ -1855,28 +1855,28 @@
     <t>2026-08-24</t>
   </si>
   <si>
-    <t>106495</t>
-  </si>
-  <si>
-    <t>104813.5</t>
-  </si>
-  <si>
-    <t>101450.5</t>
-  </si>
-  <si>
-    <t>103132</t>
-  </si>
-  <si>
-    <t>105374</t>
-  </si>
-  <si>
-    <t>100500</t>
-  </si>
-  <si>
-    <t>13898.36</t>
-  </si>
-  <si>
-    <t>13671.65</t>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>96020.5</t>
+  </si>
+  <si>
+    <t>97612</t>
+  </si>
+  <si>
+    <t>99734</t>
+  </si>
+  <si>
+    <t>101325.5</t>
+  </si>
+  <si>
+    <t>102917</t>
+  </si>
+  <si>
+    <t>105569.5</t>
+  </si>
+  <si>
+    <t>101500</t>
   </si>
   <si>
     <t>13230.26</t>
@@ -1906,7 +1906,16 @@
     <t>13791.72</t>
   </si>
   <si>
-    <t>13198.69</t>
+    <t>14014.29</t>
+  </si>
+  <si>
+    <t>14241.36</t>
+  </si>
+  <si>
+    <t>14632.66</t>
+  </si>
+  <si>
+    <t>13329.82</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10537,41 +10546,41 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" s="1">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="B592" t="s">
         <v>593</v>
       </c>
-      <c r="C592" t="s">
-        <v>613</v>
-      </c>
-      <c r="D592" t="s">
-        <v>619</v>
+      <c r="C592">
+        <v>106495</v>
+      </c>
+      <c r="D592">
+        <v>13898.36</v>
       </c>
     </row>
     <row r="593" spans="1:4">
       <c r="A593" s="1">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="B593" t="s">
         <v>594</v>
       </c>
-      <c r="C593" t="s">
-        <v>614</v>
-      </c>
-      <c r="D593" t="s">
-        <v>620</v>
+      <c r="C593">
+        <v>104813.5</v>
+      </c>
+      <c r="D593">
+        <v>13671.65</v>
       </c>
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
       <c r="C594" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D594" t="s">
         <v>621</v>
@@ -10579,13 +10588,13 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
       <c r="C595" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D595" t="s">
         <v>622</v>
@@ -10593,13 +10602,13 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
       <c r="C596" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D596" t="s">
         <v>623</v>
@@ -10607,13 +10616,13 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
       <c r="C597" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D597" t="s">
         <v>624</v>
@@ -10621,13 +10630,13 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D598" t="s">
         <v>625</v>
@@ -10635,13 +10644,13 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D599" t="s">
         <v>626</v>
@@ -10649,13 +10658,13 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D600" t="s">
         <v>627</v>
@@ -10663,13 +10672,13 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
       <c r="C601" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D601" t="s">
         <v>628</v>
@@ -10677,13 +10686,13 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
       <c r="C602" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D602" t="s">
         <v>629</v>
@@ -10719,16 +10728,16 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>603</v>
+        <v>624</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605">
-        <v>89865.5</v>
-      </c>
-      <c r="D605">
-        <v>14014.29</v>
+      <c r="C605" t="s">
+        <v>617</v>
+      </c>
+      <c r="D605" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10747,16 +10756,16 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>605</v>
+        <v>626</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
-      <c r="C607">
-        <v>91277</v>
-      </c>
-      <c r="D607">
-        <v>11954.61</v>
+      <c r="C607" t="s">
+        <v>618</v>
+      </c>
+      <c r="D607" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10775,16 +10784,16 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="1">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="B609" t="s">
         <v>610</v>
       </c>
-      <c r="C609">
-        <v>93629.5</v>
-      </c>
-      <c r="D609">
-        <v>12283.08</v>
+      <c r="C609" t="s">
+        <v>619</v>
+      </c>
+      <c r="D609" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10803,16 +10812,30 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" s="1">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="B611" t="s">
         <v>612</v>
       </c>
-      <c r="C611" t="s">
-        <v>618</v>
-      </c>
-      <c r="D611" t="s">
-        <v>630</v>
+      <c r="C611">
+        <v>100500</v>
+      </c>
+      <c r="D611">
+        <v>13198.69</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4">
+      <c r="A612" s="1">
+        <v>631</v>
+      </c>
+      <c r="B612" t="s">
+        <v>613</v>
+      </c>
+      <c r="C612" t="s">
+        <v>620</v>
+      </c>
+      <c r="D612" t="s">
+        <v>633</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="634">
   <si>
     <t>Date</t>
   </si>
@@ -1858,31 +1858,28 @@
     <t>2026-08-25</t>
   </si>
   <si>
-    <t>96020.5</t>
-  </si>
-  <si>
-    <t>97612</t>
-  </si>
-  <si>
-    <t>99734</t>
-  </si>
-  <si>
-    <t>101325.5</t>
-  </si>
-  <si>
-    <t>102917</t>
-  </si>
-  <si>
-    <t>105569.5</t>
-  </si>
-  <si>
-    <t>101500</t>
-  </si>
-  <si>
-    <t>13230.26</t>
-  </si>
-  <si>
-    <t>13262.11</t>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>79730.5</t>
+  </si>
+  <si>
+    <t>81052</t>
+  </si>
+  <si>
+    <t>82814</t>
+  </si>
+  <si>
+    <t>84135.5</t>
+  </si>
+  <si>
+    <t>88540.5</t>
+  </si>
+  <si>
+    <t>89421.5</t>
+  </si>
+  <si>
+    <t>102500</t>
   </si>
   <si>
     <t>13260.35</t>
@@ -1906,16 +1903,19 @@
     <t>13791.72</t>
   </si>
   <si>
-    <t>14014.29</t>
-  </si>
-  <si>
-    <t>14241.36</t>
-  </si>
-  <si>
-    <t>14632.66</t>
-  </si>
-  <si>
-    <t>13329.82</t>
+    <t>13792.53</t>
+  </si>
+  <si>
+    <t>14013.87</t>
+  </si>
+  <si>
+    <t>14795.73</t>
+  </si>
+  <si>
+    <t>14942.73</t>
+  </si>
+  <si>
+    <t>13464.75</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10574,170 +10574,170 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594" s="1">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="B594" t="s">
         <v>595</v>
       </c>
-      <c r="C594" t="s">
-        <v>614</v>
-      </c>
-      <c r="D594" t="s">
-        <v>621</v>
+      <c r="C594">
+        <v>96020.5</v>
+      </c>
+      <c r="D594">
+        <v>13230.26</v>
       </c>
     </row>
     <row r="595" spans="1:4">
       <c r="A595" s="1">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="B595" t="s">
         <v>596</v>
       </c>
-      <c r="C595" t="s">
-        <v>614</v>
-      </c>
-      <c r="D595" t="s">
-        <v>622</v>
+      <c r="C595">
+        <v>96020.5</v>
+      </c>
+      <c r="D595">
+        <v>13262.11</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
       <c r="C596" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D596" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
       <c r="C597" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D597" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="598" spans="1:4">
       <c r="A598" s="1">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B598" t="s">
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D598" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="599" spans="1:4">
       <c r="A599" s="1">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B599" t="s">
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D599" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="600" spans="1:4">
       <c r="A600" s="1">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B600" t="s">
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D600" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="601" spans="1:4">
       <c r="A601" s="1">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B601" t="s">
         <v>602</v>
       </c>
       <c r="C601" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D601" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="602" spans="1:4">
       <c r="A602" s="1">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B602" t="s">
         <v>603</v>
       </c>
       <c r="C602" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D602" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="603" spans="1:4">
       <c r="A603" s="1">
-        <v>601</v>
+        <v>623</v>
       </c>
       <c r="B603" t="s">
         <v>604</v>
       </c>
-      <c r="C603">
-        <v>82814</v>
-      </c>
-      <c r="D603">
-        <v>13792.53</v>
+      <c r="C603" t="s">
+        <v>617</v>
+      </c>
+      <c r="D603" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="604" spans="1:4">
       <c r="A604" s="1">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="B604" t="s">
         <v>605</v>
       </c>
-      <c r="C604">
-        <v>89865.5</v>
-      </c>
-      <c r="D604">
-        <v>11013.58</v>
+      <c r="C604" t="s">
+        <v>618</v>
+      </c>
+      <c r="D604" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605" t="s">
-        <v>617</v>
-      </c>
-      <c r="D605" t="s">
-        <v>630</v>
+      <c r="C605">
+        <v>101325.5</v>
+      </c>
+      <c r="D605">
+        <v>14014.29</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10756,16 +10756,16 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607" s="1">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="B607" t="s">
         <v>608</v>
       </c>
-      <c r="C607" t="s">
-        <v>618</v>
-      </c>
-      <c r="D607" t="s">
-        <v>631</v>
+      <c r="C607">
+        <v>102917</v>
+      </c>
+      <c r="D607">
+        <v>14241.36</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -10784,16 +10784,16 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609" s="1">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="B609" t="s">
         <v>610</v>
       </c>
-      <c r="C609" t="s">
-        <v>619</v>
-      </c>
-      <c r="D609" t="s">
-        <v>632</v>
+      <c r="C609">
+        <v>105569.5</v>
+      </c>
+      <c r="D609">
+        <v>14632.66</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -10812,21 +10812,21 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" s="1">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="B611" t="s">
         <v>612</v>
       </c>
-      <c r="C611">
-        <v>100500</v>
-      </c>
-      <c r="D611">
-        <v>13198.69</v>
+      <c r="C611" t="s">
+        <v>619</v>
+      </c>
+      <c r="D611" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="612" spans="1:4">
       <c r="A612" s="1">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B612" t="s">
         <v>613</v>
@@ -10835,6 +10835,20 @@
         <v>620</v>
       </c>
       <c r="D612" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="613" spans="1:4">
+      <c r="A613" s="1">
+        <v>633</v>
+      </c>
+      <c r="B613" t="s">
+        <v>614</v>
+      </c>
+      <c r="C613" t="s">
+        <v>621</v>
+      </c>
+      <c r="D613" t="s">
         <v>633</v>
       </c>
     </row>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="635">
   <si>
     <t>Date</t>
   </si>
@@ -1861,61 +1861,64 @@
     <t>2026-08-26</t>
   </si>
   <si>
-    <t>79730.5</t>
-  </si>
-  <si>
-    <t>81052</t>
-  </si>
-  <si>
-    <t>82814</t>
-  </si>
-  <si>
-    <t>84135.5</t>
-  </si>
-  <si>
-    <t>88540.5</t>
-  </si>
-  <si>
-    <t>89421.5</t>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>96020.5</t>
+  </si>
+  <si>
+    <t>97612</t>
+  </si>
+  <si>
+    <t>99734</t>
+  </si>
+  <si>
+    <t>101325.5</t>
+  </si>
+  <si>
+    <t>107691.5</t>
+  </si>
+  <si>
+    <t>108752.5</t>
   </si>
   <si>
     <t>102500</t>
   </si>
   <si>
-    <t>13260.35</t>
-  </si>
-  <si>
-    <t>13254.67</t>
-  </si>
-  <si>
-    <t>13272.9</t>
-  </si>
-  <si>
-    <t>13490.5</t>
-  </si>
-  <si>
-    <t>13486.91</t>
-  </si>
-  <si>
-    <t>13789.48</t>
-  </si>
-  <si>
-    <t>13791.72</t>
-  </si>
-  <si>
-    <t>13792.53</t>
-  </si>
-  <si>
-    <t>14013.87</t>
-  </si>
-  <si>
-    <t>14795.73</t>
-  </si>
-  <si>
-    <t>14942.73</t>
-  </si>
-  <si>
-    <t>13464.75</t>
+    <t>11126.36</t>
+  </si>
+  <si>
+    <t>11141.66</t>
+  </si>
+  <si>
+    <t>11324.32</t>
+  </si>
+  <si>
+    <t>11321.3</t>
+  </si>
+  <si>
+    <t>11575.29</t>
+  </si>
+  <si>
+    <t>11577.17</t>
+  </si>
+  <si>
+    <t>11577.85</t>
+  </si>
+  <si>
+    <t>11763.65</t>
+  </si>
+  <si>
+    <t>11764</t>
+  </si>
+  <si>
+    <t>12543.36</t>
+  </si>
+  <si>
+    <t>12670.33</t>
+  </si>
+  <si>
+    <t>13459.75</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D614"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10602,16 +10605,16 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596" s="1">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="B596" t="s">
         <v>597</v>
       </c>
-      <c r="C596" t="s">
-        <v>615</v>
-      </c>
-      <c r="D596" t="s">
-        <v>622</v>
+      <c r="C596">
+        <v>79730.5</v>
+      </c>
+      <c r="D596">
+        <v>13260.35</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -10622,7 +10625,7 @@
         <v>598</v>
       </c>
       <c r="C597" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D597" t="s">
         <v>623</v>
@@ -10636,7 +10639,7 @@
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D598" t="s">
         <v>624</v>
@@ -10650,7 +10653,7 @@
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D599" t="s">
         <v>625</v>
@@ -10664,7 +10667,7 @@
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D600" t="s">
         <v>626</v>
@@ -10678,7 +10681,7 @@
         <v>602</v>
       </c>
       <c r="C601" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D601" t="s">
         <v>627</v>
@@ -10692,7 +10695,7 @@
         <v>603</v>
       </c>
       <c r="C602" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D602" t="s">
         <v>628</v>
@@ -10706,7 +10709,7 @@
         <v>604</v>
       </c>
       <c r="C603" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D603" t="s">
         <v>629</v>
@@ -10720,7 +10723,7 @@
         <v>605</v>
       </c>
       <c r="C604" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D604" t="s">
         <v>630</v>
@@ -10728,16 +10731,16 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605" s="1">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="B605" t="s">
         <v>606</v>
       </c>
-      <c r="C605">
-        <v>101325.5</v>
-      </c>
-      <c r="D605">
-        <v>14014.29</v>
+      <c r="C605" t="s">
+        <v>619</v>
+      </c>
+      <c r="D605" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -10812,16 +10815,16 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611" s="1">
-        <v>631</v>
+        <v>609</v>
       </c>
       <c r="B611" t="s">
         <v>612</v>
       </c>
-      <c r="C611" t="s">
-        <v>619</v>
-      </c>
-      <c r="D611" t="s">
-        <v>631</v>
+      <c r="C611">
+        <v>88540.5</v>
+      </c>
+      <c r="D611">
+        <v>14795.73</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -10850,6 +10853,20 @@
       </c>
       <c r="D613" t="s">
         <v>633</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4">
+      <c r="A614" s="1">
+        <v>634</v>
+      </c>
+      <c r="B614" t="s">
+        <v>615</v>
+      </c>
+      <c r="C614" t="s">
+        <v>622</v>
+      </c>
+      <c r="D614" t="s">
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/antimony.xlsx
+++ b/LME/parser_beta_2.0/data/antimony.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="636">
   <si>
     <t>Date</t>
   </si>
@@ -1864,61 +1864,64 @@
     <t>2026-08-27</t>
   </si>
   <si>
-    <t>96020.5</t>
-  </si>
-  <si>
-    <t>97612</t>
-  </si>
-  <si>
-    <t>99734</t>
-  </si>
-  <si>
-    <t>101325.5</t>
-  </si>
-  <si>
-    <t>107691.5</t>
-  </si>
-  <si>
-    <t>108752.5</t>
-  </si>
-  <si>
-    <t>102500</t>
-  </si>
-  <si>
-    <t>11126.36</t>
-  </si>
-  <si>
-    <t>11141.66</t>
-  </si>
-  <si>
-    <t>11324.32</t>
-  </si>
-  <si>
-    <t>11321.3</t>
-  </si>
-  <si>
-    <t>11575.29</t>
-  </si>
-  <si>
-    <t>11577.17</t>
-  </si>
-  <si>
-    <t>11577.85</t>
-  </si>
-  <si>
-    <t>11763.65</t>
-  </si>
-  <si>
-    <t>11764</t>
-  </si>
-  <si>
-    <t>12543.36</t>
-  </si>
-  <si>
-    <t>12670.33</t>
-  </si>
-  <si>
-    <t>13459.75</t>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>79730.5</t>
+  </si>
+  <si>
+    <t>81052</t>
+  </si>
+  <si>
+    <t>82814</t>
+  </si>
+  <si>
+    <t>84135.5</t>
+  </si>
+  <si>
+    <t>85457</t>
+  </si>
+  <si>
+    <t>90302.5</t>
+  </si>
+  <si>
+    <t>103500</t>
+  </si>
+  <si>
+    <t>12562.48</t>
+  </si>
+  <si>
+    <t>12768.44</t>
+  </si>
+  <si>
+    <t>12765.04</t>
+  </si>
+  <si>
+    <t>13051.41</t>
+  </si>
+  <si>
+    <t>13053.54</t>
+  </si>
+  <si>
+    <t>13054.31</t>
+  </si>
+  <si>
+    <t>13263.8</t>
+  </si>
+  <si>
+    <t>13264.19</t>
+  </si>
+  <si>
+    <t>13475.72</t>
+  </si>
+  <si>
+    <t>14286.1</t>
+  </si>
+  <si>
+    <t>14280.8</t>
+  </si>
+  <si>
+    <t>13595.51</t>
   </si>
 </sst>
 </file>
@@ -2276,7 +2279,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D614"/>
+  <dimension ref="A1:D615"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10619,16 +10622,16 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597" s="1">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="B597" t="s">
         <v>598</v>
       </c>
-      <c r="C597" t="s">
-        <v>616</v>
-      </c>
-      <c r="D597" t="s">
-        <v>623</v>
+      <c r="C597">
+        <v>96020.5</v>
+      </c>
+      <c r="D597">
+        <v>11126.36</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -10639,7 +10642,7 @@
         <v>599</v>
       </c>
       <c r="C598" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D598" t="s">
         <v>624</v>
@@ -10653,7 +10656,7 @@
         <v>600</v>
       </c>
       <c r="C599" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D599" t="s">
         <v>625</v>
@@ -10667,7 +10670,7 @@
         <v>601</v>
       </c>
       <c r="C600" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D600" t="s">
         <v>626</v>
@@ -10681,7 +10684,7 @@
         <v>602</v>
       </c>
       <c r="C601" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D601" t="s">
         <v>627</v>
@@ -10695,7 +10698,7 @@
         <v>603</v>
       </c>
       <c r="C602" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D602" t="s">
         <v>628</v>
@@ -10709,7 +10712,7 @@
         <v>604</v>
       </c>
       <c r="C603" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D603" t="s">
         <v>629</v>
@@ -10723,7 +10726,7 @@
         <v>605</v>
       </c>
       <c r="C604" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D604" t="s">
         <v>630</v>
@@ -10737,7 +10740,7 @@
         <v>606</v>
       </c>
       <c r="C605" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D605" t="s">
         <v>631</v>
@@ -10745,16 +10748,16 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606" s="1">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="B606" t="s">
         <v>607</v>
       </c>
-      <c r="C606">
-        <v>91277</v>
-      </c>
-      <c r="D606">
-        <v>14237.78</v>
+      <c r="C606" t="s">
+        <v>621</v>
+      </c>
+      <c r="D606" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -10829,16 +10832,16 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612" s="1">
-        <v>632</v>
+        <v>610</v>
       </c>
       <c r="B612" t="s">
         <v>613</v>
       </c>
-      <c r="C612" t="s">
-        <v>620</v>
-      </c>
-      <c r="D612" t="s">
-        <v>632</v>
+      <c r="C612">
+        <v>107691.5</v>
+      </c>
+      <c r="D612">
+        <v>12543.36</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -10849,7 +10852,7 @@
         <v>614</v>
       </c>
       <c r="C613" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D613" t="s">
         <v>633</v>
@@ -10867,6 +10870,20 @@
       </c>
       <c r="D614" t="s">
         <v>634</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4">
+      <c r="A615" s="1">
+        <v>635</v>
+      </c>
+      <c r="B615" t="s">
+        <v>616</v>
+      </c>
+      <c r="C615" t="s">
+        <v>623</v>
+      </c>
+      <c r="D615" t="s">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
